--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1326,7 +1326,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 21 March 2026  |  12:41 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 22 March 2026  |  06:41 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.141922</v>
+        <v>132.146687</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.336</v>
@@ -1549,13 +1549,13 @@
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.67</v>
+        <v>28.68</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>40.96</v>
+        <v>40.97</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>-0.0718</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>922.37261</v>
+        <v>918.565802</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.304</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>280.4</v>
+        <v>279.24</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>380.02</v>
+        <v>378.45</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>599.54</v>
+        <v>597.0700000000001</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>-0.0703</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1663,25 +1663,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>677.91</v>
+        <v>677.87</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>681.3200000000001</v>
+        <v>681.27</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>-0.07780000000000001</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1726,25 +1726,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>14.068384</v>
+        <v>14.044867</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.26</v>
+        <v>15.24</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.59</v>
+        <v>17.56</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>-0.0742</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1789,25 +1789,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.411</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>801.12</v>
+        <v>801.0700000000001</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>783.51</v>
+        <v>783.47</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>-0.07539999999999999</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2975.174486</v>
+        <v>2975.310621</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.334</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3968.88</v>
+        <v>3969.06</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3873.68</v>
+        <v>3873.85</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4314</v>
+        <v>4314.2</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>-0.0104</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1915,25 +1915,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>985.64</v>
+        <v>985.58</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1176.41</v>
+        <v>1176.33</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1021.98</v>
+        <v>1021.91</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>-0.0616</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.440004</v>
+        <v>95.434067</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.269</v>
@@ -1996,7 +1996,7 @@
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116.44</v>
+        <v>116.43</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>-0.05230000000000001</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.389</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>788.62</v>
+        <v>788.58</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>776.13</v>
+        <v>776.09</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>681.3200000000001</v>
+        <v>681.27</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>-0.0789</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2104,25 +2104,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>748.3099999999999</v>
+        <v>748.27</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>880.03</v>
+        <v>879.98</v>
       </c>
       <c r="M20" s="33" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2167,25 +2167,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>425.823282</v>
+        <v>425.796789</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>503.32</v>
+        <v>503.29</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>459.04</v>
+        <v>459.01</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>574.86</v>
+        <v>574.83</v>
       </c>
       <c r="M21" s="34" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2230,25 +2230,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>2269.48994</v>
+        <v>2263.863308</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.052</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>2387.5</v>
+        <v>2381.58</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>2362.54</v>
+        <v>2356.68</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>2836.86</v>
+        <v>2829.83</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>-0.0488</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2293,25 +2293,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>470.11</v>
+        <v>470.08</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="M23" s="34" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>52.239408</v>
+        <v>52.240036</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>0.4</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2482,25 +2482,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>526.89</v>
+        <v>526.85</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>487.14</v>
+        <v>487.11</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="M26" s="33" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2608,25 +2608,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>19.17</v>
+        <v>19.16</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>-0.08890000000000001</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2671,25 +2671,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>156.231435</v>
+        <v>156.089895</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>123.74</v>
+        <v>123.62</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>130.45</v>
+        <v>130.34</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>164.04</v>
+        <v>163.89</v>
       </c>
       <c r="M29" s="34" t="n">
         <v>0.0025</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2734,25 +2734,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.987</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>560.38</v>
+        <v>560.35</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>542.21</v>
+        <v>542.1799999999999</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>510.99</v>
+        <v>510.96</v>
       </c>
       <c r="M30" s="35" t="n">
         <v>0.1016</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>74.18779499999999</v>
+        <v>74.187712</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.162</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>10.955128</v>
+        <v>10.952854</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.27</v>
@@ -2878,7 +2878,7 @@
         <v>1.2</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>13.15</v>
+        <v>13.14</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>-0.0063</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2923,25 +2923,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>8763.839464000001</v>
+        <v>8763.579604</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>-0.0643</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2986,25 +2986,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>587.64</v>
+        <v>587.6</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>536.54</v>
+        <v>536.5</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="M34" s="33" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3049,25 +3049,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.356</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>769.89</v>
+        <v>769.84</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>-0.0788</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3112,25 +3112,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>129.499339</v>
+        <v>129.437884</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>178.71</v>
+        <v>178.62</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>154.62</v>
+        <v>154.55</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>174.82</v>
+        <v>174.74</v>
       </c>
       <c r="M36" s="35" t="n">
         <v>0.0534</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3175,25 +3175,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.019</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>17.32</v>
+        <v>17.31</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>-0.0459</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3238,25 +3238,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>183.355703</v>
+        <v>183.373095</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.846</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>155.12</v>
+        <v>155.13</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>167.04</v>
+        <v>167.05</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>220.03</v>
+        <v>220.05</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>-0.0265</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>6.384583</v>
+        <v>6.384581</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.024</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3364,25 +3364,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>4159.622638</v>
+        <v>4159.707068</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.096</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>4558.95</v>
+        <v>4559.04</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>4330.17</v>
+        <v>4330.26</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>5407.51</v>
+        <v>5407.62</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>-0.08210000000000001</v>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3427,25 +3427,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1746.251649</v>
+        <v>1745.784056</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>2.669</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>4660.75</v>
+        <v>4659.5</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>4641.54</v>
+        <v>4640.29</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>4191</v>
+        <v>4189.88</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>-0.0668</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3490,25 +3490,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.291</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>732.98</v>
+        <v>732.9400000000001</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>683.59</v>
+        <v>683.55</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>738.09</v>
+        <v>738.05</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>-0.07190000000000001</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>39.960045</v>
+        <v>39.959673</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>0.968</v>
@@ -3565,7 +3565,7 @@
         <v>0.87</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>34.77</v>
+        <v>34.76</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.1</v>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3616,25 +3616,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>46.461655</v>
+        <v>46.477439</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>65.05</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>-0.0516</v>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3679,25 +3679,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>9.362730000000001</v>
+        <v>9.356132000000001</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.393</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>13.04</v>
+        <v>13.03</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.246</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>11.67</v>
+        <v>11.66</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="M45" s="36" t="n">
         <v>0.0537</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3742,25 +3742,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>63.631799</v>
+        <v>63.495071</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>1.226</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>78.01000000000001</v>
+        <v>77.84</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>74.58</v>
+        <v>74.42</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>82.72</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>-0.0555</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3805,25 +3805,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.118</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>19</v>
+        <v>18.99</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>18.99</v>
+        <v>18.97</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>-0.0866</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3868,25 +3868,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>625.6799999999999</v>
+        <v>625.64</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>568.9</v>
+        <v>568.86</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>709.71</v>
+        <v>709.66</v>
       </c>
       <c r="M48" s="33" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3931,25 +3931,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>1356.862252</v>
+        <v>1356.394702</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.76</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1031.22</v>
+        <v>1030.86</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.03</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1397.57</v>
+        <v>1397.09</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>746.27</v>
+        <v>746.02</v>
       </c>
       <c r="M49" s="36" t="n">
         <v>0.3103</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3994,25 +3994,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>1457.321924</v>
+        <v>1457.464304</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>1865.37</v>
+        <v>1865.55</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>1818.74</v>
+        <v>1818.92</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>2113.12</v>
+        <v>2113.32</v>
       </c>
       <c r="M50" s="29" t="n">
         <v>-0.0595</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>21.206005</v>
+        <v>21.204685</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.322</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4120,25 +4120,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.53</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>868.6799999999999</v>
+        <v>868.63</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>-0.08109999999999999</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4183,25 +4183,25 @@
         </is>
       </c>
       <c r="F53" s="17" t="n">
-        <v>14.609086</v>
+        <v>14.565155</v>
       </c>
       <c r="G53" s="18" t="n">
         <v>1.411</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>20.61</v>
+        <v>20.55</v>
       </c>
       <c r="I53" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>20.13</v>
+        <v>20.07</v>
       </c>
       <c r="K53" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>23.37</v>
+        <v>23.3</v>
       </c>
       <c r="M53" s="36" t="n">
         <v>0.05139999999999999</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="R53" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R54" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="F55" s="17" t="n">
-        <v>571.664381</v>
+        <v>571.663172</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>1.15</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="R55" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4372,25 +4372,25 @@
         </is>
       </c>
       <c r="F56" s="26" t="n">
-        <v>16.998056</v>
+        <v>16.984359</v>
       </c>
       <c r="G56" s="27" t="n">
         <v>1.2399</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>21.08</v>
+        <v>21.06</v>
       </c>
       <c r="I56" s="27" t="n">
         <v>1.226</v>
       </c>
       <c r="J56" s="28" t="n">
-        <v>20.84</v>
+        <v>20.82</v>
       </c>
       <c r="K56" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L56" s="28" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="M56" s="33" t="n">
         <v>0.0155</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="R56" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4435,25 +4435,25 @@
         </is>
       </c>
       <c r="F57" s="17" t="n">
-        <v>4585.708319</v>
+        <v>4585.068745</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="I57" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="J57" s="19" t="n">
-        <v>6947.35</v>
+        <v>6946.38</v>
       </c>
       <c r="K57" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>8254.27</v>
+        <v>8253.120000000001</v>
       </c>
       <c r="M57" s="34" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="R57" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="F58" s="26" t="n">
-        <v>543.774705</v>
+        <v>544.108486</v>
       </c>
       <c r="G58" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>570.96</v>
+        <v>571.3099999999999</v>
       </c>
       <c r="I58" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="J58" s="28" t="n">
-        <v>330.07</v>
+        <v>330.27</v>
       </c>
       <c r="K58" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L58" s="28" t="n">
-        <v>299.08</v>
+        <v>299.26</v>
       </c>
       <c r="M58" s="35" t="n">
         <v>0.7676999999999999</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="R58" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4561,25 +4561,25 @@
         </is>
       </c>
       <c r="F59" s="17" t="n">
-        <v>2590.700544</v>
+        <v>2585.283864</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>2849.77</v>
+        <v>2843.81</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>2671.01</v>
+        <v>2665.43</v>
       </c>
       <c r="K59" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>3238.38</v>
+        <v>3231.6</v>
       </c>
       <c r="M59" s="34" t="n">
         <v>0.0092</v>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="R59" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4624,25 +4624,25 @@
         </is>
       </c>
       <c r="F60" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="G60" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="I60" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J60" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="K60" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L60" s="28" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="M60" s="29" t="n">
         <v>-0.0762</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="R60" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="F61" s="17" t="n">
-        <v>2.921333</v>
+        <v>2.921765</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>0.8139999999999999</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="R61" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4750,25 +4750,25 @@
         </is>
       </c>
       <c r="F62" s="26" t="n">
-        <v>3778.118684</v>
+        <v>3777.748478</v>
       </c>
       <c r="G62" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>5217.58</v>
+        <v>5217.07</v>
       </c>
       <c r="I62" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J62" s="28" t="n">
-        <v>4344.84</v>
+        <v>4344.41</v>
       </c>
       <c r="K62" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L62" s="28" t="n">
-        <v>4911.55</v>
+        <v>4911.07</v>
       </c>
       <c r="M62" s="33" t="n">
         <v>0</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="R62" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="F63" s="17" t="n">
-        <v>19.541754</v>
+        <v>19.540845</v>
       </c>
       <c r="G63" s="18" t="n">
         <v>1.28</v>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="R63" s="23" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="R64" s="32" t="inlineStr">
         <is>
-          <t>2026-03-21 12:41 UTC</t>
+          <t>2026-03-22 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="E3" s="38" t="n">
-        <v>132.141922</v>
+        <v>132.146687</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.362</v>
@@ -5149,25 +5149,25 @@
         <v>0.217</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>28.67</v>
+        <v>28.68</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>28.67</v>
+        <v>28.68</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>28.67</v>
+        <v>28.68</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>40.96</v>
+        <v>40.97</v>
       </c>
       <c r="T3" s="39" t="n">
         <v>-0.0718</v>
@@ -5196,49 +5196,49 @@
         </is>
       </c>
       <c r="E4" s="41" t="n">
-        <v>922.37261</v>
+        <v>918.565802</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.327</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>301.62</v>
+        <v>300.37</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.327</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>301.62</v>
+        <v>300.37</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.327</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>301.62</v>
+        <v>300.37</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>380.02</v>
+        <v>378.45</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>380.02</v>
+        <v>378.45</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>380.02</v>
+        <v>378.45</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>599.54</v>
+        <v>597.0700000000001</v>
       </c>
       <c r="T4" s="42" t="n">
         <v>-0.0703</v>
@@ -5267,49 +5267,49 @@
         </is>
       </c>
       <c r="E5" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.247</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>708</v>
+        <v>707.96</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.247</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>708</v>
+        <v>707.96</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.247</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>708</v>
+        <v>707.96</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>677.91</v>
+        <v>677.87</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>677.91</v>
+        <v>677.87</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>677.91</v>
+        <v>677.87</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>681.3200000000001</v>
+        <v>681.27</v>
       </c>
       <c r="T5" s="39" t="n">
         <v>-0.07780000000000001</v>
@@ -5338,49 +5338,49 @@
         </is>
       </c>
       <c r="E6" s="41" t="n">
-        <v>14.068384</v>
+        <v>14.044867</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>16.49</v>
+        <v>16.46</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>16.49</v>
+        <v>16.46</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>16.49</v>
+        <v>16.46</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.59</v>
+        <v>17.56</v>
       </c>
       <c r="T6" s="42" t="n">
         <v>-0.0742</v>
@@ -5409,49 +5409,49 @@
         </is>
       </c>
       <c r="E7" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.526</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>866.41</v>
+        <v>866.35</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.526</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>866.41</v>
+        <v>866.35</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.526</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>866.41</v>
+        <v>866.35</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>783.51</v>
+        <v>783.47</v>
       </c>
       <c r="T7" s="39" t="n">
         <v>-0.07539999999999999</v>
@@ -5480,49 +5480,49 @@
         </is>
       </c>
       <c r="E8" s="41" t="n">
-        <v>2975.174486</v>
+        <v>2975.310621</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.348</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>4010.54</v>
+        <v>4010.72</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.348</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>4010.54</v>
+        <v>4010.72</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.348</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>4010.54</v>
+        <v>4010.72</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3873.68</v>
+        <v>3873.85</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3873.68</v>
+        <v>3873.85</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3873.68</v>
+        <v>3873.85</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4314</v>
+        <v>4314.2</v>
       </c>
       <c r="T8" s="42" t="n">
         <v>-0.0104</v>
@@ -5551,49 +5551,49 @@
         </is>
       </c>
       <c r="E9" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.85</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>1050.36</v>
+        <v>1050.3</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.85</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>1050.36</v>
+        <v>1050.3</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.85</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>1050.36</v>
+        <v>1050.3</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1176.41</v>
+        <v>1176.33</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1176.41</v>
+        <v>1176.33</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1176.41</v>
+        <v>1176.33</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1021.98</v>
+        <v>1021.91</v>
       </c>
       <c r="T9" s="39" t="n">
         <v>-0.0616</v>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="E10" s="41" t="n">
-        <v>95.440004</v>
+        <v>95.434067</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.339</v>
@@ -5664,7 +5664,7 @@
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116.44</v>
+        <v>116.43</v>
       </c>
       <c r="T10" s="42" t="n">
         <v>-0.05230000000000001</v>
@@ -5693,49 +5693,49 @@
         </is>
       </c>
       <c r="E11" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.508</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>856.1900000000001</v>
+        <v>856.14</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.508</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>856.1900000000001</v>
+        <v>856.14</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.508</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>856.1900000000001</v>
+        <v>856.14</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>776.13</v>
+        <v>776.09</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>776.13</v>
+        <v>776.09</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>776.13</v>
+        <v>776.09</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>681.3200000000001</v>
+        <v>681.27</v>
       </c>
       <c r="T11" s="39" t="n">
         <v>-0.0789</v>
@@ -5764,49 +5764,49 @@
         </is>
       </c>
       <c r="E12" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>748.3099999999999</v>
+        <v>748.27</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>748.3099999999999</v>
+        <v>748.27</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>748.3099999999999</v>
+        <v>748.27</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>880.03</v>
+        <v>879.98</v>
       </c>
       <c r="T12" s="43" t="n">
         <v>0</v>
@@ -5835,49 +5835,49 @@
         </is>
       </c>
       <c r="E13" s="38" t="n">
-        <v>425.823282</v>
+        <v>425.796789</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>503.32</v>
+        <v>503.29</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>503.32</v>
+        <v>503.29</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>503.32</v>
+        <v>503.29</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>459.04</v>
+        <v>459.01</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>459.04</v>
+        <v>459.01</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>459.04</v>
+        <v>459.01</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>574.86</v>
+        <v>574.83</v>
       </c>
       <c r="T13" s="40" t="n">
         <v>0</v>
@@ -5906,49 +5906,49 @@
         </is>
       </c>
       <c r="E14" s="41" t="n">
-        <v>2269.48994</v>
+        <v>2263.863308</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.106</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>2510.06</v>
+        <v>2503.83</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.106</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>2510.06</v>
+        <v>2503.83</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.106</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>2510.06</v>
+        <v>2503.83</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>2362.54</v>
+        <v>2356.68</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>2362.54</v>
+        <v>2356.68</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>2362.54</v>
+        <v>2356.68</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>2836.86</v>
+        <v>2829.83</v>
       </c>
       <c r="T14" s="42" t="n">
         <v>-0.0488</v>
@@ -5977,49 +5977,49 @@
         </is>
       </c>
       <c r="E15" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>470.11</v>
+        <v>470.08</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>470.11</v>
+        <v>470.08</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>470.11</v>
+        <v>470.08</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="T15" s="40" t="n">
         <v>0</v>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="E17" s="38" t="n">
-        <v>52.239408</v>
+        <v>52.240036</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>0.41</v>
@@ -6190,49 +6190,49 @@
         </is>
       </c>
       <c r="E18" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>526.89</v>
+        <v>526.85</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>526.89</v>
+        <v>526.85</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>526.89</v>
+        <v>526.85</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>487.14</v>
+        <v>487.11</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>487.14</v>
+        <v>487.11</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>487.14</v>
+        <v>487.11</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="T18" s="43" t="n">
         <v>0</v>
@@ -6332,49 +6332,49 @@
         </is>
       </c>
       <c r="E20" s="41" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.215</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.215</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.215</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>19.17</v>
+        <v>19.16</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>19.17</v>
+        <v>19.16</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>19.17</v>
+        <v>19.16</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="T20" s="42" t="n">
         <v>-0.08890000000000001</v>
@@ -6403,49 +6403,49 @@
         </is>
       </c>
       <c r="E21" s="38" t="n">
-        <v>156.231435</v>
+        <v>156.089895</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.79</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>123.42</v>
+        <v>123.31</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.79</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>123.42</v>
+        <v>123.31</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.79</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>123.42</v>
+        <v>123.31</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>130.45</v>
+        <v>130.34</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>130.45</v>
+        <v>130.34</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>130.45</v>
+        <v>130.34</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>164.04</v>
+        <v>163.89</v>
       </c>
       <c r="T21" s="40" t="n">
         <v>0.0025</v>
@@ -6474,49 +6474,49 @@
         </is>
       </c>
       <c r="E22" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.896</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>508.72</v>
+        <v>508.69</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.896</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>508.72</v>
+        <v>508.69</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.896</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>508.72</v>
+        <v>508.69</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>542.21</v>
+        <v>542.1799999999999</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>542.21</v>
+        <v>542.1799999999999</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>542.21</v>
+        <v>542.1799999999999</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>510.99</v>
+        <v>510.96</v>
       </c>
       <c r="T22" s="45" t="n">
         <v>0.1016</v>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="E23" s="38" t="n">
-        <v>74.18779499999999</v>
+        <v>74.187712</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>1.162</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="E24" s="41" t="n">
-        <v>10.955128</v>
+        <v>10.952854</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>1.278</v>
@@ -6640,25 +6640,25 @@
         <v>1.107</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>12.13</v>
+        <v>12.12</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>12.13</v>
+        <v>12.12</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>12.13</v>
+        <v>12.12</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>13.15</v>
+        <v>13.14</v>
       </c>
       <c r="T24" s="42" t="n">
         <v>-0.0063</v>
@@ -6687,49 +6687,49 @@
         </is>
       </c>
       <c r="E25" s="38" t="n">
-        <v>8763.839464000001</v>
+        <v>8763.579604</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>1.368</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>11988.93</v>
+        <v>11988.58</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>1.368</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>11988.93</v>
+        <v>11988.58</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>1.368</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>11988.93</v>
+        <v>11988.58</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="T25" s="39" t="n">
         <v>-0.0643</v>
@@ -6758,49 +6758,49 @@
         </is>
       </c>
       <c r="E26" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>587.64</v>
+        <v>587.6</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>587.64</v>
+        <v>587.6</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>587.64</v>
+        <v>587.6</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>536.54</v>
+        <v>536.5</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>536.54</v>
+        <v>536.5</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>536.54</v>
+        <v>536.5</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="T26" s="43" t="n">
         <v>0</v>
@@ -6829,49 +6829,49 @@
         </is>
       </c>
       <c r="E27" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.472</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>835.75</v>
+        <v>835.7</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.472</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>835.75</v>
+        <v>835.7</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.472</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>835.75</v>
+        <v>835.7</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="T27" s="39" t="n">
         <v>-0.0788</v>
@@ -6900,49 +6900,49 @@
         </is>
       </c>
       <c r="E28" s="41" t="n">
-        <v>129.499339</v>
+        <v>129.437884</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.31</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>169.64</v>
+        <v>169.56</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.31</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>169.64</v>
+        <v>169.56</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.31</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>169.64</v>
+        <v>169.56</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>154.62</v>
+        <v>154.55</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>154.62</v>
+        <v>154.55</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>154.62</v>
+        <v>154.55</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>174.82</v>
+        <v>174.74</v>
       </c>
       <c r="T28" s="45" t="n">
         <v>0.0534</v>
@@ -6971,49 +6971,49 @@
         </is>
       </c>
       <c r="E29" s="38" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.068</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.068</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.068</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="T29" s="39" t="n">
         <v>-0.0459</v>
@@ -7042,49 +7042,49 @@
         </is>
       </c>
       <c r="E30" s="41" t="n">
-        <v>183.355703</v>
+        <v>183.373095</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>0.869</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>159.34</v>
+        <v>159.35</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>0.869</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>159.34</v>
+        <v>159.35</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>0.869</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>159.34</v>
+        <v>159.35</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>167.04</v>
+        <v>167.05</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>167.04</v>
+        <v>167.05</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>167.04</v>
+        <v>167.05</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>220.03</v>
+        <v>220.05</v>
       </c>
       <c r="T30" s="42" t="n">
         <v>-0.0265</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="E31" s="38" t="n">
-        <v>6.384583</v>
+        <v>6.384581</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>0.024</v>
@@ -7184,49 +7184,49 @@
         </is>
       </c>
       <c r="E32" s="41" t="n">
-        <v>4159.622638</v>
+        <v>4159.707068</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>4966.59</v>
+        <v>4966.69</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>4966.59</v>
+        <v>4966.69</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>4966.59</v>
+        <v>4966.69</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>4330.17</v>
+        <v>4330.26</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>4330.17</v>
+        <v>4330.26</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>4330.17</v>
+        <v>4330.26</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>5407.51</v>
+        <v>5407.62</v>
       </c>
       <c r="T32" s="42" t="n">
         <v>-0.08210000000000001</v>
@@ -7255,49 +7255,49 @@
         </is>
       </c>
       <c r="E33" s="38" t="n">
-        <v>1746.251649</v>
+        <v>1745.784056</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>2.86</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>4994.28</v>
+        <v>4992.94</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>2.86</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>4994.28</v>
+        <v>4992.94</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>2.86</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>4994.28</v>
+        <v>4992.94</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>4641.54</v>
+        <v>4640.29</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>4641.54</v>
+        <v>4640.29</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>4641.54</v>
+        <v>4640.29</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>4191</v>
+        <v>4189.88</v>
       </c>
       <c r="T33" s="39" t="n">
         <v>-0.0668</v>
@@ -7326,49 +7326,49 @@
         </is>
       </c>
       <c r="E34" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.391</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>789.76</v>
+        <v>789.71</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.391</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>789.76</v>
+        <v>789.71</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.391</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>789.76</v>
+        <v>789.71</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>683.59</v>
+        <v>683.55</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>683.59</v>
+        <v>683.55</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>683.59</v>
+        <v>683.55</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>738.09</v>
+        <v>738.05</v>
       </c>
       <c r="T34" s="42" t="n">
         <v>-0.07190000000000001</v>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="E35" s="38" t="n">
-        <v>39.960045</v>
+        <v>39.959673</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>0.968</v>
@@ -7421,19 +7421,19 @@
         <v>0.87</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>34.77</v>
+        <v>34.76</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>34.77</v>
+        <v>34.76</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>34.77</v>
+        <v>34.76</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.1</v>
@@ -7468,49 +7468,49 @@
         </is>
       </c>
       <c r="E36" s="41" t="n">
-        <v>46.461655</v>
+        <v>46.477439</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.259</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>58.5</v>
+        <v>58.52</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.259</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>58.5</v>
+        <v>58.52</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.259</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>58.5</v>
+        <v>58.52</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>65.05</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="T36" s="42" t="n">
         <v>-0.0516</v>
@@ -7539,49 +7539,49 @@
         </is>
       </c>
       <c r="E37" s="38" t="n">
-        <v>9.362730000000001</v>
+        <v>9.356132000000001</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.074</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.074</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.074</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="T37" s="44" t="n">
         <v>0.0537</v>
@@ -7610,49 +7610,49 @@
         </is>
       </c>
       <c r="E38" s="41" t="n">
-        <v>63.631799</v>
+        <v>63.495071</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>82.59</v>
+        <v>82.42</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>82.59</v>
+        <v>82.42</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>82.59</v>
+        <v>82.42</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>74.58</v>
+        <v>74.42</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>74.58</v>
+        <v>74.42</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>74.58</v>
+        <v>74.42</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>82.72</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="T38" s="42" t="n">
         <v>-0.0555</v>
@@ -7681,49 +7681,49 @@
         </is>
       </c>
       <c r="E39" s="38" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>1.224</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>20.81</v>
+        <v>20.79</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>1.224</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>20.81</v>
+        <v>20.79</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>1.224</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>20.81</v>
+        <v>20.79</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>18.99</v>
+        <v>18.97</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>18.99</v>
+        <v>18.97</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>18.99</v>
+        <v>18.97</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="T39" s="39" t="n">
         <v>-0.0866</v>
@@ -7752,49 +7752,49 @@
         </is>
       </c>
       <c r="E40" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>625.6799999999999</v>
+        <v>625.64</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>625.6799999999999</v>
+        <v>625.64</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>625.6799999999999</v>
+        <v>625.64</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>568.9</v>
+        <v>568.86</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>568.9</v>
+        <v>568.86</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>568.9</v>
+        <v>568.86</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>709.71</v>
+        <v>709.66</v>
       </c>
       <c r="T40" s="43" t="n">
         <v>0</v>
@@ -7823,49 +7823,49 @@
         </is>
       </c>
       <c r="E41" s="38" t="n">
-        <v>1356.862252</v>
+        <v>1356.394702</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.58</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>786.98</v>
+        <v>786.71</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.58</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>786.98</v>
+        <v>786.71</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.58</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>786.98</v>
+        <v>786.71</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>1339.22</v>
+        <v>1338.76</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>1339.22</v>
+        <v>1338.76</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>1339.22</v>
+        <v>1338.76</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>746.27</v>
+        <v>746.02</v>
       </c>
       <c r="T41" s="44" t="n">
         <v>0.3103</v>
@@ -7894,49 +7894,49 @@
         </is>
       </c>
       <c r="E42" s="41" t="n">
-        <v>1457.321924</v>
+        <v>1457.464304</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>1983.42</v>
+        <v>1983.61</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>1983.42</v>
+        <v>1983.61</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>1983.42</v>
+        <v>1983.61</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>1818.74</v>
+        <v>1818.92</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>1818.74</v>
+        <v>1818.92</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>1818.74</v>
+        <v>1818.92</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>2113.12</v>
+        <v>2113.32</v>
       </c>
       <c r="T42" s="42" t="n">
         <v>-0.0595</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="E43" s="38" t="n">
-        <v>21.206005</v>
+        <v>21.204685</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.322</v>
@@ -8036,49 +8036,49 @@
         </is>
       </c>
       <c r="E44" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.665</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>945.33</v>
+        <v>945.27</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.665</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>945.33</v>
+        <v>945.27</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.665</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>945.33</v>
+        <v>945.27</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="T44" s="42" t="n">
         <v>-0.08109999999999999</v>
@@ -8107,49 +8107,49 @@
         </is>
       </c>
       <c r="E45" s="38" t="n">
-        <v>14.609086</v>
+        <v>14.565155</v>
       </c>
       <c r="F45" s="18" t="n">
         <v>1.342</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>19.61</v>
+        <v>19.55</v>
       </c>
       <c r="H45" s="18" t="n">
         <v>1.342</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>19.61</v>
+        <v>19.55</v>
       </c>
       <c r="J45" s="18" t="n">
         <v>1.342</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>19.61</v>
+        <v>19.55</v>
       </c>
       <c r="L45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>20.13</v>
+        <v>20.07</v>
       </c>
       <c r="N45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="O45" s="19" t="n">
-        <v>20.13</v>
+        <v>20.07</v>
       </c>
       <c r="P45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="Q45" s="19" t="n">
-        <v>20.13</v>
+        <v>20.07</v>
       </c>
       <c r="R45" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>23.37</v>
+        <v>23.3</v>
       </c>
       <c r="T45" s="44" t="n">
         <v>0.05139999999999999</v>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="E47" s="38" t="n">
-        <v>571.664381</v>
+        <v>571.663172</v>
       </c>
       <c r="F47" s="18" t="n">
         <v>0.68</v>
@@ -8320,49 +8320,49 @@
         </is>
       </c>
       <c r="E48" s="41" t="n">
-        <v>16.998056</v>
+        <v>16.984359</v>
       </c>
       <c r="F48" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="G48" s="28" t="n">
-        <v>20.75</v>
+        <v>20.74</v>
       </c>
       <c r="H48" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>20.75</v>
+        <v>20.74</v>
       </c>
       <c r="J48" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="K48" s="28" t="n">
-        <v>20.75</v>
+        <v>20.74</v>
       </c>
       <c r="L48" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="M48" s="28" t="n">
-        <v>18.32</v>
+        <v>18.31</v>
       </c>
       <c r="N48" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>18.32</v>
+        <v>18.31</v>
       </c>
       <c r="P48" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>18.32</v>
+        <v>18.31</v>
       </c>
       <c r="R48" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S48" s="28" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="T48" s="43" t="n">
         <v>0.0155</v>
@@ -8391,49 +8391,49 @@
         </is>
       </c>
       <c r="E49" s="38" t="n">
-        <v>4585.708319</v>
+        <v>4585.068745</v>
       </c>
       <c r="F49" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="H49" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="J49" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="L49" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>6947.35</v>
+        <v>6946.38</v>
       </c>
       <c r="N49" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="O49" s="19" t="n">
-        <v>6947.35</v>
+        <v>6946.38</v>
       </c>
       <c r="P49" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="Q49" s="19" t="n">
-        <v>6947.35</v>
+        <v>6946.38</v>
       </c>
       <c r="R49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>8254.27</v>
+        <v>8253.120000000001</v>
       </c>
       <c r="T49" s="40" t="n">
         <v>0</v>
@@ -8462,49 +8462,49 @@
         </is>
       </c>
       <c r="E50" s="41" t="n">
-        <v>543.774705</v>
+        <v>544.108486</v>
       </c>
       <c r="F50" s="27" t="n">
         <v>0.594</v>
       </c>
       <c r="G50" s="28" t="n">
-        <v>323</v>
+        <v>323.2</v>
       </c>
       <c r="H50" s="27" t="n">
         <v>0.594</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>323</v>
+        <v>323.2</v>
       </c>
       <c r="J50" s="27" t="n">
         <v>0.594</v>
       </c>
       <c r="K50" s="28" t="n">
-        <v>323</v>
+        <v>323.2</v>
       </c>
       <c r="L50" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="M50" s="28" t="n">
-        <v>330.07</v>
+        <v>330.27</v>
       </c>
       <c r="N50" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>330.07</v>
+        <v>330.27</v>
       </c>
       <c r="P50" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>330.07</v>
+        <v>330.27</v>
       </c>
       <c r="R50" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S50" s="28" t="n">
-        <v>299.08</v>
+        <v>299.26</v>
       </c>
       <c r="T50" s="45" t="n">
         <v>0.7676999999999999</v>
@@ -8533,49 +8533,49 @@
         </is>
       </c>
       <c r="E51" s="38" t="n">
-        <v>2590.700544</v>
+        <v>2585.283864</v>
       </c>
       <c r="F51" s="18" t="n">
         <v>1.09</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>2823.86</v>
+        <v>2817.96</v>
       </c>
       <c r="H51" s="18" t="n">
         <v>1.09</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>2823.86</v>
+        <v>2817.96</v>
       </c>
       <c r="J51" s="18" t="n">
         <v>1.09</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>2823.86</v>
+        <v>2817.96</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>2671.01</v>
+        <v>2665.43</v>
       </c>
       <c r="N51" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="O51" s="19" t="n">
-        <v>2671.01</v>
+        <v>2665.43</v>
       </c>
       <c r="P51" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="Q51" s="19" t="n">
-        <v>2671.01</v>
+        <v>2665.43</v>
       </c>
       <c r="R51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>3238.38</v>
+        <v>3231.6</v>
       </c>
       <c r="T51" s="40" t="n">
         <v>0.0092</v>
@@ -8604,49 +8604,49 @@
         </is>
       </c>
       <c r="E52" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F52" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="G52" s="28" t="n">
-        <v>693.24</v>
+        <v>693.2</v>
       </c>
       <c r="H52" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>693.24</v>
+        <v>693.2</v>
       </c>
       <c r="J52" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="K52" s="28" t="n">
-        <v>693.24</v>
+        <v>693.2</v>
       </c>
       <c r="L52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M52" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="N52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="P52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="R52" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S52" s="28" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="T52" s="42" t="n">
         <v>-0.0762</v>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="E53" s="38" t="n">
-        <v>2.921333</v>
+        <v>2.921765</v>
       </c>
       <c r="F53" s="18" t="n">
         <v>0.863</v>
@@ -8746,49 +8746,49 @@
         </is>
       </c>
       <c r="E54" s="41" t="n">
-        <v>3778.118684</v>
+        <v>3777.748478</v>
       </c>
       <c r="F54" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G54" s="28" t="n">
-        <v>5217.58</v>
+        <v>5217.07</v>
       </c>
       <c r="H54" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I54" s="28" t="n">
-        <v>5217.58</v>
+        <v>5217.07</v>
       </c>
       <c r="J54" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K54" s="28" t="n">
-        <v>5217.58</v>
+        <v>5217.07</v>
       </c>
       <c r="L54" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M54" s="28" t="n">
-        <v>4344.84</v>
+        <v>4344.41</v>
       </c>
       <c r="N54" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>4344.84</v>
+        <v>4344.41</v>
       </c>
       <c r="P54" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q54" s="28" t="n">
-        <v>4344.84</v>
+        <v>4344.41</v>
       </c>
       <c r="R54" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S54" s="28" t="n">
-        <v>4911.55</v>
+        <v>4911.07</v>
       </c>
       <c r="T54" s="43" t="n">
         <v>0</v>
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="E55" s="38" t="n">
-        <v>19.541754</v>
+        <v>19.540845</v>
       </c>
       <c r="F55" s="18" t="n">
         <v>1.48</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.141922</v>
+        <v>132.146687</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>47.84</v>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>922.37261</v>
+        <v>918.565802</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>301.62</v>
+        <v>300.37</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.327</v>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>708</v>
+        <v>707.96</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.247</v>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>14.068384</v>
+        <v>14.044867</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>16.49</v>
+        <v>16.46</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.172</v>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>866.41</v>
+        <v>866.35</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.526</v>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2975.174486</v>
+        <v>2975.310621</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>4010.54</v>
+        <v>4010.72</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.348</v>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>1050.36</v>
+        <v>1050.3</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.85</v>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.440004</v>
+        <v>95.434067</v>
       </c>
       <c r="F10" s="28" t="n">
         <v>127.79</v>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>856.1900000000001</v>
+        <v>856.14</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.508</v>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>1.418</v>
@@ -9693,10 +9693,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>425.823282</v>
+        <v>425.796789</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>503.32</v>
+        <v>503.29</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.182</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>2269.48994</v>
+        <v>2263.863308</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>2510.06</v>
+        <v>2503.83</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.106</v>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.898</v>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>52.239408</v>
+        <v>52.240036</v>
       </c>
       <c r="F17" s="19" t="n">
         <v>21.42</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>526.89</v>
+        <v>526.85</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>0.928</v>
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.215</v>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>156.231435</v>
+        <v>156.089895</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>123.42</v>
+        <v>123.31</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.79</v>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>508.72</v>
+        <v>508.69</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.896</v>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>74.18779499999999</v>
+        <v>74.187712</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>86.20999999999999</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>10.955128</v>
+        <v>10.952854</v>
       </c>
       <c r="F24" s="28" t="n">
         <v>14</v>
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>8763.839464000001</v>
+        <v>8763.579604</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>11988.93</v>
+        <v>11988.58</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.368</v>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>587.64</v>
+        <v>587.6</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.035</v>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>835.75</v>
+        <v>835.7</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.472</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>129.499339</v>
+        <v>129.437884</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>169.64</v>
+        <v>169.56</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.31</v>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.068</v>
@@ -10696,10 +10696,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>183.355703</v>
+        <v>183.373095</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>159.34</v>
+        <v>159.35</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.869</v>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>6.384583</v>
+        <v>6.384581</v>
       </c>
       <c r="F31" s="19" t="n">
         <v>0.15</v>
@@ -10814,10 +10814,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>4159.622638</v>
+        <v>4159.707068</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>4966.59</v>
+        <v>4966.69</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.194</v>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1746.251649</v>
+        <v>1745.784056</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>4994.28</v>
+        <v>4992.94</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.86</v>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>789.76</v>
+        <v>789.71</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.391</v>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>39.960045</v>
+        <v>39.959673</v>
       </c>
       <c r="F35" s="19" t="n">
         <v>38.68</v>
@@ -11050,10 +11050,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>46.461655</v>
+        <v>46.477439</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>58.5</v>
+        <v>58.52</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.259</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>9.362730000000001</v>
+        <v>9.356132000000001</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>12.38</v>
+        <v>12.37</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.322</v>
@@ -11168,10 +11168,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>63.631799</v>
+        <v>63.495071</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>82.59</v>
+        <v>82.42</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.298</v>
@@ -11227,10 +11227,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>20.81</v>
+        <v>20.79</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.224</v>
@@ -11286,10 +11286,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>625.6799999999999</v>
+        <v>625.64</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.102</v>
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>1356.862252</v>
+        <v>1356.394702</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>786.98</v>
+        <v>786.71</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.58</v>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>1457.321924</v>
+        <v>1457.464304</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>1983.42</v>
+        <v>1983.61</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.361</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>21.206005</v>
+        <v>21.204685</v>
       </c>
       <c r="F43" s="19" t="n">
         <v>28.03</v>
@@ -11522,10 +11522,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>945.33</v>
+        <v>945.27</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.665</v>
@@ -11581,10 +11581,10 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>14.609086</v>
+        <v>14.565155</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>19.61</v>
+        <v>19.55</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.342</v>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>571.664381</v>
+        <v>571.663172</v>
       </c>
       <c r="F47" s="19" t="n">
         <v>388.73</v>
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="E48" s="26" t="n">
-        <v>16.998056</v>
+        <v>16.984359</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>20.75</v>
+        <v>20.74</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.221</v>
@@ -11817,10 +11817,10 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>4585.708319</v>
+        <v>4585.068745</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>1.638</v>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="E50" s="26" t="n">
-        <v>543.774705</v>
+        <v>544.108486</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>323</v>
+        <v>323.2</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>0.594</v>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>2590.700544</v>
+        <v>2585.283864</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2823.86</v>
+        <v>2817.96</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.09</v>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="E52" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>693.24</v>
+        <v>693.2</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.221</v>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>2.921333</v>
+        <v>2.921765</v>
       </c>
       <c r="F53" s="19" t="n">
         <v>2.52</v>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="E54" s="26" t="n">
-        <v>3778.118684</v>
+        <v>3777.748478</v>
       </c>
       <c r="F54" s="28" t="n">
-        <v>5217.58</v>
+        <v>5217.07</v>
       </c>
       <c r="G54" s="27" t="n">
         <v>1.381</v>
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>19.541754</v>
+        <v>19.540845</v>
       </c>
       <c r="F55" s="19" t="n">
         <v>28.92</v>
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="D5" s="38" t="n">
-        <v>132.141922</v>
+        <v>132.146687</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.336</v>
@@ -12584,13 +12584,13 @@
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.67</v>
+        <v>28.68</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>40.96</v>
+        <v>40.97</v>
       </c>
       <c r="K5" s="39" t="n">
         <v>-0.0718</v>
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="D6" s="41" t="n">
-        <v>52.239408</v>
+        <v>52.240036</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.4</v>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="D7" s="38" t="n">
-        <v>6.384583</v>
+        <v>6.384581</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.024</v>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="D8" s="41" t="n">
-        <v>39.960045</v>
+        <v>39.959673</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>0.968</v>
@@ -12701,7 +12701,7 @@
         <v>0.87</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>34.77</v>
+        <v>34.76</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>1.1</v>
@@ -12728,25 +12728,25 @@
         </is>
       </c>
       <c r="D9" s="38" t="n">
-        <v>9.362730000000001</v>
+        <v>9.356132000000001</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>1.393</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>13.04</v>
+        <v>13.03</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.246</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>11.67</v>
+        <v>11.66</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="K9" s="44" t="n">
         <v>0.0537</v>
@@ -12767,25 +12767,25 @@
         </is>
       </c>
       <c r="D10" s="41" t="n">
-        <v>543.774705</v>
+        <v>544.108486</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>570.96</v>
+        <v>571.3099999999999</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>330.07</v>
+        <v>330.27</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>299.08</v>
+        <v>299.26</v>
       </c>
       <c r="K10" s="45" t="n">
         <v>0.7676999999999999</v>
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="D11" s="38" t="n">
-        <v>2.921333</v>
+        <v>2.921765</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>0.8139999999999999</v>
@@ -12916,25 +12916,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E17" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>677.91</v>
+        <v>677.87</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>681.3200000000001</v>
+        <v>681.27</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>-0.07780000000000001</v>
@@ -12955,25 +12955,25 @@
         </is>
       </c>
       <c r="D18" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E18" s="27" t="n">
         <v>1.411</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>801.12</v>
+        <v>801.0700000000001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.117</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>783.51</v>
+        <v>783.47</v>
       </c>
       <c r="K18" s="42" t="n">
         <v>-0.07539999999999999</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>95.440004</v>
+        <v>95.434067</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>1.269</v>
@@ -13012,7 +13012,7 @@
         <v>1.22</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>116.44</v>
+        <v>116.43</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>-0.05230000000000001</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="D20" s="41" t="n">
-        <v>74.18779499999999</v>
+        <v>74.187712</v>
       </c>
       <c r="E20" s="27" t="n">
         <v>1.162</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>10.955128</v>
+        <v>10.952854</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>1.27</v>
@@ -13090,7 +13090,7 @@
         <v>1.2</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>13.15</v>
+        <v>13.14</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>-0.0063</v>
@@ -13111,25 +13111,25 @@
         </is>
       </c>
       <c r="D22" s="41" t="n">
-        <v>8763.839464000001</v>
+        <v>8763.579604</v>
       </c>
       <c r="E22" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>11217.71</v>
+        <v>11217.38</v>
       </c>
       <c r="K22" s="42" t="n">
         <v>-0.0643</v>
@@ -13150,25 +13150,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>1.035</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>587.64</v>
+        <v>587.6</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.945</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>536.54</v>
+        <v>536.5</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="K23" s="40" t="n">
         <v>0</v>
@@ -13189,25 +13189,25 @@
         </is>
       </c>
       <c r="D24" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E24" s="27" t="n">
         <v>1.356</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>769.89</v>
+        <v>769.84</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>1.117</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>634.1900000000001</v>
+        <v>634.15</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="K24" s="42" t="n">
         <v>-0.0788</v>
@@ -13228,25 +13228,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>183.355703</v>
+        <v>183.373095</v>
       </c>
       <c r="E25" s="18" t="n">
         <v>0.846</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>155.12</v>
+        <v>155.13</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>0.911</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>167.04</v>
+        <v>167.05</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>220.03</v>
+        <v>220.05</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>-0.0265</v>
@@ -13267,25 +13267,25 @@
         </is>
       </c>
       <c r="D26" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E26" s="27" t="n">
         <v>1.291</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>732.98</v>
+        <v>732.9400000000001</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>683.59</v>
+        <v>683.55</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>738.09</v>
+        <v>738.05</v>
       </c>
       <c r="K26" s="42" t="n">
         <v>-0.07190000000000001</v>
@@ -13306,25 +13306,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E27" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>625.6799999999999</v>
+        <v>625.64</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>568.9</v>
+        <v>568.86</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>709.71</v>
+        <v>709.66</v>
       </c>
       <c r="K27" s="40" t="n">
         <v>0</v>
@@ -13345,25 +13345,25 @@
         </is>
       </c>
       <c r="D28" s="41" t="n">
-        <v>1356.862252</v>
+        <v>1356.394702</v>
       </c>
       <c r="E28" s="27" t="n">
         <v>0.76</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>1031.22</v>
+        <v>1030.86</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.03</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>1397.57</v>
+        <v>1397.09</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>746.27</v>
+        <v>746.02</v>
       </c>
       <c r="K28" s="45" t="n">
         <v>0.3103</v>
@@ -13384,25 +13384,25 @@
         </is>
       </c>
       <c r="D29" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E29" s="18" t="n">
         <v>1.53</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>868.6799999999999</v>
+        <v>868.63</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.128</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="K29" s="39" t="n">
         <v>-0.08109999999999999</v>
@@ -13462,25 +13462,25 @@
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E31" s="18" t="n">
         <v>1.128</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>640.4400000000001</v>
+        <v>640.4</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="K31" s="39" t="n">
         <v>-0.0762</v>
@@ -13572,25 +13572,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>2975.174486</v>
+        <v>2975.310621</v>
       </c>
       <c r="E37" s="18" t="n">
         <v>1.334</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>3968.88</v>
+        <v>3969.06</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.302</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>3873.68</v>
+        <v>3873.85</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>4314</v>
+        <v>4314.2</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>-0.0104</v>
@@ -13611,25 +13611,25 @@
         </is>
       </c>
       <c r="D38" s="41" t="n">
-        <v>425.823282</v>
+        <v>425.796789</v>
       </c>
       <c r="E38" s="27" t="n">
         <v>1.182</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>503.32</v>
+        <v>503.29</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>459.04</v>
+        <v>459.01</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>574.86</v>
+        <v>574.83</v>
       </c>
       <c r="K38" s="43" t="n">
         <v>0</v>
@@ -13728,25 +13728,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>156.231435</v>
+        <v>156.089895</v>
       </c>
       <c r="E41" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>123.74</v>
+        <v>123.62</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>130.45</v>
+        <v>130.34</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>164.04</v>
+        <v>163.89</v>
       </c>
       <c r="K41" s="40" t="n">
         <v>0.0025</v>
@@ -13767,25 +13767,25 @@
         </is>
       </c>
       <c r="D42" s="41" t="n">
-        <v>129.499339</v>
+        <v>129.437884</v>
       </c>
       <c r="E42" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>178.71</v>
+        <v>178.62</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>154.62</v>
+        <v>154.55</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>174.82</v>
+        <v>174.74</v>
       </c>
       <c r="K42" s="45" t="n">
         <v>0.0534</v>
@@ -13806,25 +13806,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>46.461655</v>
+        <v>46.477439</v>
       </c>
       <c r="E43" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>65.05</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K43" s="39" t="n">
         <v>-0.0516</v>
@@ -13845,25 +13845,25 @@
         </is>
       </c>
       <c r="D44" s="41" t="n">
-        <v>1457.321924</v>
+        <v>1457.464304</v>
       </c>
       <c r="E44" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>1865.37</v>
+        <v>1865.55</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>1818.74</v>
+        <v>1818.92</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>2113.12</v>
+        <v>2113.32</v>
       </c>
       <c r="K44" s="42" t="n">
         <v>-0.0595</v>
@@ -13884,25 +13884,25 @@
         </is>
       </c>
       <c r="D45" s="38" t="n">
-        <v>14.609086</v>
+        <v>14.565155</v>
       </c>
       <c r="E45" s="18" t="n">
         <v>1.411</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>20.61</v>
+        <v>20.55</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.13</v>
+        <v>20.07</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.37</v>
+        <v>23.3</v>
       </c>
       <c r="K45" s="44" t="n">
         <v>0.05139999999999999</v>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="D46" s="41" t="n">
-        <v>571.664381</v>
+        <v>571.663172</v>
       </c>
       <c r="E46" s="27" t="n">
         <v>1.15</v>
@@ -13962,25 +13962,25 @@
         </is>
       </c>
       <c r="D47" s="38" t="n">
-        <v>4585.708319</v>
+        <v>4585.068745</v>
       </c>
       <c r="E47" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>6947.35</v>
+        <v>6946.38</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>8254.27</v>
+        <v>8253.120000000001</v>
       </c>
       <c r="K47" s="40" t="n">
         <v>0</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="D48" s="41" t="n">
-        <v>2590.700544</v>
+        <v>2585.283864</v>
       </c>
       <c r="E48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>2849.77</v>
+        <v>2843.81</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.031</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>2671.01</v>
+        <v>2665.43</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>3238.38</v>
+        <v>3231.6</v>
       </c>
       <c r="K48" s="43" t="n">
         <v>0.0092</v>
@@ -14040,25 +14040,25 @@
         </is>
       </c>
       <c r="D49" s="38" t="n">
-        <v>3778.118684</v>
+        <v>3777.748478</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.381</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>5217.58</v>
+        <v>5217.07</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>4344.84</v>
+        <v>4344.41</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>4911.55</v>
+        <v>4911.07</v>
       </c>
       <c r="K49" s="40" t="n">
         <v>0</v>
@@ -14150,25 +14150,25 @@
         </is>
       </c>
       <c r="D55" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E55" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F55" s="19" t="n">
-        <v>985.64</v>
+        <v>985.58</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>1176.41</v>
+        <v>1176.33</v>
       </c>
       <c r="I55" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J55" s="19" t="n">
-        <v>1021.98</v>
+        <v>1021.91</v>
       </c>
       <c r="K55" s="39" t="n">
         <v>-0.0616</v>
@@ -14189,25 +14189,25 @@
         </is>
       </c>
       <c r="D56" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E56" s="27" t="n">
         <v>1.389</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>788.62</v>
+        <v>788.58</v>
       </c>
       <c r="G56" s="27" t="n">
         <v>1.367</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>776.13</v>
+        <v>776.09</v>
       </c>
       <c r="I56" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J56" s="28" t="n">
-        <v>681.3200000000001</v>
+        <v>681.27</v>
       </c>
       <c r="K56" s="42" t="n">
         <v>-0.0789</v>
@@ -14228,25 +14228,25 @@
         </is>
       </c>
       <c r="D57" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E57" s="18" t="n">
         <v>1.418</v>
       </c>
       <c r="F57" s="19" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>1.318</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>748.3099999999999</v>
+        <v>748.27</v>
       </c>
       <c r="I57" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J57" s="19" t="n">
-        <v>880.03</v>
+        <v>879.98</v>
       </c>
       <c r="K57" s="40" t="n">
         <v>0</v>
@@ -14267,25 +14267,25 @@
         </is>
       </c>
       <c r="D58" s="41" t="n">
-        <v>2269.48994</v>
+        <v>2263.863308</v>
       </c>
       <c r="E58" s="27" t="n">
         <v>1.052</v>
       </c>
       <c r="F58" s="28" t="n">
-        <v>2387.5</v>
+        <v>2381.58</v>
       </c>
       <c r="G58" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>2362.54</v>
+        <v>2356.68</v>
       </c>
       <c r="I58" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J58" s="28" t="n">
-        <v>2836.86</v>
+        <v>2829.83</v>
       </c>
       <c r="K58" s="42" t="n">
         <v>-0.0488</v>
@@ -14306,25 +14306,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E59" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="F59" s="19" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>470.11</v>
+        <v>470.08</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>624.54</v>
+        <v>624.5</v>
       </c>
       <c r="K59" s="40" t="n">
         <v>0</v>
@@ -14345,25 +14345,25 @@
         </is>
       </c>
       <c r="D60" s="41" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E60" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="F60" s="28" t="n">
-        <v>526.89</v>
+        <v>526.85</v>
       </c>
       <c r="G60" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>487.14</v>
+        <v>487.11</v>
       </c>
       <c r="I60" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J60" s="28" t="n">
-        <v>652.9299999999999</v>
+        <v>652.89</v>
       </c>
       <c r="K60" s="43" t="n">
         <v>0</v>
@@ -14384,25 +14384,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E61" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="F61" s="19" t="n">
-        <v>560.38</v>
+        <v>560.35</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>0.955</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>542.21</v>
+        <v>542.1799999999999</v>
       </c>
       <c r="I61" s="18" t="n">
         <v>0.9</v>
       </c>
       <c r="J61" s="19" t="n">
-        <v>510.99</v>
+        <v>510.96</v>
       </c>
       <c r="K61" s="44" t="n">
         <v>0.1016</v>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="D62" s="41" t="n">
-        <v>21.206005</v>
+        <v>21.204685</v>
       </c>
       <c r="E62" s="27" t="n">
         <v>1.322</v>
@@ -14533,25 +14533,25 @@
         </is>
       </c>
       <c r="D68" s="38" t="n">
-        <v>922.37261</v>
+        <v>918.565802</v>
       </c>
       <c r="E68" s="18" t="n">
         <v>0.304</v>
       </c>
       <c r="F68" s="19" t="n">
-        <v>280.4</v>
+        <v>279.24</v>
       </c>
       <c r="G68" s="18" t="n">
         <v>0.412</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>380.02</v>
+        <v>378.45</v>
       </c>
       <c r="I68" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J68" s="19" t="n">
-        <v>599.54</v>
+        <v>597.0700000000001</v>
       </c>
       <c r="K68" s="39" t="n">
         <v>-0.0703</v>
@@ -14572,25 +14572,25 @@
         </is>
       </c>
       <c r="D69" s="41" t="n">
-        <v>14.068384</v>
+        <v>14.044867</v>
       </c>
       <c r="E69" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F69" s="28" t="n">
-        <v>15.26</v>
+        <v>15.24</v>
       </c>
       <c r="G69" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="I69" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J69" s="28" t="n">
-        <v>17.59</v>
+        <v>17.56</v>
       </c>
       <c r="K69" s="42" t="n">
         <v>-0.0742</v>
@@ -14611,25 +14611,25 @@
         </is>
       </c>
       <c r="D70" s="38" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="E70" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="F70" s="19" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="G70" s="18" t="n">
         <v>1.128</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>19.17</v>
+        <v>19.16</v>
       </c>
       <c r="I70" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J70" s="19" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="K70" s="39" t="n">
         <v>-0.08890000000000001</v>
@@ -14650,25 +14650,25 @@
         </is>
       </c>
       <c r="D71" s="41" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="E71" s="27" t="n">
         <v>1.019</v>
       </c>
       <c r="F71" s="28" t="n">
-        <v>17.32</v>
+        <v>17.31</v>
       </c>
       <c r="G71" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="I71" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J71" s="28" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="K71" s="42" t="n">
         <v>-0.0459</v>
@@ -14689,25 +14689,25 @@
         </is>
       </c>
       <c r="D72" s="38" t="n">
-        <v>4159.622638</v>
+        <v>4159.707068</v>
       </c>
       <c r="E72" s="18" t="n">
         <v>1.096</v>
       </c>
       <c r="F72" s="19" t="n">
-        <v>4558.95</v>
+        <v>4559.04</v>
       </c>
       <c r="G72" s="18" t="n">
         <v>1.041</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>4330.17</v>
+        <v>4330.26</v>
       </c>
       <c r="I72" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J72" s="19" t="n">
-        <v>5407.51</v>
+        <v>5407.62</v>
       </c>
       <c r="K72" s="39" t="n">
         <v>-0.08210000000000001</v>
@@ -14728,25 +14728,25 @@
         </is>
       </c>
       <c r="D73" s="41" t="n">
-        <v>1746.251649</v>
+        <v>1745.784056</v>
       </c>
       <c r="E73" s="27" t="n">
         <v>2.669</v>
       </c>
       <c r="F73" s="28" t="n">
-        <v>4660.75</v>
+        <v>4659.5</v>
       </c>
       <c r="G73" s="27" t="n">
         <v>2.658</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>4641.54</v>
+        <v>4640.29</v>
       </c>
       <c r="I73" s="27" t="n">
         <v>2.4</v>
       </c>
       <c r="J73" s="28" t="n">
-        <v>4191</v>
+        <v>4189.88</v>
       </c>
       <c r="K73" s="42" t="n">
         <v>-0.0668</v>
@@ -14767,25 +14767,25 @@
         </is>
       </c>
       <c r="D74" s="38" t="n">
-        <v>63.631799</v>
+        <v>63.495071</v>
       </c>
       <c r="E74" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F74" s="19" t="n">
-        <v>78.01000000000001</v>
+        <v>77.84</v>
       </c>
       <c r="G74" s="18" t="n">
         <v>1.172</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>74.58</v>
+        <v>74.42</v>
       </c>
       <c r="I74" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J74" s="19" t="n">
-        <v>82.72</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="K74" s="39" t="n">
         <v>-0.0555</v>
@@ -14806,25 +14806,25 @@
         </is>
       </c>
       <c r="D75" s="41" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="E75" s="27" t="n">
         <v>1.118</v>
       </c>
       <c r="F75" s="28" t="n">
-        <v>19</v>
+        <v>18.99</v>
       </c>
       <c r="G75" s="27" t="n">
         <v>1.117</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>18.99</v>
+        <v>18.97</v>
       </c>
       <c r="I75" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J75" s="28" t="n">
-        <v>21.25</v>
+        <v>21.23</v>
       </c>
       <c r="K75" s="42" t="n">
         <v>-0.0866</v>
@@ -14845,25 +14845,25 @@
         </is>
       </c>
       <c r="D76" s="38" t="n">
-        <v>16.998056</v>
+        <v>16.984359</v>
       </c>
       <c r="E76" s="18" t="n">
         <v>1.2399</v>
       </c>
       <c r="F76" s="19" t="n">
-        <v>21.08</v>
+        <v>21.06</v>
       </c>
       <c r="G76" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H76" s="19" t="n">
-        <v>20.84</v>
+        <v>20.82</v>
       </c>
       <c r="I76" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J76" s="19" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="K76" s="40" t="n">
         <v>0.0155</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="D77" s="41" t="n">
-        <v>19.541754</v>
+        <v>19.540845</v>
       </c>
       <c r="E77" s="27" t="n">
         <v>1.28</v>
@@ -15193,7 +15193,7 @@
         <v>2.669</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4660.75</v>
+        <v>4659.5</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>1.736</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>985.64</v>
+        <v>985.58</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>0.304</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>280.4</v>
+        <v>279.24</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>1.638</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>7511.39</v>
+        <v>7510.34</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>1.53</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>868.6799999999999</v>
+        <v>868.63</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>0.76</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>1031.22</v>
+        <v>1030.86</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>1.418</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>805.09</v>
+        <v>805.04</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.74</v>
+        <v>123.62</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>1.411</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>801.12</v>
+        <v>801.0700000000001</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>1.411</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.61</v>
+        <v>20.55</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>0.846</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>155.12</v>
+        <v>155.13</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>1.393</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>13.04</v>
+        <v>13.03</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>0.898</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>509.85</v>
+        <v>509.82</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -16373,10 +16373,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>922.37261</v>
+        <v>918.565802</v>
       </c>
       <c r="E3" s="67" t="n">
-        <v>0.00108416</v>
+        <v>0.00108865</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -16396,10 +16396,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2975.174486</v>
+        <v>2975.310621</v>
       </c>
       <c r="E4" s="69" t="n">
-        <v>0.00033611</v>
+        <v>0.0003361</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -16419,10 +16419,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>14.068384</v>
+        <v>14.044867</v>
       </c>
       <c r="E5" s="67" t="n">
-        <v>0.07108137</v>
+        <v>0.07120039</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2269.48994</v>
+        <v>2263.863308</v>
       </c>
       <c r="E6" s="69" t="n">
-        <v>0.00044063</v>
+        <v>0.00044172</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -16465,10 +16465,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.440004</v>
+        <v>95.434067</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>0.01047779</v>
+        <v>0.01047844</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -16511,10 +16511,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.141922</v>
+        <v>132.146687</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>0.00756762</v>
+        <v>0.00756735</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -16534,10 +16534,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.239408</v>
+        <v>52.240036</v>
       </c>
       <c r="E10" s="69" t="n">
-        <v>0.01914264</v>
+        <v>0.01914241</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -16580,10 +16580,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>156.231435</v>
+        <v>156.089895</v>
       </c>
       <c r="E12" s="69" t="n">
-        <v>0.00640076</v>
+        <v>0.00640656</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -16603,10 +16603,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.955128</v>
+        <v>10.952854</v>
       </c>
       <c r="E13" s="67" t="n">
-        <v>0.09128145</v>
+        <v>0.0913004</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -16626,10 +16626,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.18779499999999</v>
+        <v>74.187712</v>
       </c>
       <c r="E14" s="69" t="n">
-        <v>0.01347931</v>
+        <v>0.01347932</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8763.839464000001</v>
+        <v>8763.579604</v>
       </c>
       <c r="E15" s="67" t="n">
         <v>0.00011411</v>
@@ -16672,10 +16672,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.499339</v>
+        <v>129.437884</v>
       </c>
       <c r="E16" s="69" t="n">
-        <v>0.00772205</v>
+        <v>0.00772571</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>425.823282</v>
+        <v>425.796789</v>
       </c>
       <c r="E17" s="67" t="n">
-        <v>0.00234839</v>
+        <v>0.00234854</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>183.355703</v>
+        <v>183.373095</v>
       </c>
       <c r="E18" s="69" t="n">
-        <v>0.00545388</v>
+        <v>0.00545336</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -16741,10 +16741,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>0.05883087</v>
+        <v>0.05887814</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -16764,10 +16764,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.384583</v>
+        <v>6.384581</v>
       </c>
       <c r="E20" s="69" t="n">
-        <v>0.1566273</v>
+        <v>0.15662735</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -16787,10 +16787,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.362730000000001</v>
+        <v>9.356132000000001</v>
       </c>
       <c r="E21" s="67" t="n">
-        <v>0.10680645</v>
+        <v>0.10688178</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -16810,10 +16810,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4159.622638</v>
+        <v>4159.707068</v>
       </c>
       <c r="E22" s="69" t="n">
-        <v>0.00024041</v>
+        <v>0.0002404</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -16833,10 +16833,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.960045</v>
+        <v>39.959673</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>0.025025</v>
+        <v>0.02502523</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -16856,10 +16856,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.461655</v>
+        <v>46.477439</v>
       </c>
       <c r="E24" s="69" t="n">
-        <v>0.02152312</v>
+        <v>0.02151582</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -16879,10 +16879,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1746.251649</v>
+        <v>1745.784056</v>
       </c>
       <c r="E25" s="67" t="n">
-        <v>0.00057266</v>
+        <v>0.00057281</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.631799</v>
+        <v>63.495071</v>
       </c>
       <c r="E26" s="69" t="n">
-        <v>0.01571541</v>
+        <v>0.01574925</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="E27" s="67" t="n">
-        <v>0.05883087</v>
+        <v>0.05887814</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1356.862252</v>
+        <v>1356.394702</v>
       </c>
       <c r="E28" s="69" t="n">
-        <v>0.00073699</v>
+        <v>0.0007372499999999999</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -16971,10 +16971,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1457.321924</v>
+        <v>1457.464304</v>
       </c>
       <c r="E29" s="67" t="n">
-        <v>0.00068619</v>
+        <v>0.00068612</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -16994,10 +16994,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.609086</v>
+        <v>14.565155</v>
       </c>
       <c r="E30" s="69" t="n">
-        <v>0.06845055</v>
+        <v>0.06865701</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -17017,10 +17017,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>543.774705</v>
+        <v>544.108486</v>
       </c>
       <c r="E31" s="67" t="n">
-        <v>0.001839</v>
+        <v>0.00183787</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.664381</v>
+        <v>571.663172</v>
       </c>
       <c r="E33" s="67" t="n">
         <v>0.00174928</v>
@@ -17086,10 +17086,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4585.708319</v>
+        <v>4585.068745</v>
       </c>
       <c r="E34" s="69" t="n">
-        <v>0.00021807</v>
+        <v>0.0002181</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -17109,10 +17109,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.206005</v>
+        <v>21.204685</v>
       </c>
       <c r="E35" s="67" t="n">
-        <v>0.04715645</v>
+        <v>0.04715939</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -17132,10 +17132,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.997879</v>
+        <v>16.984232</v>
       </c>
       <c r="E36" s="69" t="n">
-        <v>0.05883087</v>
+        <v>0.05887814</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.921333</v>
+        <v>2.921765</v>
       </c>
       <c r="E37" s="67" t="n">
-        <v>0.34230949</v>
+        <v>0.34225887</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2590.700544</v>
+        <v>2585.283864</v>
       </c>
       <c r="E38" s="69" t="n">
-        <v>0.000386</v>
+        <v>0.0003868</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -17201,10 +17201,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3778.118684</v>
+        <v>3777.748478</v>
       </c>
       <c r="E39" s="67" t="n">
-        <v>0.00026468</v>
+        <v>0.00026471</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -17224,10 +17224,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E40" s="69" t="n">
-        <v>0.00176129</v>
+        <v>0.0017614</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -17247,10 +17247,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>567.764375</v>
+        <v>567.729053</v>
       </c>
       <c r="E41" s="67" t="n">
-        <v>0.00176129</v>
+        <v>0.0017614</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.998056</v>
+        <v>16.984359</v>
       </c>
       <c r="E42" s="69" t="n">
-        <v>0.05883026</v>
+        <v>0.0588777</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.541754</v>
+        <v>19.540845</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>0.05117248</v>
+        <v>0.05117486</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="C4" s="74" t="inlineStr">
         <is>
-          <t>21 March 2026 — 12:41 UTC</t>
+          <t>22 March 2026 — 06:41 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1326,7 +1326,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 22 March 2026  |  06:41 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 23 March 2026  |  07:01 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1537,25 +1537,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.146687</v>
+        <v>132.030471</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.336</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.4</v>
+        <v>44.36</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.68</v>
+        <v>28.65</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>40.97</v>
+        <v>40.93</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>-0.0718</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>918.565802</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.304</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.24</v>
+        <v>279.73</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>378.45</v>
+        <v>379.11</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>597.0700000000001</v>
+        <v>598.11</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>-0.0703</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1663,25 +1663,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>677.87</v>
+        <v>677.55</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>681.27</v>
+        <v>680.95</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>-0.07780000000000001</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1726,25 +1726,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>14.044867</v>
+        <v>13.685731</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.24</v>
+        <v>14.85</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>16</v>
+        <v>15.59</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.56</v>
+        <v>17.11</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>-0.0742</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1789,25 +1789,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.411</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>801.0700000000001</v>
+        <v>800.6799999999999</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>783.47</v>
+        <v>783.09</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>-0.07539999999999999</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2975.310621</v>
+        <v>2973.478145</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.334</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3969.06</v>
+        <v>3966.62</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3873.85</v>
+        <v>3871.47</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4314.2</v>
+        <v>4311.54</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>-0.0104</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1915,25 +1915,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>985.58</v>
+        <v>985.11</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1176.33</v>
+        <v>1175.77</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1021.91</v>
+        <v>1021.43</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>-0.0616</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1978,25 +1978,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.434067</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.269</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>121.11</v>
+        <v>121.05</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.074</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>102.5</v>
+        <v>102.45</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116.43</v>
+        <v>116.37</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>-0.05230000000000001</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.389</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>788.58</v>
+        <v>788.2</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>776.09</v>
+        <v>775.72</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>681.27</v>
+        <v>680.95</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>-0.0789</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2104,25 +2104,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>748.27</v>
+        <v>747.91</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>879.98</v>
+        <v>879.5599999999999</v>
       </c>
       <c r="M20" s="33" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2167,25 +2167,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>425.796789</v>
+        <v>425.593787</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>503.29</v>
+        <v>503.05</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>459.01</v>
+        <v>458.79</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>574.83</v>
+        <v>574.55</v>
       </c>
       <c r="M21" s="34" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2230,25 +2230,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>2263.863308</v>
+        <v>2271.865535</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.052</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>2381.58</v>
+        <v>2390</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>2356.68</v>
+        <v>2365.01</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>2829.83</v>
+        <v>2839.83</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>-0.0488</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2293,25 +2293,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>470.08</v>
+        <v>469.86</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="M23" s="34" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>52.240036</v>
+        <v>52.260748</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>0.4</v>
@@ -2431,7 +2431,7 @@
         <v>0.394</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>20.58</v>
+        <v>20.59</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>0.44</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2482,25 +2482,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>526.85</v>
+        <v>526.6</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>487.11</v>
+        <v>486.88</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="M26" s="33" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2608,25 +2608,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>19.16</v>
+        <v>19.24</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>-0.08890000000000001</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2671,25 +2671,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>156.089895</v>
+        <v>155.991755</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>123.62</v>
+        <v>123.55</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>130.34</v>
+        <v>130.25</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>163.89</v>
+        <v>163.79</v>
       </c>
       <c r="M29" s="34" t="n">
         <v>0.0025</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2734,25 +2734,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.987</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>560.35</v>
+        <v>560.08</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>542.1799999999999</v>
+        <v>541.92</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>510.96</v>
+        <v>510.71</v>
       </c>
       <c r="M30" s="35" t="n">
         <v>0.1016</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>74.187712</v>
+        <v>74.18732300000001</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.162</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2860,25 +2860,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>10.952854</v>
+        <v>10.942196</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.27</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>12.6</v>
+        <v>12.58</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>-0.0063</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2923,25 +2923,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>8763.579604</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>-0.0643</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2986,25 +2986,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>587.6</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>536.5</v>
+        <v>536.25</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="M34" s="33" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3049,25 +3049,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.356</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>769.84</v>
+        <v>769.47</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>-0.0788</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3112,25 +3112,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>129.437884</v>
+        <v>129.16035</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>178.62</v>
+        <v>178.24</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>154.55</v>
+        <v>154.22</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>174.74</v>
+        <v>174.37</v>
       </c>
       <c r="M36" s="35" t="n">
         <v>0.0534</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3175,25 +3175,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.019</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>17.31</v>
+        <v>17.38</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>-0.0459</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3238,25 +3238,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>183.373095</v>
+        <v>182.949169</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.846</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>155.13</v>
+        <v>154.77</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>167.05</v>
+        <v>166.67</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>220.05</v>
+        <v>219.54</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>-0.0265</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>6.384581</v>
+        <v>6.384576</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.024</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3364,25 +3364,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>4159.707068</v>
+        <v>4159.198135</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.096</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>4559.04</v>
+        <v>4558.48</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>4330.26</v>
+        <v>4329.73</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>5407.62</v>
+        <v>5406.96</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>-0.08210000000000001</v>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3427,25 +3427,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1745.784056</v>
+        <v>1743.592306</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>2.669</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>4659.5</v>
+        <v>4653.65</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>4640.29</v>
+        <v>4634.47</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>4189.88</v>
+        <v>4184.62</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>-0.0668</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3490,25 +3490,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.291</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>732.9400000000001</v>
+        <v>732.59</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>683.55</v>
+        <v>683.22</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>738.05</v>
+        <v>737.7</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>-0.07190000000000001</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>39.959673</v>
+        <v>39.958994</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>0.968</v>
@@ -3571,7 +3571,7 @@
         <v>1.1</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>43.96</v>
+        <v>43.95</v>
       </c>
       <c r="M43" s="34" t="n">
         <v>0</v>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3616,25 +3616,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>46.477439</v>
+        <v>46.456446</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>65.06999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>-0.0516</v>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>9.356132000000001</v>
+        <v>9.361336</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.393</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>13.03</v>
+        <v>13.04</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.246</v>
@@ -3697,7 +3697,7 @@
         <v>0.6</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="M45" s="36" t="n">
         <v>0.0537</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3742,25 +3742,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>63.495071</v>
+        <v>63.592665</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>1.226</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>77.84</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>74.42</v>
+        <v>74.53</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>82.54000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>-0.0555</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3805,25 +3805,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.118</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>18.99</v>
+        <v>19.07</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>18.97</v>
+        <v>19.05</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>-0.0866</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3868,25 +3868,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>625.64</v>
+        <v>625.34</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>568.86</v>
+        <v>568.59</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>709.66</v>
+        <v>709.3200000000001</v>
       </c>
       <c r="M48" s="33" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3931,25 +3931,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>1356.394702</v>
+        <v>1356.44293</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.76</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1030.86</v>
+        <v>1030.9</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.03</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1397.09</v>
+        <v>1397.14</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>746.02</v>
+        <v>746.04</v>
       </c>
       <c r="M49" s="36" t="n">
         <v>0.3103</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3994,25 +3994,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>1457.464304</v>
+        <v>1458.129101</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>1865.55</v>
+        <v>1866.41</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>1818.92</v>
+        <v>1819.75</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>2113.32</v>
+        <v>2114.29</v>
       </c>
       <c r="M50" s="29" t="n">
         <v>-0.0595</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4057,25 +4057,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>21.204685</v>
+        <v>21.194576</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.222</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>25.91</v>
+        <v>25.9</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="M51" s="34" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4120,25 +4120,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.53</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>868.63</v>
+        <v>868.21</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>-0.08109999999999999</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4183,25 +4183,25 @@
         </is>
       </c>
       <c r="F53" s="17" t="n">
-        <v>14.565155</v>
+        <v>13.880458</v>
       </c>
       <c r="G53" s="18" t="n">
         <v>1.411</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>20.55</v>
+        <v>19.59</v>
       </c>
       <c r="I53" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>20.07</v>
+        <v>19.13</v>
       </c>
       <c r="K53" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>23.3</v>
+        <v>22.21</v>
       </c>
       <c r="M53" s="36" t="n">
         <v>0.05139999999999999</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="R53" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R54" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="F55" s="17" t="n">
-        <v>571.663172</v>
+        <v>571.660967</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>1.15</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="R55" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4372,25 +4372,25 @@
         </is>
       </c>
       <c r="F56" s="26" t="n">
-        <v>16.984359</v>
+        <v>17.053859</v>
       </c>
       <c r="G56" s="27" t="n">
         <v>1.2399</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>21.06</v>
+        <v>21.15</v>
       </c>
       <c r="I56" s="27" t="n">
         <v>1.226</v>
       </c>
       <c r="J56" s="28" t="n">
-        <v>20.82</v>
+        <v>20.91</v>
       </c>
       <c r="K56" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L56" s="28" t="n">
-        <v>22.93</v>
+        <v>23.02</v>
       </c>
       <c r="M56" s="33" t="n">
         <v>0.0155</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="R56" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4435,25 +4435,25 @@
         </is>
       </c>
       <c r="F57" s="17" t="n">
-        <v>4585.068745</v>
+        <v>4581.917868</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="I57" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="J57" s="19" t="n">
-        <v>6946.38</v>
+        <v>6941.61</v>
       </c>
       <c r="K57" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>8253.120000000001</v>
+        <v>8247.450000000001</v>
       </c>
       <c r="M57" s="34" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="R57" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="F58" s="26" t="n">
-        <v>544.108486</v>
+        <v>544.717652</v>
       </c>
       <c r="G58" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>571.3099999999999</v>
+        <v>571.95</v>
       </c>
       <c r="I58" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="J58" s="28" t="n">
-        <v>330.27</v>
+        <v>330.64</v>
       </c>
       <c r="K58" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L58" s="28" t="n">
-        <v>299.26</v>
+        <v>299.59</v>
       </c>
       <c r="M58" s="35" t="n">
         <v>0.7676999999999999</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="R58" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4561,25 +4561,25 @@
         </is>
       </c>
       <c r="F59" s="17" t="n">
-        <v>2585.283864</v>
+        <v>2590.03315</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>2843.81</v>
+        <v>2849.04</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>2665.43</v>
+        <v>2670.32</v>
       </c>
       <c r="K59" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>3231.6</v>
+        <v>3237.54</v>
       </c>
       <c r="M59" s="34" t="n">
         <v>0.0092</v>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="R59" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4624,25 +4624,25 @@
         </is>
       </c>
       <c r="F60" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="G60" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="I60" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J60" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="K60" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L60" s="28" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="M60" s="29" t="n">
         <v>-0.0762</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="R60" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="F61" s="17" t="n">
-        <v>2.921765</v>
+        <v>2.918309</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>0.8139999999999999</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="R61" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4750,25 +4750,25 @@
         </is>
       </c>
       <c r="F62" s="26" t="n">
-        <v>3777.748478</v>
+        <v>3776.042542</v>
       </c>
       <c r="G62" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>5217.07</v>
+        <v>5214.71</v>
       </c>
       <c r="I62" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J62" s="28" t="n">
-        <v>4344.41</v>
+        <v>4342.45</v>
       </c>
       <c r="K62" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L62" s="28" t="n">
-        <v>4911.07</v>
+        <v>4908.86</v>
       </c>
       <c r="M62" s="33" t="n">
         <v>0</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="R62" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="F63" s="17" t="n">
-        <v>19.540845</v>
+        <v>19.536613</v>
       </c>
       <c r="G63" s="18" t="n">
         <v>1.28</v>
@@ -4825,7 +4825,7 @@
         <v>1.117</v>
       </c>
       <c r="J63" s="19" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="K63" s="18" t="n">
         <v>1.3</v>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="R63" s="23" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="R64" s="32" t="inlineStr">
         <is>
-          <t>2026-03-22 06:41 UTC</t>
+          <t>2026-03-23 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -5125,49 +5125,49 @@
         </is>
       </c>
       <c r="E3" s="38" t="n">
-        <v>132.146687</v>
+        <v>132.030471</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.362</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.362</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.362</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>28.68</v>
+        <v>28.65</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>28.68</v>
+        <v>28.65</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>28.68</v>
+        <v>28.65</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>40.97</v>
+        <v>40.93</v>
       </c>
       <c r="T3" s="39" t="n">
         <v>-0.0718</v>
@@ -5196,49 +5196,49 @@
         </is>
       </c>
       <c r="E4" s="41" t="n">
-        <v>918.565802</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.327</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>300.37</v>
+        <v>300.9</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.327</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>300.37</v>
+        <v>300.9</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.327</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>300.37</v>
+        <v>300.9</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>378.45</v>
+        <v>379.11</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>378.45</v>
+        <v>379.11</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.412</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>378.45</v>
+        <v>379.11</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>597.0700000000001</v>
+        <v>598.11</v>
       </c>
       <c r="T4" s="42" t="n">
         <v>-0.0703</v>
@@ -5267,49 +5267,49 @@
         </is>
       </c>
       <c r="E5" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.247</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>707.96</v>
+        <v>707.62</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.247</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>707.96</v>
+        <v>707.62</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.247</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>707.96</v>
+        <v>707.62</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>677.87</v>
+        <v>677.55</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>677.87</v>
+        <v>677.55</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>677.87</v>
+        <v>677.55</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>681.27</v>
+        <v>680.95</v>
       </c>
       <c r="T5" s="39" t="n">
         <v>-0.07780000000000001</v>
@@ -5338,49 +5338,49 @@
         </is>
       </c>
       <c r="E6" s="41" t="n">
-        <v>14.044867</v>
+        <v>13.685731</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>16.46</v>
+        <v>16.04</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>16.46</v>
+        <v>16.04</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>16.46</v>
+        <v>16.04</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>16</v>
+        <v>15.59</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>16</v>
+        <v>15.59</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>16</v>
+        <v>15.59</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.56</v>
+        <v>17.11</v>
       </c>
       <c r="T6" s="42" t="n">
         <v>-0.0742</v>
@@ -5409,49 +5409,49 @@
         </is>
       </c>
       <c r="E7" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.526</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>866.35</v>
+        <v>865.9400000000001</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.526</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>866.35</v>
+        <v>865.9400000000001</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.526</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>866.35</v>
+        <v>865.9400000000001</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>783.47</v>
+        <v>783.09</v>
       </c>
       <c r="T7" s="39" t="n">
         <v>-0.07539999999999999</v>
@@ -5480,49 +5480,49 @@
         </is>
       </c>
       <c r="E8" s="41" t="n">
-        <v>2975.310621</v>
+        <v>2973.478145</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.348</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>4010.72</v>
+        <v>4008.25</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.348</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>4010.72</v>
+        <v>4008.25</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.348</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>4010.72</v>
+        <v>4008.25</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3873.85</v>
+        <v>3871.47</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3873.85</v>
+        <v>3871.47</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.302</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3873.85</v>
+        <v>3871.47</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4314.2</v>
+        <v>4311.54</v>
       </c>
       <c r="T8" s="42" t="n">
         <v>-0.0104</v>
@@ -5551,49 +5551,49 @@
         </is>
       </c>
       <c r="E9" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.85</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>1050.3</v>
+        <v>1049.8</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.85</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>1050.3</v>
+        <v>1049.8</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.85</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>1050.3</v>
+        <v>1049.8</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1176.33</v>
+        <v>1175.77</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1176.33</v>
+        <v>1175.77</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1176.33</v>
+        <v>1175.77</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1021.91</v>
+        <v>1021.43</v>
       </c>
       <c r="T9" s="39" t="n">
         <v>-0.0616</v>
@@ -5622,49 +5622,49 @@
         </is>
       </c>
       <c r="E10" s="41" t="n">
-        <v>95.434067</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.339</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>127.79</v>
+        <v>127.73</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.339</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>127.79</v>
+        <v>127.73</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.339</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>127.79</v>
+        <v>127.73</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.074</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>102.5</v>
+        <v>102.45</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>1.074</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>102.5</v>
+        <v>102.45</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>1.074</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>102.5</v>
+        <v>102.45</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116.43</v>
+        <v>116.37</v>
       </c>
       <c r="T10" s="42" t="n">
         <v>-0.05230000000000001</v>
@@ -5693,49 +5693,49 @@
         </is>
       </c>
       <c r="E11" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.508</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>856.14</v>
+        <v>855.73</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.508</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>856.14</v>
+        <v>855.73</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.508</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>856.14</v>
+        <v>855.73</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>776.09</v>
+        <v>775.72</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>776.09</v>
+        <v>775.72</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.367</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>776.09</v>
+        <v>775.72</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>681.27</v>
+        <v>680.95</v>
       </c>
       <c r="T11" s="39" t="n">
         <v>-0.0789</v>
@@ -5764,49 +5764,49 @@
         </is>
       </c>
       <c r="E12" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>1.418</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>748.27</v>
+        <v>747.91</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>748.27</v>
+        <v>747.91</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>1.318</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>748.27</v>
+        <v>747.91</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>879.98</v>
+        <v>879.5599999999999</v>
       </c>
       <c r="T12" s="43" t="n">
         <v>0</v>
@@ -5835,49 +5835,49 @@
         </is>
       </c>
       <c r="E13" s="38" t="n">
-        <v>425.796789</v>
+        <v>425.593787</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>503.29</v>
+        <v>503.05</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>503.29</v>
+        <v>503.05</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>1.182</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>503.29</v>
+        <v>503.05</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>459.01</v>
+        <v>458.79</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>459.01</v>
+        <v>458.79</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>1.078</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>459.01</v>
+        <v>458.79</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>574.83</v>
+        <v>574.55</v>
       </c>
       <c r="T13" s="40" t="n">
         <v>0</v>
@@ -5906,49 +5906,49 @@
         </is>
       </c>
       <c r="E14" s="41" t="n">
-        <v>2263.863308</v>
+        <v>2271.865535</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.106</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>2503.83</v>
+        <v>2512.68</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.106</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>2503.83</v>
+        <v>2512.68</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.106</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>2503.83</v>
+        <v>2512.68</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>2356.68</v>
+        <v>2365.01</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>2356.68</v>
+        <v>2365.01</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>2356.68</v>
+        <v>2365.01</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>2829.83</v>
+        <v>2839.83</v>
       </c>
       <c r="T14" s="42" t="n">
         <v>-0.0488</v>
@@ -5977,49 +5977,49 @@
         </is>
       </c>
       <c r="E15" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>470.08</v>
+        <v>469.86</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>470.08</v>
+        <v>469.86</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>470.08</v>
+        <v>469.86</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="T15" s="40" t="n">
         <v>0</v>
@@ -6119,25 +6119,25 @@
         </is>
       </c>
       <c r="E17" s="38" t="n">
-        <v>52.240036</v>
+        <v>52.260748</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>0.41</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>21.42</v>
+        <v>21.43</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>0.41</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>21.42</v>
+        <v>21.43</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>0.41</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>21.42</v>
+        <v>21.43</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0.369</v>
@@ -6190,49 +6190,49 @@
         </is>
       </c>
       <c r="E18" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>526.85</v>
+        <v>526.6</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>526.85</v>
+        <v>526.6</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>526.85</v>
+        <v>526.6</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>487.11</v>
+        <v>486.88</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>487.11</v>
+        <v>486.88</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>487.11</v>
+        <v>486.88</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="T18" s="43" t="n">
         <v>0</v>
@@ -6332,49 +6332,49 @@
         </is>
       </c>
       <c r="E20" s="41" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.215</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>20.64</v>
+        <v>20.72</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.215</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>20.64</v>
+        <v>20.72</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.215</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>20.64</v>
+        <v>20.72</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>19.16</v>
+        <v>19.24</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>19.16</v>
+        <v>19.24</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>19.16</v>
+        <v>19.24</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="T20" s="42" t="n">
         <v>-0.08890000000000001</v>
@@ -6403,49 +6403,49 @@
         </is>
       </c>
       <c r="E21" s="38" t="n">
-        <v>156.089895</v>
+        <v>155.991755</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.79</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>123.31</v>
+        <v>123.23</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.79</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>123.31</v>
+        <v>123.23</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.79</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>123.31</v>
+        <v>123.23</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>130.34</v>
+        <v>130.25</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>130.34</v>
+        <v>130.25</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>130.34</v>
+        <v>130.25</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>163.89</v>
+        <v>163.79</v>
       </c>
       <c r="T21" s="40" t="n">
         <v>0.0025</v>
@@ -6474,49 +6474,49 @@
         </is>
       </c>
       <c r="E22" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.896</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>508.69</v>
+        <v>508.44</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.896</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>508.69</v>
+        <v>508.44</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.896</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>508.69</v>
+        <v>508.44</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>542.1799999999999</v>
+        <v>541.92</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>542.1799999999999</v>
+        <v>541.92</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.955</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>542.1799999999999</v>
+        <v>541.92</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>510.96</v>
+        <v>510.71</v>
       </c>
       <c r="T22" s="45" t="n">
         <v>0.1016</v>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="E23" s="38" t="n">
-        <v>74.187712</v>
+        <v>74.18732300000001</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>1.162</v>
@@ -6616,49 +6616,49 @@
         </is>
       </c>
       <c r="E24" s="41" t="n">
-        <v>10.952854</v>
+        <v>10.942196</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>1.278</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>1.278</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>1.278</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="T24" s="42" t="n">
         <v>-0.0063</v>
@@ -6687,49 +6687,49 @@
         </is>
       </c>
       <c r="E25" s="38" t="n">
-        <v>8763.579604</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>1.368</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>11988.58</v>
+        <v>11986.92</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>1.368</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>11988.58</v>
+        <v>11986.92</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>1.368</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>11988.58</v>
+        <v>11986.92</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="T25" s="39" t="n">
         <v>-0.0643</v>
@@ -6758,49 +6758,49 @@
         </is>
       </c>
       <c r="E26" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>587.6</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>587.6</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.035</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>587.6</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>536.5</v>
+        <v>536.25</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>536.5</v>
+        <v>536.25</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>0.945</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>536.5</v>
+        <v>536.25</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="T26" s="43" t="n">
         <v>0</v>
@@ -6829,49 +6829,49 @@
         </is>
       </c>
       <c r="E27" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.472</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>835.7</v>
+        <v>835.3</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.472</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>835.7</v>
+        <v>835.3</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.472</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>835.7</v>
+        <v>835.3</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="T27" s="39" t="n">
         <v>-0.0788</v>
@@ -6900,49 +6900,49 @@
         </is>
       </c>
       <c r="E28" s="41" t="n">
-        <v>129.437884</v>
+        <v>129.16035</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.31</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>169.56</v>
+        <v>169.2</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.31</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>169.56</v>
+        <v>169.2</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.31</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>169.56</v>
+        <v>169.2</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>154.55</v>
+        <v>154.22</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>154.55</v>
+        <v>154.22</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>154.55</v>
+        <v>154.22</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>174.74</v>
+        <v>174.37</v>
       </c>
       <c r="T28" s="45" t="n">
         <v>0.0534</v>
@@ -6971,49 +6971,49 @@
         </is>
       </c>
       <c r="E29" s="38" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.068</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>18.14</v>
+        <v>18.22</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.068</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>18.14</v>
+        <v>18.22</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.068</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>18.14</v>
+        <v>18.22</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="T29" s="39" t="n">
         <v>-0.0459</v>
@@ -7042,49 +7042,49 @@
         </is>
       </c>
       <c r="E30" s="41" t="n">
-        <v>183.373095</v>
+        <v>182.949169</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>0.869</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>159.35</v>
+        <v>158.98</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>0.869</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>159.35</v>
+        <v>158.98</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>0.869</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>159.35</v>
+        <v>158.98</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>167.05</v>
+        <v>166.67</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>167.05</v>
+        <v>166.67</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>0.911</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>167.05</v>
+        <v>166.67</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>220.05</v>
+        <v>219.54</v>
       </c>
       <c r="T30" s="42" t="n">
         <v>-0.0265</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="E31" s="38" t="n">
-        <v>6.384581</v>
+        <v>6.384576</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>0.024</v>
@@ -7184,49 +7184,49 @@
         </is>
       </c>
       <c r="E32" s="41" t="n">
-        <v>4159.707068</v>
+        <v>4159.198135</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>4966.69</v>
+        <v>4966.08</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>4966.69</v>
+        <v>4966.08</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>4966.69</v>
+        <v>4966.08</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>4330.26</v>
+        <v>4329.73</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>4330.26</v>
+        <v>4329.73</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>4330.26</v>
+        <v>4329.73</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>5407.62</v>
+        <v>5406.96</v>
       </c>
       <c r="T32" s="42" t="n">
         <v>-0.08210000000000001</v>
@@ -7255,49 +7255,49 @@
         </is>
       </c>
       <c r="E33" s="38" t="n">
-        <v>1745.784056</v>
+        <v>1743.592306</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>2.86</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>4992.94</v>
+        <v>4986.67</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>2.86</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>4992.94</v>
+        <v>4986.67</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>2.86</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>4992.94</v>
+        <v>4986.67</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>4640.29</v>
+        <v>4634.47</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>4640.29</v>
+        <v>4634.47</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>2.658</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>4640.29</v>
+        <v>4634.47</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>4189.88</v>
+        <v>4184.62</v>
       </c>
       <c r="T33" s="39" t="n">
         <v>-0.0668</v>
@@ -7326,49 +7326,49 @@
         </is>
       </c>
       <c r="E34" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.391</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>789.71</v>
+        <v>789.33</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.391</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>789.71</v>
+        <v>789.33</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.391</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>789.71</v>
+        <v>789.33</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>683.55</v>
+        <v>683.22</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>683.55</v>
+        <v>683.22</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>683.55</v>
+        <v>683.22</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>738.05</v>
+        <v>737.7</v>
       </c>
       <c r="T34" s="42" t="n">
         <v>-0.07190000000000001</v>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="E35" s="38" t="n">
-        <v>39.959673</v>
+        <v>39.958994</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>0.968</v>
@@ -7439,7 +7439,7 @@
         <v>1.1</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>43.96</v>
+        <v>43.95</v>
       </c>
       <c r="T35" s="40" t="n">
         <v>0</v>
@@ -7468,49 +7468,49 @@
         </is>
       </c>
       <c r="E36" s="41" t="n">
-        <v>46.477439</v>
+        <v>46.456446</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.259</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>58.52</v>
+        <v>58.49</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.259</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>58.52</v>
+        <v>58.49</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.259</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>58.52</v>
+        <v>58.49</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>65.06999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="T36" s="42" t="n">
         <v>-0.0516</v>
@@ -7539,25 +7539,25 @@
         </is>
       </c>
       <c r="E37" s="38" t="n">
-        <v>9.356132000000001</v>
+        <v>9.361336</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.074</v>
@@ -7581,7 +7581,7 @@
         <v>0.6</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="T37" s="44" t="n">
         <v>0.0537</v>
@@ -7610,49 +7610,49 @@
         </is>
       </c>
       <c r="E38" s="41" t="n">
-        <v>63.495071</v>
+        <v>63.592665</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>82.42</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>82.42</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>82.42</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>74.42</v>
+        <v>74.53</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>74.42</v>
+        <v>74.53</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>1.172</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>74.42</v>
+        <v>74.53</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>82.54000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="T38" s="42" t="n">
         <v>-0.0555</v>
@@ -7681,49 +7681,49 @@
         </is>
       </c>
       <c r="E39" s="38" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>1.224</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>20.79</v>
+        <v>20.88</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>1.224</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>20.79</v>
+        <v>20.88</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>1.224</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>20.79</v>
+        <v>20.88</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>18.97</v>
+        <v>19.05</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>18.97</v>
+        <v>19.05</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>18.97</v>
+        <v>19.05</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="T39" s="39" t="n">
         <v>-0.0866</v>
@@ -7752,49 +7752,49 @@
         </is>
       </c>
       <c r="E40" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>625.64</v>
+        <v>625.34</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>625.64</v>
+        <v>625.34</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>625.64</v>
+        <v>625.34</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>568.86</v>
+        <v>568.59</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>568.86</v>
+        <v>568.59</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.002</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>568.86</v>
+        <v>568.59</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>709.66</v>
+        <v>709.3200000000001</v>
       </c>
       <c r="T40" s="43" t="n">
         <v>0</v>
@@ -7823,49 +7823,49 @@
         </is>
       </c>
       <c r="E41" s="38" t="n">
-        <v>1356.394702</v>
+        <v>1356.44293</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.58</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>786.71</v>
+        <v>786.74</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.58</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>786.71</v>
+        <v>786.74</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.58</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>786.71</v>
+        <v>786.74</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>1338.76</v>
+        <v>1338.81</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>1338.76</v>
+        <v>1338.81</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>1338.76</v>
+        <v>1338.81</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>746.02</v>
+        <v>746.04</v>
       </c>
       <c r="T41" s="44" t="n">
         <v>0.3103</v>
@@ -7894,49 +7894,49 @@
         </is>
       </c>
       <c r="E42" s="41" t="n">
-        <v>1457.464304</v>
+        <v>1458.129101</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>1983.61</v>
+        <v>1984.51</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>1983.61</v>
+        <v>1984.51</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>1983.61</v>
+        <v>1984.51</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>1818.92</v>
+        <v>1819.75</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>1818.92</v>
+        <v>1819.75</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>1818.92</v>
+        <v>1819.75</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>2113.32</v>
+        <v>2114.29</v>
       </c>
       <c r="T42" s="42" t="n">
         <v>-0.0595</v>
@@ -7965,49 +7965,49 @@
         </is>
       </c>
       <c r="E43" s="38" t="n">
-        <v>21.204685</v>
+        <v>21.194576</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.322</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.222</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>25.91</v>
+        <v>25.9</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.222</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>25.91</v>
+        <v>25.9</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.222</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>25.91</v>
+        <v>25.9</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0</v>
@@ -8036,49 +8036,49 @@
         </is>
       </c>
       <c r="E44" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.665</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>945.27</v>
+        <v>944.8200000000001</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.665</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>945.27</v>
+        <v>944.8200000000001</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.665</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>945.27</v>
+        <v>944.8200000000001</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.128</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="T44" s="42" t="n">
         <v>-0.08109999999999999</v>
@@ -8107,49 +8107,49 @@
         </is>
       </c>
       <c r="E45" s="38" t="n">
-        <v>14.565155</v>
+        <v>13.880458</v>
       </c>
       <c r="F45" s="18" t="n">
         <v>1.342</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>19.55</v>
+        <v>18.63</v>
       </c>
       <c r="H45" s="18" t="n">
         <v>1.342</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>19.55</v>
+        <v>18.63</v>
       </c>
       <c r="J45" s="18" t="n">
         <v>1.342</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>19.55</v>
+        <v>18.63</v>
       </c>
       <c r="L45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>20.07</v>
+        <v>19.13</v>
       </c>
       <c r="N45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="O45" s="19" t="n">
-        <v>20.07</v>
+        <v>19.13</v>
       </c>
       <c r="P45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="Q45" s="19" t="n">
-        <v>20.07</v>
+        <v>19.13</v>
       </c>
       <c r="R45" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>23.3</v>
+        <v>22.21</v>
       </c>
       <c r="T45" s="44" t="n">
         <v>0.05139999999999999</v>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="E47" s="38" t="n">
-        <v>571.663172</v>
+        <v>571.660967</v>
       </c>
       <c r="F47" s="18" t="n">
         <v>0.68</v>
@@ -8320,49 +8320,49 @@
         </is>
       </c>
       <c r="E48" s="41" t="n">
-        <v>16.984359</v>
+        <v>17.053859</v>
       </c>
       <c r="F48" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="G48" s="28" t="n">
-        <v>20.74</v>
+        <v>20.82</v>
       </c>
       <c r="H48" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>20.74</v>
+        <v>20.82</v>
       </c>
       <c r="J48" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="K48" s="28" t="n">
-        <v>20.74</v>
+        <v>20.82</v>
       </c>
       <c r="L48" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="M48" s="28" t="n">
-        <v>18.31</v>
+        <v>18.38</v>
       </c>
       <c r="N48" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>18.31</v>
+        <v>18.38</v>
       </c>
       <c r="P48" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>18.31</v>
+        <v>18.38</v>
       </c>
       <c r="R48" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S48" s="28" t="n">
-        <v>22.93</v>
+        <v>23.02</v>
       </c>
       <c r="T48" s="43" t="n">
         <v>0.0155</v>
@@ -8391,49 +8391,49 @@
         </is>
       </c>
       <c r="E49" s="38" t="n">
-        <v>4585.068745</v>
+        <v>4581.917868</v>
       </c>
       <c r="F49" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="H49" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="J49" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="L49" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>6946.38</v>
+        <v>6941.61</v>
       </c>
       <c r="N49" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="O49" s="19" t="n">
-        <v>6946.38</v>
+        <v>6941.61</v>
       </c>
       <c r="P49" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="Q49" s="19" t="n">
-        <v>6946.38</v>
+        <v>6941.61</v>
       </c>
       <c r="R49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>8253.120000000001</v>
+        <v>8247.450000000001</v>
       </c>
       <c r="T49" s="40" t="n">
         <v>0</v>
@@ -8462,49 +8462,49 @@
         </is>
       </c>
       <c r="E50" s="41" t="n">
-        <v>544.108486</v>
+        <v>544.717652</v>
       </c>
       <c r="F50" s="27" t="n">
         <v>0.594</v>
       </c>
       <c r="G50" s="28" t="n">
-        <v>323.2</v>
+        <v>323.56</v>
       </c>
       <c r="H50" s="27" t="n">
         <v>0.594</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>323.2</v>
+        <v>323.56</v>
       </c>
       <c r="J50" s="27" t="n">
         <v>0.594</v>
       </c>
       <c r="K50" s="28" t="n">
-        <v>323.2</v>
+        <v>323.56</v>
       </c>
       <c r="L50" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="M50" s="28" t="n">
-        <v>330.27</v>
+        <v>330.64</v>
       </c>
       <c r="N50" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>330.27</v>
+        <v>330.64</v>
       </c>
       <c r="P50" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>330.27</v>
+        <v>330.64</v>
       </c>
       <c r="R50" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S50" s="28" t="n">
-        <v>299.26</v>
+        <v>299.59</v>
       </c>
       <c r="T50" s="45" t="n">
         <v>0.7676999999999999</v>
@@ -8533,49 +8533,49 @@
         </is>
       </c>
       <c r="E51" s="38" t="n">
-        <v>2585.283864</v>
+        <v>2590.03315</v>
       </c>
       <c r="F51" s="18" t="n">
         <v>1.09</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>2817.96</v>
+        <v>2823.14</v>
       </c>
       <c r="H51" s="18" t="n">
         <v>1.09</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>2817.96</v>
+        <v>2823.14</v>
       </c>
       <c r="J51" s="18" t="n">
         <v>1.09</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>2817.96</v>
+        <v>2823.14</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>2665.43</v>
+        <v>2670.32</v>
       </c>
       <c r="N51" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="O51" s="19" t="n">
-        <v>2665.43</v>
+        <v>2670.32</v>
       </c>
       <c r="P51" s="18" t="n">
         <v>1.031</v>
       </c>
       <c r="Q51" s="19" t="n">
-        <v>2665.43</v>
+        <v>2670.32</v>
       </c>
       <c r="R51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>3231.6</v>
+        <v>3237.54</v>
       </c>
       <c r="T51" s="40" t="n">
         <v>0.0092</v>
@@ -8604,49 +8604,49 @@
         </is>
       </c>
       <c r="E52" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F52" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="G52" s="28" t="n">
-        <v>693.2</v>
+        <v>692.87</v>
       </c>
       <c r="H52" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>693.2</v>
+        <v>692.87</v>
       </c>
       <c r="J52" s="27" t="n">
         <v>1.221</v>
       </c>
       <c r="K52" s="28" t="n">
-        <v>693.2</v>
+        <v>692.87</v>
       </c>
       <c r="L52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M52" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="N52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="P52" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="R52" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S52" s="28" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="T52" s="42" t="n">
         <v>-0.0762</v>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="E53" s="38" t="n">
-        <v>2.921765</v>
+        <v>2.918309</v>
       </c>
       <c r="F53" s="18" t="n">
         <v>0.863</v>
@@ -8746,49 +8746,49 @@
         </is>
       </c>
       <c r="E54" s="41" t="n">
-        <v>3777.748478</v>
+        <v>3776.042542</v>
       </c>
       <c r="F54" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G54" s="28" t="n">
-        <v>5217.07</v>
+        <v>5214.71</v>
       </c>
       <c r="H54" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I54" s="28" t="n">
-        <v>5217.07</v>
+        <v>5214.71</v>
       </c>
       <c r="J54" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K54" s="28" t="n">
-        <v>5217.07</v>
+        <v>5214.71</v>
       </c>
       <c r="L54" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M54" s="28" t="n">
-        <v>4344.41</v>
+        <v>4342.45</v>
       </c>
       <c r="N54" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>4344.41</v>
+        <v>4342.45</v>
       </c>
       <c r="P54" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q54" s="28" t="n">
-        <v>4344.41</v>
+        <v>4342.45</v>
       </c>
       <c r="R54" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S54" s="28" t="n">
-        <v>4911.07</v>
+        <v>4908.86</v>
       </c>
       <c r="T54" s="43" t="n">
         <v>0</v>
@@ -8817,43 +8817,43 @@
         </is>
       </c>
       <c r="E55" s="38" t="n">
-        <v>19.540845</v>
+        <v>19.536613</v>
       </c>
       <c r="F55" s="18" t="n">
         <v>1.48</v>
       </c>
       <c r="G55" s="19" t="n">
-        <v>28.92</v>
+        <v>28.91</v>
       </c>
       <c r="H55" s="18" t="n">
         <v>1.48</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>28.92</v>
+        <v>28.91</v>
       </c>
       <c r="J55" s="18" t="n">
         <v>1.48</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>28.92</v>
+        <v>28.91</v>
       </c>
       <c r="L55" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="N55" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="O55" s="19" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="P55" s="18" t="n">
         <v>1.117</v>
       </c>
       <c r="Q55" s="19" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="R55" s="18" t="n">
         <v>1.3</v>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.146687</v>
+        <v>132.030471</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.362</v>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>918.565802</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>300.37</v>
+        <v>300.9</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.327</v>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>707.96</v>
+        <v>707.62</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.247</v>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>14.044867</v>
+        <v>13.685731</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>16.46</v>
+        <v>16.04</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.172</v>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>866.35</v>
+        <v>865.9400000000001</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.526</v>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2975.310621</v>
+        <v>2973.478145</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>4010.72</v>
+        <v>4008.25</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.348</v>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>1050.3</v>
+        <v>1049.8</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.85</v>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.434067</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>127.79</v>
+        <v>127.73</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.339</v>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>856.14</v>
+        <v>855.73</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.508</v>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>1.418</v>
@@ -9693,10 +9693,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>425.796789</v>
+        <v>425.593787</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>503.29</v>
+        <v>503.05</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.182</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>2263.863308</v>
+        <v>2271.865535</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>2503.83</v>
+        <v>2512.68</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.106</v>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.898</v>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>52.240036</v>
+        <v>52.260748</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>21.42</v>
+        <v>21.43</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>0.41</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>526.85</v>
+        <v>526.6</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>0.928</v>
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>20.64</v>
+        <v>20.72</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.215</v>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>156.089895</v>
+        <v>155.991755</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>123.31</v>
+        <v>123.23</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.79</v>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>508.69</v>
+        <v>508.44</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.896</v>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>74.187712</v>
+        <v>74.18732300000001</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>86.20999999999999</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>10.952854</v>
+        <v>10.942196</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>14</v>
+        <v>13.98</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>1.278</v>
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>8763.579604</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>11988.58</v>
+        <v>11986.92</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.368</v>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>587.6</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.035</v>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>835.7</v>
+        <v>835.3</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.472</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>129.437884</v>
+        <v>129.16035</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>169.56</v>
+        <v>169.2</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.31</v>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>18.14</v>
+        <v>18.22</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.068</v>
@@ -10696,10 +10696,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>183.373095</v>
+        <v>182.949169</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>159.35</v>
+        <v>158.98</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.869</v>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>6.384581</v>
+        <v>6.384576</v>
       </c>
       <c r="F31" s="19" t="n">
         <v>0.15</v>
@@ -10814,10 +10814,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>4159.707068</v>
+        <v>4159.198135</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>4966.69</v>
+        <v>4966.08</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.194</v>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1745.784056</v>
+        <v>1743.592306</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>4992.94</v>
+        <v>4986.67</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.86</v>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>789.71</v>
+        <v>789.33</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.391</v>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>39.959673</v>
+        <v>39.958994</v>
       </c>
       <c r="F35" s="19" t="n">
         <v>38.68</v>
@@ -11050,10 +11050,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>46.477439</v>
+        <v>46.456446</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>58.52</v>
+        <v>58.49</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.259</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>9.356132000000001</v>
+        <v>9.361336</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.322</v>
@@ -11168,10 +11168,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>63.495071</v>
+        <v>63.592665</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>82.42</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.298</v>
@@ -11227,10 +11227,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>20.79</v>
+        <v>20.88</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.224</v>
@@ -11286,10 +11286,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>625.64</v>
+        <v>625.34</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.102</v>
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>1356.394702</v>
+        <v>1356.44293</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>786.71</v>
+        <v>786.74</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.58</v>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>1457.464304</v>
+        <v>1458.129101</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>1983.61</v>
+        <v>1984.51</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.361</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>21.204685</v>
+        <v>21.194576</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.322</v>
@@ -11522,10 +11522,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>945.27</v>
+        <v>944.8200000000001</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.665</v>
@@ -11581,10 +11581,10 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>14.565155</v>
+        <v>13.880458</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>19.55</v>
+        <v>18.63</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.342</v>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>571.663172</v>
+        <v>571.660967</v>
       </c>
       <c r="F47" s="19" t="n">
         <v>388.73</v>
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="E48" s="26" t="n">
-        <v>16.984359</v>
+        <v>17.053859</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>20.74</v>
+        <v>20.82</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.221</v>
@@ -11817,10 +11817,10 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>4585.068745</v>
+        <v>4581.917868</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>1.638</v>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="E50" s="26" t="n">
-        <v>544.108486</v>
+        <v>544.717652</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>323.2</v>
+        <v>323.56</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>0.594</v>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>2585.283864</v>
+        <v>2590.03315</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2817.96</v>
+        <v>2823.14</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.09</v>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="E52" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>693.2</v>
+        <v>692.87</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.221</v>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>2.921765</v>
+        <v>2.918309</v>
       </c>
       <c r="F53" s="19" t="n">
         <v>2.52</v>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="E54" s="26" t="n">
-        <v>3777.748478</v>
+        <v>3776.042542</v>
       </c>
       <c r="F54" s="28" t="n">
-        <v>5217.07</v>
+        <v>5214.71</v>
       </c>
       <c r="G54" s="27" t="n">
         <v>1.381</v>
@@ -12171,10 +12171,10 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>19.540845</v>
+        <v>19.536613</v>
       </c>
       <c r="F55" s="19" t="n">
-        <v>28.92</v>
+        <v>28.91</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>1.48</v>
@@ -12572,25 +12572,25 @@
         </is>
       </c>
       <c r="D5" s="38" t="n">
-        <v>132.146687</v>
+        <v>132.030471</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.336</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.4</v>
+        <v>44.36</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.68</v>
+        <v>28.65</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>40.97</v>
+        <v>40.93</v>
       </c>
       <c r="K5" s="39" t="n">
         <v>-0.0718</v>
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="D6" s="41" t="n">
-        <v>52.240036</v>
+        <v>52.260748</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.4</v>
@@ -12623,7 +12623,7 @@
         <v>0.394</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>20.58</v>
+        <v>20.59</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="D7" s="38" t="n">
-        <v>6.384581</v>
+        <v>6.384576</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.024</v>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="D8" s="41" t="n">
-        <v>39.959673</v>
+        <v>39.958994</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>0.968</v>
@@ -12707,7 +12707,7 @@
         <v>1.1</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>43.96</v>
+        <v>43.95</v>
       </c>
       <c r="K8" s="43" t="n">
         <v>0</v>
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="D9" s="38" t="n">
-        <v>9.356132000000001</v>
+        <v>9.361336</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>1.393</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>13.03</v>
+        <v>13.04</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.246</v>
@@ -12746,7 +12746,7 @@
         <v>0.6</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="K9" s="44" t="n">
         <v>0.0537</v>
@@ -12767,25 +12767,25 @@
         </is>
       </c>
       <c r="D10" s="41" t="n">
-        <v>544.108486</v>
+        <v>544.717652</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>571.3099999999999</v>
+        <v>571.95</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.607</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>330.27</v>
+        <v>330.64</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>299.26</v>
+        <v>299.59</v>
       </c>
       <c r="K10" s="45" t="n">
         <v>0.7676999999999999</v>
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="D11" s="38" t="n">
-        <v>2.921765</v>
+        <v>2.918309</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>0.8139999999999999</v>
@@ -12916,25 +12916,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E17" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>677.87</v>
+        <v>677.55</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>681.27</v>
+        <v>680.95</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>-0.07780000000000001</v>
@@ -12955,25 +12955,25 @@
         </is>
       </c>
       <c r="D18" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E18" s="27" t="n">
         <v>1.411</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>801.0700000000001</v>
+        <v>800.6799999999999</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.117</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>783.47</v>
+        <v>783.09</v>
       </c>
       <c r="K18" s="42" t="n">
         <v>-0.07539999999999999</v>
@@ -12994,25 +12994,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>95.434067</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>1.269</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>121.11</v>
+        <v>121.05</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.074</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>102.5</v>
+        <v>102.45</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>116.43</v>
+        <v>116.37</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>-0.05230000000000001</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="D20" s="41" t="n">
-        <v>74.187712</v>
+        <v>74.18732300000001</v>
       </c>
       <c r="E20" s="27" t="n">
         <v>1.162</v>
@@ -13072,25 +13072,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>10.952854</v>
+        <v>10.942196</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>1.27</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>12.6</v>
+        <v>12.58</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>-0.0063</v>
@@ -13111,25 +13111,25 @@
         </is>
       </c>
       <c r="D22" s="41" t="n">
-        <v>8763.579604</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="E22" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>11217.38</v>
+        <v>11215.83</v>
       </c>
       <c r="K22" s="42" t="n">
         <v>-0.0643</v>
@@ -13150,25 +13150,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>1.035</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>587.6</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.945</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>536.5</v>
+        <v>536.25</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="K23" s="40" t="n">
         <v>0</v>
@@ -13189,25 +13189,25 @@
         </is>
       </c>
       <c r="D24" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E24" s="27" t="n">
         <v>1.356</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>769.84</v>
+        <v>769.47</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>1.117</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>634.15</v>
+        <v>633.85</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="K24" s="42" t="n">
         <v>-0.0788</v>
@@ -13228,25 +13228,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>183.373095</v>
+        <v>182.949169</v>
       </c>
       <c r="E25" s="18" t="n">
         <v>0.846</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>155.13</v>
+        <v>154.77</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>0.911</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>167.05</v>
+        <v>166.67</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>220.05</v>
+        <v>219.54</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>-0.0265</v>
@@ -13267,25 +13267,25 @@
         </is>
       </c>
       <c r="D26" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E26" s="27" t="n">
         <v>1.291</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>732.9400000000001</v>
+        <v>732.59</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.204</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>683.55</v>
+        <v>683.22</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>738.05</v>
+        <v>737.7</v>
       </c>
       <c r="K26" s="42" t="n">
         <v>-0.07190000000000001</v>
@@ -13306,25 +13306,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E27" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>625.64</v>
+        <v>625.34</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>568.86</v>
+        <v>568.59</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>709.66</v>
+        <v>709.3200000000001</v>
       </c>
       <c r="K27" s="40" t="n">
         <v>0</v>
@@ -13345,25 +13345,25 @@
         </is>
       </c>
       <c r="D28" s="41" t="n">
-        <v>1356.394702</v>
+        <v>1356.44293</v>
       </c>
       <c r="E28" s="27" t="n">
         <v>0.76</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>1030.86</v>
+        <v>1030.9</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.03</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>1397.09</v>
+        <v>1397.14</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>746.02</v>
+        <v>746.04</v>
       </c>
       <c r="K28" s="45" t="n">
         <v>0.3103</v>
@@ -13384,25 +13384,25 @@
         </is>
       </c>
       <c r="D29" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E29" s="18" t="n">
         <v>1.53</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>868.63</v>
+        <v>868.21</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.128</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="K29" s="39" t="n">
         <v>-0.08109999999999999</v>
@@ -13462,25 +13462,25 @@
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E31" s="18" t="n">
         <v>1.128</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>640.4</v>
+        <v>640.09</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="K31" s="39" t="n">
         <v>-0.0762</v>
@@ -13572,25 +13572,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>2975.310621</v>
+        <v>2973.478145</v>
       </c>
       <c r="E37" s="18" t="n">
         <v>1.334</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>3969.06</v>
+        <v>3966.62</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.302</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>3873.85</v>
+        <v>3871.47</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>4314.2</v>
+        <v>4311.54</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>-0.0104</v>
@@ -13611,25 +13611,25 @@
         </is>
       </c>
       <c r="D38" s="41" t="n">
-        <v>425.796789</v>
+        <v>425.593787</v>
       </c>
       <c r="E38" s="27" t="n">
         <v>1.182</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>503.29</v>
+        <v>503.05</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.078</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>459.01</v>
+        <v>458.79</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>574.83</v>
+        <v>574.55</v>
       </c>
       <c r="K38" s="43" t="n">
         <v>0</v>
@@ -13728,25 +13728,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>156.089895</v>
+        <v>155.991755</v>
       </c>
       <c r="E41" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>123.62</v>
+        <v>123.55</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.835</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>130.34</v>
+        <v>130.25</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>163.89</v>
+        <v>163.79</v>
       </c>
       <c r="K41" s="40" t="n">
         <v>0.0025</v>
@@ -13767,25 +13767,25 @@
         </is>
       </c>
       <c r="D42" s="41" t="n">
-        <v>129.437884</v>
+        <v>129.16035</v>
       </c>
       <c r="E42" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>178.62</v>
+        <v>178.24</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.194</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>154.55</v>
+        <v>154.22</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>174.74</v>
+        <v>174.37</v>
       </c>
       <c r="K42" s="45" t="n">
         <v>0.0534</v>
@@ -13806,25 +13806,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>46.477439</v>
+        <v>46.456446</v>
       </c>
       <c r="E43" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.194</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>55.49</v>
+        <v>55.47</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>65.06999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="K43" s="39" t="n">
         <v>-0.0516</v>
@@ -13845,25 +13845,25 @@
         </is>
       </c>
       <c r="D44" s="41" t="n">
-        <v>1457.464304</v>
+        <v>1458.129101</v>
       </c>
       <c r="E44" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>1865.55</v>
+        <v>1866.41</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.248</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>1818.92</v>
+        <v>1819.75</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>2113.32</v>
+        <v>2114.29</v>
       </c>
       <c r="K44" s="42" t="n">
         <v>-0.0595</v>
@@ -13884,25 +13884,25 @@
         </is>
       </c>
       <c r="D45" s="38" t="n">
-        <v>14.565155</v>
+        <v>13.880458</v>
       </c>
       <c r="E45" s="18" t="n">
         <v>1.411</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>20.55</v>
+        <v>19.59</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.07</v>
+        <v>19.13</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.3</v>
+        <v>22.21</v>
       </c>
       <c r="K45" s="44" t="n">
         <v>0.05139999999999999</v>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="D46" s="41" t="n">
-        <v>571.663172</v>
+        <v>571.660967</v>
       </c>
       <c r="E46" s="27" t="n">
         <v>1.15</v>
@@ -13962,25 +13962,25 @@
         </is>
       </c>
       <c r="D47" s="38" t="n">
-        <v>4585.068745</v>
+        <v>4581.917868</v>
       </c>
       <c r="E47" s="18" t="n">
         <v>1.638</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.515</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>6946.38</v>
+        <v>6941.61</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>8253.120000000001</v>
+        <v>8247.450000000001</v>
       </c>
       <c r="K47" s="40" t="n">
         <v>0</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="D48" s="41" t="n">
-        <v>2585.283864</v>
+        <v>2590.03315</v>
       </c>
       <c r="E48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="F48" s="28" t="n">
-        <v>2843.81</v>
+        <v>2849.04</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.031</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>2665.43</v>
+        <v>2670.32</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>3231.6</v>
+        <v>3237.54</v>
       </c>
       <c r="K48" s="43" t="n">
         <v>0.0092</v>
@@ -14040,25 +14040,25 @@
         </is>
       </c>
       <c r="D49" s="38" t="n">
-        <v>3777.748478</v>
+        <v>3776.042542</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.381</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>5217.07</v>
+        <v>5214.71</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>4344.41</v>
+        <v>4342.45</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>4911.07</v>
+        <v>4908.86</v>
       </c>
       <c r="K49" s="40" t="n">
         <v>0</v>
@@ -14150,25 +14150,25 @@
         </is>
       </c>
       <c r="D55" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E55" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F55" s="19" t="n">
-        <v>985.58</v>
+        <v>985.11</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>2.072</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>1176.33</v>
+        <v>1175.77</v>
       </c>
       <c r="I55" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J55" s="19" t="n">
-        <v>1021.91</v>
+        <v>1021.43</v>
       </c>
       <c r="K55" s="39" t="n">
         <v>-0.0616</v>
@@ -14189,25 +14189,25 @@
         </is>
       </c>
       <c r="D56" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E56" s="27" t="n">
         <v>1.389</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>788.58</v>
+        <v>788.2</v>
       </c>
       <c r="G56" s="27" t="n">
         <v>1.367</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>776.09</v>
+        <v>775.72</v>
       </c>
       <c r="I56" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J56" s="28" t="n">
-        <v>681.27</v>
+        <v>680.95</v>
       </c>
       <c r="K56" s="42" t="n">
         <v>-0.0789</v>
@@ -14228,25 +14228,25 @@
         </is>
       </c>
       <c r="D57" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E57" s="18" t="n">
         <v>1.418</v>
       </c>
       <c r="F57" s="19" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>1.318</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>748.27</v>
+        <v>747.91</v>
       </c>
       <c r="I57" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J57" s="19" t="n">
-        <v>879.98</v>
+        <v>879.5599999999999</v>
       </c>
       <c r="K57" s="40" t="n">
         <v>0</v>
@@ -14267,25 +14267,25 @@
         </is>
       </c>
       <c r="D58" s="41" t="n">
-        <v>2263.863308</v>
+        <v>2271.865535</v>
       </c>
       <c r="E58" s="27" t="n">
         <v>1.052</v>
       </c>
       <c r="F58" s="28" t="n">
-        <v>2381.58</v>
+        <v>2390</v>
       </c>
       <c r="G58" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>2356.68</v>
+        <v>2365.01</v>
       </c>
       <c r="I58" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J58" s="28" t="n">
-        <v>2829.83</v>
+        <v>2839.83</v>
       </c>
       <c r="K58" s="42" t="n">
         <v>-0.0488</v>
@@ -14306,25 +14306,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E59" s="18" t="n">
         <v>0.898</v>
       </c>
       <c r="F59" s="19" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>0.828</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>470.08</v>
+        <v>469.86</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>624.5</v>
+        <v>624.2</v>
       </c>
       <c r="K59" s="40" t="n">
         <v>0</v>
@@ -14345,25 +14345,25 @@
         </is>
       </c>
       <c r="D60" s="41" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E60" s="27" t="n">
         <v>0.928</v>
       </c>
       <c r="F60" s="28" t="n">
-        <v>526.85</v>
+        <v>526.6</v>
       </c>
       <c r="G60" s="27" t="n">
         <v>0.858</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>487.11</v>
+        <v>486.88</v>
       </c>
       <c r="I60" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J60" s="28" t="n">
-        <v>652.89</v>
+        <v>652.58</v>
       </c>
       <c r="K60" s="43" t="n">
         <v>0</v>
@@ -14384,25 +14384,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E61" s="18" t="n">
         <v>0.987</v>
       </c>
       <c r="F61" s="19" t="n">
-        <v>560.35</v>
+        <v>560.08</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>0.955</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>542.1799999999999</v>
+        <v>541.92</v>
       </c>
       <c r="I61" s="18" t="n">
         <v>0.9</v>
       </c>
       <c r="J61" s="19" t="n">
-        <v>510.96</v>
+        <v>510.71</v>
       </c>
       <c r="K61" s="44" t="n">
         <v>0.1016</v>
@@ -14423,25 +14423,25 @@
         </is>
       </c>
       <c r="D62" s="41" t="n">
-        <v>21.204685</v>
+        <v>21.194576</v>
       </c>
       <c r="E62" s="27" t="n">
         <v>1.322</v>
       </c>
       <c r="F62" s="28" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="G62" s="27" t="n">
         <v>1.222</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>25.91</v>
+        <v>25.9</v>
       </c>
       <c r="I62" s="27" t="n">
         <v>1.5</v>
       </c>
       <c r="J62" s="28" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="K62" s="43" t="n">
         <v>0</v>
@@ -14533,25 +14533,25 @@
         </is>
       </c>
       <c r="D68" s="38" t="n">
-        <v>918.565802</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="E68" s="18" t="n">
         <v>0.304</v>
       </c>
       <c r="F68" s="19" t="n">
-        <v>279.24</v>
+        <v>279.73</v>
       </c>
       <c r="G68" s="18" t="n">
         <v>0.412</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>378.45</v>
+        <v>379.11</v>
       </c>
       <c r="I68" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J68" s="19" t="n">
-        <v>597.0700000000001</v>
+        <v>598.11</v>
       </c>
       <c r="K68" s="39" t="n">
         <v>-0.0703</v>
@@ -14572,25 +14572,25 @@
         </is>
       </c>
       <c r="D69" s="41" t="n">
-        <v>14.044867</v>
+        <v>13.685731</v>
       </c>
       <c r="E69" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F69" s="28" t="n">
-        <v>15.24</v>
+        <v>14.85</v>
       </c>
       <c r="G69" s="27" t="n">
         <v>1.139</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>16</v>
+        <v>15.59</v>
       </c>
       <c r="I69" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J69" s="28" t="n">
-        <v>17.56</v>
+        <v>17.11</v>
       </c>
       <c r="K69" s="42" t="n">
         <v>-0.0742</v>
@@ -14611,25 +14611,25 @@
         </is>
       </c>
       <c r="D70" s="38" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="E70" s="18" t="n">
         <v>1.107</v>
       </c>
       <c r="F70" s="19" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="G70" s="18" t="n">
         <v>1.128</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>19.16</v>
+        <v>19.24</v>
       </c>
       <c r="I70" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J70" s="19" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="K70" s="39" t="n">
         <v>-0.08890000000000001</v>
@@ -14650,25 +14650,25 @@
         </is>
       </c>
       <c r="D71" s="41" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="E71" s="27" t="n">
         <v>1.019</v>
       </c>
       <c r="F71" s="28" t="n">
-        <v>17.31</v>
+        <v>17.38</v>
       </c>
       <c r="G71" s="27" t="n">
         <v>1.107</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>18.8</v>
+        <v>18.88</v>
       </c>
       <c r="I71" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J71" s="28" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="K71" s="42" t="n">
         <v>-0.0459</v>
@@ -14689,25 +14689,25 @@
         </is>
       </c>
       <c r="D72" s="38" t="n">
-        <v>4159.707068</v>
+        <v>4159.198135</v>
       </c>
       <c r="E72" s="18" t="n">
         <v>1.096</v>
       </c>
       <c r="F72" s="19" t="n">
-        <v>4559.04</v>
+        <v>4558.48</v>
       </c>
       <c r="G72" s="18" t="n">
         <v>1.041</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>4330.26</v>
+        <v>4329.73</v>
       </c>
       <c r="I72" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J72" s="19" t="n">
-        <v>5407.62</v>
+        <v>5406.96</v>
       </c>
       <c r="K72" s="39" t="n">
         <v>-0.08210000000000001</v>
@@ -14728,25 +14728,25 @@
         </is>
       </c>
       <c r="D73" s="41" t="n">
-        <v>1745.784056</v>
+        <v>1743.592306</v>
       </c>
       <c r="E73" s="27" t="n">
         <v>2.669</v>
       </c>
       <c r="F73" s="28" t="n">
-        <v>4659.5</v>
+        <v>4653.65</v>
       </c>
       <c r="G73" s="27" t="n">
         <v>2.658</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>4640.29</v>
+        <v>4634.47</v>
       </c>
       <c r="I73" s="27" t="n">
         <v>2.4</v>
       </c>
       <c r="J73" s="28" t="n">
-        <v>4189.88</v>
+        <v>4184.62</v>
       </c>
       <c r="K73" s="42" t="n">
         <v>-0.0668</v>
@@ -14767,25 +14767,25 @@
         </is>
       </c>
       <c r="D74" s="38" t="n">
-        <v>63.495071</v>
+        <v>63.592665</v>
       </c>
       <c r="E74" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F74" s="19" t="n">
-        <v>77.84</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="G74" s="18" t="n">
         <v>1.172</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>74.42</v>
+        <v>74.53</v>
       </c>
       <c r="I74" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J74" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="K74" s="39" t="n">
         <v>-0.0555</v>
@@ -14806,25 +14806,25 @@
         </is>
       </c>
       <c r="D75" s="41" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="E75" s="27" t="n">
         <v>1.118</v>
       </c>
       <c r="F75" s="28" t="n">
-        <v>18.99</v>
+        <v>19.07</v>
       </c>
       <c r="G75" s="27" t="n">
         <v>1.117</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>18.97</v>
+        <v>19.05</v>
       </c>
       <c r="I75" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J75" s="28" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="K75" s="42" t="n">
         <v>-0.0866</v>
@@ -14845,25 +14845,25 @@
         </is>
       </c>
       <c r="D76" s="38" t="n">
-        <v>16.984359</v>
+        <v>17.053859</v>
       </c>
       <c r="E76" s="18" t="n">
         <v>1.2399</v>
       </c>
       <c r="F76" s="19" t="n">
-        <v>21.06</v>
+        <v>21.15</v>
       </c>
       <c r="G76" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H76" s="19" t="n">
-        <v>20.82</v>
+        <v>20.91</v>
       </c>
       <c r="I76" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J76" s="19" t="n">
-        <v>22.93</v>
+        <v>23.02</v>
       </c>
       <c r="K76" s="40" t="n">
         <v>0.0155</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="D77" s="41" t="n">
-        <v>19.540845</v>
+        <v>19.536613</v>
       </c>
       <c r="E77" s="27" t="n">
         <v>1.28</v>
@@ -14896,7 +14896,7 @@
         <v>1.117</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="I77" s="27" t="n">
         <v>1.3</v>
@@ -15193,7 +15193,7 @@
         <v>2.669</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4659.5</v>
+        <v>4653.65</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>1.736</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>985.58</v>
+        <v>985.11</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>0.304</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.24</v>
+        <v>279.73</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>1.638</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>7510.34</v>
+        <v>7505.18</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>0.336</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.4</v>
+        <v>44.36</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>1.53</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>868.63</v>
+        <v>868.21</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>0.76</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>1030.86</v>
+        <v>1030.9</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>1.418</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>805.04</v>
+        <v>804.66</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.62</v>
+        <v>123.55</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>1.411</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>801.0700000000001</v>
+        <v>800.6799999999999</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>1.411</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.55</v>
+        <v>19.59</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>0.846</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>155.13</v>
+        <v>154.77</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>1.393</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>13.03</v>
+        <v>13.04</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>0.898</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>509.82</v>
+        <v>509.58</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -16373,10 +16373,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>918.565802</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="E3" s="67" t="n">
-        <v>0.00108865</v>
+        <v>0.00108675</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -16396,10 +16396,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2975.310621</v>
+        <v>2973.478145</v>
       </c>
       <c r="E4" s="69" t="n">
-        <v>0.0003361</v>
+        <v>0.00033631</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -16419,10 +16419,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>14.044867</v>
+        <v>13.685731</v>
       </c>
       <c r="E5" s="67" t="n">
-        <v>0.07120039</v>
+        <v>0.0730688</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2263.863308</v>
+        <v>2271.865535</v>
       </c>
       <c r="E6" s="69" t="n">
-        <v>0.00044172</v>
+        <v>0.00044017</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -16465,10 +16465,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.434067</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>0.01047844</v>
+        <v>0.01048344</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -16511,10 +16511,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.146687</v>
+        <v>132.030471</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>0.00756735</v>
+        <v>0.00757401</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -16534,10 +16534,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.240036</v>
+        <v>52.260748</v>
       </c>
       <c r="E10" s="69" t="n">
-        <v>0.01914241</v>
+        <v>0.01913482</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -16580,10 +16580,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>156.089895</v>
+        <v>155.991755</v>
       </c>
       <c r="E12" s="69" t="n">
-        <v>0.00640656</v>
+        <v>0.0064106</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -16603,10 +16603,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.952854</v>
+        <v>10.942196</v>
       </c>
       <c r="E13" s="67" t="n">
-        <v>0.0913004</v>
+        <v>0.09138933</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -16626,10 +16626,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.187712</v>
+        <v>74.18732300000001</v>
       </c>
       <c r="E14" s="69" t="n">
-        <v>0.01347932</v>
+        <v>0.01347939</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -16649,10 +16649,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8763.579604</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="E15" s="67" t="n">
-        <v>0.00011411</v>
+        <v>0.00011412</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -16672,10 +16672,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.437884</v>
+        <v>129.16035</v>
       </c>
       <c r="E16" s="69" t="n">
-        <v>0.00772571</v>
+        <v>0.00774231</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>425.796789</v>
+        <v>425.593787</v>
       </c>
       <c r="E17" s="67" t="n">
-        <v>0.00234854</v>
+        <v>0.00234966</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>183.373095</v>
+        <v>182.949169</v>
       </c>
       <c r="E18" s="69" t="n">
-        <v>0.00545336</v>
+        <v>0.005466</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -16741,10 +16741,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>0.05887814</v>
+        <v>0.05863006</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -16764,10 +16764,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.384581</v>
+        <v>6.384576</v>
       </c>
       <c r="E20" s="69" t="n">
-        <v>0.15662735</v>
+        <v>0.15662747</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -16787,10 +16787,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.356132000000001</v>
+        <v>9.361336</v>
       </c>
       <c r="E21" s="67" t="n">
-        <v>0.10688178</v>
+        <v>0.10682236</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -16810,10 +16810,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4159.707068</v>
+        <v>4159.198135</v>
       </c>
       <c r="E22" s="69" t="n">
-        <v>0.0002404</v>
+        <v>0.00024043</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -16833,10 +16833,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.959673</v>
+        <v>39.958994</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>0.02502523</v>
+        <v>0.02502566</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -16856,10 +16856,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.477439</v>
+        <v>46.456446</v>
       </c>
       <c r="E24" s="69" t="n">
-        <v>0.02151582</v>
+        <v>0.02152554</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -16879,10 +16879,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1745.784056</v>
+        <v>1743.592306</v>
       </c>
       <c r="E25" s="67" t="n">
-        <v>0.00057281</v>
+        <v>0.00057353</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.495071</v>
+        <v>63.592665</v>
       </c>
       <c r="E26" s="69" t="n">
-        <v>0.01574925</v>
+        <v>0.01572508</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="E27" s="67" t="n">
-        <v>0.05887814</v>
+        <v>0.05863006</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1356.394702</v>
+        <v>1356.44293</v>
       </c>
       <c r="E28" s="69" t="n">
-        <v>0.0007372499999999999</v>
+        <v>0.00073722</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -16971,10 +16971,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1457.464304</v>
+        <v>1458.129101</v>
       </c>
       <c r="E29" s="67" t="n">
-        <v>0.00068612</v>
+        <v>0.00068581</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -16994,10 +16994,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.565155</v>
+        <v>13.880458</v>
       </c>
       <c r="E30" s="69" t="n">
-        <v>0.06865701</v>
+        <v>0.07204373</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -17017,10 +17017,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>544.108486</v>
+        <v>544.717652</v>
       </c>
       <c r="E31" s="67" t="n">
-        <v>0.00183787</v>
+        <v>0.00183581</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -17063,10 +17063,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.663172</v>
+        <v>571.660967</v>
       </c>
       <c r="E33" s="67" t="n">
-        <v>0.00174928</v>
+        <v>0.00174929</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -17086,10 +17086,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4585.068745</v>
+        <v>4581.917868</v>
       </c>
       <c r="E34" s="69" t="n">
-        <v>0.0002181</v>
+        <v>0.00021825</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -17109,10 +17109,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.204685</v>
+        <v>21.194576</v>
       </c>
       <c r="E35" s="67" t="n">
-        <v>0.04715939</v>
+        <v>0.04718188</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -17132,10 +17132,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.984232</v>
+        <v>17.056096</v>
       </c>
       <c r="E36" s="69" t="n">
-        <v>0.05887814</v>
+        <v>0.05863006</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.921765</v>
+        <v>2.918309</v>
       </c>
       <c r="E37" s="67" t="n">
-        <v>0.34225887</v>
+        <v>0.34266419</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2585.283864</v>
+        <v>2590.03315</v>
       </c>
       <c r="E38" s="69" t="n">
-        <v>0.0003868</v>
+        <v>0.0003861</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -17201,10 +17201,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3777.748478</v>
+        <v>3776.042542</v>
       </c>
       <c r="E39" s="67" t="n">
-        <v>0.00026471</v>
+        <v>0.00026483</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -17224,10 +17224,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E40" s="69" t="n">
-        <v>0.0017614</v>
+        <v>0.00176224</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -17247,10 +17247,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>567.729053</v>
+        <v>567.458383</v>
       </c>
       <c r="E41" s="67" t="n">
-        <v>0.0017614</v>
+        <v>0.00176224</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.984359</v>
+        <v>17.053859</v>
       </c>
       <c r="E42" s="69" t="n">
-        <v>0.0588777</v>
+        <v>0.05863775</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.540845</v>
+        <v>19.536613</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>0.05117486</v>
+        <v>0.05118595</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="C4" s="74" t="inlineStr">
         <is>
-          <t>22 March 2026 — 06:41 UTC</t>
+          <t>23 March 2026 — 07:01 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 23 March 2026  |  10:45 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 23 March 2026  |  11:26 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>134.5</v>
+        <v>132.030471</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>45.23</v>
+        <v>44.4</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>29.19</v>
+        <v>28.65</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.7</v>
+        <v>40.93</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>910</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>276.46</v>
+        <v>279.55</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>375.19</v>
+        <v>379.39</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>591.5</v>
+        <v>598.11</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>694.09</v>
+        <v>652.63</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>603.86</v>
+        <v>567.8</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>724.2</v>
+        <v>680.95</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.7</v>
+        <v>13.685731</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>14.86</v>
+        <v>14.85</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.12</v>
+        <v>17.11</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>851.24</v>
+        <v>800.4</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>740.55</v>
+        <v>696.33</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>832.83</v>
+        <v>783.09</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2920</v>
+        <v>2973.478145</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3896.74</v>
+        <v>3968.11</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.161</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3390.12</v>
+        <v>3452.21</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4234</v>
+        <v>4311.54</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>1047.68</v>
+        <v>985.11</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>1.5103</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>911.47</v>
+        <v>857.03</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1086.3</v>
+        <v>1021.43</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>100.5</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>127.57</v>
+        <v>121.09</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.1044</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>110.99</v>
+        <v>105.35</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>122.61</v>
+        <v>116.37</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>838.14</v>
+        <v>788.09</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>729.21</v>
+        <v>685.66</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>724.2</v>
+        <v>680.95</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2820</v>
+        <v>2271.865535</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2967.77</v>
+        <v>2390.91</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.9156</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>2581.99</v>
+        <v>2080.12</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>3525</v>
+        <v>2839.83</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>50.2</v>
+        <v>52.260748</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>21.79</v>
+        <v>22.68</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>18.52</v>
+        <v>19.28</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>22.09</v>
+        <v>22.99</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>20.53</v>
+        <v>18.88</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>0.9628</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>17.86</v>
+        <v>16.42</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>131</v>
+        <v>155.991755</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>103.75</v>
+        <v>123.55</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>109.45</v>
+        <v>130.33</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>595.84</v>
+        <v>560.25</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>576.22</v>
+        <v>541.8099999999999</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>543.15</v>
+        <v>510.71</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>15.7</v>
+        <v>10.942196</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>18.23</v>
+        <v>12.7</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.01</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>15.86</v>
+        <v>11.05</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>18.84</v>
+        <v>13.13</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8650</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11074.59</v>
+        <v>11218.46</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>9635.23</v>
+        <v>9760.4</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11072</v>
+        <v>11215.83</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>818.47</v>
+        <v>769.59</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.1799</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>712.0700000000001</v>
+        <v>669.54</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>663.85</v>
+        <v>624.2</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>130.5</v>
+        <v>129.16035</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>167.08</v>
+        <v>165.36</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>145.36</v>
+        <v>143.87</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>176.18</v>
+        <v>174.37</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>18.92</v>
+        <v>17.4</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>0.8873</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>16.46</v>
+        <v>15.13</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>194</v>
+        <v>182.949169</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>164.18</v>
+        <v>154.83</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>176.81</v>
+        <v>166.74</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>232.8</v>
+        <v>219.54</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,25 +2785,25 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>4.85</v>
+        <v>6.384576</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="K31" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="M31" s="33" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4620</v>
+        <v>4159.198135</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>5062.6</v>
+        <v>4557.65</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>0.9533</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>4404.25</v>
+        <v>3964.96</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>6006</v>
+        <v>5406.96</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1735</v>
+        <v>1743.592306</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4630.89</v>
+        <v>4653.82</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.3221</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>4028.84</v>
+        <v>4048.8</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4164</v>
+        <v>4184.62</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>779.1799999999999</v>
+        <v>732.65</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>677.91</v>
+        <v>637.4299999999999</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>784.55</v>
+        <v>737.7</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.2</v>
+        <v>46.456446</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.14</v>
+        <v>55.45</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.0383</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>47.97</v>
+        <v>48.24</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>64.68000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>10.02</v>
+        <v>9.361336</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>13.88</v>
+        <v>12.97</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>12.08</v>
+        <v>11.28</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>6.01</v>
+        <v>5.62</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.592665</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.59</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>68.37</v>
+        <v>67.83</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>83.33</v>
+        <v>82.67</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>20.73</v>
+        <v>19.06</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>18.04</v>
+        <v>16.58</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>625.34</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>604.71</v>
+        <v>568.59</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>754.38</v>
+        <v>709.3200000000001</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1620</v>
+        <v>1356.44293</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1273.32</v>
+        <v>1066.16</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1599.43</v>
+        <v>1339.22</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>891</v>
+        <v>746.04</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1415</v>
+        <v>1458.129101</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>1811.62</v>
+        <v>1866.84</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1576.17</v>
+        <v>1624.21</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2051.75</v>
+        <v>2114.29</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.07780000000000001</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>923.23</v>
+        <v>868.1</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.3309</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>803.2</v>
+        <v>755.23</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>694.02</v>
+        <v>652.58</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.15</v>
+        <v>13.880458</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.96</v>
+        <v>19.58</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>17.36</v>
+        <v>17.03</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.64</v>
+        <v>22.21</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,25 +3604,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>24750</v>
+        <v>27056.87</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>0.044</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>18.55</v>
+        <v>17.053859</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.2369</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>22.94</v>
+        <v>21.09</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>25.56</v>
+        <v>23.5</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>25.04</v>
+        <v>23.02</v>
       </c>
       <c r="M45" s="20" t="n">
         <v>0.0504</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>510</v>
+        <v>544.717652</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>332.01</v>
+        <v>354.61</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>309.88</v>
+        <v>330.97</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>280.5</v>
+        <v>299.59</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2720</v>
+        <v>2590.03315</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2803.5</v>
+        <v>2669.55</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>0.8967000000000001</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2439.02</v>
+        <v>2322.48</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3400</v>
+        <v>3237.54</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>680.99</v>
+        <v>640.3200000000001</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>0.9817</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>592.46</v>
+        <v>557.0700000000001</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>663.85</v>
+        <v>624.2</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.921</v>
+        <v>2.918309</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.87</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3720</v>
+        <v>3776.042542</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4278</v>
+        <v>4342.45</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4836</v>
+        <v>4908.86</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>27.2</v>
+        <v>19.536613</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>34.82</v>
+        <v>25.01</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>30.3</v>
+        <v>21.76</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>35.36</v>
+        <v>25.4</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3126</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.5949</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>21.69</v>
+        <v>40.37</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>1.3876</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>18.87</v>
+        <v>35.12</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>21.08</v>
+        <v>39.23</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.1786</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 10:45 UTC</t>
+          <t>2026-03-23 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>134.5</v>
+        <v>132.030471</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.28</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.28</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.28</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.92</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.92</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.92</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.7</v>
+        <v>40.93</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>910</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.11</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.11</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.11</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.69</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.69</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.69</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>591.5</v>
+        <v>598.11</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>660.83</v>
+        <v>621.37</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>660.83</v>
+        <v>621.37</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>660.83</v>
+        <v>621.37</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>574.89</v>
+        <v>540.5599999999999</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>574.89</v>
+        <v>540.5599999999999</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>574.89</v>
+        <v>540.5599999999999</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>724.2</v>
+        <v>680.95</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.7</v>
+        <v>13.685731</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>12.19</v>
+        <v>12.18</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>12.19</v>
+        <v>12.18</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>12.19</v>
+        <v>12.18</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.12</v>
+        <v>17.11</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>762.04</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>762.04</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>762.04</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>705.0700000000001</v>
+        <v>662.96</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>705.0700000000001</v>
+        <v>662.96</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>705.0700000000001</v>
+        <v>662.96</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>832.83</v>
+        <v>783.09</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2920</v>
+        <v>2973.478145</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3501.57</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3501.57</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3501.57</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>2991.54</v>
+        <v>3046.33</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>2991.54</v>
+        <v>3046.33</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>2991.54</v>
+        <v>3046.33</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4234</v>
+        <v>4311.54</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>997.46</v>
+        <v>937.9</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>997.46</v>
+        <v>937.9</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>997.46</v>
+        <v>937.9</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>1.4379</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>867.77</v>
+        <v>815.95</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>1.4379</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>867.77</v>
+        <v>815.95</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>1.4379</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>867.77</v>
+        <v>815.95</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1086.3</v>
+        <v>1021.43</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>100.5</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.39</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.39</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.39</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>99.34999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>99.34999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>99.34999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>122.61</v>
+        <v>116.37</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>797.95</v>
+        <v>750.29</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>797.95</v>
+        <v>750.29</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>797.95</v>
+        <v>750.29</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>694.21</v>
+        <v>652.75</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>694.21</v>
+        <v>652.75</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>694.21</v>
+        <v>652.75</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>724.2</v>
+        <v>680.95</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2820</v>
+        <v>2271.865535</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2112.15</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2112.15</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2112.15</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>2280.82</v>
+        <v>1837.48</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>2280.82</v>
+        <v>1837.48</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>2280.82</v>
+        <v>1837.48</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>3525</v>
+        <v>2839.83</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>50.2</v>
+        <v>52.260748</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.51</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.51</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.51</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.73</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.73</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.73</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>22.09</v>
+        <v>22.99</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.97</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.97</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.97</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>17</v>
+        <v>15.64</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>17</v>
+        <v>15.64</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>17</v>
+        <v>15.64</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>131</v>
+        <v>155.991755</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.36</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.36</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.36</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>567.29</v>
+        <v>533.41</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>567.29</v>
+        <v>533.41</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>567.29</v>
+        <v>533.41</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>548.58</v>
+        <v>515.8200000000001</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>548.58</v>
+        <v>515.8200000000001</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>548.58</v>
+        <v>515.8200000000001</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>543.15</v>
+        <v>510.71</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>15.7</v>
+        <v>10.942196</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.09</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.09</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.09</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>15.1</v>
+        <v>10.52</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>15.1</v>
+        <v>10.52</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>15.1</v>
+        <v>10.52</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>18.84</v>
+        <v>13.13</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8650</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10408.82</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10408.82</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10408.82</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>8939.780000000001</v>
+        <v>9055.91</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>8939.780000000001</v>
+        <v>9055.91</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>8939.780000000001</v>
+        <v>9055.91</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11072</v>
+        <v>11215.83</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>779.24</v>
+        <v>732.7</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>779.24</v>
+        <v>732.7</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>779.24</v>
+        <v>732.7</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>677.91</v>
+        <v>637.4299999999999</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>677.91</v>
+        <v>637.4299999999999</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>677.91</v>
+        <v>637.4299999999999</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>663.85</v>
+        <v>624.2</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>130.5</v>
+        <v>129.16035</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.43</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.43</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.43</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>138.38</v>
+        <v>136.96</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>138.38</v>
+        <v>136.96</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>138.38</v>
+        <v>136.96</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>176.18</v>
+        <v>174.37</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.39</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.39</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.39</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>15.5</v>
+        <v>14.26</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>15.5</v>
+        <v>14.26</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>15.5</v>
+        <v>14.26</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>194</v>
+        <v>182.949169</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>142.28</v>
+        <v>134.17</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>142.28</v>
+        <v>134.17</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>142.28</v>
+        <v>134.17</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>154.31</v>
+        <v>145.52</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>154.31</v>
+        <v>145.52</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>154.31</v>
+        <v>145.52</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>232.8</v>
+        <v>219.54</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,49 +5777,49 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>4.85</v>
+        <v>6.384576</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="O23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="T23" s="40" t="n">
         <v>0</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4620</v>
+        <v>4159.198135</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.58</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.58</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.58</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>0.8448</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>3902.98</v>
+        <v>3513.69</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>0.8448</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>3902.98</v>
+        <v>3513.69</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>0.8448</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>3902.98</v>
+        <v>3513.69</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>6006</v>
+        <v>5406.96</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1735</v>
+        <v>1743.592306</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4322.71</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4322.71</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4322.71</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.1569</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3742.22</v>
+        <v>3760.75</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.1569</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3742.22</v>
+        <v>3760.75</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.1569</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3742.22</v>
+        <v>3760.75</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4164</v>
+        <v>4184.62</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>735.61</v>
+        <v>691.6799999999999</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>735.61</v>
+        <v>691.6799999999999</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>735.61</v>
+        <v>691.6799999999999</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>639.95</v>
+        <v>601.73</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>639.95</v>
+        <v>601.73</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>639.95</v>
+        <v>601.73</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>784.55</v>
+        <v>737.7</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.2</v>
+        <v>46.456446</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.83</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.83</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.83</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>44.84</v>
+        <v>45.09</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>44.84</v>
+        <v>45.09</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>44.84</v>
+        <v>45.09</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>64.68000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>10.02</v>
+        <v>9.361336</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.83</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.83</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.83</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>10.09</v>
+        <v>9.42</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>10.09</v>
+        <v>9.42</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>10.09</v>
+        <v>9.42</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>6.01</v>
+        <v>5.62</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>64.09999999999999</v>
+        <v>63.592665</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>63.37</v>
+        <v>62.87</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>63.37</v>
+        <v>62.87</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>63.37</v>
+        <v>62.87</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>83.33</v>
+        <v>82.67</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>19.74</v>
+        <v>18.15</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>19.74</v>
+        <v>18.15</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>19.74</v>
+        <v>18.15</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>17.17</v>
+        <v>15.79</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>17.17</v>
+        <v>15.79</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>17.17</v>
+        <v>15.79</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>625.34</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>625.34</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>625.34</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>604.71</v>
+        <v>568.59</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>604.71</v>
+        <v>568.59</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>604.71</v>
+        <v>568.59</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>754.38</v>
+        <v>709.3200000000001</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1620</v>
+        <v>1356.44293</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>820.04</v>
+        <v>686.63</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>869.29</v>
+        <v>727.87</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>902.02</v>
+        <v>755.27</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>937.17</v>
+        <v>784.7</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>937.17</v>
+        <v>784.7</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>937.17</v>
+        <v>784.7</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>891</v>
+        <v>746.04</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1415</v>
+        <v>1458.129101</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1732.11</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1732.11</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1732.11</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1462.4</v>
+        <v>1506.98</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1462.4</v>
+        <v>1506.98</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1462.4</v>
+        <v>1506.98</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2051.75</v>
+        <v>2114.29</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>879</v>
+        <v>826.5</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>879</v>
+        <v>826.5</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>879</v>
+        <v>826.5</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>764.76</v>
+        <v>719.08</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>764.76</v>
+        <v>719.08</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>764.76</v>
+        <v>719.08</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>694.02</v>
+        <v>652.58</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.15</v>
+        <v>13.880458</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.07</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.07</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.07</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>16.02</v>
+        <v>15.72</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>16.02</v>
+        <v>15.72</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>16.02</v>
+        <v>15.72</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.64</v>
+        <v>22.21</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6700,49 +6700,49 @@
         </is>
       </c>
       <c r="E36" s="38" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.387</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>31207.5</v>
+        <v>34116.26</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.3925</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>31331.25</v>
+        <v>34251.54</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.3981</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>31457.25</v>
+        <v>34389.29</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>24750</v>
+        <v>27056.87</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>24750</v>
+        <v>27056.87</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>24750</v>
+        <v>27056.87</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="T36" s="39" t="n">
         <v>0.044</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>18.55</v>
+        <v>17.053859</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.1776</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>21.84</v>
+        <v>20.08</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.1776</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>21.84</v>
+        <v>20.08</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.1776</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>21.84</v>
+        <v>20.08</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.84</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.84</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.84</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>25.04</v>
+        <v>23.02</v>
       </c>
       <c r="T37" s="37" t="n">
         <v>0.0504</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>510</v>
+        <v>544.717652</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.01</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.01</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.01</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>289.78</v>
+        <v>309.51</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>289.78</v>
+        <v>309.51</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>289.78</v>
+        <v>309.51</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>280.5</v>
+        <v>299.59</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2720</v>
+        <v>2590.03315</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2434.63</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2434.63</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2434.63</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>0.8178</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2224.42</v>
+        <v>2118.13</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>0.8178</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2224.42</v>
+        <v>2118.13</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>0.8178</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2224.42</v>
+        <v>2118.13</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3400</v>
+        <v>3237.54</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>648.34</v>
+        <v>609.62</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>648.34</v>
+        <v>609.62</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>648.34</v>
+        <v>609.62</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>564.03</v>
+        <v>530.35</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>564.03</v>
+        <v>530.35</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>564.03</v>
+        <v>530.35</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>663.85</v>
+        <v>624.2</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.921</v>
+        <v>2.918309</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.87</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3720</v>
+        <v>3776.042542</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4278</v>
+        <v>4342.45</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4278</v>
+        <v>4342.45</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4278</v>
+        <v>4342.45</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4836</v>
+        <v>4908.86</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>27.2</v>
+        <v>19.536613</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.82</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.82</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.82</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>30.07</v>
+        <v>21.6</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>30.07</v>
+        <v>21.6</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>30.07</v>
+        <v>21.6</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>35.36</v>
+        <v>25.4</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>13.6</v>
+        <v>25.3126</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.25</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.25</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.25</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>16.01</v>
+        <v>29.8</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>16.01</v>
+        <v>29.8</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>16.01</v>
+        <v>29.8</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>21.08</v>
+        <v>39.23</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.1786</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>134.5</v>
+        <v>132.030471</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.28</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>910</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.11</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>660.83</v>
+        <v>621.37</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.7</v>
+        <v>13.685731</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>762.04</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2920</v>
+        <v>2973.478145</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3501.57</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>997.46</v>
+        <v>937.9</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>100.5</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.39</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>797.95</v>
+        <v>750.29</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2820</v>
+        <v>2271.865535</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2112.15</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>50.2</v>
+        <v>52.260748</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.51</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.97</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>131</v>
+        <v>155.991755</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.36</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>567.29</v>
+        <v>533.41</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>15.7</v>
+        <v>10.942196</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.09</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8650</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10408.82</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>779.24</v>
+        <v>732.7</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>130.5</v>
+        <v>129.16035</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.43</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.39</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>194</v>
+        <v>182.949169</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>142.28</v>
+        <v>134.17</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>4.85</v>
+        <v>6.384576</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.0309</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4620</v>
+        <v>4159.198135</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.58</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1735</v>
+        <v>1743.592306</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4322.71</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>735.61</v>
+        <v>691.6799999999999</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.2</v>
+        <v>46.456446</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.83</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>10.02</v>
+        <v>9.361336</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.83</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.592665</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>19.74</v>
+        <v>18.15</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>625.34</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1620</v>
+        <v>1356.44293</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>820.04</v>
+        <v>686.63</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1415</v>
+        <v>1458.129101</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1732.11</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.1879</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>879</v>
+        <v>826.5</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.15</v>
+        <v>13.880458</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.07</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>31207.5</v>
+        <v>34116.26</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.387</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>18.55</v>
+        <v>17.053859</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>21.84</v>
+        <v>20.08</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.1776</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>510</v>
+        <v>544.717652</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.01</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2720</v>
+        <v>2590.03315</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2434.63</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>648.34</v>
+        <v>609.62</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.921</v>
+        <v>2.918309</v>
       </c>
       <c r="F41" s="19" t="n">
         <v>2.54</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3720</v>
+        <v>3776.042542</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>27.2</v>
+        <v>19.536613</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.82</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3126</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.25</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.3532</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>134.5</v>
+        <v>132.030471</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>45.23</v>
+        <v>44.4</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>29.19</v>
+        <v>28.65</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.7</v>
+        <v>40.93</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>50.2</v>
+        <v>52.260748</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>21.79</v>
+        <v>22.68</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>18.52</v>
+        <v>19.28</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>22.09</v>
+        <v>22.99</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,25 +10322,25 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>4.85</v>
+        <v>6.384576</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>10.02</v>
+        <v>9.361336</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>13.88</v>
+        <v>12.97</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>12.08</v>
+        <v>11.28</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>6.01</v>
+        <v>5.62</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>510</v>
+        <v>544.717652</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>332.01</v>
+        <v>354.61</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>309.88</v>
+        <v>330.97</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>280.5</v>
+        <v>299.59</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.921</v>
+        <v>2.918309</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.87</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>694.09</v>
+        <v>652.63</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>603.86</v>
+        <v>567.8</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>724.2</v>
+        <v>680.95</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>851.24</v>
+        <v>800.4</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>740.55</v>
+        <v>696.33</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>832.83</v>
+        <v>783.09</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>100.5</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>127.57</v>
+        <v>121.09</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.1044</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>110.99</v>
+        <v>105.35</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>122.61</v>
+        <v>116.37</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>15.7</v>
+        <v>10.942196</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>18.23</v>
+        <v>12.7</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.01</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>15.86</v>
+        <v>11.05</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>18.84</v>
+        <v>13.13</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8650</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11074.59</v>
+        <v>11218.46</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>9635.23</v>
+        <v>9760.4</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11072</v>
+        <v>11215.83</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>818.47</v>
+        <v>769.59</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.1799</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>712.0700000000001</v>
+        <v>669.54</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>663.85</v>
+        <v>624.2</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>194</v>
+        <v>182.949169</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>164.18</v>
+        <v>154.83</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>176.81</v>
+        <v>166.74</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>232.8</v>
+        <v>219.54</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>779.1799999999999</v>
+        <v>732.65</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>677.91</v>
+        <v>637.4299999999999</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>784.55</v>
+        <v>737.7</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>625.34</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>604.71</v>
+        <v>568.59</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>754.38</v>
+        <v>709.3200000000001</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1620</v>
+        <v>1356.44293</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1273.32</v>
+        <v>1066.16</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1599.43</v>
+        <v>1339.22</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>891</v>
+        <v>746.04</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>923.23</v>
+        <v>868.1</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.3309</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>803.2</v>
+        <v>755.23</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>694.02</v>
+        <v>652.58</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -10978,25 +10978,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="G27" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>24750</v>
+        <v>27056.87</v>
       </c>
       <c r="I27" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="K27" s="39" t="n">
         <v>0.044</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>680.99</v>
+        <v>640.3200000000001</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>0.9817</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>592.46</v>
+        <v>557.0700000000001</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>663.85</v>
+        <v>624.2</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2920</v>
+        <v>2973.478145</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3896.74</v>
+        <v>3968.11</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.161</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3390.12</v>
+        <v>3452.21</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4234</v>
+        <v>4311.54</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>131</v>
+        <v>155.991755</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>103.75</v>
+        <v>123.55</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>109.45</v>
+        <v>130.33</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>130.5</v>
+        <v>129.16035</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>167.08</v>
+        <v>165.36</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>145.36</v>
+        <v>143.87</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>176.18</v>
+        <v>174.37</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4620</v>
+        <v>4159.198135</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>5062.6</v>
+        <v>4557.65</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>0.9533</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>4404.25</v>
+        <v>3964.96</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>6006</v>
+        <v>5406.96</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1735</v>
+        <v>1743.592306</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4630.89</v>
+        <v>4653.82</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.3221</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>4028.84</v>
+        <v>4048.8</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4164</v>
+        <v>4184.62</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.2</v>
+        <v>46.456446</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.14</v>
+        <v>55.45</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.0383</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>47.97</v>
+        <v>48.24</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64.68000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1415</v>
+        <v>1458.129101</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>1811.62</v>
+        <v>1866.84</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1576.17</v>
+        <v>1624.21</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2051.75</v>
+        <v>2114.29</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.15</v>
+        <v>13.880458</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.96</v>
+        <v>19.58</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>17.36</v>
+        <v>17.03</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.64</v>
+        <v>22.21</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2720</v>
+        <v>2590.03315</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2803.5</v>
+        <v>2669.55</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>0.8967000000000001</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2439.02</v>
+        <v>2322.48</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3400</v>
+        <v>3237.54</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3720</v>
+        <v>3776.042542</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4278</v>
+        <v>4342.45</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4836</v>
+        <v>4908.86</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>1047.68</v>
+        <v>985.11</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>1.5103</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>911.47</v>
+        <v>857.03</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1086.3</v>
+        <v>1021.43</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>838.14</v>
+        <v>788.09</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>729.21</v>
+        <v>685.66</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>724.2</v>
+        <v>680.95</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2820</v>
+        <v>2271.865535</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2967.77</v>
+        <v>2390.91</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.9156</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>2581.99</v>
+        <v>2080.12</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>3525</v>
+        <v>2839.83</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>595.84</v>
+        <v>560.25</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>576.22</v>
+        <v>541.8099999999999</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>543.15</v>
+        <v>510.71</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>910</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>276.46</v>
+        <v>279.55</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>375.19</v>
+        <v>379.39</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>591.5</v>
+        <v>598.11</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.7</v>
+        <v>13.685731</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>14.86</v>
+        <v>14.85</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.12</v>
+        <v>17.11</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>20.53</v>
+        <v>18.88</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>0.9628</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>17.86</v>
+        <v>16.42</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>18.92</v>
+        <v>17.4</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>0.8873</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>16.46</v>
+        <v>15.13</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>64.09999999999999</v>
+        <v>63.592665</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.59</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>68.37</v>
+        <v>67.83</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>83.33</v>
+        <v>82.67</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>20.73</v>
+        <v>19.06</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>18.04</v>
+        <v>16.58</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>23.19</v>
+        <v>21.32</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>18.55</v>
+        <v>17.053859</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.2369</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>22.94</v>
+        <v>21.09</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>25.56</v>
+        <v>23.5</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>25.04</v>
+        <v>23.02</v>
       </c>
       <c r="K64" s="37" t="n">
         <v>0.0504</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>27.2</v>
+        <v>19.536613</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>34.82</v>
+        <v>25.01</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>30.3</v>
+        <v>21.76</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>35.36</v>
+        <v>25.4</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>13.6</v>
+        <v>25.3126</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>1.5949</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>21.69</v>
+        <v>40.37</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>1.3876</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>18.87</v>
+        <v>35.12</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>21.08</v>
+        <v>39.23</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.1786</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4630.89</v>
+        <v>4653.82</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>0.0309</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>1.736</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>1047.68</v>
+        <v>985.11</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>276.46</v>
+        <v>279.55</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.5949</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>21.69</v>
+        <v>40.37</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>45.23</v>
+        <v>44.4</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>923.23</v>
+        <v>868.1</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>21.79</v>
+        <v>22.68</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>1.448</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>332.01</v>
+        <v>354.61</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>851.24</v>
+        <v>800.4</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1273.32</v>
+        <v>1066.16</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.96</v>
+        <v>19.58</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>103.75</v>
+        <v>123.55</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.3888</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>838.14</v>
+        <v>788.09</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>164.18</v>
+        <v>154.83</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3853</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>13.88</v>
+        <v>12.97</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.381</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>5137.32</v>
+        <v>5214.71</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>595.84</v>
+        <v>560.25</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>910</v>
+        <v>920.1738360000001</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.0010989</v>
+        <v>0.00108675</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2920</v>
+        <v>2973.478145</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00034247</v>
+        <v>0.00033631</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.7</v>
+        <v>13.685731</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07299269999999999</v>
+        <v>0.0730688</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2820</v>
+        <v>2271.865535</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00035461</v>
+        <v>0.00044017</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>100.5</v>
+        <v>95.38856800000001</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.009950250000000001</v>
+        <v>0.01048344</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>177.7</v>
+        <v>177.721</v>
       </c>
       <c r="E8" s="65" t="n">
-        <v>0.00562746</v>
+        <v>0.0056268</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>134.5</v>
+        <v>132.030471</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00743494</v>
+        <v>0.00757401</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>50.2</v>
+        <v>52.260748</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01992032</v>
+        <v>0.01913482</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>131</v>
+        <v>155.991755</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.00763359</v>
+        <v>0.0064106</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>15.7</v>
+        <v>10.942196</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.06369427</v>
+        <v>0.09138933</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>73</v>
+        <v>74.18732300000001</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01369863</v>
+        <v>0.01347939</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8650</v>
+        <v>8762.367953999999</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011561</v>
+        <v>0.00011412</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>130.5</v>
+        <v>129.16035</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00766284</v>
+        <v>0.00774231</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>451</v>
+        <v>425.593787</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00221729</v>
+        <v>0.00234966</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>194</v>
+        <v>182.949169</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00515464</v>
+        <v>0.005466</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05390836</v>
+        <v>0.05863006</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>4.85</v>
+        <v>6.384576</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.20618557</v>
+        <v>0.15662747</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>10.02</v>
+        <v>9.361336</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.0998004</v>
+        <v>0.10682236</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4620</v>
+        <v>4159.198135</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00021645</v>
+        <v>0.00024043</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.5</v>
+        <v>39.958994</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02531646</v>
+        <v>0.02502566</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.2</v>
+        <v>46.456446</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02164502</v>
+        <v>0.02152554</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1735</v>
+        <v>1743.592306</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057637</v>
+        <v>0.00057353</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>64.09999999999999</v>
+        <v>63.592665</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01560062</v>
+        <v>0.01572508</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05390836</v>
+        <v>0.05863006</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1620</v>
+        <v>1356.44293</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00061728</v>
+        <v>0.00073722</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1415</v>
+        <v>1458.129101</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00070671</v>
+        <v>0.00068581</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.15</v>
+        <v>13.880458</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07067138000000001</v>
+        <v>0.07204373</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>510</v>
+        <v>544.717652</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00196078</v>
+        <v>0.00183581</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14124,10 +14124,10 @@
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="E32" s="65" t="n">
-        <v>4.444e-05</v>
+        <v>4.066e-05</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>572</v>
+        <v>571.660967</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00174825</v>
+        <v>0.00174929</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>1320</v>
+        <v>4581.917868</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00075758</v>
+        <v>0.00021825</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>22.6</v>
+        <v>21.194576</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04424779</v>
+        <v>0.04718188</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>18.55</v>
+        <v>17.056096</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05390836</v>
+        <v>0.05863006</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.921</v>
+        <v>2.918309</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34234851</v>
+        <v>0.34266419</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2720</v>
+        <v>2590.03315</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00036765</v>
+        <v>0.0003861</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3720</v>
+        <v>3776.042542</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026882</v>
+        <v>0.00026483</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.001657</v>
+        <v>0.00176224</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>603.5</v>
+        <v>567.458383</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.001657</v>
+        <v>0.00176224</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>18.55</v>
+        <v>17.053859</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05390836</v>
+        <v>0.05863775</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>27.2</v>
+        <v>19.536613</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.03676471</v>
+        <v>0.05118595</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3126</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.07352941</v>
+        <v>0.03950602</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>23 March 2026 — 10:45 UTC</t>
+          <t>23 March 2026 — 11:26 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 23 March 2026  |  11:26 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 23 March 2026  |  12:12 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 11:26 UTC</t>
+          <t>2026-03-23 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>23 March 2026 — 11:26 UTC</t>
+          <t>23 March 2026 — 12:12 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 23 March 2026  |  12:12 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 23 March 2026  |  16:23 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 12:12 UTC</t>
+          <t>2026-03-23 16:23 UTC</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>23 March 2026 — 12:12 UTC</t>
+          <t>23 March 2026 — 16:23 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 23 March 2026  |  16:23 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 24 March 2026  |  06:59 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.030471</v>
+        <v>131.547186</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.4</v>
+        <v>44.24</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.65</v>
+        <v>28.55</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>40.93</v>
+        <v>40.78</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>920.1738360000001</v>
+        <v>919.82965</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.55</v>
+        <v>279.44</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>379.39</v>
+        <v>379.25</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>598.11</v>
+        <v>597.89</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>652.63</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>567.8</v>
+        <v>566</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>680.95</v>
+        <v>678.79</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.685731</v>
+        <v>13.852778</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>14.85</v>
+        <v>15.03</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>12.92</v>
+        <v>13.08</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.11</v>
+        <v>17.32</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>800.4</v>
+        <v>797.86</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>696.33</v>
+        <v>694.12</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>783.09</v>
+        <v>780.61</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2973.478145</v>
+        <v>2980.942232</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3968.11</v>
+        <v>3978.07</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.161</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3452.21</v>
+        <v>3460.87</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4311.54</v>
+        <v>4322.37</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>985.11</v>
+        <v>981.98</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>1.5103</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>857.03</v>
+        <v>854.3099999999999</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1021.43</v>
+        <v>1018.18</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.38856800000001</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>121.09</v>
+        <v>120.7</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.1044</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>105.35</v>
+        <v>105.01</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116.37</v>
+        <v>116</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>788.09</v>
+        <v>785.58</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>685.66</v>
+        <v>683.48</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>680.95</v>
+        <v>678.79</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2271.865535</v>
+        <v>2275.872731</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2390.91</v>
+        <v>2395.13</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.9156</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>2080.12</v>
+        <v>2083.79</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2839.83</v>
+        <v>2844.84</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.260748</v>
+        <v>52.308227</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.68</v>
+        <v>22.7</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.28</v>
+        <v>19.3</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>22.99</v>
+        <v>23.02</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.88</v>
+        <v>18.62</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>0.9628</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>16.42</v>
+        <v>16.2</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.991755</v>
+        <v>155.989306</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.55</v>
+        <v>123.54</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>560.25</v>
+        <v>558.47</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>541.8099999999999</v>
+        <v>540.09</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>510.71</v>
+        <v>509.09</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.942196</v>
+        <v>10.974209</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.7</v>
+        <v>12.74</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.01</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>11.05</v>
+        <v>11.08</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.13</v>
+        <v>13.17</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8762.367953999999</v>
+        <v>8765.893312</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11218.46</v>
+        <v>11222.97</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>9760.4</v>
+        <v>9764.33</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11215.83</v>
+        <v>11220.34</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>769.59</v>
+        <v>767.14</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.1799</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>669.54</v>
+        <v>667.42</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>624.2</v>
+        <v>622.22</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.16035</v>
+        <v>129.599611</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>165.36</v>
+        <v>165.93</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>143.87</v>
+        <v>144.36</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>174.37</v>
+        <v>174.96</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.4</v>
+        <v>17.16</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>0.8873</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>15.13</v>
+        <v>14.93</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>182.949169</v>
+        <v>182.245261</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>154.83</v>
+        <v>154.23</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>166.74</v>
+        <v>166.1</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>219.54</v>
+        <v>218.69</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.384576</v>
+        <v>6.384564</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4159.198135</v>
+        <v>4159.521529</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4557.65</v>
+        <v>4558</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>0.9533</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>3964.96</v>
+        <v>3965.27</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5406.96</v>
+        <v>5407.38</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1743.592306</v>
+        <v>1749.982128</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4653.82</v>
+        <v>4670.88</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.3221</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>4048.8</v>
+        <v>4063.63</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4184.62</v>
+        <v>4199.96</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>732.65</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>637.4299999999999</v>
+        <v>635.4</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>737.7</v>
+        <v>735.35</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.456446</v>
+        <v>46.387856</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.45</v>
+        <v>55.36</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.0383</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>48.24</v>
+        <v>48.16</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>65.04000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.361336</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>12.97</v>
+        <v>12.94</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>11.28</v>
+        <v>11.26</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>5.62</v>
+        <v>5.6</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.592665</v>
+        <v>63.883392</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>77.95999999999999</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>67.83</v>
+        <v>68.14</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>82.67</v>
+        <v>83.05</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>19.06</v>
+        <v>18.8</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>16.58</v>
+        <v>16.36</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>625.34</v>
+        <v>623.35</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>568.59</v>
+        <v>566.79</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>709.3200000000001</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1356.44293</v>
+        <v>1346.267881</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1066.16</v>
+        <v>1058.17</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1339.22</v>
+        <v>1329.17</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>746.04</v>
+        <v>740.45</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1458.129101</v>
+        <v>1456.210003</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>1866.84</v>
+        <v>1864.39</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1624.21</v>
+        <v>1622.07</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2114.29</v>
+        <v>2111.5</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.07780000000000001</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>868.1</v>
+        <v>865.34</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.3309</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>755.23</v>
+        <v>752.83</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>652.58</v>
+        <v>650.51</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>13.880458</v>
+        <v>14.003188</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.58</v>
+        <v>19.75</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>17.03</v>
+        <v>17.18</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.21</v>
+        <v>22.41</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>17.053859</v>
+        <v>16.825509</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.2369</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>21.09</v>
+        <v>20.81</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.5</v>
+        <v>23.19</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>23.02</v>
+        <v>22.71</v>
       </c>
       <c r="M45" s="20" t="n">
         <v>0.0504</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>544.717652</v>
+        <v>546.182333</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>354.61</v>
+        <v>355.56</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>330.97</v>
+        <v>331.86</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>299.59</v>
+        <v>300.4</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2590.03315</v>
+        <v>2581.145435</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2669.55</v>
+        <v>2660.39</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>0.8967000000000001</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2322.48</v>
+        <v>2314.51</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3237.54</v>
+        <v>3226.43</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>640.3200000000001</v>
+        <v>638.29</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>0.9817</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>557.0700000000001</v>
+        <v>555.3099999999999</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>624.2</v>
+        <v>622.22</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.918309</v>
+        <v>2.909939</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3776.042542</v>
+        <v>3780.951081</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4342.45</v>
+        <v>4348.09</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4908.86</v>
+        <v>4915.24</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>19.536613</v>
+        <v>19.569197</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>25.01</v>
+        <v>25.05</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>21.76</v>
+        <v>21.8</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>25.4</v>
+        <v>25.44</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.3126</v>
+        <v>25.3025</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.5949</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>40.37</v>
+        <v>40.35</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>1.3876</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>35.12</v>
+        <v>35.11</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.23</v>
+        <v>39.22</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.1786</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23 16:23 UTC</t>
+          <t>2026-03-24 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>132.030471</v>
+        <v>131.547186</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.28</v>
+        <v>42.12</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.28</v>
+        <v>42.12</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.28</v>
+        <v>42.12</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>25.92</v>
+        <v>25.82</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>25.92</v>
+        <v>25.82</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>25.92</v>
+        <v>25.82</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>40.93</v>
+        <v>40.78</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>920.1738360000001</v>
+        <v>919.82965</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.11</v>
+        <v>266.01</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.11</v>
+        <v>266.01</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.11</v>
+        <v>266.01</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>351.69</v>
+        <v>351.56</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>351.69</v>
+        <v>351.56</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>351.69</v>
+        <v>351.56</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>598.11</v>
+        <v>597.89</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>621.37</v>
+        <v>619.39</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>621.37</v>
+        <v>619.39</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>621.37</v>
+        <v>619.39</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>540.5599999999999</v>
+        <v>538.84</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>540.5599999999999</v>
+        <v>538.84</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>540.5599999999999</v>
+        <v>538.84</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>680.95</v>
+        <v>678.79</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.685731</v>
+        <v>13.852778</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>12.18</v>
+        <v>12.32</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>12.18</v>
+        <v>12.32</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>12.18</v>
+        <v>12.32</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.11</v>
+        <v>17.32</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>762.04</v>
+        <v>759.62</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>762.04</v>
+        <v>759.62</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>762.04</v>
+        <v>759.62</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>662.96</v>
+        <v>660.86</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>662.96</v>
+        <v>660.86</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>662.96</v>
+        <v>660.86</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>783.09</v>
+        <v>780.61</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2973.478145</v>
+        <v>2980.942232</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3501.57</v>
+        <v>3510.36</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3501.57</v>
+        <v>3510.36</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3501.57</v>
+        <v>3510.36</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3046.33</v>
+        <v>3053.98</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3046.33</v>
+        <v>3053.98</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3046.33</v>
+        <v>3053.98</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4311.54</v>
+        <v>4322.37</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>937.9</v>
+        <v>934.92</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>937.9</v>
+        <v>934.92</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>937.9</v>
+        <v>934.92</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>1.4379</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>815.95</v>
+        <v>813.36</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>1.4379</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>815.95</v>
+        <v>813.36</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>1.4379</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>815.95</v>
+        <v>813.36</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1021.43</v>
+        <v>1018.18</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.38856800000001</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.39</v>
+        <v>108.05</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.39</v>
+        <v>108.05</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.39</v>
+        <v>108.05</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116.37</v>
+        <v>116</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>750.29</v>
+        <v>747.91</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>750.29</v>
+        <v>747.91</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>750.29</v>
+        <v>747.91</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>652.75</v>
+        <v>650.67</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>652.75</v>
+        <v>650.67</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>652.75</v>
+        <v>650.67</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>680.95</v>
+        <v>678.79</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2271.865535</v>
+        <v>2275.872731</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2112.15</v>
+        <v>2115.88</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2112.15</v>
+        <v>2115.88</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2112.15</v>
+        <v>2115.88</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1837.48</v>
+        <v>1840.73</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1837.48</v>
+        <v>1840.73</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1837.48</v>
+        <v>1840.73</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2839.83</v>
+        <v>2844.84</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.260748</v>
+        <v>52.308227</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.51</v>
+        <v>20.53</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.51</v>
+        <v>20.53</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.51</v>
+        <v>20.53</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>22.99</v>
+        <v>23.02</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>17.97</v>
+        <v>17.73</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>17.97</v>
+        <v>17.73</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>17.97</v>
+        <v>17.73</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>15.64</v>
+        <v>15.42</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>15.64</v>
+        <v>15.42</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>15.64</v>
+        <v>15.42</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,25 +5209,25 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.991755</v>
+        <v>155.989306</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.36</v>
+        <v>106.35</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.36</v>
+        <v>106.35</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.36</v>
+        <v>106.35</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>533.41</v>
+        <v>531.72</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>533.41</v>
+        <v>531.72</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>533.41</v>
+        <v>531.72</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>515.8200000000001</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>515.8200000000001</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>515.8200000000001</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>510.71</v>
+        <v>509.09</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.942196</v>
+        <v>10.974209</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.13</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.13</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.13</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>10.52</v>
+        <v>10.55</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>10.52</v>
+        <v>10.55</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>10.52</v>
+        <v>10.55</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.13</v>
+        <v>13.17</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8762.367953999999</v>
+        <v>8765.893312</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10408.82</v>
+        <v>10413</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10408.82</v>
+        <v>10413</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10408.82</v>
+        <v>10413</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>9055.91</v>
+        <v>9059.549999999999</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>9055.91</v>
+        <v>9059.549999999999</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>9055.91</v>
+        <v>9059.549999999999</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11215.83</v>
+        <v>11220.34</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>732.7</v>
+        <v>730.38</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>732.7</v>
+        <v>730.38</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>732.7</v>
+        <v>730.38</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>637.4299999999999</v>
+        <v>635.4</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>637.4299999999999</v>
+        <v>635.4</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>637.4299999999999</v>
+        <v>635.4</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>624.2</v>
+        <v>622.22</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.16035</v>
+        <v>129.599611</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>157.43</v>
+        <v>157.97</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>157.43</v>
+        <v>157.97</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>157.43</v>
+        <v>157.97</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>136.96</v>
+        <v>137.43</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>136.96</v>
+        <v>137.43</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>136.96</v>
+        <v>137.43</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>174.37</v>
+        <v>174.96</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.39</v>
+        <v>16.16</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.39</v>
+        <v>16.16</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.39</v>
+        <v>16.16</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>14.26</v>
+        <v>14.06</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>14.26</v>
+        <v>14.06</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>14.26</v>
+        <v>14.06</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>182.949169</v>
+        <v>182.245261</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>134.17</v>
+        <v>133.66</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>134.17</v>
+        <v>133.66</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>134.17</v>
+        <v>133.66</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>145.52</v>
+        <v>144.96</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>145.52</v>
+        <v>144.96</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>145.52</v>
+        <v>144.96</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>219.54</v>
+        <v>218.69</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.384576</v>
+        <v>6.384564</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4159.198135</v>
+        <v>4159.521529</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4038.58</v>
+        <v>4038.9</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4038.58</v>
+        <v>4038.9</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4038.58</v>
+        <v>4038.9</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>0.8448</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>3513.69</v>
+        <v>3513.96</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>0.8448</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>3513.69</v>
+        <v>3513.96</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>0.8448</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>3513.69</v>
+        <v>3513.96</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5406.96</v>
+        <v>5407.38</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1743.592306</v>
+        <v>1749.982128</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4322.71</v>
+        <v>4338.56</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4322.71</v>
+        <v>4338.56</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4322.71</v>
+        <v>4338.56</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.1569</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3760.75</v>
+        <v>3774.54</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.1569</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3760.75</v>
+        <v>3774.54</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.1569</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3760.75</v>
+        <v>3774.54</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4184.62</v>
+        <v>4199.96</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>691.6799999999999</v>
+        <v>689.48</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>691.6799999999999</v>
+        <v>689.48</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>691.6799999999999</v>
+        <v>689.48</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>601.73</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>601.73</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>601.73</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>737.7</v>
+        <v>735.35</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.456446</v>
+        <v>46.387856</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.83</v>
+        <v>51.75</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.83</v>
+        <v>51.75</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.83</v>
+        <v>51.75</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>45.09</v>
+        <v>45.02</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>45.09</v>
+        <v>45.02</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>45.09</v>
+        <v>45.02</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>65.04000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.361336</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>9.42</v>
+        <v>9.4</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>9.42</v>
+        <v>9.4</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>9.42</v>
+        <v>9.4</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>5.62</v>
+        <v>5.6</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.592665</v>
+        <v>63.883392</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.26000000000001</v>
+        <v>72.59</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.26000000000001</v>
+        <v>72.59</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.26000000000001</v>
+        <v>72.59</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>62.87</v>
+        <v>63.16</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>62.87</v>
+        <v>63.16</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>62.87</v>
+        <v>63.16</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>82.67</v>
+        <v>83.05</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>18.15</v>
+        <v>17.9</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>18.15</v>
+        <v>17.9</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>18.15</v>
+        <v>17.9</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>15.79</v>
+        <v>15.58</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>15.79</v>
+        <v>15.58</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>15.79</v>
+        <v>15.58</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>625.34</v>
+        <v>623.35</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>625.34</v>
+        <v>623.35</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>625.34</v>
+        <v>623.35</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>568.59</v>
+        <v>566.79</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>568.59</v>
+        <v>566.79</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>568.59</v>
+        <v>566.79</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>709.3200000000001</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1356.44293</v>
+        <v>1346.267881</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>686.63</v>
+        <v>681.48</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>727.87</v>
+        <v>722.41</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>755.27</v>
+        <v>749.6</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>784.7</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>784.7</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>784.7</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>746.04</v>
+        <v>740.45</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1458.129101</v>
+        <v>1456.210003</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1732.11</v>
+        <v>1729.83</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1732.11</v>
+        <v>1729.83</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1732.11</v>
+        <v>1729.83</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1506.98</v>
+        <v>1504.99</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1506.98</v>
+        <v>1504.99</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1506.98</v>
+        <v>1504.99</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2114.29</v>
+        <v>2111.5</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>826.5</v>
+        <v>823.88</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>826.5</v>
+        <v>823.88</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>826.5</v>
+        <v>823.88</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>719.08</v>
+        <v>716.8</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>719.08</v>
+        <v>716.8</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>719.08</v>
+        <v>716.8</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>652.58</v>
+        <v>650.51</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>13.880458</v>
+        <v>14.003188</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.07</v>
+        <v>18.23</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.07</v>
+        <v>18.23</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.07</v>
+        <v>18.23</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>15.72</v>
+        <v>15.86</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>15.72</v>
+        <v>15.86</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>15.72</v>
+        <v>15.86</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.21</v>
+        <v>22.41</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>17.053859</v>
+        <v>16.825509</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.1776</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>20.08</v>
+        <v>19.81</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.1776</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>20.08</v>
+        <v>19.81</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.1776</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>20.08</v>
+        <v>19.81</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.84</v>
+        <v>21.55</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.84</v>
+        <v>21.55</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.84</v>
+        <v>21.55</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>23.02</v>
+        <v>22.71</v>
       </c>
       <c r="T37" s="37" t="n">
         <v>0.0504</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>544.717652</v>
+        <v>546.182333</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>332.01</v>
+        <v>332.9</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>332.01</v>
+        <v>332.9</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>332.01</v>
+        <v>332.9</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>309.51</v>
+        <v>310.34</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>309.51</v>
+        <v>310.34</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>309.51</v>
+        <v>310.34</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>299.59</v>
+        <v>300.4</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2590.03315</v>
+        <v>2581.145435</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2434.63</v>
+        <v>2426.28</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2434.63</v>
+        <v>2426.28</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2434.63</v>
+        <v>2426.28</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>0.8178</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2118.13</v>
+        <v>2110.86</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>0.8178</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2118.13</v>
+        <v>2110.86</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>0.8178</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2118.13</v>
+        <v>2110.86</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3237.54</v>
+        <v>3226.43</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>609.62</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>609.62</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>609.62</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>530.35</v>
+        <v>528.66</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>530.35</v>
+        <v>528.66</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>530.35</v>
+        <v>528.66</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>624.2</v>
+        <v>622.22</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.918309</v>
+        <v>2.909939</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3776.042542</v>
+        <v>3780.951081</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4342.45</v>
+        <v>4348.09</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4342.45</v>
+        <v>4348.09</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4342.45</v>
+        <v>4348.09</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4908.86</v>
+        <v>4915.24</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>19.536613</v>
+        <v>19.569197</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.82</v>
+        <v>24.86</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.82</v>
+        <v>24.86</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.82</v>
+        <v>24.86</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>21.6</v>
+        <v>21.63</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>21.6</v>
+        <v>21.63</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>21.6</v>
+        <v>21.63</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>25.4</v>
+        <v>25.44</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.3126</v>
+        <v>25.3025</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.23</v>
+        <v>39.22</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.1786</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.030471</v>
+        <v>131.547186</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.28</v>
+        <v>42.12</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>920.1738360000001</v>
+        <v>919.82965</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.11</v>
+        <v>266.01</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>621.37</v>
+        <v>619.39</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.685731</v>
+        <v>13.852778</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14</v>
+        <v>14.17</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>762.04</v>
+        <v>759.62</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2973.478145</v>
+        <v>2980.942232</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3501.57</v>
+        <v>3510.36</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>937.9</v>
+        <v>934.92</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.38856800000001</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.39</v>
+        <v>108.05</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>750.29</v>
+        <v>747.91</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2271.865535</v>
+        <v>2275.872731</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2112.15</v>
+        <v>2115.88</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.260748</v>
+        <v>52.308227</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.51</v>
+        <v>20.53</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>17.97</v>
+        <v>17.73</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.991755</v>
+        <v>155.989306</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.36</v>
+        <v>106.35</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>533.41</v>
+        <v>531.72</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.942196</v>
+        <v>10.974209</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.13</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8762.367953999999</v>
+        <v>8765.893312</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10408.82</v>
+        <v>10413</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>732.7</v>
+        <v>730.38</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.16035</v>
+        <v>129.599611</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>157.43</v>
+        <v>157.97</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.39</v>
+        <v>16.16</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>182.949169</v>
+        <v>182.245261</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>134.17</v>
+        <v>133.66</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.384576</v>
+        <v>6.384564</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>0.2</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4159.198135</v>
+        <v>4159.521529</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4038.58</v>
+        <v>4038.9</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1743.592306</v>
+        <v>1749.982128</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4322.71</v>
+        <v>4338.56</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>691.6799999999999</v>
+        <v>689.48</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.456446</v>
+        <v>46.387856</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.83</v>
+        <v>51.75</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.361336</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.592665</v>
+        <v>63.883392</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.26000000000001</v>
+        <v>72.59</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>18.15</v>
+        <v>17.9</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>625.34</v>
+        <v>623.35</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1356.44293</v>
+        <v>1346.267881</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>686.63</v>
+        <v>681.48</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1458.129101</v>
+        <v>1456.210003</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1732.11</v>
+        <v>1729.83</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.1879</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>826.5</v>
+        <v>823.88</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>13.880458</v>
+        <v>14.003188</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.07</v>
+        <v>18.23</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>17.053859</v>
+        <v>16.825509</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>20.08</v>
+        <v>19.81</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.1776</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>544.717652</v>
+        <v>546.182333</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>332.01</v>
+        <v>332.9</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2590.03315</v>
+        <v>2581.145435</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2434.63</v>
+        <v>2426.28</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>609.62</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.918309</v>
+        <v>2.909939</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.87</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3776.042542</v>
+        <v>3780.951081</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>19.536613</v>
+        <v>19.569197</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.82</v>
+        <v>24.86</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.3126</v>
+        <v>25.3025</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.3532</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>132.030471</v>
+        <v>131.547186</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.4</v>
+        <v>44.24</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.65</v>
+        <v>28.55</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>40.93</v>
+        <v>40.78</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.260748</v>
+        <v>52.308227</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.68</v>
+        <v>22.7</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.28</v>
+        <v>19.3</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>22.99</v>
+        <v>23.02</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.384576</v>
+        <v>6.384564</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.361336</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>12.97</v>
+        <v>12.94</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>11.28</v>
+        <v>11.26</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>5.62</v>
+        <v>5.6</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>544.717652</v>
+        <v>546.182333</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>354.61</v>
+        <v>355.56</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>330.97</v>
+        <v>331.86</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>299.59</v>
+        <v>300.4</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.918309</v>
+        <v>2.909939</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.87</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.716</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>652.63</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>567.8</v>
+        <v>566</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>680.95</v>
+        <v>678.79</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>800.4</v>
+        <v>797.86</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>696.33</v>
+        <v>694.12</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>783.09</v>
+        <v>780.61</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.38856800000001</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>121.09</v>
+        <v>120.7</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.1044</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>105.35</v>
+        <v>105.01</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116.37</v>
+        <v>116</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.942196</v>
+        <v>10.974209</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.7</v>
+        <v>12.74</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.01</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>11.05</v>
+        <v>11.08</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.13</v>
+        <v>13.17</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8762.367953999999</v>
+        <v>8765.893312</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11218.46</v>
+        <v>11222.97</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>9760.4</v>
+        <v>9764.33</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11215.83</v>
+        <v>11220.34</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>769.59</v>
+        <v>767.14</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.1799</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>669.54</v>
+        <v>667.42</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>624.2</v>
+        <v>622.22</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>182.949169</v>
+        <v>182.245261</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>154.83</v>
+        <v>154.23</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>166.74</v>
+        <v>166.1</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>219.54</v>
+        <v>218.69</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>732.65</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>637.4299999999999</v>
+        <v>635.4</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>737.7</v>
+        <v>735.35</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>625.34</v>
+        <v>623.35</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>568.59</v>
+        <v>566.79</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>709.3200000000001</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1356.44293</v>
+        <v>1346.267881</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1066.16</v>
+        <v>1058.17</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1339.22</v>
+        <v>1329.17</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>746.04</v>
+        <v>740.45</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>868.1</v>
+        <v>865.34</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.3309</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>755.23</v>
+        <v>752.83</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>652.58</v>
+        <v>650.51</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>640.3200000000001</v>
+        <v>638.29</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>0.9817</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>557.0700000000001</v>
+        <v>555.3099999999999</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>624.2</v>
+        <v>622.22</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2973.478145</v>
+        <v>2980.942232</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3968.11</v>
+        <v>3978.07</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.161</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3452.21</v>
+        <v>3460.87</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4311.54</v>
+        <v>4322.37</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,13 +11166,13 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.991755</v>
+        <v>155.989306</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.55</v>
+        <v>123.54</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.16035</v>
+        <v>129.599611</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>165.36</v>
+        <v>165.93</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>143.87</v>
+        <v>144.36</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>174.37</v>
+        <v>174.96</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4159.198135</v>
+        <v>4159.521529</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4557.65</v>
+        <v>4558</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>0.9533</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>3964.96</v>
+        <v>3965.27</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5406.96</v>
+        <v>5407.38</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1743.592306</v>
+        <v>1749.982128</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4653.82</v>
+        <v>4670.88</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.3221</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>4048.8</v>
+        <v>4063.63</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4184.62</v>
+        <v>4199.96</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.456446</v>
+        <v>46.387856</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.45</v>
+        <v>55.36</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.0383</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>48.24</v>
+        <v>48.16</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>65.04000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1458.129101</v>
+        <v>1456.210003</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>1866.84</v>
+        <v>1864.39</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1624.21</v>
+        <v>1622.07</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2114.29</v>
+        <v>2111.5</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>13.880458</v>
+        <v>14.003188</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.58</v>
+        <v>19.75</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>17.03</v>
+        <v>17.18</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.21</v>
+        <v>22.41</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2590.03315</v>
+        <v>2581.145435</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2669.55</v>
+        <v>2660.39</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>0.8967000000000001</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2322.48</v>
+        <v>2314.51</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3237.54</v>
+        <v>3226.43</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3776.042542</v>
+        <v>3780.951081</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4342.45</v>
+        <v>4348.09</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4908.86</v>
+        <v>4915.24</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>985.11</v>
+        <v>981.98</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>1.5103</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>857.03</v>
+        <v>854.3099999999999</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1021.43</v>
+        <v>1018.18</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>788.09</v>
+        <v>785.58</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>685.66</v>
+        <v>683.48</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>680.95</v>
+        <v>678.79</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2271.865535</v>
+        <v>2275.872731</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2390.91</v>
+        <v>2395.13</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.9156</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>2080.12</v>
+        <v>2083.79</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2839.83</v>
+        <v>2844.84</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>560.25</v>
+        <v>558.47</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>541.8099999999999</v>
+        <v>540.09</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>510.71</v>
+        <v>509.09</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>920.1738360000001</v>
+        <v>919.82965</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>279.55</v>
+        <v>279.44</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>379.39</v>
+        <v>379.25</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>598.11</v>
+        <v>597.89</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.685731</v>
+        <v>13.852778</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>14.85</v>
+        <v>15.03</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>12.92</v>
+        <v>13.08</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.11</v>
+        <v>17.32</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.88</v>
+        <v>18.62</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>0.9628</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>16.42</v>
+        <v>16.2</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.4</v>
+        <v>17.16</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>0.8873</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>15.13</v>
+        <v>14.93</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.592665</v>
+        <v>63.883392</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>77.95999999999999</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>67.83</v>
+        <v>68.14</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>82.67</v>
+        <v>83.05</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>19.06</v>
+        <v>18.8</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>16.58</v>
+        <v>16.36</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.32</v>
+        <v>21.03</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>17.053859</v>
+        <v>16.825509</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.2369</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>21.09</v>
+        <v>20.81</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.5</v>
+        <v>23.19</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>23.02</v>
+        <v>22.71</v>
       </c>
       <c r="K64" s="37" t="n">
         <v>0.0504</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>19.536613</v>
+        <v>19.569197</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>25.01</v>
+        <v>25.05</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>21.76</v>
+        <v>21.8</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>25.4</v>
+        <v>25.44</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.3126</v>
+        <v>25.3025</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>1.5949</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>40.37</v>
+        <v>40.35</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>1.3876</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>35.12</v>
+        <v>35.11</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.23</v>
+        <v>39.22</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.1786</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4653.82</v>
+        <v>4670.88</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>1.736</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>985.11</v>
+        <v>981.98</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.55</v>
+        <v>279.44</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.5949</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>40.37</v>
+        <v>40.35</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.4</v>
+        <v>44.24</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>868.1</v>
+        <v>865.34</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.68</v>
+        <v>22.7</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>354.61</v>
+        <v>355.56</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>800.4</v>
+        <v>797.86</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1066.16</v>
+        <v>1058.17</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.58</v>
+        <v>19.75</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.55</v>
+        <v>123.54</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.3888</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>788.09</v>
+        <v>785.58</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>154.83</v>
+        <v>154.23</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3853</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>12.97</v>
+        <v>12.94</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.87</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.381</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>5214.71</v>
+        <v>5221.49</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>560.25</v>
+        <v>558.47</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>920.1738360000001</v>
+        <v>919.82965</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108675</v>
+        <v>0.00108716</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2973.478145</v>
+        <v>2980.942232</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033631</v>
+        <v>0.00033546</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.685731</v>
+        <v>13.852778</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.0730688</v>
+        <v>0.07218769</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2271.865535</v>
+        <v>2275.872731</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00044017</v>
+        <v>0.00043939</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.38856800000001</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01048344</v>
+        <v>0.01051683</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.030471</v>
+        <v>131.547186</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00757401</v>
+        <v>0.00760183</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.260748</v>
+        <v>52.308227</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01913482</v>
+        <v>0.01911745</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.991755</v>
+        <v>155.989306</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.0064106</v>
+        <v>0.0064107</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.942196</v>
+        <v>10.974209</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09138933</v>
+        <v>0.09112273999999999</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.18732300000001</v>
+        <v>74.188785</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347939</v>
+        <v>0.01347913</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8762.367953999999</v>
+        <v>8765.893312</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011412</v>
+        <v>0.00011408</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.16035</v>
+        <v>129.599611</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00774231</v>
+        <v>0.00771607</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>425.593787</v>
+        <v>424.242504</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00234966</v>
+        <v>0.00235714</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>182.949169</v>
+        <v>182.245261</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.005466</v>
+        <v>0.00548711</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05863006</v>
+        <v>0.05943405</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.384576</v>
+        <v>6.384564</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15662747</v>
+        <v>0.15662777</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.361336</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10682236</v>
+        <v>0.10704754</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4159.198135</v>
+        <v>4159.521529</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00024043</v>
+        <v>0.00024041</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.958994</v>
+        <v>39.957362</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02502566</v>
+        <v>0.02502668</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.456446</v>
+        <v>46.387856</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02152554</v>
+        <v>0.02155737</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1743.592306</v>
+        <v>1749.982128</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057353</v>
+        <v>0.00057143</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.592665</v>
+        <v>63.883392</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01572508</v>
+        <v>0.01565352</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05863006</v>
+        <v>0.05943405</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1356.44293</v>
+        <v>1346.267881</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00073722</v>
+        <v>0.00074279</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1458.129101</v>
+        <v>1456.210003</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068581</v>
+        <v>0.00068671</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>13.880458</v>
+        <v>14.003188</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07204373</v>
+        <v>0.07141231000000001</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>544.717652</v>
+        <v>546.182333</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00183581</v>
+        <v>0.00183089</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.660967</v>
+        <v>571.655665</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00174929</v>
+        <v>0.0017493</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4581.917868</v>
+        <v>4590.20962</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021825</v>
+        <v>0.00021785</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.194576</v>
+        <v>21.127282</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04718188</v>
+        <v>0.04733217</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>17.056096</v>
+        <v>16.825373</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05863006</v>
+        <v>0.05943405</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.918309</v>
+        <v>2.909939</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34266419</v>
+        <v>0.34364982</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2590.03315</v>
+        <v>2581.145435</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.0003861</v>
+        <v>0.00038742</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3776.042542</v>
+        <v>3780.951081</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026483</v>
+        <v>0.00026448</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176224</v>
+        <v>0.00176786</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>567.458383</v>
+        <v>565.656672</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176224</v>
+        <v>0.00176786</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>17.053859</v>
+        <v>16.825509</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05863775</v>
+        <v>0.05943357</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.536613</v>
+        <v>19.569197</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05118595</v>
+        <v>0.05110072</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.3126</v>
+        <v>25.3025</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03950602</v>
+        <v>0.03952179</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>23 March 2026 — 16:23 UTC</t>
+          <t>24 March 2026 — 06:59 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 24 March 2026  |  06:59 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 24 March 2026  |  08:19 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 06:59 UTC</t>
+          <t>2026-03-24 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>24 March 2026 — 06:59 UTC</t>
+          <t>24 March 2026 — 08:19 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 24 March 2026  |  08:19 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 24 March 2026  |  08:49 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>$1.145/L</t>
+          <t>$1.143/L</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.24</v>
+        <v>45.23</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.55</v>
+        <v>29.19</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1552,7 +1552,7 @@
         <v>0.1055</v>
       </c>
       <c r="O11" s="22" t="n">
-        <v>-0.8082</v>
+        <v>-0.8071</v>
       </c>
       <c r="P11" s="15" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.44</v>
+        <v>276.46</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>379.25</v>
+        <v>375.19</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>597.89</v>
+        <v>591.5</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1615,7 +1615,7 @@
         <v>0.0788</v>
       </c>
       <c r="O12" s="31" t="n">
-        <v>-0.8407</v>
+        <v>-0.8396</v>
       </c>
       <c r="P12" s="24" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>650.5599999999999</v>
+        <v>694.09</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>566</v>
+        <v>603.86</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1678,7 +1678,7 @@
         <v>0.0504</v>
       </c>
       <c r="O13" s="22" t="n">
-        <v>0.0056</v>
+        <v>0.0067</v>
       </c>
       <c r="P13" s="15" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.03</v>
+        <v>14.86</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>13.08</v>
+        <v>12.93</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.32</v>
+        <v>17.12</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1741,7 +1741,7 @@
         <v>0.0609</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>-0.0595</v>
+        <v>-0.0584</v>
       </c>
       <c r="P14" s="24" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>797.86</v>
+        <v>851.24</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>694.12</v>
+        <v>740.55</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>780.61</v>
+        <v>832.83</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1804,7 +1804,7 @@
         <v>0.0503</v>
       </c>
       <c r="O15" s="22" t="n">
-        <v>0.266</v>
+        <v>0.2671</v>
       </c>
       <c r="P15" s="15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3978.07</v>
+        <v>3896.74</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.161</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3460.87</v>
+        <v>3390.12</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4322.37</v>
+        <v>4234</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1867,7 +1867,7 @@
         <v>0.1332</v>
       </c>
       <c r="O16" s="31" t="n">
-        <v>0.19</v>
+        <v>0.1911</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>981.98</v>
+        <v>1047.68</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>1.5103</v>
+        <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>854.3099999999999</v>
+        <v>1299.94</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1018.18</v>
+        <v>1086.3</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
       </c>
       <c r="N17" s="21" t="n">
-        <v>0.0504</v>
+        <v>0</v>
       </c>
       <c r="O17" s="22" t="n">
-        <v>0.5915</v>
+        <v>0.5926</v>
       </c>
       <c r="P17" s="15" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>120.7</v>
+        <v>127.57</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.1044</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>105.01</v>
+        <v>110.99</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116</v>
+        <v>122.61</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -1993,7 +1993,7 @@
         <v>0.1171</v>
       </c>
       <c r="O18" s="31" t="n">
-        <v>0.1249</v>
+        <v>0.126</v>
       </c>
       <c r="P18" s="24" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>785.58</v>
+        <v>838.14</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>683.48</v>
+        <v>729.21</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2056,7 +2056,7 @@
         <v>0.0504</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>0.2443</v>
+        <v>0.2454</v>
       </c>
       <c r="P19" s="15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2395.13</v>
+        <v>2967.77</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.9156</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>2083.79</v>
+        <v>2581.99</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2844.84</v>
+        <v>3525</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2119,7 +2119,7 @@
         <v>0.132</v>
       </c>
       <c r="O20" s="31" t="n">
-        <v>-0.0921</v>
+        <v>-0.091</v>
       </c>
       <c r="P20" s="24" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.7</v>
+        <v>21.79</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.3</v>
+        <v>18.52</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>23.02</v>
+        <v>22.09</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2182,7 +2182,7 @@
         <v>0.1521</v>
       </c>
       <c r="O21" s="22" t="n">
-        <v>-0.7105</v>
+        <v>-0.7094</v>
       </c>
       <c r="P21" s="15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.62</v>
+        <v>20.53</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>0.9628</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>16.2</v>
+        <v>17.86</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2245,7 +2245,7 @@
         <v>0.0503</v>
       </c>
       <c r="O22" s="31" t="n">
-        <v>-0.0378</v>
+        <v>-0.0367</v>
       </c>
       <c r="P22" s="24" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.54</v>
+        <v>103.75</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>130.33</v>
+        <v>109.45</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>163.79</v>
+        <v>137.55</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2308,7 +2308,7 @@
         <v>0.326</v>
       </c>
       <c r="O23" s="22" t="n">
-        <v>-0.3525</v>
+        <v>-0.3514</v>
       </c>
       <c r="P23" s="15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>558.47</v>
+        <v>595.84</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>540.09</v>
+        <v>576.22</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>509.09</v>
+        <v>543.15</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2371,7 +2371,7 @@
         <v>0.0504</v>
       </c>
       <c r="O24" s="31" t="n">
-        <v>-0.1572</v>
+        <v>-0.1561</v>
       </c>
       <c r="P24" s="24" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.74</v>
+        <v>18.23</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.01</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>11.08</v>
+        <v>15.86</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.17</v>
+        <v>18.84</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2434,7 +2434,7 @@
         <v>0.0503</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>0.0164</v>
+        <v>0.0175</v>
       </c>
       <c r="P25" s="15" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11222.97</v>
+        <v>11074.59</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>9764.33</v>
+        <v>9635.23</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11220.34</v>
+        <v>11072</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2497,7 +2497,7 @@
         <v>0.07780000000000001</v>
       </c>
       <c r="O26" s="31" t="n">
-        <v>0.1358</v>
+        <v>0.1369</v>
       </c>
       <c r="P26" s="24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>767.14</v>
+        <v>818.47</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.1799</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>667.42</v>
+        <v>712.0700000000001</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2560,7 +2560,7 @@
         <v>0.0504</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>0.2117</v>
+        <v>0.2128</v>
       </c>
       <c r="P27" s="15" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>165.93</v>
+        <v>167.08</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>144.36</v>
+        <v>145.36</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>174.96</v>
+        <v>176.18</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2623,7 +2623,7 @@
         <v>0.0505</v>
       </c>
       <c r="O28" s="31" t="n">
-        <v>0.1358</v>
+        <v>0.1369</v>
       </c>
       <c r="P28" s="24" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.16</v>
+        <v>18.92</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>0.8873</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>14.93</v>
+        <v>16.46</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2686,7 +2686,7 @@
         <v>0.0616</v>
       </c>
       <c r="O29" s="22" t="n">
-        <v>-0.1246</v>
+        <v>-0.1235</v>
       </c>
       <c r="P29" s="15" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>154.23</v>
+        <v>164.18</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>166.1</v>
+        <v>176.81</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>218.69</v>
+        <v>232.8</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2749,7 +2749,7 @@
         <v>0.1458</v>
       </c>
       <c r="O30" s="31" t="n">
-        <v>-0.2982</v>
+        <v>-0.2971</v>
       </c>
       <c r="P30" s="24" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,25 +2785,25 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="K31" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="M31" s="33" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="22" t="n">
-        <v>-1.1136</v>
+        <v>-1.1125</v>
       </c>
       <c r="P31" s="15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4558</v>
+        <v>5062.6</v>
       </c>
       <c r="I32" s="27" t="n">
-        <v>0.9533</v>
+        <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>3965.27</v>
+        <v>7161</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5407.38</v>
+        <v>6006</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
       </c>
       <c r="N32" s="30" t="n">
-        <v>0.1284</v>
+        <v>0</v>
       </c>
       <c r="O32" s="31" t="n">
-        <v>-0.0487</v>
+        <v>-0.0476</v>
       </c>
       <c r="P32" s="24" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,34 +2911,34 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4670.88</v>
+        <v>4630.89</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>2.3221</v>
+        <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>4063.63</v>
+        <v>3496.03</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4199.96</v>
+        <v>4164</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
       </c>
       <c r="N33" s="21" t="n">
-        <v>0.0766</v>
+        <v>0</v>
       </c>
       <c r="O33" s="22" t="n">
-        <v>1.5246</v>
+        <v>1.5257</v>
       </c>
       <c r="P33" s="15" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>730.3200000000001</v>
+        <v>779.1799999999999</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>735.35</v>
+        <v>784.55</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3001,7 +3001,7 @@
         <v>0.0593</v>
       </c>
       <c r="O34" s="31" t="n">
-        <v>0.1466</v>
+        <v>0.1477</v>
       </c>
       <c r="P34" s="24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.36</v>
+        <v>55.14</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.0383</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>48.16</v>
+        <v>47.97</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>64.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3064,7 +3064,7 @@
         <v>0.0698</v>
       </c>
       <c r="O35" s="22" t="n">
-        <v>0.049</v>
+        <v>0.0501</v>
       </c>
       <c r="P35" s="15" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>12.94</v>
+        <v>13.88</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>11.26</v>
+        <v>12.08</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3127,7 +3127,7 @@
         <v>0.1973</v>
       </c>
       <c r="O36" s="31" t="n">
-        <v>0.2408</v>
+        <v>0.2419</v>
       </c>
       <c r="P36" s="24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.31999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>68.14</v>
+        <v>68.37</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>83.05</v>
+        <v>83.33</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3190,7 +3190,7 @@
         <v>0.0789</v>
       </c>
       <c r="O37" s="22" t="n">
-        <v>0.0815</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="P37" s="15" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>18.8</v>
+        <v>20.73</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>16.36</v>
+        <v>18.04</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3253,7 +3253,7 @@
         <v>0.0503</v>
       </c>
       <c r="O38" s="31" t="n">
-        <v>-0.0269</v>
+        <v>-0.0258</v>
       </c>
       <c r="P38" s="24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>754.38</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="22" t="n">
-        <v>-0.0425</v>
+        <v>-0.0414</v>
       </c>
       <c r="P39" s="15" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1058.17</v>
+        <v>1273.32</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1329.17</v>
+        <v>1599.43</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>740.45</v>
+        <v>891</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3379,7 +3379,7 @@
         <v>0.7067</v>
       </c>
       <c r="O40" s="31" t="n">
-        <v>-0.3585</v>
+        <v>-0.3574</v>
       </c>
       <c r="P40" s="24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>1864.39</v>
+        <v>1811.62</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1622.07</v>
+        <v>1576.17</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2111.5</v>
+        <v>2051.75</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.07780000000000001</v>
@@ -3442,7 +3442,7 @@
         <v>0.07780000000000001</v>
       </c>
       <c r="O41" s="22" t="n">
-        <v>0.1358</v>
+        <v>0.1369</v>
       </c>
       <c r="P41" s="15" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>865.34</v>
+        <v>923.23</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.3309</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>752.83</v>
+        <v>803.2</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>650.51</v>
+        <v>694.02</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3505,7 +3505,7 @@
         <v>0.0503</v>
       </c>
       <c r="O42" s="31" t="n">
-        <v>0.3853</v>
+        <v>0.3864</v>
       </c>
       <c r="P42" s="24" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.75</v>
+        <v>19.96</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>17.18</v>
+        <v>17.36</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.41</v>
+        <v>22.64</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3568,7 +3568,7 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="O43" s="22" t="n">
-        <v>0.266</v>
+        <v>0.2671</v>
       </c>
       <c r="P43" s="15" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,25 +3604,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>35616.69</v>
+        <v>32580</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>1.1</v>
+        <v>1.361</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>27056.87</v>
+        <v>30622.5</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>30746.45</v>
+        <v>28125</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>0.044</v>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="31" t="n">
-        <v>0.3035</v>
+        <v>0.3046</v>
       </c>
       <c r="P44" s="24" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,34 +3667,34 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>1.2369</v>
+        <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.81</v>
+        <v>22.07</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.19</v>
+        <v>25.56</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="M45" s="20" t="n">
-        <v>0.0504</v>
+        <v>25.04</v>
+      </c>
+      <c r="M45" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="N45" s="21" t="n">
         <v>0.07580000000000001</v>
       </c>
       <c r="O45" s="22" t="n">
-        <v>0.0924</v>
+        <v>0.0466</v>
       </c>
       <c r="P45" s="15" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>355.56</v>
+        <v>332.01</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>331.86</v>
+        <v>309.88</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>300.4</v>
+        <v>280.5</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3757,7 +3757,7 @@
         <v>0.0693</v>
       </c>
       <c r="O46" s="31" t="n">
-        <v>-0.4935</v>
+        <v>-0.4924</v>
       </c>
       <c r="P46" s="24" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,34 +3793,34 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2660.39</v>
+        <v>2803.5</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>0.8967000000000001</v>
+        <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2314.51</v>
+        <v>2752.64</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3226.43</v>
+        <v>3400</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
       </c>
       <c r="N47" s="21" t="n">
-        <v>0.0965</v>
+        <v>0</v>
       </c>
       <c r="O47" s="22" t="n">
-        <v>-0.1138</v>
+        <v>-0.1127</v>
       </c>
       <c r="P47" s="15" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>638.29</v>
+        <v>680.99</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>0.9817</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>555.3099999999999</v>
+        <v>592.46</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3883,7 +3883,7 @@
         <v>0.0504</v>
       </c>
       <c r="O48" s="31" t="n">
-        <v>-0.0161</v>
+        <v>-0.015</v>
       </c>
       <c r="P48" s="24" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="22" t="n">
-        <v>-0.2745</v>
+        <v>-0.2734</v>
       </c>
       <c r="P49" s="15" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4915.24</v>
+        <v>4836</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="31" t="n">
-        <v>0.2365</v>
+        <v>0.2376</v>
       </c>
       <c r="P50" s="24" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>25.05</v>
+        <v>34.82</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>21.8</v>
+        <v>30.3</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>25.44</v>
+        <v>35.36</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4072,7 +4072,7 @@
         <v>0.0077</v>
       </c>
       <c r="O51" s="22" t="n">
-        <v>0.1358</v>
+        <v>0.1369</v>
       </c>
       <c r="P51" s="15" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.5949</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>40.35</v>
+        <v>21.69</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>1.3876</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>35.11</v>
+        <v>18.87</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.22</v>
+        <v>21.08</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.1786</v>
@@ -4135,7 +4135,7 @@
         <v>0.1786</v>
       </c>
       <c r="O52" s="31" t="n">
-        <v>0.4504</v>
+        <v>0.4515</v>
       </c>
       <c r="P52" s="24" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:19 UTC</t>
+          <t>2026-03-24 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.4</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.4</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.4</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>351.56</v>
+        <v>347.8</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>351.56</v>
+        <v>347.8</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>351.56</v>
+        <v>347.8</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>597.89</v>
+        <v>591.5</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>538.84</v>
+        <v>574.89</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>538.84</v>
+        <v>574.89</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>538.84</v>
+        <v>574.89</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>12.32</v>
+        <v>12.19</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>12.32</v>
+        <v>12.19</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>12.32</v>
+        <v>12.19</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.32</v>
+        <v>17.12</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>660.86</v>
+        <v>705.0700000000001</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>660.86</v>
+        <v>705.0700000000001</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>660.86</v>
+        <v>705.0700000000001</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>780.61</v>
+        <v>832.83</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3053.98</v>
+        <v>2991.54</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3053.98</v>
+        <v>2991.54</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3053.98</v>
+        <v>2991.54</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4322.37</v>
+        <v>4234</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,55 +4783,55 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>1.4379</v>
+        <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>813.36</v>
+        <v>1299.94</v>
       </c>
       <c r="N9" s="18" t="n">
-        <v>1.4379</v>
+        <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>813.36</v>
+        <v>1299.94</v>
       </c>
       <c r="P9" s="18" t="n">
-        <v>1.4379</v>
+        <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>813.36</v>
+        <v>1299.94</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1018.18</v>
+        <v>1086.3</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U9" s="37" t="n">
-        <v>0.0504</v>
+      <c r="U9" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V9" s="15" t="n">
         <v>91</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>94</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>94</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>94</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116</v>
+        <v>122.61</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>650.67</v>
+        <v>694.21</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>650.67</v>
+        <v>694.21</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>650.67</v>
+        <v>694.21</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1840.73</v>
+        <v>2280.82</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1840.73</v>
+        <v>2280.82</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1840.73</v>
+        <v>2280.82</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2844.84</v>
+        <v>3525</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.07</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.07</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.07</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>23.02</v>
+        <v>22.09</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>15.42</v>
+        <v>17</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>15.42</v>
+        <v>17</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>15.42</v>
+        <v>17</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>163.79</v>
+        <v>137.55</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>548.58</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>548.58</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>548.58</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>509.09</v>
+        <v>543.15</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>10.55</v>
+        <v>15.1</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>10.55</v>
+        <v>15.1</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>10.55</v>
+        <v>15.1</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.17</v>
+        <v>18.84</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>9059.549999999999</v>
+        <v>8939.780000000001</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>9059.549999999999</v>
+        <v>8939.780000000001</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>9059.549999999999</v>
+        <v>8939.780000000001</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11220.34</v>
+        <v>11072</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>137.43</v>
+        <v>138.38</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>137.43</v>
+        <v>138.38</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>137.43</v>
+        <v>138.38</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>174.96</v>
+        <v>176.18</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>14.06</v>
+        <v>15.5</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>14.06</v>
+        <v>15.5</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>14.06</v>
+        <v>15.5</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>144.96</v>
+        <v>154.31</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>144.96</v>
+        <v>154.31</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>144.96</v>
+        <v>154.31</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>218.69</v>
+        <v>232.8</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,49 +5777,49 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="N23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="O23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="T23" s="40" t="n">
         <v>0</v>
@@ -5848,55 +5848,55 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="L24" s="27" t="n">
-        <v>0.8448</v>
+        <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>3513.96</v>
+        <v>7161</v>
       </c>
       <c r="N24" s="27" t="n">
-        <v>0.8448</v>
+        <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>3513.96</v>
+        <v>7161</v>
       </c>
       <c r="P24" s="27" t="n">
-        <v>0.8448</v>
+        <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>3513.96</v>
+        <v>7161</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5407.38</v>
+        <v>6006</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
       </c>
-      <c r="U24" s="39" t="n">
-        <v>0.1284</v>
+      <c r="U24" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V24" s="24" t="n">
         <v>91</v>
@@ -5919,55 +5919,55 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>2.1569</v>
+        <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3774.54</v>
+        <v>3496.03</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>2.1569</v>
+        <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3774.54</v>
+        <v>3496.03</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>2.1569</v>
+        <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3774.54</v>
+        <v>3496.03</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4199.96</v>
+        <v>4164</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
       </c>
-      <c r="U25" s="37" t="n">
-        <v>0.0766</v>
+      <c r="U25" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V25" s="15" t="n">
         <v>91</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>639.95</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>639.95</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>639.95</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>735.35</v>
+        <v>784.55</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>45.02</v>
+        <v>44.84</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>45.02</v>
+        <v>44.84</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>45.02</v>
+        <v>44.84</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>64.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>9.4</v>
+        <v>10.09</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>9.4</v>
+        <v>10.09</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>9.4</v>
+        <v>10.09</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>63.16</v>
+        <v>63.37</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>63.16</v>
+        <v>63.37</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>63.16</v>
+        <v>63.37</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>83.05</v>
+        <v>83.33</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>15.58</v>
+        <v>17.17</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>15.58</v>
+        <v>17.17</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>15.58</v>
+        <v>17.17</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>754.38</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>681.48</v>
+        <v>820.04</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>722.41</v>
+        <v>869.29</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>749.6</v>
+        <v>902.02</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>937.17</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>937.17</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>937.17</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>740.45</v>
+        <v>891</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1680.88</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1680.88</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1680.88</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1504.99</v>
+        <v>1462.4</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1504.99</v>
+        <v>1462.4</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1504.99</v>
+        <v>1462.4</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2111.5</v>
+        <v>2051.75</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>716.8</v>
+        <v>764.76</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>716.8</v>
+        <v>764.76</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>716.8</v>
+        <v>764.76</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>650.51</v>
+        <v>694.02</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>15.86</v>
+        <v>16.02</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>15.86</v>
+        <v>16.02</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>15.86</v>
+        <v>16.02</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.41</v>
+        <v>22.64</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6700,49 +6700,49 @@
         </is>
       </c>
       <c r="E36" s="38" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.387</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>34116.26</v>
+        <v>31207.5</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.3925</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>34251.54</v>
+        <v>31331.25</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.3981</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>34389.29</v>
+        <v>31457.25</v>
       </c>
       <c r="L36" s="27" t="n">
-        <v>1.1</v>
+        <v>1.361</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>27056.87</v>
+        <v>30622.5</v>
       </c>
       <c r="N36" s="27" t="n">
-        <v>1.1</v>
+        <v>1.361</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>27056.87</v>
+        <v>30622.5</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>1.1</v>
+        <v>1.361</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>27056.87</v>
+        <v>30622.5</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>30746.45</v>
+        <v>28125</v>
       </c>
       <c r="T36" s="39" t="n">
         <v>0.044</v>
@@ -6771,52 +6771,52 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>19.81</v>
+        <v>22.07</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>19.81</v>
+        <v>22.07</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>19.81</v>
+        <v>22.07</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.55</v>
+        <v>23.76</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.55</v>
+        <v>23.76</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.55</v>
+        <v>23.76</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="T37" s="37" t="n">
-        <v>0.0504</v>
+        <v>25.04</v>
+      </c>
+      <c r="T37" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="U37" s="37" t="n">
         <v>0.07580000000000001</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>310.34</v>
+        <v>289.78</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>310.34</v>
+        <v>289.78</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>310.34</v>
+        <v>289.78</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>300.4</v>
+        <v>280.5</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,55 +6913,55 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>0.8178</v>
+        <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2110.86</v>
+        <v>2752.64</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>0.8178</v>
+        <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2110.86</v>
+        <v>2752.64</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>0.8178</v>
+        <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2110.86</v>
+        <v>2752.64</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3226.43</v>
+        <v>3400</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
       </c>
-      <c r="U39" s="37" t="n">
-        <v>0.0965</v>
+      <c r="U39" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V39" s="15" t="n">
         <v>91</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>528.66</v>
+        <v>564.03</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>528.66</v>
+        <v>564.03</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>528.66</v>
+        <v>564.03</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4915.24</v>
+        <v>4836</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>21.63</v>
+        <v>30.07</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>21.63</v>
+        <v>30.07</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>21.63</v>
+        <v>30.07</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>25.44</v>
+        <v>35.36</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>34.24</v>
+        <v>18.4</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>34.24</v>
+        <v>18.4</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>34.24</v>
+        <v>18.4</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>29.79</v>
+        <v>16.01</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>29.79</v>
+        <v>16.01</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>29.79</v>
+        <v>16.01</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.22</v>
+        <v>21.08</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.1786</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.0309</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>681.48</v>
+        <v>820.04</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1680.88</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.1879</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>34116.26</v>
+        <v>31207.5</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.387</v>
@@ -9489,46 +9489,46 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>19.81</v>
+        <v>22.07</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>1.1776</v>
+        <v>1.19</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>1.1856</v>
+        <v>1.19</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>1.1856</v>
+        <v>1.19</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>1.1856</v>
+        <v>1.19</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>1.1856</v>
+        <v>1.19</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>1.2369</v>
+        <v>1.19</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>1.2369</v>
+        <v>1.19</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>1.2369</v>
+        <v>1.19</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.2369</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.87</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>34.24</v>
+        <v>18.4</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.3532</v>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.063</v>
+        <v>1.0633</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9389</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="49">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.0638</v>
+        <v>1.0641</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9389</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="50">
@@ -9994,10 +9994,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.0644</v>
+        <v>1.0647</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9389</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="51">
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.0675</v>
+        <v>1.0678</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9389</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="52">
@@ -10020,10 +10020,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.0967</v>
+        <v>1.0968</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9758</v>
+        <v>1.0126</v>
       </c>
     </row>
     <row r="53">
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.0971</v>
+        <v>1.0973</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9758</v>
+        <v>1.0126</v>
       </c>
     </row>
     <row r="54">
@@ -10046,10 +10046,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.0973</v>
+        <v>1.0974</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9758</v>
+        <v>1.0126</v>
       </c>
     </row>
     <row r="55">
@@ -10059,10 +10059,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.0978</v>
+        <v>1.0979</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9758</v>
+        <v>1.0126</v>
       </c>
     </row>
     <row r="56">
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.1392</v>
+        <v>1.138</v>
       </c>
       <c r="D56" t="n">
-        <v>1.0146</v>
+        <v>1.0458</v>
       </c>
     </row>
     <row r="57">
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.1395</v>
+        <v>1.1384</v>
       </c>
       <c r="D57" t="n">
-        <v>1.0146</v>
+        <v>1.0458</v>
       </c>
     </row>
     <row r="58">
@@ -10098,10 +10098,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.1442</v>
+        <v>1.1431</v>
       </c>
       <c r="D58" t="n">
-        <v>1.0177</v>
+        <v>1.0489</v>
       </c>
     </row>
     <row r="59">
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.1445</v>
+        <v>1.1434</v>
       </c>
       <c r="D59" t="n">
-        <v>1.0177</v>
+        <v>1.0489</v>
       </c>
     </row>
   </sheetData>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.24</v>
+        <v>45.23</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.55</v>
+        <v>29.19</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.7</v>
+        <v>21.79</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.3</v>
+        <v>18.52</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>23.02</v>
+        <v>22.09</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,25 +10322,25 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>12.94</v>
+        <v>13.88</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>11.26</v>
+        <v>12.08</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>355.56</v>
+        <v>332.01</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>331.86</v>
+        <v>309.88</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>300.4</v>
+        <v>280.5</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.87</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.716</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>650.5599999999999</v>
+        <v>694.09</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>566</v>
+        <v>603.86</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>797.86</v>
+        <v>851.24</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>694.12</v>
+        <v>740.55</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>780.61</v>
+        <v>832.83</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>120.7</v>
+        <v>127.57</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.1044</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>105.01</v>
+        <v>110.99</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116</v>
+        <v>122.61</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.74</v>
+        <v>18.23</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.01</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>11.08</v>
+        <v>15.86</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.17</v>
+        <v>18.84</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11222.97</v>
+        <v>11074.59</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>9764.33</v>
+        <v>9635.23</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11220.34</v>
+        <v>11072</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>767.14</v>
+        <v>818.47</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.1799</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>667.42</v>
+        <v>712.0700000000001</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>154.23</v>
+        <v>164.18</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>166.1</v>
+        <v>176.81</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>218.69</v>
+        <v>232.8</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>730.3200000000001</v>
+        <v>779.1799999999999</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>735.35</v>
+        <v>784.55</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>754.38</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1058.17</v>
+        <v>1273.32</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1329.17</v>
+        <v>1599.43</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>740.45</v>
+        <v>891</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>865.34</v>
+        <v>923.23</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.3309</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>752.83</v>
+        <v>803.2</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>650.51</v>
+        <v>694.02</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -10978,25 +10978,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>35616.69</v>
+        <v>32580</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>1.1</v>
+        <v>1.361</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>27056.87</v>
+        <v>30622.5</v>
       </c>
       <c r="I27" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="28" t="n">
-        <v>30746.45</v>
+        <v>28125</v>
       </c>
       <c r="K27" s="39" t="n">
         <v>0.044</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>638.29</v>
+        <v>680.99</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>0.9817</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>555.3099999999999</v>
+        <v>592.46</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11047,7 +11047,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg West Africa: Gas $1.212/L · Die $1.083/L</t>
+          <t xml:space="preserve">  Avg West Africa: Gas $1.212/L · Die $1.103/L</t>
         </is>
       </c>
     </row>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3978.07</v>
+        <v>3896.74</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.161</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3460.87</v>
+        <v>3390.12</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4322.37</v>
+        <v>4234</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.54</v>
+        <v>103.75</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>130.33</v>
+        <v>109.45</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>163.79</v>
+        <v>137.55</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>165.93</v>
+        <v>167.08</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>144.36</v>
+        <v>145.36</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>174.96</v>
+        <v>176.18</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4558</v>
+        <v>5062.6</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>0.9533</v>
+        <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>3965.27</v>
+        <v>7161</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5407.38</v>
+        <v>6006</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4670.88</v>
+        <v>4630.89</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>2.3221</v>
+        <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>4063.63</v>
+        <v>3496.03</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4199.96</v>
+        <v>4164</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.36</v>
+        <v>55.14</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.0383</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>48.16</v>
+        <v>47.97</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>1864.39</v>
+        <v>1811.62</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1622.07</v>
+        <v>1576.17</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2111.5</v>
+        <v>2051.75</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.75</v>
+        <v>19.96</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>17.18</v>
+        <v>17.36</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.41</v>
+        <v>22.64</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2660.39</v>
+        <v>2803.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.8967000000000001</v>
+        <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2314.51</v>
+        <v>2752.64</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3226.43</v>
+        <v>3400</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4915.24</v>
+        <v>4836</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11508,7 +11508,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="B44" s="51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg East Africa: Gas $1.347/L · Die $1.181/L</t>
+          <t xml:space="preserve">  Avg East Africa: Gas $1.347/L · Die $1.222/L</t>
         </is>
       </c>
     </row>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>981.98</v>
+        <v>1047.68</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>1.5103</v>
+        <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>854.3099999999999</v>
+        <v>1299.94</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1018.18</v>
+        <v>1086.3</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>785.58</v>
+        <v>838.14</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>683.48</v>
+        <v>729.21</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2395.13</v>
+        <v>2967.77</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.9156</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>2083.79</v>
+        <v>2581.99</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2844.84</v>
+        <v>3525</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>558.47</v>
+        <v>595.84</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>540.09</v>
+        <v>576.22</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>509.09</v>
+        <v>543.15</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11735,7 +11735,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="B53" s="53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg Central Africa: Gas $1.291/L · Die $1.147/L</t>
+          <t xml:space="preserve">  Avg Central Africa: Gas $1.291/L · Die $1.308/L</t>
         </is>
       </c>
     </row>
@@ -11815,31 +11815,31 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>279.44</v>
+        <v>276.46</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>379.25</v>
+        <v>375.19</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>597.89</v>
+        <v>591.5</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
       </c>
       <c r="L58" s="43" t="n">
-        <v>-0.8041</v>
+        <v>-0.7989000000000001</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -11854,31 +11854,31 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15.03</v>
+        <v>14.86</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>13.08</v>
+        <v>12.93</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.32</v>
+        <v>17.12</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
       </c>
       <c r="L59" s="44" t="n">
-        <v>-0.0229</v>
+        <v>-0.0177</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
@@ -11893,31 +11893,31 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.62</v>
+        <v>20.53</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>0.9628</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>16.2</v>
+        <v>17.86</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="L60" s="43" t="n">
-        <v>-0.0012</v>
+      <c r="L60" s="46" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
@@ -11932,31 +11932,31 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.16</v>
+        <v>18.92</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>0.8873</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>14.93</v>
+        <v>16.46</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
       </c>
       <c r="L61" s="44" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0828</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
@@ -11971,31 +11971,31 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.31999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>68.14</v>
+        <v>68.37</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>83.05</v>
+        <v>83.33</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
       </c>
       <c r="L62" s="46" t="n">
-        <v>0.1181</v>
+        <v>0.1233</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -12010,31 +12010,31 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>18.8</v>
+        <v>20.73</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>16.36</v>
+        <v>18.04</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
       </c>
       <c r="L63" s="45" t="n">
-        <v>0.0097</v>
+        <v>0.0149</v>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
@@ -12049,31 +12049,31 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>1.2369</v>
+        <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>20.81</v>
+        <v>22.07</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.19</v>
+        <v>25.56</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="K64" s="37" t="n">
-        <v>0.0504</v>
+        <v>25.04</v>
+      </c>
+      <c r="K64" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="L64" s="46" t="n">
-        <v>0.129</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -12088,31 +12088,31 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>25.05</v>
+        <v>34.82</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>21.8</v>
+        <v>30.3</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>25.44</v>
+        <v>35.36</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
       </c>
       <c r="L65" s="45" t="n">
-        <v>0.1724</v>
+        <v>0.1776</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
@@ -12127,37 +12127,37 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>1.5949</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>40.35</v>
+        <v>21.69</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>1.3876</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>35.11</v>
+        <v>18.87</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.22</v>
+        <v>21.08</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.1786</v>
       </c>
       <c r="L66" s="46" t="n">
-        <v>0.487</v>
+        <v>0.4922</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg Southern Africa: Gas $1.108/L · Die $1.014/L</t>
+          <t xml:space="preserve">  Avg Southern Africa: Gas $1.103/L · Die $1.014/L</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
         <v>1.212</v>
       </c>
       <c r="D73" t="n">
-        <v>1.083</v>
+        <v>1.103</v>
       </c>
     </row>
     <row r="74">
@@ -12214,7 +12214,7 @@
         <v>1.347</v>
       </c>
       <c r="D74" t="n">
-        <v>1.181</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="75">
@@ -12227,7 +12227,7 @@
         <v>1.291</v>
       </c>
       <c r="D75" t="n">
-        <v>1.147</v>
+        <v>1.308</v>
       </c>
     </row>
     <row r="76">
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.108</v>
+        <v>1.103</v>
       </c>
       <c r="D76" t="n">
         <v>1.014</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4670.88</v>
+        <v>4630.89</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>0.0309</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>1.736</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>981.98</v>
+        <v>1047.68</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.44</v>
+        <v>276.46</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.5949</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>40.35</v>
+        <v>21.69</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.24</v>
+        <v>45.23</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>865.34</v>
+        <v>923.23</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.7</v>
+        <v>21.79</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>1.448</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>35616.69</v>
+        <v>32580</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>355.56</v>
+        <v>332.01</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>797.86</v>
+        <v>851.24</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1058.17</v>
+        <v>1273.32</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.75</v>
+        <v>19.96</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.54</v>
+        <v>103.75</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.3888</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>785.58</v>
+        <v>838.14</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>154.23</v>
+        <v>164.18</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3853</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>12.94</v>
+        <v>13.88</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.87</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.381</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>558.47</v>
+        <v>595.84</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13134,31 +13134,31 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.2369</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.226</v>
+        <v>1.1935</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.1935</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="40">
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108716</v>
+        <v>0.0010989</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033546</v>
+        <v>0.00034247</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07218769</v>
+        <v>0.07299269999999999</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00043939</v>
+        <v>0.00035461</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01051683</v>
+        <v>0.009950250000000001</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>177.721</v>
+        <v>177.7</v>
       </c>
       <c r="E8" s="65" t="n">
-        <v>0.0056268</v>
+        <v>0.00562746</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00760183</v>
+        <v>0.00743494</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01911745</v>
+        <v>0.01992032</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.0064107</v>
+        <v>0.00763359</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09112273999999999</v>
+        <v>0.06369427</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.188785</v>
+        <v>73</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347913</v>
+        <v>0.01369863</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011408</v>
+        <v>0.00011561</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00771607</v>
+        <v>0.00766284</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>424.242504</v>
+        <v>451</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00235714</v>
+        <v>0.00221729</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00548711</v>
+        <v>0.00515464</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05943405</v>
+        <v>0.05390836</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15662777</v>
+        <v>0.20618557</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10704754</v>
+        <v>0.0998004</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00024041</v>
+        <v>0.00021645</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.957362</v>
+        <v>39.5</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02502668</v>
+        <v>0.02531646</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02155737</v>
+        <v>0.02164502</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057143</v>
+        <v>0.00057637</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01565352</v>
+        <v>0.01560062</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05943405</v>
+        <v>0.05390836</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00074279</v>
+        <v>0.00061728</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068671</v>
+        <v>0.00070671</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07141231000000001</v>
+        <v>0.07067138000000001</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00183089</v>
+        <v>0.00196078</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14124,10 +14124,10 @@
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="E32" s="65" t="n">
-        <v>4.066e-05</v>
+        <v>4.444e-05</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.655665</v>
+        <v>572</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.0017493</v>
+        <v>0.00174825</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4590.20962</v>
+        <v>1320</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021785</v>
+        <v>0.00075758</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.127282</v>
+        <v>22.6</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04733217</v>
+        <v>0.04424779</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05943405</v>
+        <v>0.05390836</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34364982</v>
+        <v>0.34234851</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00038742</v>
+        <v>0.00036765</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026448</v>
+        <v>0.00026882</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176786</v>
+        <v>0.001657</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176786</v>
+        <v>0.001657</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05943357</v>
+        <v>0.05390836</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05110072</v>
+        <v>0.03676471</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03952179</v>
+        <v>0.07352941</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>24 March 2026 — 08:19 UTC</t>
+          <t>24 March 2026 — 08:49 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 24 March 2026  |  08:49 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 24 March 2026  |  09:07 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>45.23</v>
+        <v>44.24</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>29.19</v>
+        <v>28.55</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.7</v>
+        <v>40.78</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>276.46</v>
+        <v>279.44</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>375.19</v>
+        <v>379.25</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>591.5</v>
+        <v>597.89</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>694.09</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>603.86</v>
+        <v>566</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>14.86</v>
+        <v>15.03</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>12.93</v>
+        <v>13.08</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.12</v>
+        <v>17.32</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>851.24</v>
+        <v>797.86</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>740.55</v>
+        <v>694.12</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>832.83</v>
+        <v>780.61</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3896.74</v>
+        <v>3978.07</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.161</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3390.12</v>
+        <v>3460.87</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4234</v>
+        <v>4322.37</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>1047.68</v>
+        <v>981.98</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1086.3</v>
+        <v>1018.18</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>127.57</v>
+        <v>120.7</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.1044</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>110.99</v>
+        <v>105.01</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>122.61</v>
+        <v>116</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>838.14</v>
+        <v>785.58</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>729.21</v>
+        <v>683.48</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2967.77</v>
+        <v>2395.13</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.9156</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>2581.99</v>
+        <v>2083.79</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>3525</v>
+        <v>2844.84</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>18.52</v>
+        <v>19.3</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>22.09</v>
+        <v>23.02</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>20.53</v>
+        <v>18.62</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>0.9628</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>17.86</v>
+        <v>16.2</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>103.75</v>
+        <v>123.54</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>109.45</v>
+        <v>130.33</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>595.84</v>
+        <v>558.47</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>576.22</v>
+        <v>540.09</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>543.15</v>
+        <v>509.09</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>18.23</v>
+        <v>12.74</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.01</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>15.86</v>
+        <v>11.08</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>18.84</v>
+        <v>13.17</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11074.59</v>
+        <v>11222.97</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>9635.23</v>
+        <v>9764.33</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11072</v>
+        <v>11220.34</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>818.47</v>
+        <v>767.14</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.1799</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>712.0700000000001</v>
+        <v>667.42</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>167.08</v>
+        <v>165.93</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>145.36</v>
+        <v>144.36</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>176.18</v>
+        <v>174.96</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>18.92</v>
+        <v>17.16</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>0.8873</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>16.46</v>
+        <v>14.93</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>164.18</v>
+        <v>154.23</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>176.81</v>
+        <v>166.1</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>232.8</v>
+        <v>218.69</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,25 +2785,25 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="K31" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="M31" s="33" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>5062.6</v>
+        <v>4558</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>6006</v>
+        <v>5407.38</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4630.89</v>
+        <v>4670.88</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4164</v>
+        <v>4199.96</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>779.1799999999999</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>784.55</v>
+        <v>735.35</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.14</v>
+        <v>55.36</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.0383</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>47.97</v>
+        <v>48.16</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>64.68000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>13.88</v>
+        <v>12.94</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>12.08</v>
+        <v>11.26</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>6.01</v>
+        <v>5.6</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.59</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>68.37</v>
+        <v>68.14</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>83.33</v>
+        <v>83.05</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>20.73</v>
+        <v>18.8</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>18.04</v>
+        <v>16.36</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>754.38</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1273.32</v>
+        <v>1058.17</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1599.43</v>
+        <v>1329.17</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>891</v>
+        <v>740.45</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>1811.62</v>
+        <v>1864.39</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1576.17</v>
+        <v>1622.07</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2051.75</v>
+        <v>2111.5</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.07780000000000001</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>923.23</v>
+        <v>865.34</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.3309</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>803.2</v>
+        <v>752.83</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>694.02</v>
+        <v>650.51</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.96</v>
+        <v>19.75</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.2271</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>17.36</v>
+        <v>17.18</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.64</v>
+        <v>22.41</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,25 +3604,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>0.044</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>25.56</v>
+        <v>23.19</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>25.04</v>
+        <v>22.71</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>332.01</v>
+        <v>355.56</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>309.88</v>
+        <v>331.86</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>280.5</v>
+        <v>300.4</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2803.5</v>
+        <v>2660.39</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3400</v>
+        <v>3226.43</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>680.99</v>
+        <v>638.29</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>0.9817</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>592.46</v>
+        <v>555.3099999999999</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4836</v>
+        <v>4915.24</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>34.82</v>
+        <v>25.05</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>30.3</v>
+        <v>21.8</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>35.36</v>
+        <v>25.44</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>1.5949</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>21.69</v>
+        <v>40.35</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>1.3876</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>18.87</v>
+        <v>35.11</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>21.08</v>
+        <v>39.22</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.1786</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 08:49 UTC</t>
+          <t>2026-03-24 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.7</v>
+        <v>40.78</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.56</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.56</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.56</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>591.5</v>
+        <v>597.89</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>574.89</v>
+        <v>538.84</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>574.89</v>
+        <v>538.84</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>0.9526</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>574.89</v>
+        <v>538.84</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>12.19</v>
+        <v>12.32</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>12.19</v>
+        <v>12.32</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>0.8897</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>12.19</v>
+        <v>12.32</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.12</v>
+        <v>17.32</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>705.0700000000001</v>
+        <v>660.86</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>705.0700000000001</v>
+        <v>660.86</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.1683</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>705.0700000000001</v>
+        <v>660.86</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>832.83</v>
+        <v>780.61</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>2991.54</v>
+        <v>3053.98</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>2991.54</v>
+        <v>3053.98</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.0245</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>2991.54</v>
+        <v>3053.98</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4234</v>
+        <v>4322.37</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1086.3</v>
+        <v>1018.18</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>99.34999999999999</v>
+        <v>94</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>99.34999999999999</v>
+        <v>94</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>99.34999999999999</v>
+        <v>94</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>122.61</v>
+        <v>116</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>694.21</v>
+        <v>650.67</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>694.21</v>
+        <v>650.67</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>694.21</v>
+        <v>650.67</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>2280.82</v>
+        <v>1840.73</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>2280.82</v>
+        <v>1840.73</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.8088</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>2280.82</v>
+        <v>1840.73</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>3525</v>
+        <v>2844.84</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.75</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.75</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.75</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>22.09</v>
+        <v>23.02</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>17</v>
+        <v>15.42</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>17</v>
+        <v>15.42</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>0.9167</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>17</v>
+        <v>15.42</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>548.58</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>548.58</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>548.58</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>543.15</v>
+        <v>509.09</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>15.1</v>
+        <v>10.55</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>15.1</v>
+        <v>10.55</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>0.9616</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>15.1</v>
+        <v>10.55</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>18.84</v>
+        <v>13.17</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>8939.780000000001</v>
+        <v>9059.549999999999</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>8939.780000000001</v>
+        <v>9059.549999999999</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>8939.780000000001</v>
+        <v>9059.549999999999</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11072</v>
+        <v>11220.34</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.1233</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>138.38</v>
+        <v>137.43</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>138.38</v>
+        <v>137.43</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>138.38</v>
+        <v>137.43</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>176.18</v>
+        <v>174.96</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>15.5</v>
+        <v>14.06</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>15.5</v>
+        <v>14.06</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>0.8358</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>15.5</v>
+        <v>14.06</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>154.31</v>
+        <v>144.96</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>154.31</v>
+        <v>144.96</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>154.31</v>
+        <v>144.96</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>232.8</v>
+        <v>218.69</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,49 +5777,49 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="O23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="T23" s="40" t="n">
         <v>0</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>6006</v>
+        <v>5407.38</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4164</v>
+        <v>4199.96</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>639.95</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>639.95</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>639.95</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>784.55</v>
+        <v>735.35</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>44.84</v>
+        <v>45.02</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>44.84</v>
+        <v>45.02</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>0.9706</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>44.84</v>
+        <v>45.02</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>64.68000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>10.09</v>
+        <v>9.4</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>10.09</v>
+        <v>9.4</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.0066</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>10.09</v>
+        <v>9.4</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>6.01</v>
+        <v>5.6</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>63.37</v>
+        <v>63.16</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>63.37</v>
+        <v>63.16</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>0.9886</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>63.37</v>
+        <v>63.16</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>83.33</v>
+        <v>83.05</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>17.17</v>
+        <v>15.58</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>17.17</v>
+        <v>15.58</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>0.9257</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>17.17</v>
+        <v>15.58</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>754.38</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>820.04</v>
+        <v>681.48</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>869.29</v>
+        <v>722.41</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>902.02</v>
+        <v>749.6</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>937.17</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>937.17</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>937.17</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>891</v>
+        <v>740.45</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1729.83</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1729.83</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.1879</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1729.83</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1462.4</v>
+        <v>1504.99</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1462.4</v>
+        <v>1504.99</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.0335</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1462.4</v>
+        <v>1504.99</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2051.75</v>
+        <v>2111.5</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>764.76</v>
+        <v>716.8</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>764.76</v>
+        <v>716.8</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.2672</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>764.76</v>
+        <v>716.8</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>694.02</v>
+        <v>650.51</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>16.02</v>
+        <v>15.86</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>16.02</v>
+        <v>15.86</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.1324</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>16.02</v>
+        <v>15.86</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.64</v>
+        <v>22.41</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6700,49 +6700,49 @@
         </is>
       </c>
       <c r="E36" s="38" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.387</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>31207.5</v>
+        <v>34116.26</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.3925</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>31331.25</v>
+        <v>34251.54</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.3981</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>31457.25</v>
+        <v>34389.29</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="T36" s="39" t="n">
         <v>0.044</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.55</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.55</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.55</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>25.04</v>
+        <v>22.71</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>289.78</v>
+        <v>310.34</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>289.78</v>
+        <v>310.34</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>289.78</v>
+        <v>310.34</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>280.5</v>
+        <v>300.4</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3400</v>
+        <v>3226.43</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>564.03</v>
+        <v>528.66</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>564.03</v>
+        <v>528.66</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>0.9346</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>564.03</v>
+        <v>528.66</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.87</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.716</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4836</v>
+        <v>4915.24</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>30.07</v>
+        <v>21.63</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>30.07</v>
+        <v>21.63</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.1054</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>30.07</v>
+        <v>21.63</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>35.36</v>
+        <v>25.44</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.24</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.24</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.3532</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.24</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>16.01</v>
+        <v>29.79</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>16.01</v>
+        <v>29.79</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.1773</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>16.01</v>
+        <v>29.79</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>21.08</v>
+        <v>39.22</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.1786</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.0309</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>820.04</v>
+        <v>681.48</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1680.88</v>
+        <v>1729.83</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.1879</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>31207.5</v>
+        <v>34116.26</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.387</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.87</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>18.4</v>
+        <v>34.24</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.3532</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>45.23</v>
+        <v>44.24</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>29.19</v>
+        <v>28.55</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.7</v>
+        <v>40.78</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>18.52</v>
+        <v>19.3</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>22.09</v>
+        <v>23.02</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,25 +10322,25 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>13.88</v>
+        <v>12.94</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.2052</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>12.08</v>
+        <v>11.26</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>6.01</v>
+        <v>5.6</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>332.01</v>
+        <v>355.56</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>309.88</v>
+        <v>331.86</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>280.5</v>
+        <v>300.4</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.87</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.716</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>694.09</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.0006</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>603.86</v>
+        <v>566</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>851.24</v>
+        <v>797.86</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>740.55</v>
+        <v>694.12</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>832.83</v>
+        <v>780.61</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>127.57</v>
+        <v>120.7</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.1044</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>110.99</v>
+        <v>105.01</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>122.61</v>
+        <v>116</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>18.23</v>
+        <v>12.74</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.01</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>15.86</v>
+        <v>11.08</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>18.84</v>
+        <v>13.17</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11074.59</v>
+        <v>11222.97</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>9635.23</v>
+        <v>9764.33</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11072</v>
+        <v>11220.34</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>818.47</v>
+        <v>767.14</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.1799</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>712.0700000000001</v>
+        <v>667.42</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>164.18</v>
+        <v>154.23</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>176.81</v>
+        <v>166.1</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>232.8</v>
+        <v>218.69</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>779.1799999999999</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>784.55</v>
+        <v>735.35</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>754.38</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1273.32</v>
+        <v>1058.17</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1599.43</v>
+        <v>1329.17</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>891</v>
+        <v>740.45</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>923.23</v>
+        <v>865.34</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.3309</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>803.2</v>
+        <v>752.83</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>694.02</v>
+        <v>650.51</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -10978,25 +10978,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="G27" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="I27" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="K27" s="39" t="n">
         <v>0.044</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>680.99</v>
+        <v>638.29</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>0.9817</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>592.46</v>
+        <v>555.3099999999999</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3896.74</v>
+        <v>3978.07</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.161</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3390.12</v>
+        <v>3460.87</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4234</v>
+        <v>4322.37</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>103.75</v>
+        <v>123.54</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>109.45</v>
+        <v>130.33</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>167.08</v>
+        <v>165.93</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>145.36</v>
+        <v>144.36</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>176.18</v>
+        <v>174.96</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>5062.6</v>
+        <v>4558</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>6006</v>
+        <v>5407.38</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4630.89</v>
+        <v>4670.88</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4164</v>
+        <v>4199.96</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.14</v>
+        <v>55.36</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.0383</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>47.97</v>
+        <v>48.16</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64.68000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>1811.62</v>
+        <v>1864.39</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.1139</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1576.17</v>
+        <v>1622.07</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2051.75</v>
+        <v>2111.5</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.96</v>
+        <v>19.75</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.2271</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>17.36</v>
+        <v>17.18</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.64</v>
+        <v>22.41</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2803.5</v>
+        <v>2660.39</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3400</v>
+        <v>3226.43</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4836</v>
+        <v>4915.24</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>1047.68</v>
+        <v>981.98</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1086.3</v>
+        <v>1018.18</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>838.14</v>
+        <v>785.58</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>729.21</v>
+        <v>683.48</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2967.77</v>
+        <v>2395.13</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.9156</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>2581.99</v>
+        <v>2083.79</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>3525</v>
+        <v>2844.84</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>595.84</v>
+        <v>558.47</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>576.22</v>
+        <v>540.09</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>543.15</v>
+        <v>509.09</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>276.46</v>
+        <v>279.44</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>375.19</v>
+        <v>379.25</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>591.5</v>
+        <v>597.89</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>14.86</v>
+        <v>15.03</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>0.9439</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>12.93</v>
+        <v>13.08</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.12</v>
+        <v>17.32</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>20.53</v>
+        <v>18.62</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>0.9628</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>17.86</v>
+        <v>16.2</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>18.92</v>
+        <v>17.16</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>0.8873</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>16.46</v>
+        <v>14.93</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.59</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.0666</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>68.37</v>
+        <v>68.14</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>83.33</v>
+        <v>83.05</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>20.73</v>
+        <v>18.8</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>0.9723000000000001</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>18.04</v>
+        <v>16.36</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>25.56</v>
+        <v>23.19</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>25.04</v>
+        <v>22.71</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>34.82</v>
+        <v>25.05</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.1139</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>30.3</v>
+        <v>21.8</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>35.36</v>
+        <v>25.44</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>1.5949</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>21.69</v>
+        <v>40.35</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>1.3876</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>18.87</v>
+        <v>35.11</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>21.08</v>
+        <v>39.22</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.1786</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4630.89</v>
+        <v>4670.88</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>0.0309</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>1.736</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>1047.68</v>
+        <v>981.98</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>276.46</v>
+        <v>279.44</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.5949</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>21.69</v>
+        <v>40.35</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>45.23</v>
+        <v>44.24</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>923.23</v>
+        <v>865.34</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>1.448</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>332.01</v>
+        <v>355.56</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>851.24</v>
+        <v>797.86</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1273.32</v>
+        <v>1058.17</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.96</v>
+        <v>19.75</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>103.75</v>
+        <v>123.54</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.3888</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>838.14</v>
+        <v>785.58</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>164.18</v>
+        <v>154.23</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3853</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>13.88</v>
+        <v>12.94</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.87</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.381</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>595.84</v>
+        <v>558.47</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.0010989</v>
+        <v>0.00108716</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00034247</v>
+        <v>0.00033546</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07299269999999999</v>
+        <v>0.07218769</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00035461</v>
+        <v>0.00043939</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.009950250000000001</v>
+        <v>0.01051683</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>177.7</v>
+        <v>177.721</v>
       </c>
       <c r="E8" s="65" t="n">
-        <v>0.00562746</v>
+        <v>0.0056268</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00743494</v>
+        <v>0.00760183</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01992032</v>
+        <v>0.01911745</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.00763359</v>
+        <v>0.0064107</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.06369427</v>
+        <v>0.09112273999999999</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>73</v>
+        <v>74.188785</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01369863</v>
+        <v>0.01347913</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011561</v>
+        <v>0.00011408</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00766284</v>
+        <v>0.00771607</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>451</v>
+        <v>424.242504</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00221729</v>
+        <v>0.00235714</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00515464</v>
+        <v>0.00548711</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05390836</v>
+        <v>0.05943405</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.20618557</v>
+        <v>0.15662777</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.0998004</v>
+        <v>0.10704754</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00021645</v>
+        <v>0.00024041</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.5</v>
+        <v>39.957362</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02531646</v>
+        <v>0.02502668</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02164502</v>
+        <v>0.02155737</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057637</v>
+        <v>0.00057143</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01560062</v>
+        <v>0.01565352</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05390836</v>
+        <v>0.05943405</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00061728</v>
+        <v>0.00074279</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00070671</v>
+        <v>0.00068671</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07067138000000001</v>
+        <v>0.07141231000000001</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00196078</v>
+        <v>0.00183089</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14124,10 +14124,10 @@
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="E32" s="65" t="n">
-        <v>4.444e-05</v>
+        <v>4.066e-05</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>572</v>
+        <v>571.655665</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00174825</v>
+        <v>0.0017493</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>1320</v>
+        <v>4590.20962</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00075758</v>
+        <v>0.00021785</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>22.6</v>
+        <v>21.127282</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04424779</v>
+        <v>0.04733217</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05390836</v>
+        <v>0.05943405</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34234851</v>
+        <v>0.34364982</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00036765</v>
+        <v>0.00038742</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026882</v>
+        <v>0.00026448</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.001657</v>
+        <v>0.00176786</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.001657</v>
+        <v>0.00176786</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05390836</v>
+        <v>0.05943357</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.03676471</v>
+        <v>0.05110072</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.07352941</v>
+        <v>0.03952179</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>24 March 2026 — 08:49 UTC</t>
+          <t>24 March 2026 — 09:07 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 24 March 2026  |  09:07 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 24 March 2026  |  11:50 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>$1.143/L</t>
+          <t>$1.160/L</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.24</v>
+        <v>45.23</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.55</v>
+        <v>29.19</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1552,7 +1552,7 @@
         <v>0.1055</v>
       </c>
       <c r="O11" s="22" t="n">
-        <v>-0.8071</v>
+        <v>-0.8237</v>
       </c>
       <c r="P11" s="15" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.44</v>
+        <v>276.46</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>379.25</v>
+        <v>375.19</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>597.89</v>
+        <v>591.5</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1615,7 +1615,7 @@
         <v>0.0788</v>
       </c>
       <c r="O12" s="31" t="n">
-        <v>-0.8396</v>
+        <v>-0.8562</v>
       </c>
       <c r="P12" s="24" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,34 +1651,34 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>650.5599999999999</v>
+        <v>694.09</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>1.0006</v>
+        <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>566</v>
+        <v>750.15</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
       </c>
       <c r="N13" s="21" t="n">
-        <v>0.0504</v>
+        <v>0</v>
       </c>
       <c r="O13" s="22" t="n">
-        <v>0.0067</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="P13" s="15" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.03</v>
+        <v>14.86</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>0.9439</v>
+        <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>13.08</v>
+        <v>14.26</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.32</v>
+        <v>17.12</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
       </c>
       <c r="N14" s="30" t="n">
-        <v>0.0609</v>
+        <v>0</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>-0.0584</v>
+        <v>-0.075</v>
       </c>
       <c r="P14" s="24" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,34 +1777,34 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>797.86</v>
+        <v>851.24</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>1.2271</v>
+        <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>694.12</v>
+        <v>710.3200000000001</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>780.61</v>
+        <v>832.83</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
       </c>
       <c r="N15" s="21" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
       <c r="O15" s="22" t="n">
-        <v>0.2671</v>
+        <v>0.2505</v>
       </c>
       <c r="P15" s="15" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3978.07</v>
+        <v>3896.74</v>
       </c>
       <c r="I16" s="27" t="n">
-        <v>1.161</v>
+        <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3460.87</v>
+        <v>3760.96</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4322.37</v>
+        <v>4234</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
       </c>
       <c r="N16" s="30" t="n">
-        <v>0.1332</v>
+        <v>0</v>
       </c>
       <c r="O16" s="31" t="n">
-        <v>0.1911</v>
+        <v>0.1745</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>981.98</v>
+        <v>1047.68</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1218.42</v>
+        <v>1299.94</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1018.18</v>
+        <v>1086.3</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="22" t="n">
-        <v>0.5926</v>
+        <v>0.576</v>
       </c>
       <c r="P17" s="15" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>120.7</v>
+        <v>127.57</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>1.1044</v>
+        <v>1.121</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>105.01</v>
+        <v>112.66</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116</v>
+        <v>122.61</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
       </c>
       <c r="N18" s="30" t="n">
-        <v>0.1171</v>
+        <v>0</v>
       </c>
       <c r="O18" s="31" t="n">
-        <v>0.126</v>
+        <v>0.1094</v>
       </c>
       <c r="P18" s="24" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>785.58</v>
+        <v>838.14</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>683.48</v>
+        <v>729.21</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2056,7 +2056,7 @@
         <v>0.0504</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>0.2454</v>
+        <v>0.2288</v>
       </c>
       <c r="P19" s="15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2395.13</v>
+        <v>2967.77</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>0.9156</v>
+        <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>2083.79</v>
+        <v>2430.84</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2844.84</v>
+        <v>3525</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
       </c>
       <c r="N20" s="30" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="O20" s="31" t="n">
-        <v>-0.091</v>
+        <v>-0.1076</v>
       </c>
       <c r="P20" s="24" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.7</v>
+        <v>21.79</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.3</v>
+        <v>18.52</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>23.02</v>
+        <v>22.09</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2182,7 +2182,7 @@
         <v>0.1521</v>
       </c>
       <c r="O21" s="22" t="n">
-        <v>-0.7094</v>
+        <v>-0.726</v>
       </c>
       <c r="P21" s="15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,34 +2218,34 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.62</v>
+        <v>20.53</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>0.9628</v>
+        <v>1.199</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>16.2</v>
+        <v>22.24</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
       </c>
       <c r="N22" s="30" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
       <c r="O22" s="31" t="n">
-        <v>-0.0367</v>
+        <v>-0.0533</v>
       </c>
       <c r="P22" s="24" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.54</v>
+        <v>103.75</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>130.33</v>
+        <v>109.45</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>163.79</v>
+        <v>137.55</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2308,7 +2308,7 @@
         <v>0.326</v>
       </c>
       <c r="O23" s="22" t="n">
-        <v>-0.3514</v>
+        <v>-0.368</v>
       </c>
       <c r="P23" s="15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>558.47</v>
+        <v>595.84</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>540.09</v>
+        <v>576.22</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>509.09</v>
+        <v>543.15</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2371,7 +2371,7 @@
         <v>0.0504</v>
       </c>
       <c r="O24" s="31" t="n">
-        <v>-0.1561</v>
+        <v>-0.1727</v>
       </c>
       <c r="P24" s="24" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,34 +2407,34 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.74</v>
+        <v>18.23</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>11.08</v>
+        <v>17.27</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.17</v>
+        <v>18.84</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
       </c>
       <c r="N25" s="21" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>0.0175</v>
+        <v>0.0009</v>
       </c>
       <c r="P25" s="15" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11222.97</v>
+        <v>11074.59</v>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1.1139</v>
+        <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>9764.33</v>
+        <v>11599.65</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11220.34</v>
+        <v>11072</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
       </c>
       <c r="N26" s="30" t="n">
-        <v>0.07780000000000001</v>
+        <v>0</v>
       </c>
       <c r="O26" s="31" t="n">
-        <v>0.1369</v>
+        <v>0.1203</v>
       </c>
       <c r="P26" s="24" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,34 +2533,34 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>767.14</v>
+        <v>818.47</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>1.1799</v>
+        <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>667.42</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
       </c>
       <c r="N27" s="21" t="n">
-        <v>0.0504</v>
+        <v>0</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>0.2128</v>
+        <v>0.1962</v>
       </c>
       <c r="P27" s="15" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>165.93</v>
+        <v>167.08</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>1.1139</v>
+        <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>144.36</v>
+        <v>166.91</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>174.96</v>
+        <v>176.18</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
       </c>
       <c r="N28" s="30" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="O28" s="31" t="n">
-        <v>0.1369</v>
+        <v>0.1203</v>
       </c>
       <c r="P28" s="24" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,34 +2659,34 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.16</v>
+        <v>18.92</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0.8873</v>
+        <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>14.93</v>
+        <v>21.44</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
       </c>
       <c r="N29" s="21" t="n">
-        <v>0.0616</v>
+        <v>0</v>
       </c>
       <c r="O29" s="22" t="n">
-        <v>-0.1235</v>
+        <v>-0.1401</v>
       </c>
       <c r="P29" s="15" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>154.23</v>
+        <v>164.18</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>166.1</v>
+        <v>176.81</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>218.69</v>
+        <v>232.8</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2749,7 +2749,7 @@
         <v>0.1458</v>
       </c>
       <c r="O30" s="31" t="n">
-        <v>-0.2971</v>
+        <v>-0.3137</v>
       </c>
       <c r="P30" s="24" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,25 +2785,25 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="K31" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="M31" s="33" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="22" t="n">
-        <v>-1.1125</v>
+        <v>-1.1291</v>
       </c>
       <c r="P31" s="15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4558</v>
+        <v>5062.6</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>6447.26</v>
+        <v>7161</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5407.38</v>
+        <v>6006</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="31" t="n">
-        <v>-0.0476</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="P32" s="24" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4670.88</v>
+        <v>4630.89</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3526.21</v>
+        <v>3496.03</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4199.96</v>
+        <v>4164</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="22" t="n">
-        <v>1.5257</v>
+        <v>1.5091</v>
       </c>
       <c r="P33" s="15" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>730.3200000000001</v>
+        <v>779.1799999999999</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>735.35</v>
+        <v>784.55</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3001,7 +3001,7 @@
         <v>0.0593</v>
       </c>
       <c r="O34" s="31" t="n">
-        <v>0.1477</v>
+        <v>0.1311</v>
       </c>
       <c r="P34" s="24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.36</v>
+        <v>55.14</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>1.0383</v>
+        <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>48.16</v>
+        <v>58.95</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>64.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
       </c>
       <c r="N35" s="21" t="n">
-        <v>0.0698</v>
+        <v>0</v>
       </c>
       <c r="O35" s="22" t="n">
-        <v>0.0501</v>
+        <v>0.0335</v>
       </c>
       <c r="P35" s="15" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>12.94</v>
+        <v>13.88</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>1.2052</v>
+        <v>1.317</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>11.26</v>
+        <v>13.2</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
       </c>
       <c r="N36" s="30" t="n">
-        <v>0.1973</v>
+        <v>0</v>
       </c>
       <c r="O36" s="31" t="n">
-        <v>0.2419</v>
+        <v>0.2253</v>
       </c>
       <c r="P36" s="24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,34 +3163,34 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.31999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>1.0666</v>
+        <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>68.14</v>
+        <v>79.16</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>83.05</v>
+        <v>83.33</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
       </c>
       <c r="N37" s="21" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="O37" s="22" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="P37" s="15" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>18.8</v>
+        <v>20.73</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>0.9723000000000001</v>
+        <v>1.102</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>16.36</v>
+        <v>20.44</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
       </c>
       <c r="N38" s="30" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
       <c r="O38" s="31" t="n">
-        <v>-0.0258</v>
+        <v>-0.0424</v>
       </c>
       <c r="P38" s="24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>754.38</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="22" t="n">
-        <v>-0.0414</v>
+        <v>-0.058</v>
       </c>
       <c r="P39" s="15" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1058.17</v>
+        <v>1273.32</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1329.17</v>
+        <v>1599.43</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>740.45</v>
+        <v>891</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3379,7 +3379,7 @@
         <v>0.7067</v>
       </c>
       <c r="O40" s="31" t="n">
-        <v>-0.3574</v>
+        <v>-0.374</v>
       </c>
       <c r="P40" s="24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,38 +3415,38 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>1.2803</v>
+        <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>1864.39</v>
+        <v>1989.07</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>1.1139</v>
+        <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1622.07</v>
+        <v>1853.65</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2111.5</v>
+        <v>2051.75</v>
       </c>
       <c r="M41" s="20" t="n">
-        <v>0.07780000000000001</v>
+        <v>0.1524</v>
       </c>
       <c r="N41" s="21" t="n">
-        <v>0.07780000000000001</v>
+        <v>0</v>
       </c>
       <c r="O41" s="22" t="n">
-        <v>0.1369</v>
+        <v>0.2457</v>
       </c>
       <c r="P41" s="15" t="inlineStr">
         <is>
-          <t>🟡 MID</t>
+          <t>🔴 HIGH</t>
         </is>
       </c>
       <c r="Q41" s="15" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>865.34</v>
+        <v>923.23</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>1.3309</v>
+        <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>752.83</v>
+        <v>783.34</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>650.51</v>
+        <v>694.02</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
       </c>
       <c r="N42" s="30" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
       <c r="O42" s="31" t="n">
-        <v>0.3864</v>
+        <v>0.3698</v>
       </c>
       <c r="P42" s="24" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,34 +3541,34 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.75</v>
+        <v>19.96</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>1.2271</v>
+        <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>17.18</v>
+        <v>18.82</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.41</v>
+        <v>22.64</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
       </c>
       <c r="N43" s="21" t="n">
-        <v>0.08359999999999999</v>
+        <v>0</v>
       </c>
       <c r="O43" s="22" t="n">
-        <v>0.2671</v>
+        <v>0.2505</v>
       </c>
       <c r="P43" s="15" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,25 +3604,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>35616.69</v>
+        <v>32580</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>33476.73</v>
+        <v>30622.5</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>30746.45</v>
+        <v>28125</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>0.044</v>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="31" t="n">
-        <v>0.3046</v>
+        <v>0.288</v>
       </c>
       <c r="P44" s="24" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.02</v>
+        <v>22.07</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.19</v>
+        <v>25.56</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>22.71</v>
+        <v>25.04</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="O45" s="22" t="n">
-        <v>0.0466</v>
+        <v>0.03</v>
       </c>
       <c r="P45" s="15" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>355.56</v>
+        <v>332.01</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>331.86</v>
+        <v>309.88</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>300.4</v>
+        <v>280.5</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3757,7 +3757,7 @@
         <v>0.0693</v>
       </c>
       <c r="O46" s="31" t="n">
-        <v>-0.4924</v>
+        <v>-0.509</v>
       </c>
       <c r="P46" s="24" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2660.39</v>
+        <v>2803.5</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2612.12</v>
+        <v>2752.64</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3226.43</v>
+        <v>3400</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="22" t="n">
-        <v>-0.1127</v>
+        <v>-0.1293</v>
       </c>
       <c r="P47" s="15" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>638.29</v>
+        <v>680.99</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>0.9817</v>
+        <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>555.3099999999999</v>
+        <v>712.73</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
       </c>
       <c r="N48" s="30" t="n">
-        <v>0.0504</v>
+        <v>0</v>
       </c>
       <c r="O48" s="31" t="n">
-        <v>-0.015</v>
+        <v>-0.0316</v>
       </c>
       <c r="P48" s="24" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
         <v>2.53</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>0.716</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="22" t="n">
-        <v>-0.2734</v>
+        <v>-0.2939</v>
       </c>
       <c r="P49" s="15" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4915.24</v>
+        <v>4836</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="31" t="n">
-        <v>0.2376</v>
+        <v>0.221</v>
       </c>
       <c r="P50" s="24" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,34 +4045,34 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>25.05</v>
+        <v>34.82</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>1.1139</v>
+        <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>21.8</v>
+        <v>27.77</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>25.44</v>
+        <v>35.36</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
       </c>
       <c r="N51" s="21" t="n">
-        <v>0.0077</v>
+        <v>0</v>
       </c>
       <c r="O51" s="22" t="n">
-        <v>0.1369</v>
+        <v>0.1203</v>
       </c>
       <c r="P51" s="15" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>1.5949</v>
+        <v>2.17</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>40.35</v>
+        <v>29.51</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>1.3876</v>
+        <v>2.05</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>35.11</v>
+        <v>27.88</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.22</v>
+        <v>21.08</v>
       </c>
       <c r="M52" s="29" t="n">
-        <v>0.1786</v>
+        <v>0.391</v>
       </c>
       <c r="N52" s="30" t="n">
-        <v>0.1786</v>
+        <v>0.3487</v>
       </c>
       <c r="O52" s="31" t="n">
-        <v>0.4515</v>
+        <v>1.01</v>
       </c>
       <c r="P52" s="24" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 09:07 UTC</t>
+          <t>2026-03-24 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.4</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.4</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.4</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>351.56</v>
+        <v>347.8</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>351.56</v>
+        <v>347.8</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>351.56</v>
+        <v>347.8</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>597.89</v>
+        <v>591.5</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,55 +4499,55 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="L5" s="18" t="n">
-        <v>0.9526</v>
+        <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>538.84</v>
+        <v>750.15</v>
       </c>
       <c r="N5" s="18" t="n">
-        <v>0.9526</v>
+        <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>538.84</v>
+        <v>750.15</v>
       </c>
       <c r="P5" s="18" t="n">
-        <v>0.9526</v>
+        <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>538.84</v>
+        <v>750.15</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U5" s="37" t="n">
-        <v>0.0504</v>
+      <c r="U5" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V5" s="15" t="n">
         <v>91</v>
@@ -4570,55 +4570,55 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="L6" s="27" t="n">
-        <v>0.8897</v>
+        <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>12.32</v>
+        <v>14.26</v>
       </c>
       <c r="N6" s="27" t="n">
-        <v>0.8897</v>
+        <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>12.32</v>
+        <v>14.26</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>0.8897</v>
+        <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>12.32</v>
+        <v>14.26</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.32</v>
+        <v>17.12</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
       </c>
-      <c r="U6" s="39" t="n">
-        <v>0.0609</v>
+      <c r="U6" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V6" s="24" t="n">
         <v>93</v>
@@ -4641,55 +4641,55 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>1.1683</v>
+        <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>660.86</v>
+        <v>710.3200000000001</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>1.1683</v>
+        <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>660.86</v>
+        <v>710.3200000000001</v>
       </c>
       <c r="P7" s="18" t="n">
-        <v>1.1683</v>
+        <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>660.86</v>
+        <v>710.3200000000001</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>780.61</v>
+        <v>832.83</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U7" s="37" t="n">
-        <v>0.0503</v>
+      <c r="U7" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V7" s="15" t="n">
         <v>91</v>
@@ -4712,55 +4712,55 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>1.0245</v>
+        <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3053.98</v>
+        <v>3760.96</v>
       </c>
       <c r="N8" s="27" t="n">
-        <v>1.0245</v>
+        <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3053.98</v>
+        <v>3760.96</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>1.0245</v>
+        <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3053.98</v>
+        <v>3760.96</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4322.37</v>
+        <v>4234</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
       </c>
-      <c r="U8" s="39" t="n">
-        <v>0.1332</v>
+      <c r="U8" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V8" s="24" t="n">
         <v>91</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1218.42</v>
+        <v>1299.94</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1218.42</v>
+        <v>1299.94</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1218.42</v>
+        <v>1299.94</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1018.18</v>
+        <v>1086.3</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,55 +4854,55 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="L10" s="27" t="n">
-        <v>0.9886</v>
+        <v>1.121</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>94</v>
+        <v>112.66</v>
       </c>
       <c r="N10" s="27" t="n">
-        <v>0.9886</v>
+        <v>1.121</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>94</v>
+        <v>112.66</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>0.9886</v>
+        <v>1.121</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>94</v>
+        <v>112.66</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116</v>
+        <v>122.61</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
       </c>
-      <c r="U10" s="39" t="n">
-        <v>0.1171</v>
+      <c r="U10" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V10" s="24" t="n">
         <v>91</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>650.67</v>
+        <v>694.21</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>650.67</v>
+        <v>694.21</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>650.67</v>
+        <v>694.21</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,55 +4996,55 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="L12" s="27" t="n">
-        <v>0.8088</v>
+        <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1840.73</v>
+        <v>2430.84</v>
       </c>
       <c r="N12" s="27" t="n">
-        <v>0.8088</v>
+        <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1840.73</v>
+        <v>2430.84</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>0.8088</v>
+        <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1840.73</v>
+        <v>2430.84</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2844.84</v>
+        <v>3525</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
       </c>
-      <c r="U12" s="39" t="n">
-        <v>0.132</v>
+      <c r="U12" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V12" s="24" t="n">
         <v>91</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.07</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.07</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.07</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>23.02</v>
+        <v>22.09</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,55 +5138,55 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="L14" s="27" t="n">
-        <v>0.9167</v>
+        <v>1.199</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>15.42</v>
+        <v>22.24</v>
       </c>
       <c r="N14" s="27" t="n">
-        <v>0.9167</v>
+        <v>1.199</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>15.42</v>
+        <v>22.24</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>0.9167</v>
+        <v>1.199</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>15.42</v>
+        <v>22.24</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U14" s="39" t="n">
-        <v>0.0503</v>
+      <c r="U14" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V14" s="24" t="n">
         <v>93</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>163.79</v>
+        <v>137.55</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>548.58</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>548.58</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>548.58</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>509.09</v>
+        <v>543.15</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,55 +5351,55 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>0.9616</v>
+        <v>1.1</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>10.55</v>
+        <v>17.27</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>0.9616</v>
+        <v>1.1</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>10.55</v>
+        <v>17.27</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>0.9616</v>
+        <v>1.1</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>10.55</v>
+        <v>17.27</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.17</v>
+        <v>18.84</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U17" s="37" t="n">
-        <v>0.0503</v>
+      <c r="U17" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V17" s="15" t="n">
         <v>91</v>
@@ -5422,55 +5422,55 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="L18" s="27" t="n">
-        <v>1.0335</v>
+        <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>9059.549999999999</v>
+        <v>11599.65</v>
       </c>
       <c r="N18" s="27" t="n">
-        <v>1.0335</v>
+        <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>9059.549999999999</v>
+        <v>11599.65</v>
       </c>
       <c r="P18" s="27" t="n">
-        <v>1.0335</v>
+        <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>9059.549999999999</v>
+        <v>11599.65</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11220.34</v>
+        <v>11072</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
       </c>
-      <c r="U18" s="39" t="n">
-        <v>0.07780000000000001</v>
+      <c r="U18" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V18" s="24" t="n">
         <v>91</v>
@@ -5493,55 +5493,55 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>1.1233</v>
+        <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>635.4</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>1.1233</v>
+        <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>635.4</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="P19" s="18" t="n">
-        <v>1.1233</v>
+        <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>635.4</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U19" s="37" t="n">
-        <v>0.0504</v>
+      <c r="U19" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V19" s="15" t="n">
         <v>91</v>
@@ -5564,55 +5564,55 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="L20" s="27" t="n">
-        <v>1.0604</v>
+        <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>137.43</v>
+        <v>166.91</v>
       </c>
       <c r="N20" s="27" t="n">
-        <v>1.0604</v>
+        <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>137.43</v>
+        <v>166.91</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>1.0604</v>
+        <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>137.43</v>
+        <v>166.91</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>174.96</v>
+        <v>176.18</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
       </c>
-      <c r="U20" s="39" t="n">
-        <v>0.0505</v>
+      <c r="U20" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V20" s="24" t="n">
         <v>93</v>
@@ -5635,55 +5635,55 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>0.8358</v>
+        <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>14.06</v>
+        <v>21.44</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>0.8358</v>
+        <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>14.06</v>
+        <v>21.44</v>
       </c>
       <c r="P21" s="18" t="n">
-        <v>0.8358</v>
+        <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>14.06</v>
+        <v>21.44</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
       </c>
-      <c r="U21" s="37" t="n">
-        <v>0.0616</v>
+      <c r="U21" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V21" s="15" t="n">
         <v>93</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>144.96</v>
+        <v>154.31</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>144.96</v>
+        <v>154.31</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>144.96</v>
+        <v>154.31</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>218.69</v>
+        <v>232.8</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,49 +5777,49 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="N23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="O23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="T23" s="40" t="n">
         <v>0</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>6447.26</v>
+        <v>7161</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>6447.26</v>
+        <v>7161</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>6447.26</v>
+        <v>7161</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5407.38</v>
+        <v>6006</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3526.21</v>
+        <v>3496.03</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3526.21</v>
+        <v>3496.03</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3526.21</v>
+        <v>3496.03</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4199.96</v>
+        <v>4164</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>639.95</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>639.95</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>639.95</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>735.35</v>
+        <v>784.55</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,55 +6061,55 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>0.9706</v>
+        <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>45.02</v>
+        <v>58.95</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>0.9706</v>
+        <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>45.02</v>
+        <v>58.95</v>
       </c>
       <c r="P27" s="18" t="n">
-        <v>0.9706</v>
+        <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>45.02</v>
+        <v>58.95</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>64.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
       </c>
-      <c r="U27" s="37" t="n">
-        <v>0.0698</v>
+      <c r="U27" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V27" s="15" t="n">
         <v>95</v>
@@ -6132,55 +6132,55 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="L28" s="27" t="n">
-        <v>1.0066</v>
+        <v>1.317</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>9.4</v>
+        <v>13.2</v>
       </c>
       <c r="N28" s="27" t="n">
-        <v>1.0066</v>
+        <v>1.317</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>9.4</v>
+        <v>13.2</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>1.0066</v>
+        <v>1.317</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>9.4</v>
+        <v>13.2</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
       </c>
-      <c r="U28" s="39" t="n">
-        <v>0.1973</v>
+      <c r="U28" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V28" s="24" t="n">
         <v>95</v>
@@ -6203,55 +6203,55 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>0.9886</v>
+        <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>63.16</v>
+        <v>79.16</v>
       </c>
       <c r="N29" s="18" t="n">
-        <v>0.9886</v>
+        <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>63.16</v>
+        <v>79.16</v>
       </c>
       <c r="P29" s="18" t="n">
-        <v>0.9886</v>
+        <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>63.16</v>
+        <v>79.16</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>83.05</v>
+        <v>83.33</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
       </c>
-      <c r="U29" s="37" t="n">
-        <v>0.0789</v>
+      <c r="U29" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V29" s="15" t="n">
         <v>91</v>
@@ -6274,55 +6274,55 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="L30" s="27" t="n">
-        <v>0.9257</v>
+        <v>1.102</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>15.58</v>
+        <v>20.44</v>
       </c>
       <c r="N30" s="27" t="n">
-        <v>0.9257</v>
+        <v>1.102</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>15.58</v>
+        <v>20.44</v>
       </c>
       <c r="P30" s="27" t="n">
-        <v>0.9257</v>
+        <v>1.102</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>15.58</v>
+        <v>20.44</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
       </c>
-      <c r="U30" s="39" t="n">
-        <v>0.0503</v>
+      <c r="U30" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V30" s="24" t="n">
         <v>93</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>754.38</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>681.48</v>
+        <v>820.04</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>722.41</v>
+        <v>869.29</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>749.6</v>
+        <v>902.02</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>937.17</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>937.17</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>937.17</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>740.45</v>
+        <v>891</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,55 +6487,55 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1726.02</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1726.02</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1726.02</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>1.0335</v>
+        <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1504.99</v>
+        <v>1853.65</v>
       </c>
       <c r="N33" s="18" t="n">
-        <v>1.0335</v>
+        <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1504.99</v>
+        <v>1853.65</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>1.0335</v>
+        <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1504.99</v>
+        <v>1853.65</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2111.5</v>
+        <v>2051.75</v>
       </c>
       <c r="T33" s="37" t="n">
-        <v>0.07780000000000001</v>
-      </c>
-      <c r="U33" s="37" t="n">
-        <v>0.07780000000000001</v>
+        <v>0.1524</v>
+      </c>
+      <c r="U33" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V33" s="15" t="n">
         <v>91</v>
@@ -6558,55 +6558,55 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="L34" s="27" t="n">
-        <v>1.2672</v>
+        <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>716.8</v>
+        <v>783.34</v>
       </c>
       <c r="N34" s="27" t="n">
-        <v>1.2672</v>
+        <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>716.8</v>
+        <v>783.34</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>1.2672</v>
+        <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>716.8</v>
+        <v>783.34</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>650.51</v>
+        <v>694.02</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
       </c>
-      <c r="U34" s="39" t="n">
-        <v>0.0503</v>
+      <c r="U34" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V34" s="24" t="n">
         <v>91</v>
@@ -6629,55 +6629,55 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>1.1324</v>
+        <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>15.86</v>
+        <v>18.82</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>1.1324</v>
+        <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>15.86</v>
+        <v>18.82</v>
       </c>
       <c r="P35" s="18" t="n">
-        <v>1.1324</v>
+        <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>15.86</v>
+        <v>18.82</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.41</v>
+        <v>22.64</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
       </c>
-      <c r="U35" s="37" t="n">
-        <v>0.08359999999999999</v>
+      <c r="U35" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="V35" s="15" t="n">
         <v>95</v>
@@ -6700,49 +6700,49 @@
         </is>
       </c>
       <c r="E36" s="38" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.387</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>34116.26</v>
+        <v>31207.5</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.3925</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>34251.54</v>
+        <v>31331.25</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.3981</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>34389.29</v>
+        <v>31457.25</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>33476.73</v>
+        <v>30622.5</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>33476.73</v>
+        <v>30622.5</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>33476.73</v>
+        <v>30622.5</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>30746.45</v>
+        <v>28125</v>
       </c>
       <c r="T36" s="39" t="n">
         <v>0.044</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>20.02</v>
+        <v>22.07</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>20.02</v>
+        <v>22.07</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>20.02</v>
+        <v>22.07</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.55</v>
+        <v>23.76</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.55</v>
+        <v>23.76</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.55</v>
+        <v>23.76</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>22.71</v>
+        <v>25.04</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>310.34</v>
+        <v>289.78</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>310.34</v>
+        <v>289.78</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>310.34</v>
+        <v>289.78</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>300.4</v>
+        <v>280.5</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2612.12</v>
+        <v>2752.64</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2612.12</v>
+        <v>2752.64</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2612.12</v>
+        <v>2752.64</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3226.43</v>
+        <v>3400</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,55 +6984,55 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="L40" s="27" t="n">
-        <v>0.9346</v>
+        <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>528.66</v>
+        <v>712.73</v>
       </c>
       <c r="N40" s="27" t="n">
-        <v>0.9346</v>
+        <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>528.66</v>
+        <v>712.73</v>
       </c>
       <c r="P40" s="27" t="n">
-        <v>0.9346</v>
+        <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>528.66</v>
+        <v>712.73</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
       </c>
-      <c r="U40" s="39" t="n">
-        <v>0.0504</v>
+      <c r="U40" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="V40" s="24" t="n">
         <v>91</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
         <v>2.53</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
         <v>2.53</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
         <v>2.53</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>0.716</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>0.716</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.716</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4915.24</v>
+        <v>4836</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,55 +7197,55 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>1.1054</v>
+        <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>21.63</v>
+        <v>27.77</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>1.1054</v>
+        <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>21.63</v>
+        <v>27.77</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>1.1054</v>
+        <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>21.63</v>
+        <v>27.77</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>25.44</v>
+        <v>35.36</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
       </c>
       <c r="U43" s="40" t="n">
-        <v>0.0077</v>
+        <v>0</v>
       </c>
       <c r="V43" s="15" t="n">
         <v>93</v>
@@ -7268,55 +7268,55 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>34.24</v>
+        <v>21.22</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>34.24</v>
+        <v>21.22</v>
       </c>
       <c r="J44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>34.24</v>
+        <v>21.22</v>
       </c>
       <c r="L44" s="27" t="n">
-        <v>1.1773</v>
+        <v>1.52</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>29.79</v>
+        <v>20.67</v>
       </c>
       <c r="N44" s="27" t="n">
-        <v>1.1773</v>
+        <v>1.52</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>29.79</v>
+        <v>20.67</v>
       </c>
       <c r="P44" s="27" t="n">
-        <v>1.1773</v>
+        <v>1.52</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>29.79</v>
+        <v>20.67</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.22</v>
+        <v>21.08</v>
       </c>
       <c r="T44" s="39" t="n">
-        <v>0.1786</v>
+        <v>0.391</v>
       </c>
       <c r="U44" s="39" t="n">
-        <v>0.1786</v>
+        <v>0.3487</v>
       </c>
       <c r="V44" s="24" t="n">
         <v>91</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.12</v>
+        <v>43.07</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.01</v>
+        <v>263.17</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>619.39</v>
+        <v>660.83</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.01</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>759.62</v>
+        <v>810.4400000000001</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3438.59</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>934.92</v>
+        <v>997.46</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.05</v>
+        <v>114.2</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>747.91</v>
+        <v>797.95</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2621.75</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.53</v>
+        <v>19.7</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>17.73</v>
+        <v>19.55</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>531.72</v>
+        <v>567.29</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.13</v>
+        <v>17.35</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10413</v>
+        <v>10275.33</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>730.38</v>
+        <v>779.24</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>157.97</v>
+        <v>159.07</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.16</v>
+        <v>17.82</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>133.66</v>
+        <v>142.28</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.0309</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4486.02</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4301.41</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>689.48</v>
+        <v>735.61</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>10.81</v>
+        <v>11.59</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.84</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>17.9</v>
+        <v>19.74</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>681.48</v>
+        <v>820.04</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,46 +9253,46 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1729.83</v>
+        <v>1726.02</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>1.1879</v>
+        <v>1.2198</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>1.2272</v>
+        <v>1.2721</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>1.2272</v>
+        <v>1.2721</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>1.2272</v>
+        <v>1.2721</v>
       </c>
       <c r="N33" s="18" t="n">
-        <v>1.2272</v>
+        <v>1.2721</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>1.2803</v>
+        <v>1.4057</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>1.2803</v>
+        <v>1.4057</v>
       </c>
       <c r="Q33" s="18" t="n">
-        <v>1.2803</v>
+        <v>1.4057</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.2803</v>
+        <v>1.4057</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>823.88</v>
+        <v>879</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.42</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>34116.26</v>
+        <v>31207.5</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.387</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>20.02</v>
+        <v>22.07</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9507,16 +9507,16 @@
         <v>1.19</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>1.19</v>
+        <v>1.1856</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>1.19</v>
+        <v>1.1856</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>1.19</v>
+        <v>1.1856</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>1.19</v>
+        <v>1.1856</v>
       </c>
       <c r="O37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>332.9</v>
+        <v>310.85</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2556.8</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>648.34</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,46 +9725,46 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="F41" s="19" t="n">
         <v>2.53</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.86</v>
+        <v>34.56</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,46 +9902,46 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>34.24</v>
+        <v>21.22</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="J44" s="27" t="n">
-        <v>1.3532</v>
+        <v>1.56</v>
       </c>
       <c r="K44" s="27" t="n">
-        <v>1.5288</v>
+        <v>1.56</v>
       </c>
       <c r="L44" s="27" t="n">
-        <v>1.5288</v>
+        <v>1.56</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.5288</v>
+        <v>1.56</v>
       </c>
       <c r="N44" s="27" t="n">
-        <v>1.5288</v>
+        <v>1.56</v>
       </c>
       <c r="O44" s="27" t="n">
-        <v>1.5949</v>
+        <v>1.71</v>
       </c>
       <c r="P44" s="27" t="n">
-        <v>1.5949</v>
+        <v>1.71</v>
       </c>
       <c r="Q44" s="27" t="n">
-        <v>1.5949</v>
+        <v>2.17</v>
       </c>
       <c r="R44" s="27" t="n">
-        <v>1.5949</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="47">
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.0633</v>
+        <v>1.0688</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9802</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="49">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.0641</v>
+        <v>1.0697</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9802</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="50">
@@ -9994,10 +9994,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.0647</v>
+        <v>1.0703</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9802</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="51">
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.0678</v>
+        <v>1.0734</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9802</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="52">
@@ -10020,10 +10020,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.0968</v>
+        <v>1.0984</v>
       </c>
       <c r="D52" t="n">
-        <v>1.0126</v>
+        <v>1.0999</v>
       </c>
     </row>
     <row r="53">
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.0973</v>
+        <v>1.0989</v>
       </c>
       <c r="D53" t="n">
-        <v>1.0126</v>
+        <v>1.0999</v>
       </c>
     </row>
     <row r="54">
@@ -10046,10 +10046,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.0974</v>
+        <v>1.099</v>
       </c>
       <c r="D54" t="n">
-        <v>1.0126</v>
+        <v>1.0999</v>
       </c>
     </row>
     <row r="55">
@@ -10059,10 +10059,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.0979</v>
+        <v>1.0995</v>
       </c>
       <c r="D55" t="n">
-        <v>1.0126</v>
+        <v>1.0999</v>
       </c>
     </row>
     <row r="56">
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.138</v>
+        <v>1.1437</v>
       </c>
       <c r="D56" t="n">
-        <v>1.0458</v>
+        <v>1.1155</v>
       </c>
     </row>
     <row r="57">
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.1384</v>
+        <v>1.144</v>
       </c>
       <c r="D57" t="n">
-        <v>1.0458</v>
+        <v>1.1155</v>
       </c>
     </row>
     <row r="58">
@@ -10098,10 +10098,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.1431</v>
+        <v>1.1597</v>
       </c>
       <c r="D58" t="n">
-        <v>1.0489</v>
+        <v>1.1221</v>
       </c>
     </row>
     <row r="59">
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.1434</v>
+        <v>1.16</v>
       </c>
       <c r="D59" t="n">
-        <v>1.0489</v>
+        <v>1.1221</v>
       </c>
     </row>
   </sheetData>
@@ -10244,31 +10244,31 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.24</v>
+        <v>45.23</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.55</v>
+        <v>29.19</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>40.78</v>
+        <v>41.7</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
       </c>
       <c r="L5" s="43" t="n">
-        <v>-0.2816</v>
+        <v>-0.281</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -10283,31 +10283,31 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.7</v>
+        <v>21.79</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.3</v>
+        <v>18.52</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>23.02</v>
+        <v>22.09</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
       </c>
       <c r="L6" s="44" t="n">
-        <v>-0.1839</v>
+        <v>-0.1833</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -10322,31 +10322,31 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="43" t="n">
-        <v>-0.587</v>
+        <v>-0.5864</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -10361,31 +10361,31 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>12.94</v>
+        <v>13.88</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>1.2052</v>
+        <v>1.317</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>11.26</v>
+        <v>13.2</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>5.6</v>
+        <v>6.01</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
       </c>
       <c r="L8" s="45" t="n">
-        <v>0.7674</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -10400,31 +10400,31 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>355.56</v>
+        <v>332.01</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>331.86</v>
+        <v>309.88</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>300.4</v>
+        <v>280.5</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="L9" s="46" t="n">
-        <v>0.0331</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -10439,37 +10439,37 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
         <v>2.53</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>0.716</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="45" t="n">
-        <v>0.2521</v>
+        <v>0.2488</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="B11" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg North Africa: Gas $0.618/L · Die $0.524/L</t>
+          <t xml:space="preserve">  Avg North Africa: Gas $0.617/L · Die $0.550/L</t>
         </is>
       </c>
     </row>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>650.5599999999999</v>
+        <v>694.09</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>1.0006</v>
+        <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>566</v>
+        <v>750.15</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>797.86</v>
+        <v>851.24</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>1.2271</v>
+        <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>694.12</v>
+        <v>710.3200000000001</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>780.61</v>
+        <v>832.83</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>120.7</v>
+        <v>127.57</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>1.1044</v>
+        <v>1.121</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>105.01</v>
+        <v>112.66</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116</v>
+        <v>122.61</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.74</v>
+        <v>18.23</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>11.08</v>
+        <v>17.27</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.17</v>
+        <v>18.84</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11222.97</v>
+        <v>11074.59</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>1.1139</v>
+        <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>9764.33</v>
+        <v>11599.65</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11220.34</v>
+        <v>11072</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>767.14</v>
+        <v>818.47</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>1.1799</v>
+        <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>667.42</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>154.23</v>
+        <v>164.18</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>166.1</v>
+        <v>176.81</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>218.69</v>
+        <v>232.8</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>730.3200000000001</v>
+        <v>779.1799999999999</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>635.4</v>
+        <v>677.91</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>735.35</v>
+        <v>784.55</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>623.35</v>
+        <v>665.0599999999999</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>566.79</v>
+        <v>604.71</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>754.38</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1058.17</v>
+        <v>1273.32</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1329.17</v>
+        <v>1599.43</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>740.45</v>
+        <v>891</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>865.34</v>
+        <v>923.23</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>1.3309</v>
+        <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>752.83</v>
+        <v>783.34</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>650.51</v>
+        <v>694.02</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -10978,25 +10978,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>35616.69</v>
+        <v>32580</v>
       </c>
       <c r="G27" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>33476.73</v>
+        <v>30622.5</v>
       </c>
       <c r="I27" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="28" t="n">
-        <v>30746.45</v>
+        <v>28125</v>
       </c>
       <c r="K27" s="39" t="n">
         <v>0.044</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>638.29</v>
+        <v>680.99</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.9817</v>
+        <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>555.3099999999999</v>
+        <v>712.73</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>622.22</v>
+        <v>663.85</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11047,7 +11047,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg West Africa: Gas $1.212/L · Die $1.103/L</t>
+          <t xml:space="preserve">  Avg West Africa: Gas $1.212/L · Die $1.155/L</t>
         </is>
       </c>
     </row>
@@ -11127,31 +11127,31 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3978.07</v>
+        <v>3896.74</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>1.161</v>
+        <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3460.87</v>
+        <v>3760.96</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4322.37</v>
+        <v>4234</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
       </c>
       <c r="L34" s="43" t="n">
-        <v>-0.0123</v>
+        <v>-0.0248</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -11166,31 +11166,31 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.54</v>
+        <v>103.75</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>130.33</v>
+        <v>109.45</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>163.79</v>
+        <v>137.55</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
       </c>
       <c r="L35" s="44" t="n">
-        <v>-0.5548</v>
+        <v>-0.5673</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -11205,31 +11205,31 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>165.93</v>
+        <v>167.08</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>1.1139</v>
+        <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>144.36</v>
+        <v>166.91</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>174.96</v>
+        <v>176.18</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
       </c>
       <c r="L36" s="43" t="n">
-        <v>-0.0665</v>
+        <v>-0.079</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
@@ -11244,31 +11244,31 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4558</v>
+        <v>5062.6</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>6447.26</v>
+        <v>7161</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5407.38</v>
+        <v>6006</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
       </c>
       <c r="L37" s="44" t="n">
-        <v>-0.251</v>
+        <v>-0.2635</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -11283,31 +11283,31 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4670.88</v>
+        <v>4630.89</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3526.21</v>
+        <v>3496.03</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4199.96</v>
+        <v>4164</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
       </c>
       <c r="L38" s="46" t="n">
-        <v>1.3223</v>
+        <v>1.3098</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
@@ -11322,31 +11322,31 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.36</v>
+        <v>55.14</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>1.0383</v>
+        <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>48.16</v>
+        <v>58.95</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
       </c>
       <c r="L39" s="44" t="n">
-        <v>-0.1533</v>
+        <v>-0.1658</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -11361,31 +11361,31 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>1.2803</v>
+        <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>1864.39</v>
+        <v>1989.07</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>1.1139</v>
+        <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1622.07</v>
+        <v>1853.65</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2111.5</v>
+        <v>2051.75</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>0.07780000000000001</v>
-      </c>
-      <c r="L40" s="43" t="n">
-        <v>-0.0665</v>
+        <v>0.1524</v>
+      </c>
+      <c r="L40" s="46" t="n">
+        <v>0.0464</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
@@ -11400,31 +11400,31 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.75</v>
+        <v>19.96</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>1.2271</v>
+        <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>17.18</v>
+        <v>18.82</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.41</v>
+        <v>22.64</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
       </c>
       <c r="L41" s="45" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
@@ -11439,31 +11439,31 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2660.39</v>
+        <v>2803.5</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2612.12</v>
+        <v>2752.64</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3226.43</v>
+        <v>3400</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
       </c>
       <c r="L42" s="43" t="n">
-        <v>-0.3161</v>
+        <v>-0.3286</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
@@ -11478,37 +11478,37 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5221.49</v>
+        <v>5137.32</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4348.09</v>
+        <v>4278</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4915.24</v>
+        <v>4836</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="45" t="n">
-        <v>0.0342</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="B44" s="51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg East Africa: Gas $1.347/L · Die $1.222/L</t>
+          <t xml:space="preserve">  Avg East Africa: Gas $1.359/L · Die $1.305/L</t>
         </is>
       </c>
     </row>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>981.98</v>
+        <v>1047.68</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1218.42</v>
+        <v>1299.94</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1018.18</v>
+        <v>1086.3</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>785.58</v>
+        <v>838.14</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>683.48</v>
+        <v>729.21</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>678.79</v>
+        <v>724.2</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2395.13</v>
+        <v>2967.77</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.9156</v>
+        <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>2083.79</v>
+        <v>2430.84</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2844.84</v>
+        <v>3525</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>558.47</v>
+        <v>595.84</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>540.09</v>
+        <v>576.22</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>509.09</v>
+        <v>543.15</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11735,7 +11735,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="B53" s="53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg Central Africa: Gas $1.291/L · Die $1.308/L</t>
+          <t xml:space="preserve">  Avg Central Africa: Gas $1.291/L · Die $1.295/L</t>
         </is>
       </c>
     </row>
@@ -11815,31 +11815,31 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>279.44</v>
+        <v>276.46</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>379.25</v>
+        <v>375.19</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>597.89</v>
+        <v>591.5</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
       </c>
       <c r="L58" s="43" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.8628</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
@@ -11854,31 +11854,31 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15.03</v>
+        <v>14.86</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>0.9439</v>
+        <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>13.08</v>
+        <v>14.26</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.32</v>
+        <v>17.12</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
       </c>
       <c r="L59" s="44" t="n">
-        <v>-0.0177</v>
+        <v>-0.08160000000000001</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
@@ -11893,31 +11893,31 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.62</v>
+        <v>20.53</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.9628</v>
+        <v>1.199</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>16.2</v>
+        <v>22.24</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
       </c>
-      <c r="L60" s="46" t="n">
-        <v>0.004</v>
+      <c r="L60" s="43" t="n">
+        <v>-0.0599</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
@@ -11932,31 +11932,31 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.16</v>
+        <v>18.92</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>0.8873</v>
+        <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>14.93</v>
+        <v>21.44</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
       </c>
       <c r="L61" s="44" t="n">
-        <v>-0.0828</v>
+        <v>-0.1467</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
@@ -11971,31 +11971,31 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.31999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>1.0666</v>
+        <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>68.14</v>
+        <v>79.16</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>83.05</v>
+        <v>83.33</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
       </c>
       <c r="L62" s="46" t="n">
-        <v>0.1233</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -12010,31 +12010,31 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>18.8</v>
+        <v>20.73</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>0.9723000000000001</v>
+        <v>1.102</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>16.36</v>
+        <v>20.44</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.03</v>
+        <v>23.19</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
       </c>
-      <c r="L63" s="45" t="n">
-        <v>0.0149</v>
+      <c r="L63" s="44" t="n">
+        <v>-0.049</v>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
@@ -12049,31 +12049,31 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>20.02</v>
+        <v>22.07</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.19</v>
+        <v>25.56</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>22.71</v>
+        <v>25.04</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="46" t="n">
-        <v>0.0873</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
@@ -12088,31 +12088,31 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>25.05</v>
+        <v>34.82</v>
       </c>
       <c r="G65" s="27" t="n">
-        <v>1.1139</v>
+        <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>21.8</v>
+        <v>27.77</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>25.44</v>
+        <v>35.36</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
       </c>
       <c r="L65" s="45" t="n">
-        <v>0.1776</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
@@ -12127,37 +12127,37 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>1.5949</v>
+        <v>2.17</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>40.35</v>
+        <v>29.51</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>1.3876</v>
+        <v>2.05</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>35.11</v>
+        <v>27.88</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.22</v>
+        <v>21.08</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>0.1786</v>
+        <v>0.391</v>
       </c>
       <c r="L66" s="46" t="n">
-        <v>0.4922</v>
+        <v>1.0034</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Avg Southern Africa: Gas $1.103/L · Die $1.014/L</t>
+          <t xml:space="preserve">  Avg Southern Africa: Gas $1.167/L · Die $1.177/L</t>
         </is>
       </c>
     </row>
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.618</v>
+        <v>0.617</v>
       </c>
       <c r="D72" t="n">
-        <v>0.524</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="73">
@@ -12201,7 +12201,7 @@
         <v>1.212</v>
       </c>
       <c r="D73" t="n">
-        <v>1.103</v>
+        <v>1.155</v>
       </c>
     </row>
     <row r="74">
@@ -12211,10 +12211,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.347</v>
+        <v>1.359</v>
       </c>
       <c r="D74" t="n">
-        <v>1.222</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="75">
@@ -12227,7 +12227,7 @@
         <v>1.291</v>
       </c>
       <c r="D75" t="n">
-        <v>1.308</v>
+        <v>1.295</v>
       </c>
     </row>
     <row r="76">
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.103</v>
+        <v>1.167</v>
       </c>
       <c r="D76" t="n">
-        <v>1.014</v>
+        <v>1.177</v>
       </c>
     </row>
   </sheetData>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4670.88</v>
+        <v>4630.89</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>0.0309</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
@@ -12441,27 +12441,27 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="E6" s="60" t="n">
-        <v>1.736</v>
+        <v>2.17</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>981.98</v>
+        <v>29.51</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="H6" s="41" t="n">
-        <v>0.0503</v>
+        <v>0.391</v>
       </c>
       <c r="J6" s="24" t="n">
         <v>2</v>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.44</v>
+        <v>276.46</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12497,27 +12497,27 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="E7" s="58" t="n">
-        <v>1.5949</v>
+        <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>40.35</v>
+        <v>1047.68</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="H7" s="40" t="n">
-        <v>0.1786</v>
+        <v>0.0503</v>
       </c>
       <c r="J7" s="15" t="n">
         <v>3</v>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.24</v>
+        <v>45.23</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>865.34</v>
+        <v>923.23</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.7</v>
+        <v>21.79</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>1.448</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>35616.69</v>
+        <v>32580</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>355.56</v>
+        <v>332.01</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>797.86</v>
+        <v>851.24</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1058.17</v>
+        <v>1273.32</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.75</v>
+        <v>19.96</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.54</v>
+        <v>103.75</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12777,27 +12777,27 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="E12" s="60" t="n">
-        <v>1.3888</v>
+        <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>785.58</v>
+        <v>1989.07</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="H12" s="41" t="n">
-        <v>0.0504</v>
+        <v>0.1524</v>
       </c>
       <c r="J12" s="24" t="n">
         <v>8</v>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>154.23</v>
+        <v>164.18</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12833,27 +12833,27 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="E13" s="58" t="n">
-        <v>1.3853</v>
+        <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>12.94</v>
+        <v>838.14</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="H13" s="40" t="n">
-        <v>0.1973</v>
+        <v>0.0504</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>9</v>
@@ -12869,7 +12869,7 @@
         </is>
       </c>
       <c r="M13" s="59" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
         <v>2.53</v>
@@ -12889,27 +12889,27 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="E14" s="60" t="n">
-        <v>1.381</v>
+        <v>1.3853</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>5221.49</v>
+        <v>13.88</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="H14" s="41" t="n">
-        <v>0</v>
+        <v>0.1973</v>
       </c>
       <c r="J14" s="24" t="n">
         <v>10</v>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>558.47</v>
+        <v>595.84</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -12964,21 +12964,21 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.736</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.5949</v>
+        <v>1.736</v>
       </c>
     </row>
     <row r="22">
@@ -13024,77 +13024,77 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3888</v>
+        <v>1.4057</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.3853</v>
+        <v>1.3888</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.381</v>
+        <v>1.3853</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.3562</v>
+        <v>1.381</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.3345</v>
+        <v>1.3562</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.2911</v>
+        <v>1.3345</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.2803</v>
+        <v>1.2911</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -13104,7 +13104,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.87</v>
+        <v>0.8661</v>
       </c>
     </row>
     <row r="53">
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>919.82965</v>
+        <v>910</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108716</v>
+        <v>0.0010989</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2920</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033546</v>
+        <v>0.00034247</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.852778</v>
+        <v>13.7</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07218769</v>
+        <v>0.07299269999999999</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2820</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00043939</v>
+        <v>0.00035461</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.08570400000001</v>
+        <v>100.5</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01051683</v>
+        <v>0.009950250000000001</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>177.721</v>
+        <v>177.7</v>
       </c>
       <c r="E8" s="65" t="n">
-        <v>0.0056268</v>
+        <v>0.00562746</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>131.547186</v>
+        <v>134.5</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00760183</v>
+        <v>0.00743494</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.308227</v>
+        <v>50.2</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01911745</v>
+        <v>0.01992032</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.989306</v>
+        <v>131</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.0064107</v>
+        <v>0.00763359</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.974209</v>
+        <v>15.7</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09112273999999999</v>
+        <v>0.06369427</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.188785</v>
+        <v>73</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347913</v>
+        <v>0.01369863</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8765.893312</v>
+        <v>8650</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011408</v>
+        <v>0.00011561</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.599611</v>
+        <v>130.5</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00771607</v>
+        <v>0.00766284</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>424.242504</v>
+        <v>451</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00235714</v>
+        <v>0.00221729</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>182.245261</v>
+        <v>194</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00548711</v>
+        <v>0.00515464</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05943405</v>
+        <v>0.05390836</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.384564</v>
+        <v>4.85</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15662777</v>
+        <v>0.20618557</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.341644000000001</v>
+        <v>10.02</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10704754</v>
+        <v>0.0998004</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4620</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00024041</v>
+        <v>0.00021645</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.957362</v>
+        <v>39.5</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02502668</v>
+        <v>0.02531646</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.387856</v>
+        <v>46.2</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02155737</v>
+        <v>0.02164502</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1735</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057143</v>
+        <v>0.00057637</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.883392</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01565352</v>
+        <v>0.01560062</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05943405</v>
+        <v>0.05390836</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1620</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00074279</v>
+        <v>0.00061728</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1415</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068671</v>
+        <v>0.00070671</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.003188</v>
+        <v>14.15</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07141231000000001</v>
+        <v>0.07067138000000001</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>546.182333</v>
+        <v>510</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00183089</v>
+        <v>0.00196078</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14124,10 +14124,10 @@
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>24597.158802</v>
+        <v>22500</v>
       </c>
       <c r="E32" s="65" t="n">
-        <v>4.066e-05</v>
+        <v>4.444e-05</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.655665</v>
+        <v>572</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.0017493</v>
+        <v>0.00174825</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4590.20962</v>
+        <v>1320</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021785</v>
+        <v>0.00075758</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.127282</v>
+        <v>22.6</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04733217</v>
+        <v>0.04424779</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.825373</v>
+        <v>18.55</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05943405</v>
+        <v>0.05390836</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.921</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34364982</v>
+        <v>0.34234851</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2581.145435</v>
+        <v>2720</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00038742</v>
+        <v>0.00036765</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3780.951081</v>
+        <v>3720</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026448</v>
+        <v>0.00026882</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176786</v>
+        <v>0.001657</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>565.656672</v>
+        <v>603.5</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176786</v>
+        <v>0.001657</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.825509</v>
+        <v>18.55</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05943357</v>
+        <v>0.05390836</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.569197</v>
+        <v>27.2</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05110072</v>
+        <v>0.03676471</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.3025</v>
+        <v>13.6</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03952179</v>
+        <v>0.07352941</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>24 March 2026 — 09:07 UTC</t>
+          <t>24 March 2026 — 11:50 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 24 March 2026  |  11:50 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 24 March 2026  |  12:04 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>45.23</v>
+        <v>44.24</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>29.19</v>
+        <v>28.55</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.7</v>
+        <v>40.78</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>276.46</v>
+        <v>279.44</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>375.19</v>
+        <v>379.25</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>591.5</v>
+        <v>597.89</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>694.09</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>750.15</v>
+        <v>703.11</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>14.86</v>
+        <v>15.03</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>14.26</v>
+        <v>14.42</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.12</v>
+        <v>17.32</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>851.24</v>
+        <v>797.86</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>710.3200000000001</v>
+        <v>665.78</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>832.83</v>
+        <v>780.61</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3896.74</v>
+        <v>3978.07</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3760.96</v>
+        <v>3839.45</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4234</v>
+        <v>4322.37</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>1047.68</v>
+        <v>981.98</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1086.3</v>
+        <v>1018.18</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>127.57</v>
+        <v>120.7</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>112.66</v>
+        <v>106.59</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>122.61</v>
+        <v>116</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>838.14</v>
+        <v>785.58</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>729.21</v>
+        <v>683.48</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2967.77</v>
+        <v>2395.13</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>2430.84</v>
+        <v>1961.8</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>3525</v>
+        <v>2844.84</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>18.52</v>
+        <v>19.3</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>22.09</v>
+        <v>23.02</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>20.53</v>
+        <v>18.62</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>22.24</v>
+        <v>20.17</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>103.75</v>
+        <v>123.54</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>109.45</v>
+        <v>130.33</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>595.84</v>
+        <v>558.47</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>576.22</v>
+        <v>540.09</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>543.15</v>
+        <v>509.09</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>18.23</v>
+        <v>12.74</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>17.27</v>
+        <v>12.07</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>18.84</v>
+        <v>13.17</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11074.59</v>
+        <v>11222.97</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>11599.65</v>
+        <v>11755.06</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11072</v>
+        <v>11220.34</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>818.47</v>
+        <v>767.14</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>703.6799999999999</v>
+        <v>659.5599999999999</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>167.08</v>
+        <v>165.93</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>166.91</v>
+        <v>165.76</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>176.18</v>
+        <v>174.96</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>18.92</v>
+        <v>17.16</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>21.44</v>
+        <v>19.45</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>164.18</v>
+        <v>154.23</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>176.81</v>
+        <v>166.1</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>232.8</v>
+        <v>218.69</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,25 +2785,25 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I31" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="K31" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="M31" s="33" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>5062.6</v>
+        <v>4558</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>6006</v>
+        <v>5407.38</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4630.89</v>
+        <v>4670.88</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4164</v>
+        <v>4199.96</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>779.1799999999999</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>784.55</v>
+        <v>735.35</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.14</v>
+        <v>55.36</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>58.95</v>
+        <v>59.19</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>64.68000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>13.88</v>
+        <v>12.94</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>6.01</v>
+        <v>5.6</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.59</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>79.16</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>83.33</v>
+        <v>83.05</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>20.73</v>
+        <v>18.8</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>20.44</v>
+        <v>18.54</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>754.38</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1273.32</v>
+        <v>1058.17</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1599.43</v>
+        <v>1329.17</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>891</v>
+        <v>740.45</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>1989.07</v>
+        <v>2046.99</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1853.65</v>
+        <v>1907.64</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2051.75</v>
+        <v>2111.5</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.1524</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>923.23</v>
+        <v>865.34</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>783.34</v>
+        <v>734.22</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>694.02</v>
+        <v>650.51</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.96</v>
+        <v>19.75</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>18.82</v>
+        <v>18.62</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.64</v>
+        <v>22.41</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,25 +3604,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>0.044</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>25.56</v>
+        <v>23.19</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>25.04</v>
+        <v>22.71</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>332.01</v>
+        <v>355.56</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>309.88</v>
+        <v>331.86</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>280.5</v>
+        <v>300.4</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2803.5</v>
+        <v>2660.39</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3400</v>
+        <v>3226.43</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>680.99</v>
+        <v>638.29</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>712.73</v>
+        <v>668.04</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4836</v>
+        <v>4915.24</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>34.82</v>
+        <v>25.05</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>27.77</v>
+        <v>19.98</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>35.36</v>
+        <v>25.44</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>29.51</v>
+        <v>54.91</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>2.05</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>27.88</v>
+        <v>51.87</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>21.08</v>
+        <v>39.22</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.391</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 11:50 UTC</t>
+          <t>2026-03-24 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>26.4</v>
+        <v>25.82</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.7</v>
+        <v>40.78</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.56</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.56</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>347.8</v>
+        <v>351.56</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>591.5</v>
+        <v>597.89</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>750.15</v>
+        <v>703.11</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>750.15</v>
+        <v>703.11</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>750.15</v>
+        <v>703.11</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>14.26</v>
+        <v>14.42</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>14.26</v>
+        <v>14.42</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>14.26</v>
+        <v>14.42</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.12</v>
+        <v>17.32</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>710.3200000000001</v>
+        <v>665.78</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>710.3200000000001</v>
+        <v>665.78</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>710.3200000000001</v>
+        <v>665.78</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>832.83</v>
+        <v>780.61</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3760.96</v>
+        <v>3839.45</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3760.96</v>
+        <v>3839.45</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3760.96</v>
+        <v>3839.45</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4234</v>
+        <v>4322.37</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1086.3</v>
+        <v>1018.18</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>112.66</v>
+        <v>106.59</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>112.66</v>
+        <v>106.59</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>112.66</v>
+        <v>106.59</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>122.61</v>
+        <v>116</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>694.21</v>
+        <v>650.67</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>694.21</v>
+        <v>650.67</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>694.21</v>
+        <v>650.67</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>2430.84</v>
+        <v>1961.8</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>2430.84</v>
+        <v>1961.8</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>2430.84</v>
+        <v>1961.8</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>3525</v>
+        <v>2844.84</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.75</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.75</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.07</v>
+        <v>16.75</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>22.09</v>
+        <v>23.02</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>22.24</v>
+        <v>20.17</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>22.24</v>
+        <v>20.17</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>22.24</v>
+        <v>20.17</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>82.54000000000001</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>548.58</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>548.58</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>548.58</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>543.15</v>
+        <v>509.09</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>17.27</v>
+        <v>12.07</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>17.27</v>
+        <v>12.07</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>17.27</v>
+        <v>12.07</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>18.84</v>
+        <v>13.17</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>11599.65</v>
+        <v>11755.06</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>11599.65</v>
+        <v>11755.06</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>11599.65</v>
+        <v>11755.06</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11072</v>
+        <v>11220.34</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>703.6799999999999</v>
+        <v>659.5599999999999</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>703.6799999999999</v>
+        <v>659.5599999999999</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>703.6799999999999</v>
+        <v>659.5599999999999</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>166.91</v>
+        <v>165.76</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>166.91</v>
+        <v>165.76</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>166.91</v>
+        <v>165.76</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>176.18</v>
+        <v>174.96</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>21.44</v>
+        <v>19.45</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>21.44</v>
+        <v>19.45</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>21.44</v>
+        <v>19.45</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>154.31</v>
+        <v>144.96</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>154.31</v>
+        <v>144.96</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>154.31</v>
+        <v>144.96</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>232.8</v>
+        <v>218.69</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,49 +5777,49 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="J23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="O23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="T23" s="40" t="n">
         <v>0</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>6006</v>
+        <v>5407.38</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4164</v>
+        <v>4199.96</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>639.95</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>639.95</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>639.95</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>784.55</v>
+        <v>735.35</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>58.95</v>
+        <v>59.19</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>58.95</v>
+        <v>59.19</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>58.95</v>
+        <v>59.19</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>64.68000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>6.01</v>
+        <v>5.6</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>79.16</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>79.16</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>79.16</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>83.33</v>
+        <v>83.05</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>20.44</v>
+        <v>18.54</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>20.44</v>
+        <v>18.54</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>20.44</v>
+        <v>18.54</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>754.38</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>820.04</v>
+        <v>681.48</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>869.29</v>
+        <v>722.41</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>902.02</v>
+        <v>749.6</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>937.17</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>937.17</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>937.17</v>
+        <v>778.8200000000001</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>891</v>
+        <v>740.45</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1726.02</v>
+        <v>1776.28</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1726.02</v>
+        <v>1776.28</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1726.02</v>
+        <v>1776.28</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1853.65</v>
+        <v>1907.64</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1853.65</v>
+        <v>1907.64</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1853.65</v>
+        <v>1907.64</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2051.75</v>
+        <v>2111.5</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.1524</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>783.34</v>
+        <v>734.22</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>783.34</v>
+        <v>734.22</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>783.34</v>
+        <v>734.22</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>694.02</v>
+        <v>650.51</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>18.82</v>
+        <v>18.62</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>18.82</v>
+        <v>18.62</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>18.82</v>
+        <v>18.62</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.64</v>
+        <v>22.41</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6700,49 +6700,49 @@
         </is>
       </c>
       <c r="E36" s="38" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.387</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>31207.5</v>
+        <v>34116.26</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.3925</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>31331.25</v>
+        <v>34251.54</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.3981</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>31457.25</v>
+        <v>34389.29</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="T36" s="39" t="n">
         <v>0.044</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.55</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.55</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>23.76</v>
+        <v>21.55</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>25.04</v>
+        <v>22.71</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>289.78</v>
+        <v>310.34</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>289.78</v>
+        <v>310.34</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>289.78</v>
+        <v>310.34</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>280.5</v>
+        <v>300.4</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3400</v>
+        <v>3226.43</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>712.73</v>
+        <v>668.04</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>712.73</v>
+        <v>668.04</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>712.73</v>
+        <v>668.04</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4836</v>
+        <v>4915.24</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>27.77</v>
+        <v>19.98</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>27.77</v>
+        <v>19.98</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>27.77</v>
+        <v>19.98</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>35.36</v>
+        <v>25.44</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>21.22</v>
+        <v>39.47</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>21.22</v>
+        <v>39.47</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>21.22</v>
+        <v>39.47</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>20.67</v>
+        <v>38.46</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>20.67</v>
+        <v>38.46</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>20.67</v>
+        <v>38.46</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>21.08</v>
+        <v>39.22</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.391</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>43.07</v>
+        <v>42.12</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>263.17</v>
+        <v>266.01</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>660.83</v>
+        <v>619.39</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>810.4400000000001</v>
+        <v>759.62</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3438.59</v>
+        <v>3510.36</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>997.46</v>
+        <v>934.92</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>114.2</v>
+        <v>108.05</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>797.95</v>
+        <v>747.91</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2621.75</v>
+        <v>2115.88</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>19.7</v>
+        <v>20.53</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>19.55</v>
+        <v>17.73</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>106.35</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>567.29</v>
+        <v>531.72</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10275.33</v>
+        <v>10413</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>779.24</v>
+        <v>730.38</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>159.07</v>
+        <v>157.97</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>17.82</v>
+        <v>16.16</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>142.28</v>
+        <v>133.66</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.0309</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4486.02</v>
+        <v>4038.9</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4301.41</v>
+        <v>4338.56</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>735.61</v>
+        <v>689.48</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>11.59</v>
+        <v>10.81</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.84</v>
+        <v>72.59</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>19.74</v>
+        <v>17.9</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>820.04</v>
+        <v>681.48</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1726.02</v>
+        <v>1776.28</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.2198</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>879</v>
+        <v>823.88</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>31207.5</v>
+        <v>34116.26</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.387</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>310.85</v>
+        <v>332.9</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2556.8</v>
+        <v>2426.28</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>648.34</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.8661</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>34.56</v>
+        <v>24.86</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>21.22</v>
+        <v>39.47</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.56</v>
@@ -10075,7 +10075,7 @@
         <v>1.1437</v>
       </c>
       <c r="D56" t="n">
-        <v>1.1155</v>
+        <v>1.1154</v>
       </c>
     </row>
     <row r="57">
@@ -10088,7 +10088,7 @@
         <v>1.144</v>
       </c>
       <c r="D57" t="n">
-        <v>1.1155</v>
+        <v>1.1154</v>
       </c>
     </row>
     <row r="58">
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>45.23</v>
+        <v>44.24</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>29.19</v>
+        <v>28.55</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.7</v>
+        <v>40.78</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>18.52</v>
+        <v>19.3</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>22.09</v>
+        <v>23.02</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,25 +10322,25 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0.0309</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>13.88</v>
+        <v>12.94</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>6.01</v>
+        <v>5.6</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>332.01</v>
+        <v>355.56</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>309.88</v>
+        <v>331.86</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>280.5</v>
+        <v>300.4</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>694.09</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>750.15</v>
+        <v>703.11</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>851.24</v>
+        <v>797.86</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>710.3200000000001</v>
+        <v>665.78</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>832.83</v>
+        <v>780.61</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>127.57</v>
+        <v>120.7</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.121</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>112.66</v>
+        <v>106.59</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>122.61</v>
+        <v>116</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>18.23</v>
+        <v>12.74</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>17.27</v>
+        <v>12.07</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>18.84</v>
+        <v>13.17</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11074.59</v>
+        <v>11222.97</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>11599.65</v>
+        <v>11755.06</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11072</v>
+        <v>11220.34</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>818.47</v>
+        <v>767.14</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>703.6799999999999</v>
+        <v>659.5599999999999</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>164.18</v>
+        <v>154.23</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>176.81</v>
+        <v>166.1</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>232.8</v>
+        <v>218.69</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>779.1799999999999</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>677.91</v>
+        <v>635.4</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>784.55</v>
+        <v>735.35</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>665.0599999999999</v>
+        <v>623.35</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>604.71</v>
+        <v>566.79</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>754.38</v>
+        <v>707.0700000000001</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1273.32</v>
+        <v>1058.17</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1599.43</v>
+        <v>1329.17</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>891</v>
+        <v>740.45</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>923.23</v>
+        <v>865.34</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>783.34</v>
+        <v>734.22</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>694.02</v>
+        <v>650.51</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -10978,25 +10978,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="G27" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>30622.5</v>
+        <v>33476.73</v>
       </c>
       <c r="I27" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="28" t="n">
-        <v>28125</v>
+        <v>30746.45</v>
       </c>
       <c r="K27" s="39" t="n">
         <v>0.044</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>680.99</v>
+        <v>638.29</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>712.73</v>
+        <v>668.04</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>663.85</v>
+        <v>622.22</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3896.74</v>
+        <v>3978.07</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3760.96</v>
+        <v>3839.45</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4234</v>
+        <v>4322.37</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>103.75</v>
+        <v>123.54</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>109.45</v>
+        <v>130.33</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>137.55</v>
+        <v>163.79</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>167.08</v>
+        <v>165.93</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>166.91</v>
+        <v>165.76</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>176.18</v>
+        <v>174.96</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>5062.6</v>
+        <v>4558</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>7161</v>
+        <v>6447.26</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>6006</v>
+        <v>5407.38</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4630.89</v>
+        <v>4670.88</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3496.03</v>
+        <v>3526.21</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4164</v>
+        <v>4199.96</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.14</v>
+        <v>55.36</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>58.95</v>
+        <v>59.19</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64.68000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>1989.07</v>
+        <v>2046.99</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1853.65</v>
+        <v>1907.64</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2051.75</v>
+        <v>2111.5</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.1524</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.96</v>
+        <v>19.75</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>18.82</v>
+        <v>18.62</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.64</v>
+        <v>22.41</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2803.5</v>
+        <v>2660.39</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2752.64</v>
+        <v>2612.12</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3400</v>
+        <v>3226.43</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5137.32</v>
+        <v>5221.49</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4278</v>
+        <v>4348.09</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4836</v>
+        <v>4915.24</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>1047.68</v>
+        <v>981.98</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1299.94</v>
+        <v>1218.42</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1086.3</v>
+        <v>1018.18</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>838.14</v>
+        <v>785.58</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>729.21</v>
+        <v>683.48</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>724.2</v>
+        <v>678.79</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2967.77</v>
+        <v>2395.13</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>2430.84</v>
+        <v>1961.8</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>3525</v>
+        <v>2844.84</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>595.84</v>
+        <v>558.47</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>576.22</v>
+        <v>540.09</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>543.15</v>
+        <v>509.09</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>276.46</v>
+        <v>279.44</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>375.19</v>
+        <v>379.25</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>591.5</v>
+        <v>597.89</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>14.86</v>
+        <v>15.03</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>14.26</v>
+        <v>14.42</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.12</v>
+        <v>17.32</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>20.53</v>
+        <v>18.62</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>1.199</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>22.24</v>
+        <v>20.17</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>18.92</v>
+        <v>17.16</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>21.44</v>
+        <v>19.45</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.59</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>79.16</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>83.33</v>
+        <v>83.05</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>20.73</v>
+        <v>18.8</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>20.44</v>
+        <v>18.54</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>23.19</v>
+        <v>21.03</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>22.07</v>
+        <v>20.02</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>25.56</v>
+        <v>23.19</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>25.04</v>
+        <v>22.71</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>34.82</v>
+        <v>25.05</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>27.77</v>
+        <v>19.98</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>35.36</v>
+        <v>25.44</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>2.17</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>29.51</v>
+        <v>54.91</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>2.05</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>27.88</v>
+        <v>51.87</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>21.08</v>
+        <v>39.22</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.391</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4630.89</v>
+        <v>4670.88</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>0.0309</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>2.17</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>29.51</v>
+        <v>54.91</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>276.46</v>
+        <v>279.44</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>1047.68</v>
+        <v>981.98</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>45.23</v>
+        <v>44.24</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>923.23</v>
+        <v>865.34</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>1.448</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>32580</v>
+        <v>35616.69</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>332.01</v>
+        <v>355.56</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>851.24</v>
+        <v>797.86</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1273.32</v>
+        <v>1058.17</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.96</v>
+        <v>19.75</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>103.75</v>
+        <v>123.54</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>1989.07</v>
+        <v>2046.99</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>164.18</v>
+        <v>154.23</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>838.14</v>
+        <v>785.58</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.3853</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>13.88</v>
+        <v>12.94</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>595.84</v>
+        <v>558.47</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>910</v>
+        <v>919.82965</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.0010989</v>
+        <v>0.00108716</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2920</v>
+        <v>2980.942232</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00034247</v>
+        <v>0.00033546</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.7</v>
+        <v>13.852778</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07299269999999999</v>
+        <v>0.07218769</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2820</v>
+        <v>2275.872731</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00035461</v>
+        <v>0.00043939</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>100.5</v>
+        <v>95.08570400000001</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.009950250000000001</v>
+        <v>0.01051683</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>177.7</v>
+        <v>177.721</v>
       </c>
       <c r="E8" s="65" t="n">
-        <v>0.00562746</v>
+        <v>0.0056268</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>134.5</v>
+        <v>131.547186</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00743494</v>
+        <v>0.00760183</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>50.2</v>
+        <v>52.308227</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01992032</v>
+        <v>0.01911745</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>131</v>
+        <v>155.989306</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.00763359</v>
+        <v>0.0064107</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>15.7</v>
+        <v>10.974209</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.06369427</v>
+        <v>0.09112273999999999</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>73</v>
+        <v>74.188785</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01369863</v>
+        <v>0.01347913</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8650</v>
+        <v>8765.893312</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011561</v>
+        <v>0.00011408</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>130.5</v>
+        <v>129.599611</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00766284</v>
+        <v>0.00771607</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>451</v>
+        <v>424.242504</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00221729</v>
+        <v>0.00235714</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>194</v>
+        <v>182.245261</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00515464</v>
+        <v>0.00548711</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05390836</v>
+        <v>0.05943405</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>4.85</v>
+        <v>6.384564</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.20618557</v>
+        <v>0.15662777</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>10.02</v>
+        <v>9.341644000000001</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.0998004</v>
+        <v>0.10704754</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4620</v>
+        <v>4159.521529</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00021645</v>
+        <v>0.00024041</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.5</v>
+        <v>39.957362</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02531646</v>
+        <v>0.02502668</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.2</v>
+        <v>46.387856</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02164502</v>
+        <v>0.02155737</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1735</v>
+        <v>1749.982128</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057637</v>
+        <v>0.00057143</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>64.09999999999999</v>
+        <v>63.883392</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01560062</v>
+        <v>0.01565352</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05390836</v>
+        <v>0.05943405</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1620</v>
+        <v>1346.267881</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00061728</v>
+        <v>0.00074279</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1415</v>
+        <v>1456.210003</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00070671</v>
+        <v>0.00068671</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.15</v>
+        <v>14.003188</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07067138000000001</v>
+        <v>0.07141231000000001</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>510</v>
+        <v>546.182333</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00196078</v>
+        <v>0.00183089</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14124,10 +14124,10 @@
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>22500</v>
+        <v>24597.158802</v>
       </c>
       <c r="E32" s="65" t="n">
-        <v>4.444e-05</v>
+        <v>4.066e-05</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>572</v>
+        <v>571.655665</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00174825</v>
+        <v>0.0017493</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>1320</v>
+        <v>4590.20962</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00075758</v>
+        <v>0.00021785</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>22.6</v>
+        <v>21.127282</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04424779</v>
+        <v>0.04733217</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825373</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05390836</v>
+        <v>0.05943405</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.921</v>
+        <v>2.909939</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34234851</v>
+        <v>0.34364982</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2720</v>
+        <v>2581.145435</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00036765</v>
+        <v>0.00038742</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3720</v>
+        <v>3780.951081</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026882</v>
+        <v>0.00026448</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.001657</v>
+        <v>0.00176786</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>603.5</v>
+        <v>565.656672</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.001657</v>
+        <v>0.00176786</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>18.55</v>
+        <v>16.825509</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05390836</v>
+        <v>0.05943357</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>27.2</v>
+        <v>19.569197</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.03676471</v>
+        <v>0.05110072</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>13.6</v>
+        <v>25.3025</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.07352941</v>
+        <v>0.03952179</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>24 March 2026 — 11:50 UTC</t>
+          <t>24 March 2026 — 12:04 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 24 March 2026  |  12:04 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 25 March 2026  |  06:58 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>131.547186</v>
+        <v>132.69024</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.24</v>
+        <v>44.62</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.55</v>
+        <v>28.79</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>40.78</v>
+        <v>41.13</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>919.82965</v>
+        <v>921.654437</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.44</v>
+        <v>280</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>379.25</v>
+        <v>380</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>597.89</v>
+        <v>599.08</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>650.5599999999999</v>
+        <v>650.55</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>703.11</v>
+        <v>703.1</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>678.79</v>
+        <v>678.77</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.852778</v>
+        <v>13.936582</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.03</v>
+        <v>15.12</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>14.42</v>
+        <v>14.51</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.32</v>
+        <v>17.42</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>797.86</v>
+        <v>797.84</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>665.78</v>
+        <v>665.76</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>780.61</v>
+        <v>780.59</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2979.2747</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3978.07</v>
+        <v>3975.84</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3839.45</v>
+        <v>3837.31</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4322.37</v>
+        <v>4319.95</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>981.98</v>
+        <v>981.96</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1218.42</v>
+        <v>1218.4</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1018.18</v>
+        <v>1018.16</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.08570400000001</v>
+        <v>95.083783</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>785.58</v>
+        <v>785.5700000000001</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>683.48</v>
+        <v>683.47</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>678.79</v>
+        <v>678.77</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2293.820921</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2395.13</v>
+        <v>2414.02</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>1961.8</v>
+        <v>1977.27</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2844.84</v>
+        <v>2867.28</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.308227</v>
+        <v>52.653427</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.7</v>
+        <v>22.85</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.3</v>
+        <v>19.42</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>23.02</v>
+        <v>23.17</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.62</v>
+        <v>18.79</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>20.17</v>
+        <v>20.36</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.989306</v>
+        <v>156.411282</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.54</v>
+        <v>123.88</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>130.33</v>
+        <v>130.68</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>163.79</v>
+        <v>164.23</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>558.47</v>
+        <v>558.46</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>540.09</v>
+        <v>540.08</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>509.09</v>
+        <v>509.08</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.974209</v>
+        <v>10.947001</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.74</v>
+        <v>12.71</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8765.893312</v>
+        <v>8763.575505999999</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11222.97</v>
+        <v>11220.01</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>11755.06</v>
+        <v>11751.95</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11220.34</v>
+        <v>11217.38</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>767.14</v>
+        <v>767.13</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>659.5599999999999</v>
+        <v>659.54</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>622.22</v>
+        <v>622.21</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.599611</v>
+        <v>129.631198</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>165.93</v>
+        <v>165.97</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>165.76</v>
+        <v>165.8</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>174.96</v>
+        <v>175</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.16</v>
+        <v>17.32</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>19.45</v>
+        <v>19.63</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>182.245261</v>
+        <v>183.20154</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>154.23</v>
+        <v>155.04</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>166.1</v>
+        <v>166.97</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>218.69</v>
+        <v>219.84</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.384564</v>
+        <v>6.401624</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4175.886479</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4558</v>
+        <v>4575.94</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>6447.26</v>
+        <v>6472.62</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5407.38</v>
+        <v>5428.65</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1742.820706</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4670.88</v>
+        <v>4651.76</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3526.21</v>
+        <v>3511.78</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4199.96</v>
+        <v>4182.77</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>730.3200000000001</v>
+        <v>730.3</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>635.4</v>
+        <v>635.39</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>735.35</v>
+        <v>735.34</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.387856</v>
+        <v>46.495437</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.36</v>
+        <v>55.49</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>59.19</v>
+        <v>59.33</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>64.94</v>
+        <v>65.09</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,19 +3100,19 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.341644000000001</v>
+        <v>9.332912</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.883392</v>
+        <v>63.587796</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.31999999999999</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>83.05</v>
+        <v>82.66</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>18.8</v>
+        <v>18.98</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>18.54</v>
+        <v>18.71</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>623.35</v>
+        <v>623.34</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>566.79</v>
+        <v>566.78</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>707.0599999999999</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1376.136423</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1058.17</v>
+        <v>1081.64</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1329.17</v>
+        <v>1358.66</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>740.45</v>
+        <v>756.88</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1457.689642</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>2046.99</v>
+        <v>2049.07</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1907.64</v>
+        <v>1909.57</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2111.5</v>
+        <v>2113.65</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.1524</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>865.34</v>
+        <v>865.3200000000001</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>734.22</v>
+        <v>734.21</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>650.51</v>
+        <v>650.49</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.003188</v>
+        <v>14.565684</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.75</v>
+        <v>20.54</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>18.62</v>
+        <v>19.37</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.41</v>
+        <v>23.31</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>16.825509</v>
+        <v>16.966421</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.19</v>
+        <v>23.38</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>22.71</v>
+        <v>22.9</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>546.182333</v>
+        <v>449.349587</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>355.56</v>
+        <v>292.53</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>331.86</v>
+        <v>273.02</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>300.4</v>
+        <v>247.14</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2581.145435</v>
+        <v>2576.948396</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2660.39</v>
+        <v>2656.06</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2612.12</v>
+        <v>2607.87</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3226.43</v>
+        <v>3221.19</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>638.29</v>
+        <v>638.27</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>668.04</v>
+        <v>668.03</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>622.22</v>
+        <v>622.21</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.923734</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3780.951081</v>
+        <v>3763.160564</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5221.49</v>
+        <v>5196.92</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4348.09</v>
+        <v>4327.63</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4915.24</v>
+        <v>4892.11</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>19.569197</v>
+        <v>19.41701</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>25.05</v>
+        <v>24.86</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>19.98</v>
+        <v>19.82</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>25.44</v>
+        <v>25.24</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.3025</v>
+        <v>25.3127</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>54.91</v>
+        <v>54.93</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>2.05</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>51.87</v>
+        <v>51.89</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.22</v>
+        <v>39.23</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.391</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24 12:04 UTC</t>
+          <t>2026-03-25 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>131.547186</v>
+        <v>132.69024</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.12</v>
+        <v>42.49</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.12</v>
+        <v>42.49</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.12</v>
+        <v>42.49</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.05</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.05</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>25.82</v>
+        <v>26.05</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>40.78</v>
+        <v>41.13</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>919.82965</v>
+        <v>921.654437</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.01</v>
+        <v>266.54</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.01</v>
+        <v>266.54</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.01</v>
+        <v>266.54</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>351.56</v>
+        <v>352.26</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>351.56</v>
+        <v>352.26</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>351.56</v>
+        <v>352.26</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>597.89</v>
+        <v>599.08</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>619.39</v>
+        <v>619.38</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>619.39</v>
+        <v>619.38</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>619.39</v>
+        <v>619.38</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>703.11</v>
+        <v>703.1</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>703.11</v>
+        <v>703.1</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>703.11</v>
+        <v>703.1</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>678.79</v>
+        <v>678.77</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.852778</v>
+        <v>13.936582</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.25</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.25</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.25</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>14.42</v>
+        <v>14.51</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>14.42</v>
+        <v>14.51</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>14.42</v>
+        <v>14.51</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.32</v>
+        <v>17.42</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>759.62</v>
+        <v>759.61</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>759.62</v>
+        <v>759.61</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>759.62</v>
+        <v>759.61</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>665.78</v>
+        <v>665.76</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>665.78</v>
+        <v>665.76</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>665.78</v>
+        <v>665.76</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>780.61</v>
+        <v>780.59</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2980.942232</v>
+        <v>2979.2747</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3508.39</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3508.39</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3508.39</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3839.45</v>
+        <v>3837.31</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3839.45</v>
+        <v>3837.31</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3839.45</v>
+        <v>3837.31</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4322.37</v>
+        <v>4319.95</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>934.92</v>
+        <v>934.9</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>934.92</v>
+        <v>934.9</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>934.92</v>
+        <v>934.9</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1218.42</v>
+        <v>1218.4</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1218.42</v>
+        <v>1218.4</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1218.42</v>
+        <v>1218.4</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1018.18</v>
+        <v>1018.16</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,25 +4854,25 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.08570400000001</v>
+        <v>95.083783</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.05</v>
+        <v>108.04</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.05</v>
+        <v>108.04</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.05</v>
+        <v>108.04</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.121</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>747.91</v>
+        <v>747.9</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>747.91</v>
+        <v>747.9</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>747.91</v>
+        <v>747.9</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>650.67</v>
+        <v>650.66</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>650.67</v>
+        <v>650.66</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>650.67</v>
+        <v>650.66</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>678.79</v>
+        <v>678.77</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2275.872731</v>
+        <v>2293.820921</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2132.57</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2132.57</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2132.57</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1961.8</v>
+        <v>1977.27</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1961.8</v>
+        <v>1977.27</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1961.8</v>
+        <v>1977.27</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2844.84</v>
+        <v>2867.28</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.308227</v>
+        <v>52.653427</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.53</v>
+        <v>20.67</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.53</v>
+        <v>20.67</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.53</v>
+        <v>20.67</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.86</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.86</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.75</v>
+        <v>16.86</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>23.02</v>
+        <v>23.17</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>17.73</v>
+        <v>17.89</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>17.73</v>
+        <v>17.89</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>17.73</v>
+        <v>17.89</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>20.17</v>
+        <v>20.36</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>20.17</v>
+        <v>20.36</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>20.17</v>
+        <v>20.36</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.989306</v>
+        <v>156.411282</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.35</v>
+        <v>106.64</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.35</v>
+        <v>106.64</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.35</v>
+        <v>106.64</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>98.55</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>98.55</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>98.29000000000001</v>
+        <v>98.55</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>163.79</v>
+        <v>164.23</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>531.72</v>
+        <v>531.71</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>531.72</v>
+        <v>531.71</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>531.72</v>
+        <v>531.71</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>514.17</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>514.17</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>514.1799999999999</v>
+        <v>514.17</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>509.09</v>
+        <v>509.08</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.974209</v>
+        <v>10.947001</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8765.893312</v>
+        <v>8763.575505999999</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10413</v>
+        <v>10410.25</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10413</v>
+        <v>10410.25</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10413</v>
+        <v>10410.25</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>11755.06</v>
+        <v>11751.95</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>11755.06</v>
+        <v>11751.95</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>11755.06</v>
+        <v>11751.95</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11220.34</v>
+        <v>11217.38</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>730.38</v>
+        <v>730.36</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>730.38</v>
+        <v>730.36</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>730.38</v>
+        <v>730.36</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>659.5599999999999</v>
+        <v>659.54</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>659.5599999999999</v>
+        <v>659.54</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>659.5599999999999</v>
+        <v>659.54</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>622.22</v>
+        <v>622.21</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.599611</v>
+        <v>129.631198</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>157.97</v>
+        <v>158.01</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>157.97</v>
+        <v>158.01</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>157.97</v>
+        <v>158.01</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>165.76</v>
+        <v>165.8</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>165.76</v>
+        <v>165.8</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>165.76</v>
+        <v>165.8</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>174.96</v>
+        <v>175</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.16</v>
+        <v>16.31</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.16</v>
+        <v>16.31</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.16</v>
+        <v>16.31</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>19.45</v>
+        <v>19.63</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>19.45</v>
+        <v>19.63</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>19.45</v>
+        <v>19.63</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>182.245261</v>
+        <v>183.20154</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>133.66</v>
+        <v>134.36</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>133.66</v>
+        <v>134.36</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>133.66</v>
+        <v>134.36</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>144.96</v>
+        <v>145.72</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>144.96</v>
+        <v>145.72</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>144.96</v>
+        <v>145.72</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>218.69</v>
+        <v>219.84</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.384564</v>
+        <v>6.401624</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4159.521529</v>
+        <v>4175.886479</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4054.79</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4054.79</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4054.79</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>6447.26</v>
+        <v>6472.62</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>6447.26</v>
+        <v>6472.62</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>6447.26</v>
+        <v>6472.62</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5407.38</v>
+        <v>5428.65</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1749.982128</v>
+        <v>1742.820706</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4320.8</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4320.8</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4320.8</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3526.21</v>
+        <v>3511.78</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3526.21</v>
+        <v>3511.78</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3526.21</v>
+        <v>3511.78</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4199.96</v>
+        <v>4182.77</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>689.48</v>
+        <v>689.46</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>689.48</v>
+        <v>689.46</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>689.48</v>
+        <v>689.46</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>599.8099999999999</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>599.8099999999999</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>599.8200000000001</v>
+        <v>599.8099999999999</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>735.35</v>
+        <v>735.34</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.387856</v>
+        <v>46.495437</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.87</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.87</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.87</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>59.19</v>
+        <v>59.33</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>59.19</v>
+        <v>59.33</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>59.19</v>
+        <v>59.33</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>64.94</v>
+        <v>65.09</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,43 +6132,43 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.341644000000001</v>
+        <v>9.332912</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.883392</v>
+        <v>63.587796</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.25</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.25</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.25</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>83.05</v>
+        <v>82.66</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>17.9</v>
+        <v>18.07</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>17.9</v>
+        <v>18.07</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>17.9</v>
+        <v>18.07</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>18.54</v>
+        <v>18.71</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>18.54</v>
+        <v>18.71</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>18.54</v>
+        <v>18.71</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>623.35</v>
+        <v>623.34</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>623.35</v>
+        <v>623.34</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>623.35</v>
+        <v>623.34</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>566.79</v>
+        <v>566.78</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>566.79</v>
+        <v>566.78</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>566.79</v>
+        <v>566.78</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>707.0599999999999</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1346.267881</v>
+        <v>1376.136423</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>681.48</v>
+        <v>696.6</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>722.41</v>
+        <v>738.4299999999999</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>749.6</v>
+        <v>766.23</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>796.09</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>796.09</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>778.8200000000001</v>
+        <v>796.09</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>740.45</v>
+        <v>756.88</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1456.210003</v>
+        <v>1457.689642</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1776.28</v>
+        <v>1778.09</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1776.28</v>
+        <v>1778.09</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1776.28</v>
+        <v>1778.09</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1907.64</v>
+        <v>1909.57</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1907.64</v>
+        <v>1909.57</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1907.64</v>
+        <v>1909.57</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2111.5</v>
+        <v>2113.65</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.1524</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>823.88</v>
+        <v>823.86</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>823.88</v>
+        <v>823.86</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>823.88</v>
+        <v>823.86</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>734.22</v>
+        <v>734.21</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>734.22</v>
+        <v>734.21</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>734.22</v>
+        <v>734.21</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>650.51</v>
+        <v>650.49</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.003188</v>
+        <v>14.565684</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.96</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.96</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.96</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>18.62</v>
+        <v>19.37</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>18.62</v>
+        <v>19.37</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>18.62</v>
+        <v>19.37</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.41</v>
+        <v>23.31</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>16.825509</v>
+        <v>16.966421</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.55</v>
+        <v>21.73</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.55</v>
+        <v>21.73</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.55</v>
+        <v>21.73</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>22.71</v>
+        <v>22.9</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>546.182333</v>
+        <v>449.349587</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>332.9</v>
+        <v>273.88</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>332.9</v>
+        <v>273.88</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>332.9</v>
+        <v>273.88</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>310.34</v>
+        <v>255.32</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>310.34</v>
+        <v>255.32</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>310.34</v>
+        <v>255.32</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>300.4</v>
+        <v>247.14</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2581.145435</v>
+        <v>2576.948396</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2422.33</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2422.33</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2422.33</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2612.12</v>
+        <v>2607.87</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2612.12</v>
+        <v>2607.87</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2612.12</v>
+        <v>2607.87</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3226.43</v>
+        <v>3221.19</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>607.67</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>607.67</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>607.67</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>668.04</v>
+        <v>668.03</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>668.04</v>
+        <v>668.03</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>668.04</v>
+        <v>668.03</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>622.22</v>
+        <v>622.21</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.909939</v>
+        <v>2.923734</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3780.951081</v>
+        <v>3763.160564</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5196.92</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5196.92</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5196.92</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4327.63</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4327.63</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4348.09</v>
+        <v>4327.63</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4915.24</v>
+        <v>4892.11</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>19.569197</v>
+        <v>19.41701</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.86</v>
+        <v>24.67</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.86</v>
+        <v>24.67</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.86</v>
+        <v>24.67</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>19.98</v>
+        <v>19.82</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>19.98</v>
+        <v>19.82</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>19.98</v>
+        <v>19.82</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>25.44</v>
+        <v>25.24</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.3025</v>
+        <v>25.3127</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>39.47</v>
+        <v>39.49</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>39.47</v>
+        <v>39.49</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>39.47</v>
+        <v>39.49</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>38.46</v>
+        <v>38.48</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>38.46</v>
+        <v>38.48</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>38.46</v>
+        <v>38.48</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.22</v>
+        <v>39.23</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.391</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>131.547186</v>
+        <v>132.69024</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.12</v>
+        <v>42.49</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>919.82965</v>
+        <v>921.654437</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.01</v>
+        <v>266.54</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>619.39</v>
+        <v>619.38</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.852778</v>
+        <v>13.936582</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.17</v>
+        <v>14.25</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>759.62</v>
+        <v>759.61</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2979.2747</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3510.36</v>
+        <v>3508.39</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>934.92</v>
+        <v>934.9</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.08570400000001</v>
+        <v>95.083783</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.05</v>
+        <v>108.04</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>747.91</v>
+        <v>747.9</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2293.820921</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2115.88</v>
+        <v>2132.57</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.308227</v>
+        <v>52.653427</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.53</v>
+        <v>20.67</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>17.73</v>
+        <v>17.89</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.989306</v>
+        <v>156.411282</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.35</v>
+        <v>106.64</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>531.72</v>
+        <v>531.71</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.974209</v>
+        <v>10.947001</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8765.893312</v>
+        <v>8763.575505999999</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10413</v>
+        <v>10410.25</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>730.38</v>
+        <v>730.36</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.599611</v>
+        <v>129.631198</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>157.97</v>
+        <v>158.01</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.16</v>
+        <v>16.31</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>182.245261</v>
+        <v>183.20154</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>133.66</v>
+        <v>134.36</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.384564</v>
+        <v>6.401624</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>0.2</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4175.886479</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4038.9</v>
+        <v>4054.79</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1742.820706</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4338.56</v>
+        <v>4320.8</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>689.48</v>
+        <v>689.46</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.387856</v>
+        <v>46.495437</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.75</v>
+        <v>51.87</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.341644000000001</v>
+        <v>9.332912</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.883392</v>
+        <v>63.587796</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.59</v>
+        <v>72.25</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>17.9</v>
+        <v>18.07</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>623.35</v>
+        <v>623.34</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1376.136423</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>681.48</v>
+        <v>696.6</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1457.689642</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1776.28</v>
+        <v>1778.09</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.2198</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>823.88</v>
+        <v>823.86</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.003188</v>
+        <v>14.565684</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.23</v>
+        <v>18.96</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>16.825509</v>
+        <v>16.966421</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>546.182333</v>
+        <v>449.349587</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>332.9</v>
+        <v>273.88</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2581.145435</v>
+        <v>2576.948396</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2426.28</v>
+        <v>2422.33</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>607.6799999999999</v>
+        <v>607.67</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.923734</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.8661</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3780.951081</v>
+        <v>3763.160564</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5221.49</v>
+        <v>5196.92</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>19.569197</v>
+        <v>19.41701</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.86</v>
+        <v>24.67</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.3025</v>
+        <v>25.3127</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>39.47</v>
+        <v>39.49</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.56</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>131.547186</v>
+        <v>132.69024</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.24</v>
+        <v>44.62</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.55</v>
+        <v>28.79</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>40.78</v>
+        <v>41.13</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.308227</v>
+        <v>52.653427</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.7</v>
+        <v>22.85</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.3</v>
+        <v>19.42</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>23.02</v>
+        <v>23.17</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.384564</v>
+        <v>6.401624</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
@@ -10361,19 +10361,19 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.341644000000001</v>
+        <v>9.332912</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>546.182333</v>
+        <v>449.349587</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>355.56</v>
+        <v>292.53</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>331.86</v>
+        <v>273.02</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>300.4</v>
+        <v>247.14</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.909939</v>
+        <v>2.923734</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>650.5599999999999</v>
+        <v>650.55</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>703.11</v>
+        <v>703.1</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>678.79</v>
+        <v>678.77</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>797.86</v>
+        <v>797.84</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>665.78</v>
+        <v>665.76</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>780.61</v>
+        <v>780.59</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.08570400000001</v>
+        <v>95.083783</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.974209</v>
+        <v>10.947001</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.74</v>
+        <v>12.71</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8765.893312</v>
+        <v>8763.575505999999</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11222.97</v>
+        <v>11220.01</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>11755.06</v>
+        <v>11751.95</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11220.34</v>
+        <v>11217.38</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>767.14</v>
+        <v>767.13</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>659.5599999999999</v>
+        <v>659.54</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>622.22</v>
+        <v>622.21</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>182.245261</v>
+        <v>183.20154</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>154.23</v>
+        <v>155.04</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>166.1</v>
+        <v>166.97</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>218.69</v>
+        <v>219.84</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>730.3200000000001</v>
+        <v>730.3</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>635.4</v>
+        <v>635.39</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>735.35</v>
+        <v>735.34</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>623.35</v>
+        <v>623.34</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>566.79</v>
+        <v>566.78</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>707.0700000000001</v>
+        <v>707.0599999999999</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1346.267881</v>
+        <v>1376.136423</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1058.17</v>
+        <v>1081.64</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1329.17</v>
+        <v>1358.66</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>740.45</v>
+        <v>756.88</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>865.34</v>
+        <v>865.3200000000001</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>734.22</v>
+        <v>734.21</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>650.51</v>
+        <v>650.49</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>638.29</v>
+        <v>638.27</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>668.04</v>
+        <v>668.03</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>622.22</v>
+        <v>622.21</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2980.942232</v>
+        <v>2979.2747</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3978.07</v>
+        <v>3975.84</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3839.45</v>
+        <v>3837.31</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4322.37</v>
+        <v>4319.95</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.989306</v>
+        <v>156.411282</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.54</v>
+        <v>123.88</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>130.33</v>
+        <v>130.68</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>163.79</v>
+        <v>164.23</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.599611</v>
+        <v>129.631198</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>165.93</v>
+        <v>165.97</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>165.76</v>
+        <v>165.8</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>174.96</v>
+        <v>175</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4159.521529</v>
+        <v>4175.886479</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4558</v>
+        <v>4575.94</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>6447.26</v>
+        <v>6472.62</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5407.38</v>
+        <v>5428.65</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1749.982128</v>
+        <v>1742.820706</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4670.88</v>
+        <v>4651.76</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3526.21</v>
+        <v>3511.78</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4199.96</v>
+        <v>4182.77</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.387856</v>
+        <v>46.495437</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.36</v>
+        <v>55.49</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>59.19</v>
+        <v>59.33</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>64.94</v>
+        <v>65.09</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1456.210003</v>
+        <v>1457.689642</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>2046.99</v>
+        <v>2049.07</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1907.64</v>
+        <v>1909.57</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2111.5</v>
+        <v>2113.65</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.1524</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.003188</v>
+        <v>14.565684</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.75</v>
+        <v>20.54</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>18.62</v>
+        <v>19.37</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.41</v>
+        <v>23.31</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2581.145435</v>
+        <v>2576.948396</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2660.39</v>
+        <v>2656.06</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2612.12</v>
+        <v>2607.87</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3226.43</v>
+        <v>3221.19</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3780.951081</v>
+        <v>3763.160564</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5221.49</v>
+        <v>5196.92</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4348.09</v>
+        <v>4327.63</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4915.24</v>
+        <v>4892.11</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>981.98</v>
+        <v>981.96</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1218.42</v>
+        <v>1218.4</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1018.18</v>
+        <v>1018.16</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>785.58</v>
+        <v>785.5700000000001</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>683.48</v>
+        <v>683.47</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>678.79</v>
+        <v>678.77</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2275.872731</v>
+        <v>2293.820921</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2395.13</v>
+        <v>2414.02</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>1961.8</v>
+        <v>1977.27</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2844.84</v>
+        <v>2867.28</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>558.47</v>
+        <v>558.46</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>540.09</v>
+        <v>540.08</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>509.09</v>
+        <v>509.08</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>919.82965</v>
+        <v>921.654437</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>279.44</v>
+        <v>280</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>379.25</v>
+        <v>380</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>597.89</v>
+        <v>599.08</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.852778</v>
+        <v>13.936582</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15.03</v>
+        <v>15.12</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>14.42</v>
+        <v>14.51</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.32</v>
+        <v>17.42</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.62</v>
+        <v>18.79</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>1.199</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>20.17</v>
+        <v>20.36</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.16</v>
+        <v>17.32</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>19.45</v>
+        <v>19.63</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.883392</v>
+        <v>63.587796</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.31999999999999</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>83.05</v>
+        <v>82.66</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>18.8</v>
+        <v>18.98</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>18.54</v>
+        <v>18.71</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.03</v>
+        <v>21.22</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>16.825509</v>
+        <v>16.966421</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>20.02</v>
+        <v>20.19</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.19</v>
+        <v>23.38</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>22.71</v>
+        <v>22.9</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>19.569197</v>
+        <v>19.41701</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>25.05</v>
+        <v>24.86</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>19.98</v>
+        <v>19.82</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>25.44</v>
+        <v>25.24</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.3025</v>
+        <v>25.3127</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>2.17</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>54.91</v>
+        <v>54.93</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>2.05</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>51.87</v>
+        <v>51.89</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.22</v>
+        <v>39.23</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.391</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4670.88</v>
+        <v>4651.76</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>2.17</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>54.91</v>
+        <v>54.93</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.44</v>
+        <v>280</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>981.98</v>
+        <v>981.96</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.24</v>
+        <v>44.62</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>865.34</v>
+        <v>865.3200000000001</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.7</v>
+        <v>22.85</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>355.56</v>
+        <v>292.53</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>797.86</v>
+        <v>797.84</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1058.17</v>
+        <v>1081.64</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.75</v>
+        <v>20.54</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.54</v>
+        <v>123.88</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2046.99</v>
+        <v>2049.07</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>154.23</v>
+        <v>155.04</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>785.58</v>
+        <v>785.5700000000001</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.3853</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>558.47</v>
+        <v>558.46</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>919.82965</v>
+        <v>921.654437</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108716</v>
+        <v>0.00108501</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2980.942232</v>
+        <v>2979.2747</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033546</v>
+        <v>0.00033565</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.852778</v>
+        <v>13.936582</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07218769</v>
+        <v>0.07175361</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2275.872731</v>
+        <v>2293.820921</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00043939</v>
+        <v>0.00043595</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.08570400000001</v>
+        <v>95.083783</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01051683</v>
+        <v>0.01051704</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>131.547186</v>
+        <v>132.69024</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00760183</v>
+        <v>0.00753635</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.308227</v>
+        <v>52.653427</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01911745</v>
+        <v>0.01899212</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.989306</v>
+        <v>156.411282</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.0064107</v>
+        <v>0.0063934</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.974209</v>
+        <v>10.947001</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09112273999999999</v>
+        <v>0.09134921999999999</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.188785</v>
+        <v>74.185925</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347913</v>
+        <v>0.01347965</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8765.893312</v>
+        <v>8763.575505999999</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011408</v>
+        <v>0.00011411</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.599611</v>
+        <v>129.631198</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00771607</v>
+        <v>0.00771419</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>424.242504</v>
+        <v>424.233934</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00235714</v>
+        <v>0.00235719</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>182.245261</v>
+        <v>183.20154</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00548711</v>
+        <v>0.00545847</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05943405</v>
+        <v>0.05889836</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.384564</v>
+        <v>6.401624</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15662777</v>
+        <v>0.15621036</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.341644000000001</v>
+        <v>9.332912</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10704754</v>
+        <v>0.10714769</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4159.521529</v>
+        <v>4175.886479</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00024041</v>
+        <v>0.00023947</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.957362</v>
+        <v>39.977849</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02502668</v>
+        <v>0.02501385</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.387856</v>
+        <v>46.495437</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02155737</v>
+        <v>0.02150749</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1749.982128</v>
+        <v>1742.820706</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057143</v>
+        <v>0.00057378</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.883392</v>
+        <v>63.587796</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01565352</v>
+        <v>0.01572629</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05943405</v>
+        <v>0.05889836</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1346.267881</v>
+        <v>1376.136423</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00074279</v>
+        <v>0.00072667</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1456.210003</v>
+        <v>1457.689642</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068671</v>
+        <v>0.00068602</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.003188</v>
+        <v>14.565684</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07141231000000001</v>
+        <v>0.06865452</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>546.182333</v>
+        <v>449.349587</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00183089</v>
+        <v>0.00222544</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.655665</v>
+        <v>572.006198</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.0017493</v>
+        <v>0.00174823</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4590.20962</v>
+        <v>4590.90068</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021785</v>
+        <v>0.00021782</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.127282</v>
+        <v>21.126855</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04733217</v>
+        <v>0.04733312</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.825373</v>
+        <v>16.978401</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05943405</v>
+        <v>0.05889836</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.909939</v>
+        <v>2.923734</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34364982</v>
+        <v>0.34202838</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2581.145435</v>
+        <v>2576.948396</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00038742</v>
+        <v>0.00038806</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3780.951081</v>
+        <v>3763.160564</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026448</v>
+        <v>0.00026573</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176786</v>
+        <v>0.00176789</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>565.656672</v>
+        <v>565.645246</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176786</v>
+        <v>0.00176789</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.825509</v>
+        <v>16.966421</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05943357</v>
+        <v>0.05893995</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.569197</v>
+        <v>19.41701</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05110072</v>
+        <v>0.05150124</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.3025</v>
+        <v>25.3127</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03952179</v>
+        <v>0.03950586</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>24 March 2026 — 12:04 UTC</t>
+          <t>25 March 2026 — 06:58 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 25 March 2026  |  06:58 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 26 March 2026  |  07:04 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.69024</v>
+        <v>132.541246</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.62</v>
+        <v>44.57</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.79</v>
+        <v>28.76</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.13</v>
+        <v>41.09</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>921.654437</v>
+        <v>920.836259</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>280</v>
+        <v>279.75</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>380</v>
+        <v>379.66</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>599.08</v>
+        <v>598.54</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>650.55</v>
+        <v>651.64</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>703.1</v>
+        <v>704.28</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>678.77</v>
+        <v>679.92</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.936582</v>
+        <v>13.863743</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.12</v>
+        <v>15.04</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>14.51</v>
+        <v>14.43</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.42</v>
+        <v>17.33</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>797.84</v>
+        <v>799.1900000000001</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>665.76</v>
+        <v>666.89</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>780.59</v>
+        <v>781.91</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2979.2747</v>
+        <v>2975.095377</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3975.84</v>
+        <v>3970.26</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3837.31</v>
+        <v>3831.92</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4319.95</v>
+        <v>4313.89</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>981.96</v>
+        <v>983.61</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1218.4</v>
+        <v>1220.45</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1018.16</v>
+        <v>1019.88</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.083783</v>
+        <v>95.244001</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>120.7</v>
+        <v>120.9</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>106.59</v>
+        <v>106.77</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116</v>
+        <v>116.2</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>785.5700000000001</v>
+        <v>786.89</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>683.47</v>
+        <v>684.62</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>678.77</v>
+        <v>679.92</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2293.820921</v>
+        <v>2286.084927</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2414.02</v>
+        <v>2405.88</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>1977.27</v>
+        <v>1970.61</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2867.28</v>
+        <v>2857.61</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.653427</v>
+        <v>52.563613</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.85</v>
+        <v>22.81</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.42</v>
+        <v>19.39</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.79</v>
+        <v>18.76</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>20.36</v>
+        <v>20.32</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>156.411282</v>
+        <v>155.741325</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.88</v>
+        <v>123.35</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>130.68</v>
+        <v>130.12</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>164.23</v>
+        <v>163.53</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>558.46</v>
+        <v>559.4</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>540.08</v>
+        <v>540.99</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>509.08</v>
+        <v>509.94</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.947001</v>
+        <v>10.978531</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.71</v>
+        <v>12.74</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8763.575505999999</v>
+        <v>8762.726264999999</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11220.01</v>
+        <v>11218.92</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>11751.95</v>
+        <v>11750.82</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11217.38</v>
+        <v>11216.29</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>767.13</v>
+        <v>768.42</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>659.54</v>
+        <v>660.65</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>622.21</v>
+        <v>623.26</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.631198</v>
+        <v>129.652926</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>165.97</v>
+        <v>165.99</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>165.8</v>
+        <v>165.83</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>175</v>
+        <v>175.03</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.32</v>
+        <v>17.29</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>19.63</v>
+        <v>19.59</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>183.20154</v>
+        <v>183.541926</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>155.04</v>
+        <v>155.33</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>166.97</v>
+        <v>167.28</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>219.84</v>
+        <v>220.25</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.401624</v>
+        <v>6.374747</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4175.886479</v>
+        <v>4180.42642</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4575.94</v>
+        <v>4580.91</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>6472.62</v>
+        <v>6479.66</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5428.65</v>
+        <v>5434.55</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1742.820706</v>
+        <v>1739.141887</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4651.76</v>
+        <v>4641.94</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3511.78</v>
+        <v>3504.37</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4182.77</v>
+        <v>4173.94</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>730.3</v>
+        <v>731.54</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>635.39</v>
+        <v>636.46</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>735.34</v>
+        <v>736.58</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.495437</v>
+        <v>46.451311</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.49</v>
+        <v>55.44</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>59.33</v>
+        <v>59.27</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>65.09</v>
+        <v>65.03</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.332912</v>
+        <v>9.324045999999999</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.587796</v>
+        <v>63.688413</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>77.95999999999999</v>
+        <v>78.08</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>78.53</v>
+        <v>78.66</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>82.66</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>18.98</v>
+        <v>18.94</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>18.71</v>
+        <v>18.68</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>623.34</v>
+        <v>624.39</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>566.78</v>
+        <v>567.73</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>707.0599999999999</v>
+        <v>708.25</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1376.136423</v>
+        <v>1377.066908</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1081.64</v>
+        <v>1082.37</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1358.66</v>
+        <v>1359.58</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>756.88</v>
+        <v>757.39</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1457.689642</v>
+        <v>1458.768366</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>2049.07</v>
+        <v>2050.59</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1909.57</v>
+        <v>1910.99</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2113.65</v>
+        <v>2115.21</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.1524</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>865.3200000000001</v>
+        <v>866.78</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>734.21</v>
+        <v>735.4400000000001</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>650.49</v>
+        <v>651.59</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.565684</v>
+        <v>14.336314</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>20.54</v>
+        <v>20.22</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>19.37</v>
+        <v>19.07</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>23.31</v>
+        <v>22.94</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,25 +3604,25 @@
         </is>
       </c>
       <c r="F44" s="26" t="n">
-        <v>24597.158802</v>
+        <v>24602.424754</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>35616.69</v>
+        <v>35624.31</v>
       </c>
       <c r="I44" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="J44" s="28" t="n">
-        <v>33476.73</v>
+        <v>33483.9</v>
       </c>
       <c r="K44" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L44" s="28" t="n">
-        <v>30746.45</v>
+        <v>30753.03</v>
       </c>
       <c r="M44" s="29" t="n">
         <v>0.044</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>16.966421</v>
+        <v>16.947691</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.38</v>
+        <v>23.35</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>22.9</v>
+        <v>22.88</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>449.349587</v>
+        <v>544.306151</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>292.53</v>
+        <v>354.34</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>273.02</v>
+        <v>330.72</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>247.14</v>
+        <v>299.37</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2576.948396</v>
+        <v>2569.139667</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2656.06</v>
+        <v>2648.01</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2607.87</v>
+        <v>2599.97</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3221.19</v>
+        <v>3211.42</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>638.27</v>
+        <v>639.35</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>668.03</v>
+        <v>669.15</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>622.21</v>
+        <v>623.26</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.923734</v>
+        <v>2.912732</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3763.160564</v>
+        <v>3725.483569</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5196.92</v>
+        <v>5144.89</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4327.63</v>
+        <v>4284.31</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4892.11</v>
+        <v>4843.13</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>19.41701</v>
+        <v>18.961288</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>24.86</v>
+        <v>24.28</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>19.82</v>
+        <v>19.36</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>25.24</v>
+        <v>24.65</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.3127</v>
+        <v>25.2603</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>54.93</v>
+        <v>54.81</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>2.05</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>51.89</v>
+        <v>51.78</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.391</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25 06:58 UTC</t>
+          <t>2026-03-26 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>132.69024</v>
+        <v>132.541246</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.49</v>
+        <v>42.44</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.49</v>
+        <v>42.44</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.49</v>
+        <v>42.44</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>26.05</v>
+        <v>26.02</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>26.05</v>
+        <v>26.02</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>26.05</v>
+        <v>26.02</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.13</v>
+        <v>41.09</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>921.654437</v>
+        <v>920.836259</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.54</v>
+        <v>266.31</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.54</v>
+        <v>266.31</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.54</v>
+        <v>266.31</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>352.26</v>
+        <v>351.94</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>352.26</v>
+        <v>351.94</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>352.26</v>
+        <v>351.94</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>599.08</v>
+        <v>598.54</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>619.38</v>
+        <v>620.4299999999999</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>619.38</v>
+        <v>620.4299999999999</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>619.38</v>
+        <v>620.4299999999999</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>703.1</v>
+        <v>704.28</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>703.1</v>
+        <v>704.28</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>703.1</v>
+        <v>704.28</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>678.77</v>
+        <v>679.92</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.936582</v>
+        <v>13.863743</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.25</v>
+        <v>14.18</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.25</v>
+        <v>14.18</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.25</v>
+        <v>14.18</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>14.51</v>
+        <v>14.43</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>14.51</v>
+        <v>14.43</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>14.51</v>
+        <v>14.43</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.42</v>
+        <v>17.33</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>759.61</v>
+        <v>760.88</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>759.61</v>
+        <v>760.88</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>759.61</v>
+        <v>760.88</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>665.76</v>
+        <v>666.89</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>665.76</v>
+        <v>666.89</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>665.76</v>
+        <v>666.89</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>780.59</v>
+        <v>781.91</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2979.2747</v>
+        <v>2975.095377</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3508.39</v>
+        <v>3503.47</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3508.39</v>
+        <v>3503.47</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3508.39</v>
+        <v>3503.47</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3837.31</v>
+        <v>3831.92</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3837.31</v>
+        <v>3831.92</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3837.31</v>
+        <v>3831.92</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4319.95</v>
+        <v>4313.89</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>934.9</v>
+        <v>936.47</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>934.9</v>
+        <v>936.47</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>934.9</v>
+        <v>936.47</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1218.4</v>
+        <v>1220.45</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1218.4</v>
+        <v>1220.45</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1218.4</v>
+        <v>1220.45</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1018.16</v>
+        <v>1019.88</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.083783</v>
+        <v>95.244001</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.04</v>
+        <v>108.23</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.04</v>
+        <v>108.23</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.04</v>
+        <v>108.23</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>106.59</v>
+        <v>106.77</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>106.59</v>
+        <v>106.77</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>106.59</v>
+        <v>106.77</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116</v>
+        <v>116.2</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>747.9</v>
+        <v>749.16</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>747.9</v>
+        <v>749.16</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>747.9</v>
+        <v>749.16</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>650.66</v>
+        <v>651.76</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>650.66</v>
+        <v>651.76</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>650.66</v>
+        <v>651.76</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>678.77</v>
+        <v>679.92</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2293.820921</v>
+        <v>2286.084927</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2132.57</v>
+        <v>2125.37</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2132.57</v>
+        <v>2125.37</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2132.57</v>
+        <v>2125.37</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1977.27</v>
+        <v>1970.61</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1977.27</v>
+        <v>1970.61</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1977.27</v>
+        <v>1970.61</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2867.28</v>
+        <v>2857.61</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.653427</v>
+        <v>52.563613</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.67</v>
+        <v>20.63</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.67</v>
+        <v>20.63</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.67</v>
+        <v>20.63</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.86</v>
+        <v>16.83</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.86</v>
+        <v>16.83</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.86</v>
+        <v>16.83</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>17.89</v>
+        <v>17.86</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>17.89</v>
+        <v>17.86</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>17.89</v>
+        <v>17.86</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>20.36</v>
+        <v>20.32</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>20.36</v>
+        <v>20.32</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>20.36</v>
+        <v>20.32</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>156.411282</v>
+        <v>155.741325</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.64</v>
+        <v>106.18</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.64</v>
+        <v>106.18</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.64</v>
+        <v>106.18</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>98.55</v>
+        <v>98.13</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>98.55</v>
+        <v>98.13</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>98.55</v>
+        <v>98.13</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>164.23</v>
+        <v>163.53</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>531.71</v>
+        <v>532.6</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>531.71</v>
+        <v>532.6</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>531.71</v>
+        <v>532.6</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>514.17</v>
+        <v>515.04</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>514.17</v>
+        <v>515.04</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>514.17</v>
+        <v>515.04</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>509.08</v>
+        <v>509.94</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.947001</v>
+        <v>10.978531</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.1</v>
+        <v>12.13</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.1</v>
+        <v>12.13</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.1</v>
+        <v>12.13</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8763.575505999999</v>
+        <v>8762.726264999999</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10410.25</v>
+        <v>10409.24</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10410.25</v>
+        <v>10409.24</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10410.25</v>
+        <v>10409.24</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>11751.95</v>
+        <v>11750.82</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>11751.95</v>
+        <v>11750.82</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>11751.95</v>
+        <v>11750.82</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11217.38</v>
+        <v>11216.29</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>730.36</v>
+        <v>731.59</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>730.36</v>
+        <v>731.59</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>730.36</v>
+        <v>731.59</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>659.54</v>
+        <v>660.65</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>659.54</v>
+        <v>660.65</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>659.54</v>
+        <v>660.65</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>622.21</v>
+        <v>623.26</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.631198</v>
+        <v>129.652926</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>158.01</v>
+        <v>158.03</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>158.01</v>
+        <v>158.03</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>158.01</v>
+        <v>158.03</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>165.8</v>
+        <v>165.83</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>165.8</v>
+        <v>165.83</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>165.8</v>
+        <v>165.83</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>175</v>
+        <v>175.03</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.31</v>
+        <v>16.28</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.31</v>
+        <v>16.28</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.31</v>
+        <v>16.28</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>19.63</v>
+        <v>19.59</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>19.63</v>
+        <v>19.59</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>19.63</v>
+        <v>19.59</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>183.20154</v>
+        <v>183.541926</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>134.36</v>
+        <v>134.61</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>134.36</v>
+        <v>134.61</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>134.36</v>
+        <v>134.61</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>145.72</v>
+        <v>145.99</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>145.72</v>
+        <v>145.99</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>145.72</v>
+        <v>145.99</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>219.84</v>
+        <v>220.25</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.401624</v>
+        <v>6.374747</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4175.886479</v>
+        <v>4180.42642</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4054.79</v>
+        <v>4059.19</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4054.79</v>
+        <v>4059.19</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4054.79</v>
+        <v>4059.19</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>6472.62</v>
+        <v>6479.66</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>6472.62</v>
+        <v>6479.66</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>6472.62</v>
+        <v>6479.66</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5428.65</v>
+        <v>5434.55</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1742.820706</v>
+        <v>1739.141887</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4320.8</v>
+        <v>4311.68</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4320.8</v>
+        <v>4311.68</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4320.8</v>
+        <v>4311.68</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3511.78</v>
+        <v>3504.37</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3511.78</v>
+        <v>3504.37</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3511.78</v>
+        <v>3504.37</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4182.77</v>
+        <v>4173.94</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>689.46</v>
+        <v>690.63</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>689.46</v>
+        <v>690.63</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>689.46</v>
+        <v>690.63</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>599.8099999999999</v>
+        <v>600.8200000000001</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>599.8099999999999</v>
+        <v>600.8200000000001</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>599.8099999999999</v>
+        <v>600.8200000000001</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>735.34</v>
+        <v>736.58</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.495437</v>
+        <v>46.451311</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.87</v>
+        <v>51.82</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.87</v>
+        <v>51.82</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.87</v>
+        <v>51.82</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>59.33</v>
+        <v>59.27</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>59.33</v>
+        <v>59.27</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>59.33</v>
+        <v>59.27</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>65.09</v>
+        <v>65.03</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.332912</v>
+        <v>9.324045999999999</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.587796</v>
+        <v>63.688413</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.25</v>
+        <v>72.37</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.25</v>
+        <v>72.37</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.25</v>
+        <v>72.37</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>78.53</v>
+        <v>78.66</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>78.53</v>
+        <v>78.66</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>78.53</v>
+        <v>78.66</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>82.66</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>18.07</v>
+        <v>18.04</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>18.07</v>
+        <v>18.04</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>18.07</v>
+        <v>18.04</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>18.71</v>
+        <v>18.68</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>18.71</v>
+        <v>18.68</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>18.71</v>
+        <v>18.68</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>623.34</v>
+        <v>624.39</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>623.34</v>
+        <v>624.39</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>623.34</v>
+        <v>624.39</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>566.78</v>
+        <v>567.73</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>566.78</v>
+        <v>567.73</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>566.78</v>
+        <v>567.73</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>707.0599999999999</v>
+        <v>708.25</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1376.136423</v>
+        <v>1377.066908</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>696.6</v>
+        <v>697.0700000000001</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>738.4299999999999</v>
+        <v>738.9299999999999</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>766.23</v>
+        <v>766.75</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>796.09</v>
+        <v>796.63</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>796.09</v>
+        <v>796.63</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>796.09</v>
+        <v>796.63</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>756.88</v>
+        <v>757.39</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1457.689642</v>
+        <v>1458.768366</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1778.09</v>
+        <v>1779.41</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1778.09</v>
+        <v>1779.41</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1778.09</v>
+        <v>1779.41</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1909.57</v>
+        <v>1910.99</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1909.57</v>
+        <v>1910.99</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1909.57</v>
+        <v>1910.99</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2113.65</v>
+        <v>2115.21</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.1524</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>823.86</v>
+        <v>825.25</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>823.86</v>
+        <v>825.25</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>823.86</v>
+        <v>825.25</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>734.21</v>
+        <v>735.4400000000001</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>734.21</v>
+        <v>735.4400000000001</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>734.21</v>
+        <v>735.4400000000001</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>650.49</v>
+        <v>651.59</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.565684</v>
+        <v>14.336314</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.96</v>
+        <v>18.66</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.96</v>
+        <v>18.66</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.96</v>
+        <v>18.66</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>19.37</v>
+        <v>19.07</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>19.37</v>
+        <v>19.07</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>19.37</v>
+        <v>19.07</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>23.31</v>
+        <v>22.94</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6700,49 +6700,49 @@
         </is>
       </c>
       <c r="E36" s="38" t="n">
-        <v>24597.158802</v>
+        <v>24602.424754</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>1.387</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>34116.26</v>
+        <v>34123.56</v>
       </c>
       <c r="H36" s="27" t="n">
         <v>1.3925</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>34251.54</v>
+        <v>34258.88</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>1.3981</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>34389.29</v>
+        <v>34396.65</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="M36" s="28" t="n">
-        <v>33476.73</v>
+        <v>33483.9</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>33476.73</v>
+        <v>33483.9</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="Q36" s="28" t="n">
-        <v>33476.73</v>
+        <v>33483.9</v>
       </c>
       <c r="R36" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" s="28" t="n">
-        <v>30746.45</v>
+        <v>30753.03</v>
       </c>
       <c r="T36" s="39" t="n">
         <v>0.044</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>16.966421</v>
+        <v>16.947691</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.73</v>
+        <v>21.71</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.73</v>
+        <v>21.71</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.73</v>
+        <v>21.71</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>22.9</v>
+        <v>22.88</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>449.349587</v>
+        <v>544.306151</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>273.88</v>
+        <v>331.75</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>273.88</v>
+        <v>331.75</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>273.88</v>
+        <v>331.75</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>255.32</v>
+        <v>309.27</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>255.32</v>
+        <v>309.27</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>255.32</v>
+        <v>309.27</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>247.14</v>
+        <v>299.37</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2576.948396</v>
+        <v>2569.139667</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2422.33</v>
+        <v>2414.99</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2422.33</v>
+        <v>2414.99</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2422.33</v>
+        <v>2414.99</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2607.87</v>
+        <v>2599.97</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2607.87</v>
+        <v>2599.97</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2607.87</v>
+        <v>2599.97</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3221.19</v>
+        <v>3211.42</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>607.67</v>
+        <v>608.7</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>607.67</v>
+        <v>608.7</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>607.67</v>
+        <v>608.7</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>668.03</v>
+        <v>669.15</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>668.03</v>
+        <v>669.15</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>668.03</v>
+        <v>669.15</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>622.21</v>
+        <v>623.26</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.923734</v>
+        <v>2.912732</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3763.160564</v>
+        <v>3725.483569</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5196.92</v>
+        <v>5144.89</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5196.92</v>
+        <v>5144.89</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5196.92</v>
+        <v>5144.89</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4327.63</v>
+        <v>4284.31</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4327.63</v>
+        <v>4284.31</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4327.63</v>
+        <v>4284.31</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4892.11</v>
+        <v>4843.13</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>19.41701</v>
+        <v>18.961288</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.67</v>
+        <v>24.09</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.67</v>
+        <v>24.09</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.67</v>
+        <v>24.09</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>19.82</v>
+        <v>19.36</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>19.82</v>
+        <v>19.36</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>19.82</v>
+        <v>19.36</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>25.24</v>
+        <v>24.65</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.3127</v>
+        <v>25.2603</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>39.49</v>
+        <v>39.41</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>39.49</v>
+        <v>39.41</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>39.49</v>
+        <v>39.41</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>38.48</v>
+        <v>38.4</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>38.48</v>
+        <v>38.4</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>38.48</v>
+        <v>38.4</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.391</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.69024</v>
+        <v>132.541246</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.49</v>
+        <v>42.44</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>921.654437</v>
+        <v>920.836259</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.54</v>
+        <v>266.31</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>619.38</v>
+        <v>620.4299999999999</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.936582</v>
+        <v>13.863743</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.25</v>
+        <v>14.18</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>759.61</v>
+        <v>760.88</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2979.2747</v>
+        <v>2975.095377</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3508.39</v>
+        <v>3503.47</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>934.9</v>
+        <v>936.47</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.083783</v>
+        <v>95.244001</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.04</v>
+        <v>108.23</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>747.9</v>
+        <v>749.16</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2293.820921</v>
+        <v>2286.084927</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2132.57</v>
+        <v>2125.37</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.653427</v>
+        <v>52.563613</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.67</v>
+        <v>20.63</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>17.89</v>
+        <v>17.86</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>156.411282</v>
+        <v>155.741325</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.64</v>
+        <v>106.18</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>531.71</v>
+        <v>532.6</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.947001</v>
+        <v>10.978531</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.1</v>
+        <v>12.13</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8763.575505999999</v>
+        <v>8762.726264999999</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10410.25</v>
+        <v>10409.24</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>730.36</v>
+        <v>731.59</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.631198</v>
+        <v>129.652926</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>158.01</v>
+        <v>158.03</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.31</v>
+        <v>16.28</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>183.20154</v>
+        <v>183.541926</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>134.36</v>
+        <v>134.61</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.401624</v>
+        <v>6.374747</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>0.2</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4175.886479</v>
+        <v>4180.42642</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4054.79</v>
+        <v>4059.19</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1742.820706</v>
+        <v>1739.141887</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4320.8</v>
+        <v>4311.68</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>689.46</v>
+        <v>690.63</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.495437</v>
+        <v>46.451311</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.87</v>
+        <v>51.82</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.332912</v>
+        <v>9.324045999999999</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.587796</v>
+        <v>63.688413</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.25</v>
+        <v>72.37</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>18.07</v>
+        <v>18.04</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>623.34</v>
+        <v>624.39</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1376.136423</v>
+        <v>1377.066908</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>696.6</v>
+        <v>697.0700000000001</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1457.689642</v>
+        <v>1458.768366</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1778.09</v>
+        <v>1779.41</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.2198</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>823.86</v>
+        <v>825.25</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.565684</v>
+        <v>14.336314</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.96</v>
+        <v>18.66</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>24597.158802</v>
+        <v>24602.424754</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>34116.26</v>
+        <v>34123.56</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.387</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>16.966421</v>
+        <v>16.947691</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>449.349587</v>
+        <v>544.306151</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>273.88</v>
+        <v>331.75</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2576.948396</v>
+        <v>2569.139667</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2422.33</v>
+        <v>2414.99</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>607.67</v>
+        <v>608.7</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.923734</v>
+        <v>2.912732</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.8661</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3763.160564</v>
+        <v>3725.483569</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5196.92</v>
+        <v>5144.89</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>19.41701</v>
+        <v>18.961288</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.67</v>
+        <v>24.09</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.3127</v>
+        <v>25.2603</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>39.49</v>
+        <v>39.41</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.56</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>132.69024</v>
+        <v>132.541246</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.62</v>
+        <v>44.57</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.79</v>
+        <v>28.76</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.13</v>
+        <v>41.09</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.653427</v>
+        <v>52.563613</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.85</v>
+        <v>22.81</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.42</v>
+        <v>19.39</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.401624</v>
+        <v>6.374747</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.332912</v>
+        <v>9.324045999999999</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>449.349587</v>
+        <v>544.306151</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>292.53</v>
+        <v>354.34</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>273.02</v>
+        <v>330.72</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>247.14</v>
+        <v>299.37</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.923734</v>
+        <v>2.912732</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>650.55</v>
+        <v>651.64</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>703.1</v>
+        <v>704.28</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>678.77</v>
+        <v>679.92</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>797.84</v>
+        <v>799.1900000000001</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>665.76</v>
+        <v>666.89</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>780.59</v>
+        <v>781.91</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.083783</v>
+        <v>95.244001</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>120.7</v>
+        <v>120.9</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.121</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>106.59</v>
+        <v>106.77</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116</v>
+        <v>116.2</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.947001</v>
+        <v>10.978531</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.71</v>
+        <v>12.74</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8763.575505999999</v>
+        <v>8762.726264999999</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11220.01</v>
+        <v>11218.92</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>11751.95</v>
+        <v>11750.82</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11217.38</v>
+        <v>11216.29</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>767.13</v>
+        <v>768.42</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>659.54</v>
+        <v>660.65</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>622.21</v>
+        <v>623.26</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>183.20154</v>
+        <v>183.541926</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>155.04</v>
+        <v>155.33</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>166.97</v>
+        <v>167.28</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>219.84</v>
+        <v>220.25</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>730.3</v>
+        <v>731.54</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>635.39</v>
+        <v>636.46</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>735.34</v>
+        <v>736.58</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>623.34</v>
+        <v>624.39</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>566.78</v>
+        <v>567.73</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>707.0599999999999</v>
+        <v>708.25</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1376.136423</v>
+        <v>1377.066908</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1081.64</v>
+        <v>1082.37</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1358.66</v>
+        <v>1359.58</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>756.88</v>
+        <v>757.39</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>865.3200000000001</v>
+        <v>866.78</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>734.21</v>
+        <v>735.4400000000001</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>650.49</v>
+        <v>651.59</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -10978,25 +10978,25 @@
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>24597.158802</v>
+        <v>24602.424754</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>1.448</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>35616.69</v>
+        <v>35624.31</v>
       </c>
       <c r="G27" s="27" t="n">
         <v>1.361</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>33476.73</v>
+        <v>33483.9</v>
       </c>
       <c r="I27" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J27" s="28" t="n">
-        <v>30746.45</v>
+        <v>30753.03</v>
       </c>
       <c r="K27" s="39" t="n">
         <v>0.044</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>638.27</v>
+        <v>639.35</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>668.03</v>
+        <v>669.15</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>622.21</v>
+        <v>623.26</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2979.2747</v>
+        <v>2975.095377</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3975.84</v>
+        <v>3970.26</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3837.31</v>
+        <v>3831.92</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4319.95</v>
+        <v>4313.89</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>156.411282</v>
+        <v>155.741325</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.88</v>
+        <v>123.35</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>130.68</v>
+        <v>130.12</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>164.23</v>
+        <v>163.53</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.631198</v>
+        <v>129.652926</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>165.97</v>
+        <v>165.99</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>165.8</v>
+        <v>165.83</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>175</v>
+        <v>175.03</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4175.886479</v>
+        <v>4180.42642</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4575.94</v>
+        <v>4580.91</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>6472.62</v>
+        <v>6479.66</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5428.65</v>
+        <v>5434.55</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1742.820706</v>
+        <v>1739.141887</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4651.76</v>
+        <v>4641.94</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3511.78</v>
+        <v>3504.37</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4182.77</v>
+        <v>4173.94</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.495437</v>
+        <v>46.451311</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.49</v>
+        <v>55.44</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>59.33</v>
+        <v>59.27</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>65.09</v>
+        <v>65.03</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1457.689642</v>
+        <v>1458.768366</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>2049.07</v>
+        <v>2050.59</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1909.57</v>
+        <v>1910.99</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2113.65</v>
+        <v>2115.21</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.1524</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.565684</v>
+        <v>14.336314</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>20.54</v>
+        <v>20.22</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>19.37</v>
+        <v>19.07</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>23.31</v>
+        <v>22.94</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2576.948396</v>
+        <v>2569.139667</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2656.06</v>
+        <v>2648.01</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2607.87</v>
+        <v>2599.97</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3221.19</v>
+        <v>3211.42</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3763.160564</v>
+        <v>3725.483569</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5196.92</v>
+        <v>5144.89</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4327.63</v>
+        <v>4284.31</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4892.11</v>
+        <v>4843.13</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>981.96</v>
+        <v>983.61</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1218.4</v>
+        <v>1220.45</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1018.16</v>
+        <v>1019.88</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>785.5700000000001</v>
+        <v>786.89</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>683.47</v>
+        <v>684.62</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>678.77</v>
+        <v>679.92</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2293.820921</v>
+        <v>2286.084927</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2414.02</v>
+        <v>2405.88</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>1977.27</v>
+        <v>1970.61</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2867.28</v>
+        <v>2857.61</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>558.46</v>
+        <v>559.4</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>540.08</v>
+        <v>540.99</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>509.08</v>
+        <v>509.94</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>921.654437</v>
+        <v>920.836259</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>280</v>
+        <v>279.75</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>380</v>
+        <v>379.66</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>599.08</v>
+        <v>598.54</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.936582</v>
+        <v>13.863743</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15.12</v>
+        <v>15.04</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>14.51</v>
+        <v>14.43</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.42</v>
+        <v>17.33</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.79</v>
+        <v>18.76</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>1.199</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>20.36</v>
+        <v>20.32</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.32</v>
+        <v>17.29</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>19.63</v>
+        <v>19.59</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.587796</v>
+        <v>63.688413</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>77.95999999999999</v>
+        <v>78.08</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>78.53</v>
+        <v>78.66</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>82.66</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>18.98</v>
+        <v>18.94</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>18.71</v>
+        <v>18.68</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>16.966421</v>
+        <v>16.947691</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.38</v>
+        <v>23.35</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>22.9</v>
+        <v>22.88</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>19.41701</v>
+        <v>18.961288</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>24.86</v>
+        <v>24.28</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>19.82</v>
+        <v>19.36</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>25.24</v>
+        <v>24.65</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.3127</v>
+        <v>25.2603</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>2.17</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>54.93</v>
+        <v>54.81</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>2.05</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>51.89</v>
+        <v>51.78</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.391</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4651.76</v>
+        <v>4641.94</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>2.17</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>54.93</v>
+        <v>54.81</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>280</v>
+        <v>279.75</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>981.96</v>
+        <v>983.61</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.62</v>
+        <v>44.57</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>865.3200000000001</v>
+        <v>866.78</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.85</v>
+        <v>22.81</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>1.448</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>35616.69</v>
+        <v>35624.31</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>292.53</v>
+        <v>354.34</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>797.84</v>
+        <v>799.1900000000001</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1081.64</v>
+        <v>1082.37</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>20.54</v>
+        <v>20.22</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.88</v>
+        <v>123.35</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2049.07</v>
+        <v>2050.59</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>155.04</v>
+        <v>155.33</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>785.5700000000001</v>
+        <v>786.89</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.3853</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>558.46</v>
+        <v>559.4</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>921.654437</v>
+        <v>920.836259</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108501</v>
+        <v>0.00108597</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2979.2747</v>
+        <v>2975.095377</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033565</v>
+        <v>0.00033612</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.936582</v>
+        <v>13.863743</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07175361</v>
+        <v>0.07213058999999999</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2293.820921</v>
+        <v>2286.084927</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00043595</v>
+        <v>0.00043743</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.083783</v>
+        <v>95.244001</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01051704</v>
+        <v>0.01049935</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.69024</v>
+        <v>132.541246</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00753635</v>
+        <v>0.00754482</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.653427</v>
+        <v>52.563613</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01899212</v>
+        <v>0.01902457</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>156.411282</v>
+        <v>155.741325</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.0063934</v>
+        <v>0.0064209</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.947001</v>
+        <v>10.978531</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09134921999999999</v>
+        <v>0.09108687</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.185925</v>
+        <v>74.192116</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347965</v>
+        <v>0.01347852</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8763.575505999999</v>
+        <v>8762.726264999999</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011411</v>
+        <v>0.00011412</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.631198</v>
+        <v>129.652926</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00771419</v>
+        <v>0.0077129</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>424.233934</v>
+        <v>424.948775</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00235719</v>
+        <v>0.00235322</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>183.20154</v>
+        <v>183.541926</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00545847</v>
+        <v>0.00544835</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05889836</v>
+        <v>0.05899513</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.401624</v>
+        <v>6.374747</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15621036</v>
+        <v>0.15686897</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.332912</v>
+        <v>9.324045999999999</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10714769</v>
+        <v>0.10724958</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4175.886479</v>
+        <v>4180.42642</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00023947</v>
+        <v>0.00023921</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.977849</v>
+        <v>39.950679</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02501385</v>
+        <v>0.02503086</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.495437</v>
+        <v>46.451311</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02150749</v>
+        <v>0.02152792</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1742.820706</v>
+        <v>1739.141887</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057378</v>
+        <v>0.000575</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.587796</v>
+        <v>63.688413</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01572629</v>
+        <v>0.01570144</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05889836</v>
+        <v>0.05899513</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1376.136423</v>
+        <v>1377.066908</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00072667</v>
+        <v>0.00072618</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1457.689642</v>
+        <v>1458.768366</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068602</v>
+        <v>0.00068551</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.565684</v>
+        <v>14.336314</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.06865452</v>
+        <v>0.06975294</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>449.349587</v>
+        <v>544.306151</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00222544</v>
+        <v>0.0018372</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14124,10 +14124,10 @@
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>24597.158802</v>
+        <v>24602.424754</v>
       </c>
       <c r="E32" s="65" t="n">
-        <v>4.066e-05</v>
+        <v>4.065e-05</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>572.006198</v>
+        <v>571.7388089999999</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00174823</v>
+        <v>0.00174905</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4590.90068</v>
+        <v>4577.161678</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021782</v>
+        <v>0.00021848</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.126855</v>
+        <v>21.162454</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04733312</v>
+        <v>0.0472535</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.978401</v>
+        <v>16.950552</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05889836</v>
+        <v>0.05899513</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.923734</v>
+        <v>2.912732</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34202838</v>
+        <v>0.34332029</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2576.948396</v>
+        <v>2569.139667</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00038806</v>
+        <v>0.00038924</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3763.160564</v>
+        <v>3725.483569</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026573</v>
+        <v>0.00026842</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176789</v>
+        <v>0.00176492</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>565.645246</v>
+        <v>566.5983670000001</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176789</v>
+        <v>0.00176492</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.966421</v>
+        <v>16.947691</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05893995</v>
+        <v>0.05900509</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>19.41701</v>
+        <v>18.961288</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05150124</v>
+        <v>0.05273903</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.3127</v>
+        <v>25.2603</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03950586</v>
+        <v>0.03958781</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>25 March 2026 — 06:58 UTC</t>
+          <t>26 March 2026 — 07:04 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 26 March 2026  |  07:04 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 27 March 2026  |  07:03 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.541246</v>
+        <v>132.813465</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.57</v>
+        <v>44.67</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.76</v>
+        <v>28.82</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.09</v>
+        <v>41.17</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>920.836259</v>
+        <v>921.5132</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.75</v>
+        <v>279.96</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>379.66</v>
+        <v>379.94</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>598.54</v>
+        <v>598.98</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>651.64</v>
+        <v>653.42</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>704.28</v>
+        <v>706.2</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>679.92</v>
+        <v>681.77</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.863743</v>
+        <v>13.821664</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.04</v>
+        <v>15</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.33</v>
+        <v>17.28</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>799.1900000000001</v>
+        <v>801.37</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>666.89</v>
+        <v>668.7</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>781.91</v>
+        <v>784.04</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2975.095377</v>
+        <v>2977.370928</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3970.26</v>
+        <v>3973.3</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3831.92</v>
+        <v>3834.85</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4313.89</v>
+        <v>4317.19</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>983.61</v>
+        <v>986.3</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1220.45</v>
+        <v>1223.78</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1019.88</v>
+        <v>1022.66</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.244001</v>
+        <v>95.503606</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>120.9</v>
+        <v>121.23</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>106.77</v>
+        <v>107.06</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116.2</v>
+        <v>116.51</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>786.89</v>
+        <v>789.04</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>684.62</v>
+        <v>686.49</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>679.92</v>
+        <v>681.77</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2286.084927</v>
+        <v>2275.826544</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2405.88</v>
+        <v>2395.08</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>1970.61</v>
+        <v>1961.76</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2857.61</v>
+        <v>2844.78</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.563613</v>
+        <v>52.771794</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.81</v>
+        <v>22.9</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.39</v>
+        <v>19.47</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>23.13</v>
+        <v>23.22</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.76</v>
+        <v>18.91</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>20.32</v>
+        <v>20.48</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.741325</v>
+        <v>155.603496</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.35</v>
+        <v>123.24</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>130.12</v>
+        <v>130.01</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>163.53</v>
+        <v>163.38</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>559.4</v>
+        <v>560.9299999999999</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>540.99</v>
+        <v>542.46</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>509.94</v>
+        <v>511.33</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.978531</v>
+        <v>10.991376</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.74</v>
+        <v>12.76</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.17</v>
+        <v>13.19</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8762.726264999999</v>
+        <v>8764.846654000001</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11218.92</v>
+        <v>11221.63</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>11750.82</v>
+        <v>11753.66</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11216.29</v>
+        <v>11219</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>768.42</v>
+        <v>770.52</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>660.65</v>
+        <v>662.45</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>623.26</v>
+        <v>624.96</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.652926</v>
+        <v>129.727984</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>165.99</v>
+        <v>166.09</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>165.83</v>
+        <v>165.92</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>175.03</v>
+        <v>175.13</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.29</v>
+        <v>17.42</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>19.59</v>
+        <v>19.75</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>183.541926</v>
+        <v>183.918613</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>155.33</v>
+        <v>155.65</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>167.28</v>
+        <v>167.62</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>220.25</v>
+        <v>220.7</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.374747</v>
+        <v>6.37494</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4180.42642</v>
+        <v>4179.221302</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4580.91</v>
+        <v>4579.59</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>6479.66</v>
+        <v>6477.79</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5434.55</v>
+        <v>5432.99</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1739.141887</v>
+        <v>1740.954025</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4641.94</v>
+        <v>4646.78</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3504.37</v>
+        <v>3508.02</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4173.94</v>
+        <v>4178.29</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>731.54</v>
+        <v>733.53</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>636.46</v>
+        <v>638.1900000000001</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>736.58</v>
+        <v>738.59</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.451311</v>
+        <v>46.56209</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.44</v>
+        <v>55.57</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>59.27</v>
+        <v>59.41</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>65.03</v>
+        <v>65.19</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.324045999999999</v>
+        <v>9.329299000000001</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
@@ -3112,13 +3112,13 @@
         <v>1.317</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.688413</v>
+        <v>63.606663</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>78.08</v>
+        <v>77.98</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>78.66</v>
+        <v>78.55</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>82.79000000000001</v>
+        <v>82.69</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>18.94</v>
+        <v>19.09</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>18.68</v>
+        <v>18.83</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>624.39</v>
+        <v>626.09</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>567.73</v>
+        <v>569.28</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>708.25</v>
+        <v>710.1799999999999</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1377.066908</v>
+        <v>1384.423957</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1082.37</v>
+        <v>1088.16</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1359.58</v>
+        <v>1366.84</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>757.39</v>
+        <v>761.4299999999999</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1458.768366</v>
+        <v>1458.426834</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>2050.59</v>
+        <v>2050.11</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1910.99</v>
+        <v>1910.54</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2115.21</v>
+        <v>2114.72</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.1524</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>866.78</v>
+        <v>869.14</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>735.4400000000001</v>
+        <v>737.45</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>651.59</v>
+        <v>653.36</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.336314</v>
+        <v>14.390704</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>20.22</v>
+        <v>20.3</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>19.07</v>
+        <v>19.14</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.94</v>
+        <v>23.03</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>16.947691</v>
+        <v>17.079628</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.35</v>
+        <v>23.54</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>22.88</v>
+        <v>23.06</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>544.306151</v>
+        <v>511.988564</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>354.34</v>
+        <v>333.3</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>330.72</v>
+        <v>311.08</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>299.37</v>
+        <v>281.59</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2569.139667</v>
+        <v>2563.751605</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2648.01</v>
+        <v>2642.46</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2599.97</v>
+        <v>2594.52</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3211.42</v>
+        <v>3204.69</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>639.35</v>
+        <v>641.09</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>669.15</v>
+        <v>670.98</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>623.26</v>
+        <v>624.96</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,25 +3919,25 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.912732</v>
+        <v>2.92239</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="K49" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="M49" s="33" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3725.483569</v>
+        <v>3717.465047</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5144.89</v>
+        <v>5133.82</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4284.31</v>
+        <v>4275.08</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4843.13</v>
+        <v>4832.7</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>18.961288</v>
+        <v>18.810418</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>24.28</v>
+        <v>24.08</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>19.36</v>
+        <v>19.21</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>24.65</v>
+        <v>24.45</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.2603</v>
+        <v>25.3672</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>54.81</v>
+        <v>55.05</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>2.05</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>51.78</v>
+        <v>52</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.15</v>
+        <v>39.32</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.391</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-26 07:04 UTC</t>
+          <t>2026-03-27 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>132.541246</v>
+        <v>132.813465</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.44</v>
+        <v>42.53</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.44</v>
+        <v>42.53</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.44</v>
+        <v>42.53</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>26.02</v>
+        <v>26.07</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>26.02</v>
+        <v>26.07</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>26.02</v>
+        <v>26.07</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.09</v>
+        <v>41.17</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>920.836259</v>
+        <v>921.5132</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.31</v>
+        <v>266.5</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.31</v>
+        <v>266.5</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.31</v>
+        <v>266.5</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>351.94</v>
+        <v>352.2</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>351.94</v>
+        <v>352.2</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>351.94</v>
+        <v>352.2</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>598.54</v>
+        <v>598.98</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>620.4299999999999</v>
+        <v>622.12</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>620.4299999999999</v>
+        <v>622.12</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>620.4299999999999</v>
+        <v>622.12</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>704.28</v>
+        <v>706.2</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>704.28</v>
+        <v>706.2</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>704.28</v>
+        <v>706.2</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>679.92</v>
+        <v>681.77</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.863743</v>
+        <v>13.821664</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.18</v>
+        <v>14.14</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.18</v>
+        <v>14.14</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.18</v>
+        <v>14.14</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.33</v>
+        <v>17.28</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>760.88</v>
+        <v>762.96</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>760.88</v>
+        <v>762.96</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>760.88</v>
+        <v>762.96</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>666.89</v>
+        <v>668.7</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>666.89</v>
+        <v>668.7</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>666.89</v>
+        <v>668.7</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>781.91</v>
+        <v>784.04</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2975.095377</v>
+        <v>2977.370928</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3503.47</v>
+        <v>3506.15</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3503.47</v>
+        <v>3506.15</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3503.47</v>
+        <v>3506.15</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3831.92</v>
+        <v>3834.85</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3831.92</v>
+        <v>3834.85</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3831.92</v>
+        <v>3834.85</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4313.89</v>
+        <v>4317.19</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>936.47</v>
+        <v>939.03</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>936.47</v>
+        <v>939.03</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>936.47</v>
+        <v>939.03</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1220.45</v>
+        <v>1223.78</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1220.45</v>
+        <v>1223.78</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1220.45</v>
+        <v>1223.78</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1019.88</v>
+        <v>1022.66</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.244001</v>
+        <v>95.503606</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.23</v>
+        <v>108.52</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.23</v>
+        <v>108.52</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.23</v>
+        <v>108.52</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>106.77</v>
+        <v>107.06</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>106.77</v>
+        <v>107.06</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>106.77</v>
+        <v>107.06</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116.2</v>
+        <v>116.51</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>749.16</v>
+        <v>751.2</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>749.16</v>
+        <v>751.2</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>749.16</v>
+        <v>751.2</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>651.76</v>
+        <v>653.53</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>651.76</v>
+        <v>653.53</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>651.76</v>
+        <v>653.53</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>679.92</v>
+        <v>681.77</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2286.084927</v>
+        <v>2275.826544</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2125.37</v>
+        <v>2115.84</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2125.37</v>
+        <v>2115.84</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2125.37</v>
+        <v>2115.84</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1970.61</v>
+        <v>1961.76</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1970.61</v>
+        <v>1961.76</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1970.61</v>
+        <v>1961.76</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2857.61</v>
+        <v>2844.78</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.563613</v>
+        <v>52.771794</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.83</v>
+        <v>16.9</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.83</v>
+        <v>16.9</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.83</v>
+        <v>16.9</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>23.13</v>
+        <v>23.22</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>20.32</v>
+        <v>20.48</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>20.32</v>
+        <v>20.48</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>20.32</v>
+        <v>20.48</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.741325</v>
+        <v>155.603496</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.18</v>
+        <v>106.09</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.18</v>
+        <v>106.09</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.18</v>
+        <v>106.09</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>98.13</v>
+        <v>98.05</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>98.13</v>
+        <v>98.05</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>98.13</v>
+        <v>98.05</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>163.53</v>
+        <v>163.38</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>532.6</v>
+        <v>534.05</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>532.6</v>
+        <v>534.05</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>532.6</v>
+        <v>534.05</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>515.04</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>515.04</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>515.04</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>509.94</v>
+        <v>511.33</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.978531</v>
+        <v>10.991376</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.17</v>
+        <v>13.19</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8762.726264999999</v>
+        <v>8764.846654000001</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10409.24</v>
+        <v>10411.76</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10409.24</v>
+        <v>10411.76</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10409.24</v>
+        <v>10411.76</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>11750.82</v>
+        <v>11753.66</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>11750.82</v>
+        <v>11753.66</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>11750.82</v>
+        <v>11753.66</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11216.29</v>
+        <v>11219</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>731.59</v>
+        <v>733.59</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>731.59</v>
+        <v>733.59</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>731.59</v>
+        <v>733.59</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>660.65</v>
+        <v>662.45</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>660.65</v>
+        <v>662.45</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>660.65</v>
+        <v>662.45</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>623.26</v>
+        <v>624.96</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.652926</v>
+        <v>129.727984</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>158.03</v>
+        <v>158.13</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>158.03</v>
+        <v>158.13</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>158.03</v>
+        <v>158.13</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>165.83</v>
+        <v>165.92</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>165.83</v>
+        <v>165.92</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>165.83</v>
+        <v>165.92</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>175.03</v>
+        <v>175.13</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.28</v>
+        <v>16.41</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.28</v>
+        <v>16.41</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.28</v>
+        <v>16.41</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>19.59</v>
+        <v>19.75</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>19.59</v>
+        <v>19.75</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>19.59</v>
+        <v>19.75</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>183.541926</v>
+        <v>183.918613</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>134.61</v>
+        <v>134.89</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>134.61</v>
+        <v>134.89</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>134.61</v>
+        <v>134.89</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>145.99</v>
+        <v>146.29</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>145.99</v>
+        <v>146.29</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>145.99</v>
+        <v>146.29</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>220.25</v>
+        <v>220.7</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.374747</v>
+        <v>6.37494</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4180.42642</v>
+        <v>4179.221302</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4059.19</v>
+        <v>4058.02</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4059.19</v>
+        <v>4058.02</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4059.19</v>
+        <v>4058.02</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>6479.66</v>
+        <v>6477.79</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>6479.66</v>
+        <v>6477.79</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>6479.66</v>
+        <v>6477.79</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5434.55</v>
+        <v>5432.99</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1739.141887</v>
+        <v>1740.954025</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4311.68</v>
+        <v>4316.17</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4311.68</v>
+        <v>4316.17</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4311.68</v>
+        <v>4316.17</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3504.37</v>
+        <v>3508.02</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3504.37</v>
+        <v>3508.02</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3504.37</v>
+        <v>3508.02</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4173.94</v>
+        <v>4178.29</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>690.63</v>
+        <v>692.51</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>690.63</v>
+        <v>692.51</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>690.63</v>
+        <v>692.51</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>600.8200000000001</v>
+        <v>602.46</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>600.8200000000001</v>
+        <v>602.46</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>600.8200000000001</v>
+        <v>602.46</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>736.58</v>
+        <v>738.59</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.451311</v>
+        <v>46.56209</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.82</v>
+        <v>51.94</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.82</v>
+        <v>51.94</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.82</v>
+        <v>51.94</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>59.27</v>
+        <v>59.41</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>59.27</v>
+        <v>59.41</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>59.27</v>
+        <v>59.41</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>65.03</v>
+        <v>65.19</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.324045999999999</v>
+        <v>9.329299000000001</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
@@ -6156,25 +6156,25 @@
         <v>1.317</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.688413</v>
+        <v>63.606663</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.37</v>
+        <v>72.28</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.37</v>
+        <v>72.28</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.37</v>
+        <v>72.28</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>78.66</v>
+        <v>78.55</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>78.66</v>
+        <v>78.55</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>78.66</v>
+        <v>78.55</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>82.79000000000001</v>
+        <v>82.69</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>18.04</v>
+        <v>18.18</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>18.04</v>
+        <v>18.18</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>18.04</v>
+        <v>18.18</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>18.68</v>
+        <v>18.83</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>18.68</v>
+        <v>18.83</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>18.68</v>
+        <v>18.83</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>624.39</v>
+        <v>626.09</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>624.39</v>
+        <v>626.09</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>624.39</v>
+        <v>626.09</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>567.73</v>
+        <v>569.28</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>567.73</v>
+        <v>569.28</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>567.73</v>
+        <v>569.28</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>708.25</v>
+        <v>710.1799999999999</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1377.066908</v>
+        <v>1384.423957</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>697.0700000000001</v>
+        <v>700.8</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>738.9299999999999</v>
+        <v>742.88</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>766.75</v>
+        <v>770.85</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>796.63</v>
+        <v>800.89</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>796.63</v>
+        <v>800.89</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>796.63</v>
+        <v>800.89</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>757.39</v>
+        <v>761.4299999999999</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1458.768366</v>
+        <v>1458.426834</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1779.41</v>
+        <v>1778.99</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1779.41</v>
+        <v>1778.99</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1779.41</v>
+        <v>1778.99</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1910.99</v>
+        <v>1910.54</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1910.99</v>
+        <v>1910.54</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1910.99</v>
+        <v>1910.54</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2115.21</v>
+        <v>2114.72</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.1524</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>825.25</v>
+        <v>827.5</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>825.25</v>
+        <v>827.5</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>825.25</v>
+        <v>827.5</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>735.4400000000001</v>
+        <v>737.45</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>735.4400000000001</v>
+        <v>737.45</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>735.4400000000001</v>
+        <v>737.45</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>651.59</v>
+        <v>653.36</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.336314</v>
+        <v>14.390704</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.66</v>
+        <v>18.73</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.66</v>
+        <v>18.73</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.66</v>
+        <v>18.73</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>19.07</v>
+        <v>19.14</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>19.07</v>
+        <v>19.14</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>19.07</v>
+        <v>19.14</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.94</v>
+        <v>23.03</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>16.947691</v>
+        <v>17.079628</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.71</v>
+        <v>21.88</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.71</v>
+        <v>21.88</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.71</v>
+        <v>21.88</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>22.88</v>
+        <v>23.06</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>544.306151</v>
+        <v>511.988564</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>331.75</v>
+        <v>312.06</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>331.75</v>
+        <v>312.06</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>331.75</v>
+        <v>312.06</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>309.27</v>
+        <v>290.91</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>309.27</v>
+        <v>290.91</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>309.27</v>
+        <v>290.91</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>299.37</v>
+        <v>281.59</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2569.139667</v>
+        <v>2563.751605</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2414.99</v>
+        <v>2409.93</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2414.99</v>
+        <v>2409.93</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2414.99</v>
+        <v>2409.93</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2599.97</v>
+        <v>2594.52</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2599.97</v>
+        <v>2594.52</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2599.97</v>
+        <v>2594.52</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3211.42</v>
+        <v>3204.69</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>608.7</v>
+        <v>610.36</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>608.7</v>
+        <v>610.36</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>608.7</v>
+        <v>610.36</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>669.15</v>
+        <v>670.98</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>669.15</v>
+        <v>670.98</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>669.15</v>
+        <v>670.98</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>623.26</v>
+        <v>624.96</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,49 +7055,49 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.912732</v>
+        <v>2.92239</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="N41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R41" s="18" t="n">
         <v>0.78</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="T41" s="40" t="n">
         <v>0</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3725.483569</v>
+        <v>3717.465047</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5144.89</v>
+        <v>5133.82</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5144.89</v>
+        <v>5133.82</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5144.89</v>
+        <v>5133.82</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4284.31</v>
+        <v>4275.08</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4284.31</v>
+        <v>4275.08</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4284.31</v>
+        <v>4275.08</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4843.13</v>
+        <v>4832.7</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>18.961288</v>
+        <v>18.810418</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.09</v>
+        <v>23.9</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.09</v>
+        <v>23.9</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.09</v>
+        <v>23.9</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>19.36</v>
+        <v>19.21</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>19.36</v>
+        <v>19.21</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>19.36</v>
+        <v>19.21</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>24.65</v>
+        <v>24.45</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.2603</v>
+        <v>25.3672</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>39.41</v>
+        <v>39.57</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>39.41</v>
+        <v>39.57</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>39.41</v>
+        <v>39.57</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>38.4</v>
+        <v>38.56</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>38.4</v>
+        <v>38.56</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>38.4</v>
+        <v>38.56</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.15</v>
+        <v>39.32</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.391</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.541246</v>
+        <v>132.813465</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.44</v>
+        <v>42.53</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>920.836259</v>
+        <v>921.5132</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.31</v>
+        <v>266.5</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>620.4299999999999</v>
+        <v>622.12</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.863743</v>
+        <v>13.821664</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.18</v>
+        <v>14.14</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>760.88</v>
+        <v>762.96</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2975.095377</v>
+        <v>2977.370928</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3503.47</v>
+        <v>3506.15</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>936.47</v>
+        <v>939.03</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.244001</v>
+        <v>95.503606</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.23</v>
+        <v>108.52</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>749.16</v>
+        <v>751.2</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2286.084927</v>
+        <v>2275.826544</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2125.37</v>
+        <v>2115.84</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.563613</v>
+        <v>52.771794</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.741325</v>
+        <v>155.603496</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.18</v>
+        <v>106.09</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>532.6</v>
+        <v>534.05</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.978531</v>
+        <v>10.991376</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8762.726264999999</v>
+        <v>8764.846654000001</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10409.24</v>
+        <v>10411.76</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>731.59</v>
+        <v>733.59</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.652926</v>
+        <v>129.727984</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>158.03</v>
+        <v>158.13</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.28</v>
+        <v>16.41</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>183.541926</v>
+        <v>183.918613</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>134.61</v>
+        <v>134.89</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.374747</v>
+        <v>6.37494</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>0.2</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4180.42642</v>
+        <v>4179.221302</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4059.19</v>
+        <v>4058.02</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1739.141887</v>
+        <v>1740.954025</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4311.68</v>
+        <v>4316.17</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>690.63</v>
+        <v>692.51</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.451311</v>
+        <v>46.56209</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.82</v>
+        <v>51.94</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.324045999999999</v>
+        <v>9.329299000000001</v>
       </c>
       <c r="F28" s="28" t="n">
         <v>10.79</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.688413</v>
+        <v>63.606663</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.37</v>
+        <v>72.28</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>18.04</v>
+        <v>18.18</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>624.39</v>
+        <v>626.09</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1377.066908</v>
+        <v>1384.423957</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>697.0700000000001</v>
+        <v>700.8</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1458.768366</v>
+        <v>1458.426834</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1779.41</v>
+        <v>1778.99</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.2198</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>825.25</v>
+        <v>827.5</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.336314</v>
+        <v>14.390704</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.66</v>
+        <v>18.73</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>16.947691</v>
+        <v>17.079628</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>544.306151</v>
+        <v>511.988564</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>331.75</v>
+        <v>312.06</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2569.139667</v>
+        <v>2563.751605</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2414.99</v>
+        <v>2409.93</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>608.7</v>
+        <v>610.36</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.912732</v>
+        <v>2.92239</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.8661</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3725.483569</v>
+        <v>3717.465047</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5144.89</v>
+        <v>5133.82</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>18.961288</v>
+        <v>18.810418</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.09</v>
+        <v>23.9</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.2603</v>
+        <v>25.3672</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>39.41</v>
+        <v>39.57</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.56</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>132.541246</v>
+        <v>132.813465</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.57</v>
+        <v>44.67</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.76</v>
+        <v>28.82</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.09</v>
+        <v>41.17</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.563613</v>
+        <v>52.771794</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.81</v>
+        <v>22.9</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.39</v>
+        <v>19.47</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>23.13</v>
+        <v>23.22</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.374747</v>
+        <v>6.37494</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.324045999999999</v>
+        <v>9.329299000000001</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
@@ -10373,13 +10373,13 @@
         <v>1.317</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>544.306151</v>
+        <v>511.988564</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>354.34</v>
+        <v>333.3</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>330.72</v>
+        <v>311.08</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>299.37</v>
+        <v>281.59</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,25 +10439,25 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.912732</v>
+        <v>2.92239</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.7566000000000001</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>0.78</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="K10" s="41" t="n">
         <v>0</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>651.64</v>
+        <v>653.42</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>704.28</v>
+        <v>706.2</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>679.92</v>
+        <v>681.77</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>799.1900000000001</v>
+        <v>801.37</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>666.89</v>
+        <v>668.7</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>781.91</v>
+        <v>784.04</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.244001</v>
+        <v>95.503606</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>120.9</v>
+        <v>121.23</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.121</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>106.77</v>
+        <v>107.06</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116.2</v>
+        <v>116.51</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.978531</v>
+        <v>10.991376</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.74</v>
+        <v>12.76</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.17</v>
+        <v>13.19</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8762.726264999999</v>
+        <v>8764.846654000001</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11218.92</v>
+        <v>11221.63</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>11750.82</v>
+        <v>11753.66</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11216.29</v>
+        <v>11219</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>768.42</v>
+        <v>770.52</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>660.65</v>
+        <v>662.45</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>623.26</v>
+        <v>624.96</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>183.541926</v>
+        <v>183.918613</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>155.33</v>
+        <v>155.65</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>167.28</v>
+        <v>167.62</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>220.25</v>
+        <v>220.7</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>731.54</v>
+        <v>733.53</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>636.46</v>
+        <v>638.1900000000001</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>736.58</v>
+        <v>738.59</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>624.39</v>
+        <v>626.09</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>567.73</v>
+        <v>569.28</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>708.25</v>
+        <v>710.1799999999999</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1377.066908</v>
+        <v>1384.423957</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1082.37</v>
+        <v>1088.16</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1359.58</v>
+        <v>1366.84</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>757.39</v>
+        <v>761.4299999999999</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>866.78</v>
+        <v>869.14</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>735.4400000000001</v>
+        <v>737.45</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>651.59</v>
+        <v>653.36</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>639.35</v>
+        <v>641.09</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>669.15</v>
+        <v>670.98</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>623.26</v>
+        <v>624.96</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2975.095377</v>
+        <v>2977.370928</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3970.26</v>
+        <v>3973.3</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3831.92</v>
+        <v>3834.85</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4313.89</v>
+        <v>4317.19</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.741325</v>
+        <v>155.603496</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.35</v>
+        <v>123.24</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>130.12</v>
+        <v>130.01</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>163.53</v>
+        <v>163.38</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.652926</v>
+        <v>129.727984</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>165.99</v>
+        <v>166.09</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>165.83</v>
+        <v>165.92</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>175.03</v>
+        <v>175.13</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4180.42642</v>
+        <v>4179.221302</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4580.91</v>
+        <v>4579.59</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>6479.66</v>
+        <v>6477.79</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5434.55</v>
+        <v>5432.99</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1739.141887</v>
+        <v>1740.954025</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4641.94</v>
+        <v>4646.78</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3504.37</v>
+        <v>3508.02</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4173.94</v>
+        <v>4178.29</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.451311</v>
+        <v>46.56209</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.44</v>
+        <v>55.57</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>59.27</v>
+        <v>59.41</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>65.03</v>
+        <v>65.19</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1458.768366</v>
+        <v>1458.426834</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>2050.59</v>
+        <v>2050.11</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1910.99</v>
+        <v>1910.54</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2115.21</v>
+        <v>2114.72</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.1524</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.336314</v>
+        <v>14.390704</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>20.22</v>
+        <v>20.3</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>19.07</v>
+        <v>19.14</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.94</v>
+        <v>23.03</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2569.139667</v>
+        <v>2563.751605</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2648.01</v>
+        <v>2642.46</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2599.97</v>
+        <v>2594.52</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3211.42</v>
+        <v>3204.69</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3725.483569</v>
+        <v>3717.465047</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5144.89</v>
+        <v>5133.82</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4284.31</v>
+        <v>4275.08</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4843.13</v>
+        <v>4832.7</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>983.61</v>
+        <v>986.3</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1220.45</v>
+        <v>1223.78</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1019.88</v>
+        <v>1022.66</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>786.89</v>
+        <v>789.04</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>684.62</v>
+        <v>686.49</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>679.92</v>
+        <v>681.77</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2286.084927</v>
+        <v>2275.826544</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2405.88</v>
+        <v>2395.08</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>1970.61</v>
+        <v>1961.76</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2857.61</v>
+        <v>2844.78</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>559.4</v>
+        <v>560.9299999999999</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>540.99</v>
+        <v>542.46</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>509.94</v>
+        <v>511.33</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>920.836259</v>
+        <v>921.5132</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>279.75</v>
+        <v>279.96</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>379.66</v>
+        <v>379.94</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>598.54</v>
+        <v>598.98</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.863743</v>
+        <v>13.821664</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15.04</v>
+        <v>15</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.33</v>
+        <v>17.28</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.76</v>
+        <v>18.91</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>1.199</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>20.32</v>
+        <v>20.48</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.29</v>
+        <v>17.42</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>19.59</v>
+        <v>19.75</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.688413</v>
+        <v>63.606663</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>78.08</v>
+        <v>77.98</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>78.66</v>
+        <v>78.55</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>82.79000000000001</v>
+        <v>82.69</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>18.94</v>
+        <v>19.09</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>18.68</v>
+        <v>18.83</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.19</v>
+        <v>21.35</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>16.947691</v>
+        <v>17.079628</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.35</v>
+        <v>23.54</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>22.88</v>
+        <v>23.06</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>18.961288</v>
+        <v>18.810418</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>24.28</v>
+        <v>24.08</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>19.36</v>
+        <v>19.21</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>24.65</v>
+        <v>24.45</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.2603</v>
+        <v>25.3672</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>2.17</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>54.81</v>
+        <v>55.05</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>2.05</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>51.78</v>
+        <v>52</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.15</v>
+        <v>39.32</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.391</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4641.94</v>
+        <v>4646.78</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>2.17</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>54.81</v>
+        <v>55.05</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.75</v>
+        <v>279.96</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>983.61</v>
+        <v>986.3</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.57</v>
+        <v>44.67</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>866.78</v>
+        <v>869.14</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.81</v>
+        <v>22.9</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>354.34</v>
+        <v>333.3</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>799.1900000000001</v>
+        <v>801.37</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1082.37</v>
+        <v>1088.16</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>20.22</v>
+        <v>20.3</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.35</v>
+        <v>123.24</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2050.59</v>
+        <v>2050.11</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>155.33</v>
+        <v>155.65</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>786.89</v>
+        <v>789.04</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>559.4</v>
+        <v>560.9299999999999</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>920.836259</v>
+        <v>921.5132</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108597</v>
+        <v>0.00108517</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2975.095377</v>
+        <v>2977.370928</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033612</v>
+        <v>0.00033587</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.863743</v>
+        <v>13.821664</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07213058999999999</v>
+        <v>0.07235018999999999</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2286.084927</v>
+        <v>2275.826544</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00043743</v>
+        <v>0.0004394</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.244001</v>
+        <v>95.503606</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01049935</v>
+        <v>0.01047081</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.541246</v>
+        <v>132.813465</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00754482</v>
+        <v>0.00752936</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.563613</v>
+        <v>52.771794</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01902457</v>
+        <v>0.01894952</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.741325</v>
+        <v>155.603496</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.0064209</v>
+        <v>0.00642659</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.978531</v>
+        <v>10.991376</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09108687</v>
+        <v>0.09098042000000001</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.192116</v>
+        <v>74.188412</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347852</v>
+        <v>0.01347919</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8762.726264999999</v>
+        <v>8764.846654000001</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011412</v>
+        <v>0.00011409</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.652926</v>
+        <v>129.727984</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.0077129</v>
+        <v>0.00770844</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>424.948775</v>
+        <v>426.107053</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00235322</v>
+        <v>0.00234683</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>183.541926</v>
+        <v>183.918613</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00544835</v>
+        <v>0.00543719</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05899513</v>
+        <v>0.05853803</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.374747</v>
+        <v>6.37494</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15686897</v>
+        <v>0.15686422</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.324045999999999</v>
+        <v>9.329299000000001</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10724958</v>
+        <v>0.10718919</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4180.42642</v>
+        <v>4179.221302</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00023921</v>
+        <v>0.00023928</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.950679</v>
+        <v>39.897062</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02503086</v>
+        <v>0.0250645</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.451311</v>
+        <v>46.56209</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02152792</v>
+        <v>0.0214767</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1739.141887</v>
+        <v>1740.954025</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.000575</v>
+        <v>0.0005744</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.688413</v>
+        <v>63.606663</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01570144</v>
+        <v>0.01572162</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05899513</v>
+        <v>0.05853803</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1377.066908</v>
+        <v>1384.423957</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00072618</v>
+        <v>0.00072232</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1458.768366</v>
+        <v>1458.426834</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068551</v>
+        <v>0.00068567</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.336314</v>
+        <v>14.390704</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.06975294</v>
+        <v>0.0694893</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>544.306151</v>
+        <v>511.988564</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.0018372</v>
+        <v>0.00195317</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.7388089999999</v>
+        <v>571.3158079999999</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00174905</v>
+        <v>0.00175035</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4577.161678</v>
+        <v>4582.400006</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021848</v>
+        <v>0.00021823</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.162454</v>
+        <v>21.220136</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.0472535</v>
+        <v>0.04712505</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>16.950552</v>
+        <v>17.082912</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05899513</v>
+        <v>0.05853803</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.912732</v>
+        <v>2.92239</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34332029</v>
+        <v>0.34218568</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2569.139667</v>
+        <v>2563.751605</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00038924</v>
+        <v>0.00039005</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3725.483569</v>
+        <v>3717.465047</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026842</v>
+        <v>0.000269</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176492</v>
+        <v>0.00176012</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>566.5983670000001</v>
+        <v>568.142738</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176492</v>
+        <v>0.00176012</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>16.947691</v>
+        <v>17.079628</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05900509</v>
+        <v>0.05854928</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>18.961288</v>
+        <v>18.810418</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05273903</v>
+        <v>0.05316203</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.2603</v>
+        <v>25.3672</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03958781</v>
+        <v>0.03942098</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>26 March 2026 — 07:04 UTC</t>
+          <t>27 March 2026 — 07:03 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 27 March 2026  |  07:03 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 28 March 2026  |  06:53 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.813465</v>
+        <v>132.722332</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.67</v>
+        <v>44.63</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>28.82</v>
+        <v>28.8</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.17</v>
+        <v>41.14</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>921.5132</v>
+        <v>922.0653620000001</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>279.96</v>
+        <v>280.12</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>379.94</v>
+        <v>380.17</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>598.98</v>
+        <v>599.34</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>653.42</v>
+        <v>654.9400000000001</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>706.2</v>
+        <v>707.84</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>681.77</v>
+        <v>683.36</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>13.821664</v>
+        <v>14.031222</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>14.39</v>
+        <v>14.61</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.28</v>
+        <v>17.54</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>801.37</v>
+        <v>803.23</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>668.7</v>
+        <v>670.26</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>784.04</v>
+        <v>785.86</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2977.370928</v>
+        <v>2979.243996</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3973.3</v>
+        <v>3975.8</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3834.85</v>
+        <v>3837.27</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4317.19</v>
+        <v>4319.9</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>986.3</v>
+        <v>988.59</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1223.78</v>
+        <v>1226.62</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1022.66</v>
+        <v>1025.03</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.503606</v>
+        <v>95.725523</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>121.23</v>
+        <v>121.51</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>107.06</v>
+        <v>107.31</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116.51</v>
+        <v>116.79</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>789.04</v>
+        <v>790.87</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>686.49</v>
+        <v>688.08</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>681.77</v>
+        <v>683.36</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2275.826544</v>
+        <v>2291.748711</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2395.08</v>
+        <v>2411.84</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>1961.76</v>
+        <v>1975.49</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2844.78</v>
+        <v>2864.69</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.771794</v>
+        <v>52.745937</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.9</v>
+        <v>22.89</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>19.47</v>
+        <v>19.46</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>23.22</v>
+        <v>23.21</v>
       </c>
       <c r="M21" s="20" t="n">
         <v>0.1057</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.91</v>
+        <v>18.95</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>20.48</v>
+        <v>20.53</v>
       </c>
       <c r="K22" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.603496</v>
+        <v>155.27097</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>123.24</v>
+        <v>122.97</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>130.01</v>
+        <v>129.73</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>163.38</v>
+        <v>163.03</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>560.9299999999999</v>
+        <v>562.23</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>542.46</v>
+        <v>543.72</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>511.33</v>
+        <v>512.52</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>10.991376</v>
+        <v>11.020442</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>12.76</v>
+        <v>12.79</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8764.846654000001</v>
+        <v>8767.130045</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11221.63</v>
+        <v>11224.56</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>11753.66</v>
+        <v>11756.72</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11219</v>
+        <v>11221.93</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>770.52</v>
+        <v>772.3099999999999</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>662.45</v>
+        <v>663.99</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>624.96</v>
+        <v>626.41</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.727984</v>
+        <v>129.765701</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>166.09</v>
+        <v>166.14</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>165.92</v>
+        <v>165.97</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>175.13</v>
+        <v>175.18</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.42</v>
+        <v>17.46</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>19.75</v>
+        <v>19.79</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>183.918613</v>
+        <v>183.689846</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>155.65</v>
+        <v>155.46</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>167.62</v>
+        <v>167.41</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>220.7</v>
+        <v>220.43</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.37494</v>
+        <v>6.374935</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4179.221302</v>
+        <v>4174.357607</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4579.59</v>
+        <v>4574.26</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>6477.79</v>
+        <v>6470.25</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5432.99</v>
+        <v>5426.66</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1740.954025</v>
+        <v>1744.734226</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4646.78</v>
+        <v>4656.87</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3508.02</v>
+        <v>3515.64</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4178.29</v>
+        <v>4187.36</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>733.53</v>
+        <v>735.23</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>638.1900000000001</v>
+        <v>639.6799999999999</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>738.59</v>
+        <v>740.3</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.56209</v>
+        <v>46.664963</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.57</v>
+        <v>55.69</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>59.41</v>
+        <v>59.54</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>65.19</v>
+        <v>65.33</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,25 +3100,25 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.329299000000001</v>
+        <v>9.343978</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="I36" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="K36" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="L36" s="28" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="M36" s="29" t="n">
         <v>0.1973</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,19 +3163,19 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.606663</v>
+        <v>63.61008</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>77.98</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>78.55</v>
+        <v>78.56</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,25 +3226,25 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>19.09</v>
+        <v>19.14</v>
       </c>
       <c r="I38" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="K38" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>626.09</v>
+        <v>627.55</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>569.28</v>
+        <v>570.6</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>710.1799999999999</v>
+        <v>711.83</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1384.423957</v>
+        <v>1382.529699</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1088.16</v>
+        <v>1086.67</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1366.84</v>
+        <v>1364.97</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>761.4299999999999</v>
+        <v>760.39</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1458.426834</v>
+        <v>1457.46283</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>2050.11</v>
+        <v>2048.76</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1910.54</v>
+        <v>1909.28</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2114.72</v>
+        <v>2113.32</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.1524</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>869.14</v>
+        <v>871.16</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>737.45</v>
+        <v>739.16</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>653.36</v>
+        <v>654.88</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.390704</v>
+        <v>14.114736</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>20.3</v>
+        <v>19.91</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>19.14</v>
+        <v>18.77</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>23.03</v>
+        <v>22.58</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>17.079628</v>
+        <v>17.121639</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="I45" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>23.54</v>
+        <v>23.59</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>23.06</v>
+        <v>23.11</v>
       </c>
       <c r="M45" s="33" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>511.988564</v>
+        <v>511.014831</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>333.3</v>
+        <v>332.67</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>311.08</v>
+        <v>310.49</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>281.59</v>
+        <v>281.06</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2563.751605</v>
+        <v>2579.094525</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2642.46</v>
+        <v>2658.27</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2594.52</v>
+        <v>2610.04</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3204.69</v>
+        <v>3223.87</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>641.09</v>
+        <v>642.58</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>670.98</v>
+        <v>672.54</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>624.96</v>
+        <v>626.41</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,13 +3919,13 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.92239</v>
+        <v>2.927391</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.7566000000000001</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3717.465047</v>
+        <v>3724.737851</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5133.82</v>
+        <v>5143.86</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4275.08</v>
+        <v>4283.45</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4832.7</v>
+        <v>4842.16</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>18.810418</v>
+        <v>18.969397</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>24.08</v>
+        <v>24.29</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>19.21</v>
+        <v>19.37</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>24.45</v>
+        <v>24.66</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
         </is>
       </c>
       <c r="F52" s="26" t="n">
-        <v>25.3672</v>
+        <v>25.3745</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>55.05</v>
+        <v>55.06</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>2.05</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>52</v>
+        <v>52.02</v>
       </c>
       <c r="K52" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="L52" s="28" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
       <c r="M52" s="29" t="n">
         <v>0.391</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-27 07:03 UTC</t>
+          <t>2026-03-28 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>132.813465</v>
+        <v>132.722332</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>42.53</v>
+        <v>42.5</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>42.53</v>
+        <v>42.5</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>42.53</v>
+        <v>42.5</v>
       </c>
       <c r="L3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>26.07</v>
+        <v>26.05</v>
       </c>
       <c r="N3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>26.07</v>
+        <v>26.05</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>0.1963</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>26.07</v>
+        <v>26.05</v>
       </c>
       <c r="R3" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.17</v>
+        <v>41.14</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>921.5132</v>
+        <v>922.0653620000001</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.5</v>
+        <v>266.66</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.5</v>
+        <v>266.66</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.5</v>
+        <v>266.66</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>352.2</v>
+        <v>352.41</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>352.2</v>
+        <v>352.41</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>352.2</v>
+        <v>352.41</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>598.98</v>
+        <v>599.34</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>622.12</v>
+        <v>623.5599999999999</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>622.12</v>
+        <v>623.5599999999999</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>622.12</v>
+        <v>623.5599999999999</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>706.2</v>
+        <v>707.84</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>706.2</v>
+        <v>707.84</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>706.2</v>
+        <v>707.84</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>681.77</v>
+        <v>683.36</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>13.821664</v>
+        <v>14.031222</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.14</v>
+        <v>14.35</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.14</v>
+        <v>14.35</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.14</v>
+        <v>14.35</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>14.39</v>
+        <v>14.61</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>14.39</v>
+        <v>14.61</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>14.39</v>
+        <v>14.61</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.28</v>
+        <v>17.54</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>762.96</v>
+        <v>764.73</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>762.96</v>
+        <v>764.73</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>762.96</v>
+        <v>764.73</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>668.7</v>
+        <v>670.26</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>668.7</v>
+        <v>670.26</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>668.7</v>
+        <v>670.26</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>784.04</v>
+        <v>785.86</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2977.370928</v>
+        <v>2979.243996</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3506.15</v>
+        <v>3508.36</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3506.15</v>
+        <v>3508.36</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3506.15</v>
+        <v>3508.36</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3834.85</v>
+        <v>3837.27</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3834.85</v>
+        <v>3837.27</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3834.85</v>
+        <v>3837.27</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4317.19</v>
+        <v>4319.9</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>939.03</v>
+        <v>941.21</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>939.03</v>
+        <v>941.21</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>939.03</v>
+        <v>941.21</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1223.78</v>
+        <v>1226.62</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1223.78</v>
+        <v>1226.62</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1223.78</v>
+        <v>1226.62</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1022.66</v>
+        <v>1025.03</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.503606</v>
+        <v>95.725523</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.52</v>
+        <v>108.77</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.52</v>
+        <v>108.77</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.52</v>
+        <v>108.77</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>107.06</v>
+        <v>107.31</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>107.06</v>
+        <v>107.31</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>107.06</v>
+        <v>107.31</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116.51</v>
+        <v>116.79</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>751.2</v>
+        <v>752.9400000000001</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>751.2</v>
+        <v>752.9400000000001</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>751.2</v>
+        <v>752.9400000000001</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>653.53</v>
+        <v>655.05</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>653.53</v>
+        <v>655.05</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>653.53</v>
+        <v>655.05</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>681.77</v>
+        <v>683.36</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2275.826544</v>
+        <v>2291.748711</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2115.84</v>
+        <v>2130.64</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2115.84</v>
+        <v>2130.64</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2115.84</v>
+        <v>2130.64</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1961.76</v>
+        <v>1975.49</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1961.76</v>
+        <v>1975.49</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1961.76</v>
+        <v>1975.49</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2844.78</v>
+        <v>2864.69</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,49 +5067,49 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.771794</v>
+        <v>52.745937</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>16.9</v>
+        <v>16.89</v>
       </c>
       <c r="N13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>16.9</v>
+        <v>16.89</v>
       </c>
       <c r="P13" s="18" t="n">
         <v>0.3202</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>16.9</v>
+        <v>16.89</v>
       </c>
       <c r="R13" s="18" t="n">
         <v>0.44</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>23.22</v>
+        <v>23.21</v>
       </c>
       <c r="T13" s="37" t="n">
         <v>0.1057</v>
@@ -5138,49 +5138,49 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>18</v>
+        <v>18.04</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>18</v>
+        <v>18.04</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>18</v>
+        <v>18.04</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="M14" s="28" t="n">
-        <v>20.48</v>
+        <v>20.53</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>20.48</v>
+        <v>20.53</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>1.199</v>
       </c>
       <c r="Q14" s="28" t="n">
-        <v>20.48</v>
+        <v>20.53</v>
       </c>
       <c r="R14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.603496</v>
+        <v>155.27097</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>106.09</v>
+        <v>105.86</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>106.09</v>
+        <v>105.86</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>106.09</v>
+        <v>105.86</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>98.05</v>
+        <v>97.84</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>98.05</v>
+        <v>97.84</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>98.05</v>
+        <v>97.84</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>163.38</v>
+        <v>163.03</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>534.05</v>
+        <v>535.3</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>534.05</v>
+        <v>535.3</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>534.05</v>
+        <v>535.3</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>516.4400000000001</v>
+        <v>517.64</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>516.4400000000001</v>
+        <v>517.64</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>516.4400000000001</v>
+        <v>517.64</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>511.33</v>
+        <v>512.52</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,49 +5351,49 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>10.991376</v>
+        <v>11.020442</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.15</v>
+        <v>12.18</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>12.15</v>
+        <v>12.18</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1.1053</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>12.15</v>
+        <v>12.18</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="N17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="T17" s="37" t="n">
         <v>0.0503</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8764.846654000001</v>
+        <v>8767.130045</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10411.76</v>
+        <v>10414.47</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10411.76</v>
+        <v>10414.47</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10411.76</v>
+        <v>10414.47</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>11753.66</v>
+        <v>11756.72</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>11753.66</v>
+        <v>11756.72</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>11753.66</v>
+        <v>11756.72</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11219</v>
+        <v>11221.93</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>733.59</v>
+        <v>735.29</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>733.59</v>
+        <v>735.29</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>733.59</v>
+        <v>735.29</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>662.45</v>
+        <v>663.99</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>662.45</v>
+        <v>663.99</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>662.45</v>
+        <v>663.99</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>624.96</v>
+        <v>626.41</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.727984</v>
+        <v>129.765701</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>158.13</v>
+        <v>158.17</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>158.13</v>
+        <v>158.17</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>158.13</v>
+        <v>158.17</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>165.92</v>
+        <v>165.97</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>165.92</v>
+        <v>165.97</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>165.92</v>
+        <v>165.97</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>175.13</v>
+        <v>175.18</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,49 +5635,49 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>16.41</v>
+        <v>16.45</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>16.41</v>
+        <v>16.45</v>
       </c>
       <c r="J21" s="18" t="n">
         <v>0.9607</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>16.41</v>
+        <v>16.45</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>19.75</v>
+        <v>19.79</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>19.75</v>
+        <v>19.79</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>19.75</v>
+        <v>19.79</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>183.918613</v>
+        <v>183.689846</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>134.89</v>
+        <v>134.72</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>134.89</v>
+        <v>134.72</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>134.89</v>
+        <v>134.72</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>146.29</v>
+        <v>146.11</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>146.29</v>
+        <v>146.11</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>146.29</v>
+        <v>146.11</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>220.7</v>
+        <v>220.43</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.37494</v>
+        <v>6.374935</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4179.221302</v>
+        <v>4174.357607</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4058.02</v>
+        <v>4053.3</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4058.02</v>
+        <v>4053.3</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4058.02</v>
+        <v>4053.3</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>6477.79</v>
+        <v>6470.25</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>6477.79</v>
+        <v>6470.25</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>6477.79</v>
+        <v>6470.25</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5432.99</v>
+        <v>5426.66</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1740.954025</v>
+        <v>1744.734226</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4316.17</v>
+        <v>4325.55</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4316.17</v>
+        <v>4325.55</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4316.17</v>
+        <v>4325.55</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3508.02</v>
+        <v>3515.64</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3508.02</v>
+        <v>3515.64</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3508.02</v>
+        <v>3515.64</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4178.29</v>
+        <v>4187.36</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>692.51</v>
+        <v>694.12</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>692.51</v>
+        <v>694.12</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>692.51</v>
+        <v>694.12</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>602.46</v>
+        <v>603.86</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>602.46</v>
+        <v>603.86</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>602.46</v>
+        <v>603.86</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>738.59</v>
+        <v>740.3</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.56209</v>
+        <v>46.664963</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>51.94</v>
+        <v>52.06</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>51.94</v>
+        <v>52.06</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>51.94</v>
+        <v>52.06</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>59.41</v>
+        <v>59.54</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>59.41</v>
+        <v>59.54</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>59.41</v>
+        <v>59.54</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>65.19</v>
+        <v>65.33</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,49 +6132,49 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.329299000000001</v>
+        <v>9.343978</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>10.79</v>
+        <v>10.81</v>
       </c>
       <c r="H28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>10.79</v>
+        <v>10.81</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>1.157</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>10.79</v>
+        <v>10.81</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="M28" s="28" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="R28" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="28" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="T28" s="39" t="n">
         <v>0.1973</v>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.606663</v>
+        <v>63.61008</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
@@ -6227,19 +6227,19 @@
         <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>78.55</v>
+        <v>78.56</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>78.55</v>
+        <v>78.56</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>78.55</v>
+        <v>78.56</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="G30" s="28" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="H30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>1.064</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="M30" s="28" t="n">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="N30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="R30" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>626.09</v>
+        <v>627.55</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>626.09</v>
+        <v>627.55</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>626.09</v>
+        <v>627.55</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>569.28</v>
+        <v>570.6</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>569.28</v>
+        <v>570.6</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>569.28</v>
+        <v>570.6</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>710.1799999999999</v>
+        <v>711.83</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1384.423957</v>
+        <v>1382.529699</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>700.8</v>
+        <v>699.84</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>742.88</v>
+        <v>741.87</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>770.85</v>
+        <v>769.79</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>800.89</v>
+        <v>799.79</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>800.89</v>
+        <v>799.79</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>800.89</v>
+        <v>799.79</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>761.4299999999999</v>
+        <v>760.39</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1458.426834</v>
+        <v>1457.46283</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1778.99</v>
+        <v>1777.81</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1778.99</v>
+        <v>1777.81</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1778.99</v>
+        <v>1777.81</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1910.54</v>
+        <v>1909.28</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1910.54</v>
+        <v>1909.28</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1910.54</v>
+        <v>1909.28</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2114.72</v>
+        <v>2113.32</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.1524</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>827.5</v>
+        <v>829.42</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>827.5</v>
+        <v>829.42</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>827.5</v>
+        <v>829.42</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>737.45</v>
+        <v>739.16</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>737.45</v>
+        <v>739.16</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>737.45</v>
+        <v>739.16</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>653.36</v>
+        <v>654.88</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.390704</v>
+        <v>14.114736</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.73</v>
+        <v>18.37</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.73</v>
+        <v>18.37</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.73</v>
+        <v>18.37</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>19.14</v>
+        <v>18.77</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>19.14</v>
+        <v>18.77</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>19.14</v>
+        <v>18.77</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>23.03</v>
+        <v>22.58</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>17.079628</v>
+        <v>17.121639</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="L37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>21.88</v>
+        <v>21.93</v>
       </c>
       <c r="N37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>21.88</v>
+        <v>21.93</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>1.2809</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>21.88</v>
+        <v>21.93</v>
       </c>
       <c r="R37" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>23.06</v>
+        <v>23.11</v>
       </c>
       <c r="T37" s="40" t="n">
         <v>0</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>511.988564</v>
+        <v>511.014831</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>312.06</v>
+        <v>311.46</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>312.06</v>
+        <v>311.46</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>312.06</v>
+        <v>311.46</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>290.91</v>
+        <v>290.36</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>290.91</v>
+        <v>290.36</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>290.91</v>
+        <v>290.36</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>281.59</v>
+        <v>281.06</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2563.751605</v>
+        <v>2579.094525</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2409.93</v>
+        <v>2424.35</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2409.93</v>
+        <v>2424.35</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2409.93</v>
+        <v>2424.35</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2594.52</v>
+        <v>2610.04</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2594.52</v>
+        <v>2610.04</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2594.52</v>
+        <v>2610.04</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3204.69</v>
+        <v>3223.87</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>610.36</v>
+        <v>611.77</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>610.36</v>
+        <v>611.77</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>610.36</v>
+        <v>611.77</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>670.98</v>
+        <v>672.54</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>670.98</v>
+        <v>672.54</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>670.98</v>
+        <v>672.54</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>624.96</v>
+        <v>626.41</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,25 +7055,25 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.92239</v>
+        <v>2.927391</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.7566000000000001</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3717.465047</v>
+        <v>3724.737851</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5133.82</v>
+        <v>5143.86</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5133.82</v>
+        <v>5143.86</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5133.82</v>
+        <v>5143.86</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4275.08</v>
+        <v>4283.45</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4275.08</v>
+        <v>4283.45</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4275.08</v>
+        <v>4283.45</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4832.7</v>
+        <v>4842.16</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>18.810418</v>
+        <v>18.969397</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>19.21</v>
+        <v>19.37</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>19.21</v>
+        <v>19.37</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>19.21</v>
+        <v>19.37</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>24.45</v>
+        <v>24.66</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7268,49 +7268,49 @@
         </is>
       </c>
       <c r="E44" s="38" t="n">
-        <v>25.3672</v>
+        <v>25.3745</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="G44" s="28" t="n">
-        <v>39.57</v>
+        <v>39.58</v>
       </c>
       <c r="H44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>39.57</v>
+        <v>39.58</v>
       </c>
       <c r="J44" s="27" t="n">
         <v>1.56</v>
       </c>
       <c r="K44" s="28" t="n">
-        <v>39.57</v>
+        <v>39.58</v>
       </c>
       <c r="L44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="M44" s="28" t="n">
-        <v>38.56</v>
+        <v>38.57</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>38.56</v>
+        <v>38.57</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>1.52</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>38.56</v>
+        <v>38.57</v>
       </c>
       <c r="R44" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="S44" s="28" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
       <c r="T44" s="39" t="n">
         <v>0.391</v>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.813465</v>
+        <v>132.722332</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>42.53</v>
+        <v>42.5</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>0.3202</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>921.5132</v>
+        <v>922.0653620000001</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.5</v>
+        <v>266.66</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>622.12</v>
+        <v>623.5599999999999</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.821664</v>
+        <v>14.031222</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.14</v>
+        <v>14.35</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>762.96</v>
+        <v>764.73</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2977.370928</v>
+        <v>2979.243996</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3506.15</v>
+        <v>3508.36</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>939.03</v>
+        <v>941.21</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.503606</v>
+        <v>95.725523</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.52</v>
+        <v>108.77</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>751.2</v>
+        <v>752.9400000000001</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2275.826544</v>
+        <v>2291.748711</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2115.84</v>
+        <v>2130.64</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.771794</v>
+        <v>52.745937</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>18</v>
+        <v>18.04</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.603496</v>
+        <v>155.27097</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>106.09</v>
+        <v>105.86</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>534.05</v>
+        <v>535.3</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,10 +8309,10 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10.991376</v>
+        <v>11.020442</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>12.15</v>
+        <v>12.18</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.1053</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8764.846654000001</v>
+        <v>8767.130045</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10411.76</v>
+        <v>10414.47</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>733.59</v>
+        <v>735.29</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.727984</v>
+        <v>129.765701</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>158.13</v>
+        <v>158.17</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>16.41</v>
+        <v>16.45</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.9607</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>183.918613</v>
+        <v>183.689846</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>134.89</v>
+        <v>134.72</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.37494</v>
+        <v>6.374935</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>0.2</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4179.221302</v>
+        <v>4174.357607</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4058.02</v>
+        <v>4053.3</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1740.954025</v>
+        <v>1744.734226</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4316.17</v>
+        <v>4325.55</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>692.51</v>
+        <v>694.12</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.56209</v>
+        <v>46.664963</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>51.94</v>
+        <v>52.06</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.329299000000001</v>
+        <v>9.343978</v>
       </c>
       <c r="F28" s="28" t="n">
-        <v>10.79</v>
+        <v>10.81</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.157</v>
@@ -9017,7 +9017,7 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.606663</v>
+        <v>63.61008</v>
       </c>
       <c r="F29" s="19" t="n">
         <v>72.28</v>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>1.064</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>626.09</v>
+        <v>627.55</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1384.423957</v>
+        <v>1382.529699</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>700.8</v>
+        <v>699.84</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1458.426834</v>
+        <v>1457.46283</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1778.99</v>
+        <v>1777.81</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.2198</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>827.5</v>
+        <v>829.42</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.390704</v>
+        <v>14.114736</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.73</v>
+        <v>18.37</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>17.079628</v>
+        <v>17.121639</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.19</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>511.988564</v>
+        <v>511.014831</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>312.06</v>
+        <v>311.46</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2563.751605</v>
+        <v>2579.094525</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2409.93</v>
+        <v>2424.35</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>610.36</v>
+        <v>611.77</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.92239</v>
+        <v>2.927391</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.8661</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3717.465047</v>
+        <v>3724.737851</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5133.82</v>
+        <v>5143.86</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>18.810418</v>
+        <v>18.969397</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>25.3672</v>
+        <v>25.3745</v>
       </c>
       <c r="F44" s="28" t="n">
-        <v>39.57</v>
+        <v>39.58</v>
       </c>
       <c r="G44" s="27" t="n">
         <v>1.56</v>
@@ -10244,25 +10244,25 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>132.813465</v>
+        <v>132.722332</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.67</v>
+        <v>44.63</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>28.82</v>
+        <v>28.8</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.17</v>
+        <v>41.14</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,25 +10283,25 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.771794</v>
+        <v>52.745937</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.9</v>
+        <v>22.89</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>19.47</v>
+        <v>19.46</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>0.44</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>23.22</v>
+        <v>23.21</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>0.1057</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.37494</v>
+        <v>6.374935</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
@@ -10361,25 +10361,25 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.329299000000001</v>
+        <v>9.343978</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.317</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="28" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>0.1973</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>511.988564</v>
+        <v>511.014831</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>333.3</v>
+        <v>332.67</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>311.08</v>
+        <v>310.49</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>281.59</v>
+        <v>281.06</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,13 +10439,13 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.92239</v>
+        <v>2.927391</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.7566000000000001</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>653.42</v>
+        <v>654.9400000000001</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>706.2</v>
+        <v>707.84</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>681.77</v>
+        <v>683.36</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>801.37</v>
+        <v>803.23</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>668.7</v>
+        <v>670.26</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>784.04</v>
+        <v>785.86</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.503606</v>
+        <v>95.725523</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>121.23</v>
+        <v>121.51</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.121</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>107.06</v>
+        <v>107.31</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116.51</v>
+        <v>116.79</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,25 +10666,25 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>10.991376</v>
+        <v>11.020442</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>12.76</v>
+        <v>12.79</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="I19" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J19" s="28" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="K19" s="39" t="n">
         <v>0.0503</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8764.846654000001</v>
+        <v>8767.130045</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11221.63</v>
+        <v>11224.56</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>11753.66</v>
+        <v>11756.72</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11219</v>
+        <v>11221.93</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>770.52</v>
+        <v>772.3099999999999</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>662.45</v>
+        <v>663.99</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>624.96</v>
+        <v>626.41</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>183.918613</v>
+        <v>183.689846</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>155.65</v>
+        <v>155.46</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>167.62</v>
+        <v>167.41</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>220.7</v>
+        <v>220.43</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>733.53</v>
+        <v>735.23</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>638.1900000000001</v>
+        <v>639.6799999999999</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>738.59</v>
+        <v>740.3</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>626.09</v>
+        <v>627.55</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>569.28</v>
+        <v>570.6</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>710.1799999999999</v>
+        <v>711.83</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1384.423957</v>
+        <v>1382.529699</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1088.16</v>
+        <v>1086.67</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1366.84</v>
+        <v>1364.97</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>761.4299999999999</v>
+        <v>760.39</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>869.14</v>
+        <v>871.16</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>737.45</v>
+        <v>739.16</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>653.36</v>
+        <v>654.88</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>641.09</v>
+        <v>642.58</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>670.98</v>
+        <v>672.54</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>624.96</v>
+        <v>626.41</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2977.370928</v>
+        <v>2979.243996</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3973.3</v>
+        <v>3975.8</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3834.85</v>
+        <v>3837.27</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4317.19</v>
+        <v>4319.9</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.603496</v>
+        <v>155.27097</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>123.24</v>
+        <v>122.97</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>130.01</v>
+        <v>129.73</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>163.38</v>
+        <v>163.03</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.727984</v>
+        <v>129.765701</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>166.09</v>
+        <v>166.14</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>165.92</v>
+        <v>165.97</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>175.13</v>
+        <v>175.18</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4179.221302</v>
+        <v>4174.357607</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4579.59</v>
+        <v>4574.26</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>6477.79</v>
+        <v>6470.25</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5432.99</v>
+        <v>5426.66</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1740.954025</v>
+        <v>1744.734226</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4646.78</v>
+        <v>4656.87</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3508.02</v>
+        <v>3515.64</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4178.29</v>
+        <v>4187.36</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.56209</v>
+        <v>46.664963</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.57</v>
+        <v>55.69</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>59.41</v>
+        <v>59.54</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>65.19</v>
+        <v>65.33</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1458.426834</v>
+        <v>1457.46283</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>2050.11</v>
+        <v>2048.76</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1910.54</v>
+        <v>1909.28</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2114.72</v>
+        <v>2113.32</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.1524</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.390704</v>
+        <v>14.114736</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>20.3</v>
+        <v>19.91</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>19.14</v>
+        <v>18.77</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>23.03</v>
+        <v>22.58</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2563.751605</v>
+        <v>2579.094525</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2642.46</v>
+        <v>2658.27</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2594.52</v>
+        <v>2610.04</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3204.69</v>
+        <v>3223.87</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3717.465047</v>
+        <v>3724.737851</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5133.82</v>
+        <v>5143.86</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4275.08</v>
+        <v>4283.45</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4832.7</v>
+        <v>4842.16</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>986.3</v>
+        <v>988.59</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1223.78</v>
+        <v>1226.62</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1022.66</v>
+        <v>1025.03</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>789.04</v>
+        <v>790.87</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>686.49</v>
+        <v>688.08</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>681.77</v>
+        <v>683.36</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2275.826544</v>
+        <v>2291.748711</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2395.08</v>
+        <v>2411.84</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>1961.76</v>
+        <v>1975.49</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2844.78</v>
+        <v>2864.69</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>560.9299999999999</v>
+        <v>562.23</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>542.46</v>
+        <v>543.72</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>511.33</v>
+        <v>512.52</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>921.5132</v>
+        <v>922.0653620000001</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>279.96</v>
+        <v>280.12</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>379.94</v>
+        <v>380.17</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>598.98</v>
+        <v>599.34</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>13.821664</v>
+        <v>14.031222</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>14.39</v>
+        <v>14.61</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.28</v>
+        <v>17.54</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,25 +11893,25 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
       </c>
       <c r="F60" s="19" t="n">
-        <v>18.91</v>
+        <v>18.95</v>
       </c>
       <c r="G60" s="18" t="n">
         <v>1.199</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>20.48</v>
+        <v>20.53</v>
       </c>
       <c r="I60" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.42</v>
+        <v>17.46</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>19.75</v>
+        <v>19.79</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,19 +11971,19 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.606663</v>
+        <v>63.61008</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>77.98</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>78.55</v>
+        <v>78.56</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
@@ -12010,25 +12010,25 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
       </c>
       <c r="F63" s="28" t="n">
-        <v>19.09</v>
+        <v>19.14</v>
       </c>
       <c r="G63" s="27" t="n">
         <v>1.102</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="I63" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.35</v>
+        <v>21.4</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,25 +12049,25 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>17.079628</v>
+        <v>17.121639</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
       </c>
       <c r="F64" s="19" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>1.378</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>23.54</v>
+        <v>23.59</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>23.06</v>
+        <v>23.11</v>
       </c>
       <c r="K64" s="40" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>18.810418</v>
+        <v>18.969397</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>24.08</v>
+        <v>24.29</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>19.21</v>
+        <v>19.37</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>24.45</v>
+        <v>24.66</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12127,25 +12127,25 @@
         </is>
       </c>
       <c r="D66" s="36" t="n">
-        <v>25.3672</v>
+        <v>25.3745</v>
       </c>
       <c r="E66" s="18" t="n">
         <v>2.17</v>
       </c>
       <c r="F66" s="19" t="n">
-        <v>55.05</v>
+        <v>55.06</v>
       </c>
       <c r="G66" s="18" t="n">
         <v>2.05</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>52</v>
+        <v>52.02</v>
       </c>
       <c r="I66" s="18" t="n">
         <v>1.55</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
       <c r="K66" s="37" t="n">
         <v>0.391</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4646.78</v>
+        <v>4656.87</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>2.17</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>55.05</v>
+        <v>55.06</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>279.96</v>
+        <v>280.12</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>986.3</v>
+        <v>988.59</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.67</v>
+        <v>44.63</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>869.14</v>
+        <v>871.16</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.9</v>
+        <v>22.89</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>333.3</v>
+        <v>332.67</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>801.37</v>
+        <v>803.23</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1088.16</v>
+        <v>1086.67</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>20.3</v>
+        <v>19.91</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>123.24</v>
+        <v>122.97</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2050.11</v>
+        <v>2048.76</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>155.65</v>
+        <v>155.46</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>789.04</v>
+        <v>790.87</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>1.3853</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>560.9299999999999</v>
+        <v>562.23</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>921.5132</v>
+        <v>922.0653620000001</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108517</v>
+        <v>0.00108452</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2977.370928</v>
+        <v>2979.243996</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033587</v>
+        <v>0.00033566</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>13.821664</v>
+        <v>14.031222</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07235018999999999</v>
+        <v>0.07126963</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2275.826544</v>
+        <v>2291.748711</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.0004394</v>
+        <v>0.00043635</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.503606</v>
+        <v>95.725523</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01047081</v>
+        <v>0.01044653</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.813465</v>
+        <v>132.722332</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00752936</v>
+        <v>0.00753453</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.771794</v>
+        <v>52.745937</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01894952</v>
+        <v>0.01895881</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.603496</v>
+        <v>155.27097</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.00642659</v>
+        <v>0.00644035</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>10.991376</v>
+        <v>11.020442</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09098042000000001</v>
+        <v>0.09074046</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.188412</v>
+        <v>74.18787</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347919</v>
+        <v>0.01347929</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8764.846654000001</v>
+        <v>8767.130045</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011409</v>
+        <v>0.00011406</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.727984</v>
+        <v>129.765701</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.00770844</v>
+        <v>0.0077062</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>426.107053</v>
+        <v>427.097178</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00234683</v>
+        <v>0.00234139</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>183.918613</v>
+        <v>183.689846</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00543719</v>
+        <v>0.00544396</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05853803</v>
+        <v>0.05840584</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.37494</v>
+        <v>6.374935</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15686422</v>
+        <v>0.15686434</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.329299000000001</v>
+        <v>9.343978</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.10718919</v>
+        <v>0.1070208</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4179.221302</v>
+        <v>4174.357607</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00023928</v>
+        <v>0.00023956</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.897062</v>
+        <v>39.897298</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.0250645</v>
+        <v>0.02506435</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.56209</v>
+        <v>46.664963</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.0214767</v>
+        <v>0.02142935</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1740.954025</v>
+        <v>1744.734226</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.0005744</v>
+        <v>0.00057315</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.606663</v>
+        <v>63.61008</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01572162</v>
+        <v>0.01572078</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05853803</v>
+        <v>0.05840584</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1384.423957</v>
+        <v>1382.529699</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00072232</v>
+        <v>0.00072331</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1458.426834</v>
+        <v>1457.46283</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068567</v>
+        <v>0.00068612</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.390704</v>
+        <v>14.114736</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.0694893</v>
+        <v>0.07084794</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>511.988564</v>
+        <v>511.014831</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00195317</v>
+        <v>0.00195689</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.3158079999999</v>
+        <v>571.311717</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00175035</v>
+        <v>0.00175036</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4582.400006</v>
+        <v>4586.66529</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021823</v>
+        <v>0.00021802</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.220136</v>
+        <v>21.269445</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.04712505</v>
+        <v>0.0470158</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>17.082912</v>
+        <v>17.121575</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05853803</v>
+        <v>0.05840584</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.92239</v>
+        <v>2.927391</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.34218568</v>
+        <v>0.3416011</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2563.751605</v>
+        <v>2579.094525</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00039005</v>
+        <v>0.00038773</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3717.465047</v>
+        <v>3724.737851</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.000269</v>
+        <v>0.00026848</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00176012</v>
+        <v>0.00175604</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>568.142738</v>
+        <v>569.462904</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00176012</v>
+        <v>0.00175604</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>17.079628</v>
+        <v>17.121639</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05854928</v>
+        <v>0.05840562</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>18.810418</v>
+        <v>18.969397</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05316203</v>
+        <v>0.05271649</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>25.3672</v>
+        <v>25.3745</v>
       </c>
       <c r="E44" s="65" t="n">
-        <v>0.03942098</v>
+        <v>0.03940964</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>27 March 2026 — 07:03 UTC</t>
+          <t>28 March 2026 — 06:53 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/africa_fuel_prices.xlsx
+++ b/docs/africa_fuel_prices.xlsx
@@ -1314,7 +1314,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Updated: 28 March 2026  |  06:53 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
+          <t>Updated: 29 March 2026  |  07:00 UTC  ·  54 Countries  ·  5 Regions  ·  Prices in USD/L and Local Currency/L  ·  Sources: GlobalPetrolPrices · OPEC · World Bank</t>
         </is>
       </c>
     </row>
@@ -1525,13 +1525,13 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>132.722332</v>
+        <v>132.727443</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>44.63</v>
+        <v>44.64</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>0.217</v>
@@ -1543,7 +1543,7 @@
         <v>0.31</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>41.14</v>
+        <v>41.15</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>0.0503</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>922.0653620000001</v>
+        <v>916.813803</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.3038</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>280.12</v>
+        <v>278.53</v>
       </c>
       <c r="I12" s="27" t="n">
         <v>0.4123</v>
       </c>
       <c r="J12" s="28" t="n">
-        <v>380.17</v>
+        <v>378</v>
       </c>
       <c r="K12" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="L12" s="28" t="n">
-        <v>599.34</v>
+        <v>595.9299999999999</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>0.0505</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>654.9400000000001</v>
+        <v>654.87</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>707.84</v>
+        <v>707.77</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>683.36</v>
+        <v>683.29</v>
       </c>
       <c r="M13" s="20" t="n">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1714,25 +1714,25 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>14.031222</v>
+        <v>14.002901</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>15.22</v>
+        <v>15.19</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="J14" s="28" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
       <c r="K14" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L14" s="28" t="n">
-        <v>17.54</v>
+        <v>17.5</v>
       </c>
       <c r="M14" s="29" t="n">
         <v>0.0609</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>803.23</v>
+        <v>803.15</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>670.26</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>785.86</v>
+        <v>785.78</v>
       </c>
       <c r="M15" s="20" t="n">
         <v>0.0503</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,25 +1840,25 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2979.243996</v>
+        <v>2979.382137</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>1.3345</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>3975.8</v>
+        <v>3975.99</v>
       </c>
       <c r="I16" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="J16" s="28" t="n">
-        <v>3837.27</v>
+        <v>3837.44</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="L16" s="28" t="n">
-        <v>4319.9</v>
+        <v>4320.1</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>0.1332</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>988.59</v>
+        <v>988.49</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1226.62</v>
+        <v>1226.5</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>1025.03</v>
+        <v>1024.93</v>
       </c>
       <c r="M17" s="20" t="n">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1966,25 @@
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>95.725523</v>
+        <v>95.716026</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.2694</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>121.51</v>
+        <v>121.5</v>
       </c>
       <c r="I18" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>107.31</v>
+        <v>107.3</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="L18" s="28" t="n">
-        <v>116.79</v>
+        <v>116.77</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>0.1171</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.3888</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>790.87</v>
+        <v>790.79</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>1.2083</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>688.08</v>
+        <v>688.01</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>683.36</v>
+        <v>683.29</v>
       </c>
       <c r="M19" s="20" t="n">
         <v>0.0504</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2291.748711</v>
+        <v>2283.099339</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.0524</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>2411.84</v>
+        <v>2402.73</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="J20" s="28" t="n">
-        <v>1975.49</v>
+        <v>1968.03</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="L20" s="28" t="n">
-        <v>2864.69</v>
+        <v>2853.87</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>0.132</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>52.745937</v>
+        <v>52.759664</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>0.434</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>22.89</v>
+        <v>22.9</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>0.3689</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.1067</v>
@@ -2236,7 +2236,7 @@
         <v>1.25</v>
       </c>
       <c r="L22" s="28" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="M22" s="29" t="n">
         <v>0.0503</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>155.27097</v>
+        <v>155.184648</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>0.792</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>122.97</v>
+        <v>122.91</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>0.8355</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>129.73</v>
+        <v>129.66</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>163.03</v>
+        <v>162.94</v>
       </c>
       <c r="M23" s="20" t="n">
         <v>0.1616</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="F24" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>562.23</v>
+        <v>562.17</v>
       </c>
       <c r="I24" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="J24" s="28" t="n">
-        <v>543.72</v>
+        <v>543.67</v>
       </c>
       <c r="K24" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="L24" s="28" t="n">
-        <v>512.52</v>
+        <v>512.47</v>
       </c>
       <c r="M24" s="29" t="n">
         <v>0.0503</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="R24" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>11.020442</v>
+        <v>11.015379</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>1.1609</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2470,25 +2470,25 @@
         </is>
       </c>
       <c r="F26" s="26" t="n">
-        <v>8767.130045</v>
+        <v>8766.83993</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>11224.56</v>
+        <v>11224.19</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="J26" s="28" t="n">
-        <v>11756.72</v>
+        <v>11756.33</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="L26" s="28" t="n">
-        <v>11221.93</v>
+        <v>11221.56</v>
       </c>
       <c r="M26" s="29" t="n">
         <v>0.07780000000000001</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R26" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.3562</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>772.3099999999999</v>
+        <v>772.23</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>663.99</v>
+        <v>663.9299999999999</v>
       </c>
       <c r="K27" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>626.41</v>
+        <v>626.35</v>
       </c>
       <c r="M27" s="20" t="n">
         <v>0.0503</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,25 +2596,25 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>129.765701</v>
+        <v>129.773208</v>
       </c>
       <c r="G28" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>166.14</v>
+        <v>166.15</v>
       </c>
       <c r="I28" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="J28" s="28" t="n">
-        <v>165.97</v>
+        <v>165.98</v>
       </c>
       <c r="K28" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="L28" s="28" t="n">
-        <v>175.18</v>
+        <v>175.19</v>
       </c>
       <c r="M28" s="29" t="n">
         <v>0.0504</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.0199</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.46</v>
+        <v>17.47</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="K29" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="M29" s="20" t="n">
         <v>0.0616</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F30" s="26" t="n">
-        <v>183.689846</v>
+        <v>183.703402</v>
       </c>
       <c r="G30" s="27" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>155.46</v>
+        <v>155.47</v>
       </c>
       <c r="I30" s="27" t="n">
         <v>0.9114</v>
       </c>
       <c r="J30" s="28" t="n">
-        <v>167.41</v>
+        <v>167.43</v>
       </c>
       <c r="K30" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="L30" s="28" t="n">
-        <v>220.43</v>
+        <v>220.44</v>
       </c>
       <c r="M30" s="29" t="n">
         <v>0.1539</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R30" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6.374935</v>
+        <v>6.374928</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>0.0309</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="F32" s="26" t="n">
-        <v>4174.357607</v>
+        <v>4174.132824</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>4574.26</v>
+        <v>4574.01</v>
       </c>
       <c r="I32" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="J32" s="28" t="n">
-        <v>6470.25</v>
+        <v>6469.91</v>
       </c>
       <c r="K32" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L32" s="28" t="n">
-        <v>5426.66</v>
+        <v>5426.37</v>
       </c>
       <c r="M32" s="29" t="n">
         <v>0.1285</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="R32" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>1744.734226</v>
+        <v>1744.076495</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>4656.87</v>
+        <v>4655.11</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>3515.64</v>
+        <v>3514.31</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>4187.36</v>
+        <v>4185.78</v>
       </c>
       <c r="M33" s="20" t="n">
         <v>0.0766</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,25 +2974,25 @@
         </is>
       </c>
       <c r="F34" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>735.23</v>
+        <v>735.16</v>
       </c>
       <c r="I34" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>639.6799999999999</v>
+        <v>639.61</v>
       </c>
       <c r="K34" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L34" s="28" t="n">
-        <v>740.3</v>
+        <v>740.23</v>
       </c>
       <c r="M34" s="29" t="n">
         <v>0.0592</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R34" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3037,25 +3037,25 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>46.664963</v>
+        <v>46.642551</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.1935</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>55.69</v>
+        <v>55.67</v>
       </c>
       <c r="I35" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>59.54</v>
+        <v>59.52</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>65.33</v>
+        <v>65.3</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>0.0698</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="F36" s="26" t="n">
-        <v>9.343978</v>
+        <v>9.344307000000001</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>1.3853</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="R36" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>63.61008</v>
+        <v>63.423144</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>77.98999999999999</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="I37" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>78.56</v>
+        <v>78.33</v>
       </c>
       <c r="K37" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>82.69</v>
+        <v>82.45</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>0.0789</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F38" s="26" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>1.1176</v>
@@ -3244,7 +3244,7 @@
         <v>1.25</v>
       </c>
       <c r="L38" s="28" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="M38" s="29" t="n">
         <v>0.0504</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R38" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>627.55</v>
+        <v>627.49</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>570.6</v>
+        <v>570.55</v>
       </c>
       <c r="K39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>711.83</v>
+        <v>711.76</v>
       </c>
       <c r="M39" s="33" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3352,25 @@
         </is>
       </c>
       <c r="F40" s="26" t="n">
-        <v>1382.529699</v>
+        <v>1381.9143</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>1086.67</v>
+        <v>1086.18</v>
       </c>
       <c r="I40" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>1364.97</v>
+        <v>1364.36</v>
       </c>
       <c r="K40" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L40" s="28" t="n">
-        <v>760.39</v>
+        <v>760.05</v>
       </c>
       <c r="M40" s="29" t="n">
         <v>0.5527000000000001</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="R40" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1457.46283</v>
+        <v>1457.626546</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>2048.76</v>
+        <v>2048.99</v>
       </c>
       <c r="I41" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1909.28</v>
+        <v>1909.49</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>2113.32</v>
+        <v>2113.56</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>0.1524</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="F42" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.5298</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>871.16</v>
+        <v>871.08</v>
       </c>
       <c r="I42" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="J42" s="28" t="n">
-        <v>739.16</v>
+        <v>739.09</v>
       </c>
       <c r="K42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="L42" s="28" t="n">
-        <v>654.88</v>
+        <v>654.8200000000001</v>
       </c>
       <c r="M42" s="29" t="n">
         <v>0.0503</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="R42" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>14.114736</v>
+        <v>14.130415</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.4105</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>19.91</v>
+        <v>19.93</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>18.77</v>
+        <v>18.79</v>
       </c>
       <c r="K43" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>0.0837</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R44" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>17.121639</v>
+        <v>17.11952</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>1.19</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,25 +3730,25 @@
         </is>
       </c>
       <c r="F46" s="26" t="n">
-        <v>511.014831</v>
+        <v>509.538566</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>0.651</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>332.67</v>
+        <v>331.71</v>
       </c>
       <c r="I46" s="27" t="n">
         <v>0.6076</v>
       </c>
       <c r="J46" s="28" t="n">
-        <v>310.49</v>
+        <v>309.6</v>
       </c>
       <c r="K46" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="L46" s="28" t="n">
-        <v>281.06</v>
+        <v>280.25</v>
       </c>
       <c r="M46" s="29" t="n">
         <v>0.06809999999999999</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R46" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3793,25 +3793,25 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>2579.094525</v>
+        <v>2569.132481</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>2658.27</v>
+        <v>2648</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>2610.04</v>
+        <v>2599.96</v>
       </c>
       <c r="K47" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>3223.87</v>
+        <v>3211.42</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>0.0965</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3856,25 +3856,25 @@
         </is>
       </c>
       <c r="F48" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="G48" s="27" t="n">
         <v>1.1284</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>642.58</v>
+        <v>642.52</v>
       </c>
       <c r="I48" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="J48" s="28" t="n">
-        <v>672.54</v>
+        <v>672.47</v>
       </c>
       <c r="K48" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="L48" s="28" t="n">
-        <v>626.41</v>
+        <v>626.35</v>
       </c>
       <c r="M48" s="29" t="n">
         <v>0.0504</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R48" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,13 +3919,13 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>2.927391</v>
+        <v>2.926309</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>0.7566000000000001</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3724.737851</v>
+        <v>3723.861301</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>5143.86</v>
+        <v>5142.65</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>4283.45</v>
+        <v>4282.44</v>
       </c>
       <c r="K50" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="L50" s="28" t="n">
-        <v>4842.16</v>
+        <v>4841.02</v>
       </c>
       <c r="M50" s="34" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="R50" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4045,25 +4045,25 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>18.969397</v>
+        <v>18.956944</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>24.29</v>
+        <v>24.27</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>19.37</v>
+        <v>19.36</v>
       </c>
       <c r="K51" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>24.66</v>
+        <v>24.64</v>
       </c>
       <c r="M51" s="33" t="n">
         <v>0.0076</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="R52" s="32" t="inlineStr">
         <is>
-          <t>2026-03-28 06:53 UTC</t>
+          <t>2026-03-29 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>132.722332</v>
+        <v>132.727443</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.3202</v>
@@ -4399,7 +4399,7 @@
         <v>0.31</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>41.14</v>
+        <v>41.15</v>
       </c>
       <c r="T3" s="37" t="n">
         <v>0.0503</v>
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>922.0653620000001</v>
+        <v>916.813803</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>266.66</v>
+        <v>265.14</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>266.66</v>
+        <v>265.14</v>
       </c>
       <c r="J4" s="27" t="n">
         <v>0.2892</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>266.66</v>
+        <v>265.14</v>
       </c>
       <c r="L4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>352.41</v>
+        <v>350.41</v>
       </c>
       <c r="N4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>352.41</v>
+        <v>350.41</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>0.3822</v>
       </c>
       <c r="Q4" s="28" t="n">
-        <v>352.41</v>
+        <v>350.41</v>
       </c>
       <c r="R4" s="27" t="n">
         <v>0.65</v>
       </c>
       <c r="S4" s="28" t="n">
-        <v>599.34</v>
+        <v>595.9299999999999</v>
       </c>
       <c r="T4" s="39" t="n">
         <v>0.0505</v>
@@ -4499,49 +4499,49 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>623.5599999999999</v>
+        <v>623.5</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>623.5599999999999</v>
+        <v>623.5</v>
       </c>
       <c r="J5" s="18" t="n">
         <v>1.095</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>623.5599999999999</v>
+        <v>623.5</v>
       </c>
       <c r="L5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>707.84</v>
+        <v>707.77</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>707.84</v>
+        <v>707.77</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>707.84</v>
+        <v>707.77</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>683.36</v>
+        <v>683.29</v>
       </c>
       <c r="T5" s="37" t="n">
         <v>0.0503</v>
@@ -4570,49 +4570,49 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>14.031222</v>
+        <v>14.002901</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>1.0227</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
       <c r="N6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
       <c r="P6" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="Q6" s="28" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
       <c r="R6" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" s="28" t="n">
-        <v>17.54</v>
+        <v>17.5</v>
       </c>
       <c r="T6" s="39" t="n">
         <v>0.0609</v>
@@ -4641,49 +4641,49 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>764.73</v>
+        <v>764.66</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>764.73</v>
+        <v>764.66</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.3429</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>764.73</v>
+        <v>764.66</v>
       </c>
       <c r="L7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>670.26</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>670.26</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>1.177</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>670.26</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="R7" s="18" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>785.86</v>
+        <v>785.78</v>
       </c>
       <c r="T7" s="37" t="n">
         <v>0.0503</v>
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>2979.243996</v>
+        <v>2979.382137</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3508.36</v>
+        <v>3508.52</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>3508.36</v>
+        <v>3508.52</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>1.1776</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>3508.36</v>
+        <v>3508.52</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="M8" s="28" t="n">
-        <v>3837.27</v>
+        <v>3837.44</v>
       </c>
       <c r="N8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>3837.27</v>
+        <v>3837.44</v>
       </c>
       <c r="P8" s="27" t="n">
         <v>1.288</v>
       </c>
       <c r="Q8" s="28" t="n">
-        <v>3837.27</v>
+        <v>3837.44</v>
       </c>
       <c r="R8" s="27" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" s="28" t="n">
-        <v>4319.9</v>
+        <v>4320.1</v>
       </c>
       <c r="T8" s="39" t="n">
         <v>0.1332</v>
@@ -4783,49 +4783,49 @@
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>941.21</v>
+        <v>941.11</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>941.21</v>
+        <v>941.11</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.6528</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>941.21</v>
+        <v>941.11</v>
       </c>
       <c r="L9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>1226.62</v>
+        <v>1226.5</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>1226.62</v>
+        <v>1226.5</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>1226.62</v>
+        <v>1226.5</v>
       </c>
       <c r="R9" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1025.03</v>
+        <v>1024.93</v>
       </c>
       <c r="T9" s="37" t="n">
         <v>0.0503</v>
@@ -4854,49 +4854,49 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95.725523</v>
+        <v>95.716026</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>108.77</v>
+        <v>108.76</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>108.77</v>
+        <v>108.76</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>1.1363</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>108.77</v>
+        <v>108.76</v>
       </c>
       <c r="L10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="M10" s="28" t="n">
-        <v>107.31</v>
+        <v>107.3</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>107.31</v>
+        <v>107.3</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>1.121</v>
       </c>
       <c r="Q10" s="28" t="n">
-        <v>107.31</v>
+        <v>107.3</v>
       </c>
       <c r="R10" s="27" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" s="28" t="n">
-        <v>116.79</v>
+        <v>116.77</v>
       </c>
       <c r="T10" s="39" t="n">
         <v>0.1171</v>
@@ -4925,49 +4925,49 @@
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>752.9400000000001</v>
+        <v>752.87</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>752.9400000000001</v>
+        <v>752.87</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>1.3222</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>752.9400000000001</v>
+        <v>752.87</v>
       </c>
       <c r="L11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>655.05</v>
+        <v>654.99</v>
       </c>
       <c r="N11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>655.05</v>
+        <v>654.99</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>1.1503</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>655.05</v>
+        <v>654.99</v>
       </c>
       <c r="R11" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>683.36</v>
+        <v>683.29</v>
       </c>
       <c r="T11" s="37" t="n">
         <v>0.0504</v>
@@ -4996,49 +4996,49 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>2291.748711</v>
+        <v>2283.099339</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2130.64</v>
+        <v>2122.6</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>2130.64</v>
+        <v>2122.6</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>0.9297</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>2130.64</v>
+        <v>2122.6</v>
       </c>
       <c r="L12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="M12" s="28" t="n">
-        <v>1975.49</v>
+        <v>1968.03</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>1975.49</v>
+        <v>1968.03</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0.862</v>
       </c>
       <c r="Q12" s="28" t="n">
-        <v>1975.49</v>
+        <v>1968.03</v>
       </c>
       <c r="R12" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="28" t="n">
-        <v>2864.69</v>
+        <v>2853.87</v>
       </c>
       <c r="T12" s="39" t="n">
         <v>0.132</v>
@@ -5067,25 +5067,25 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>52.745937</v>
+        <v>52.759664</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>20.7</v>
+        <v>20.71</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>20.7</v>
+        <v>20.71</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>0.3925</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>20.7</v>
+        <v>20.71</v>
       </c>
       <c r="L13" s="18" t="n">
         <v>0.3202</v>
@@ -5138,25 +5138,25 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>18.04</v>
+        <v>18.05</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>18.04</v>
+        <v>18.05</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1.0537</v>
       </c>
       <c r="K14" s="28" t="n">
-        <v>18.04</v>
+        <v>18.05</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>1.199</v>
@@ -5180,7 +5180,7 @@
         <v>1.25</v>
       </c>
       <c r="S14" s="28" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="T14" s="39" t="n">
         <v>0.0503</v>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>155.27097</v>
+        <v>155.184648</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>105.86</v>
+        <v>105.8</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>105.86</v>
+        <v>105.8</v>
       </c>
       <c r="J15" s="18" t="n">
         <v>0.6818</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>105.86</v>
+        <v>105.8</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>97.84</v>
+        <v>97.78</v>
       </c>
       <c r="N15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>97.84</v>
+        <v>97.78</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>0.6301</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>97.84</v>
+        <v>97.78</v>
       </c>
       <c r="R15" s="18" t="n">
         <v>1.05</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>163.03</v>
+        <v>162.94</v>
       </c>
       <c r="T15" s="37" t="n">
         <v>0.1616</v>
@@ -5280,49 +5280,49 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>535.3</v>
+        <v>535.24</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>535.3</v>
+        <v>535.24</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>535.3</v>
+        <v>535.24</v>
       </c>
       <c r="L16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="M16" s="28" t="n">
-        <v>517.64</v>
+        <v>517.59</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>517.64</v>
+        <v>517.59</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0.909</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>517.64</v>
+        <v>517.59</v>
       </c>
       <c r="R16" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="S16" s="28" t="n">
-        <v>512.52</v>
+        <v>512.47</v>
       </c>
       <c r="T16" s="39" t="n">
         <v>0.0503</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.020442</v>
+        <v>11.015379</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>1.1053</v>
@@ -5422,49 +5422,49 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>8767.130045</v>
+        <v>8766.83993</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>10414.47</v>
+        <v>10414.13</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>10414.47</v>
+        <v>10414.13</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>1.1879</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>10414.47</v>
+        <v>10414.13</v>
       </c>
       <c r="L18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="M18" s="28" t="n">
-        <v>11756.72</v>
+        <v>11756.33</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>11756.72</v>
+        <v>11756.33</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>1.341</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>11756.72</v>
+        <v>11756.33</v>
       </c>
       <c r="R18" s="27" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" s="28" t="n">
-        <v>11221.93</v>
+        <v>11221.56</v>
       </c>
       <c r="T18" s="39" t="n">
         <v>0.07780000000000001</v>
@@ -5493,49 +5493,49 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>735.29</v>
+        <v>735.22</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>735.29</v>
+        <v>735.22</v>
       </c>
       <c r="J19" s="18" t="n">
         <v>1.2912</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>735.29</v>
+        <v>735.22</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>663.99</v>
+        <v>663.9299999999999</v>
       </c>
       <c r="N19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>663.99</v>
+        <v>663.9299999999999</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>1.166</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>663.99</v>
+        <v>663.9299999999999</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>626.41</v>
+        <v>626.35</v>
       </c>
       <c r="T19" s="37" t="n">
         <v>0.0503</v>
@@ -5564,49 +5564,49 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>129.765701</v>
+        <v>129.773208</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>158.17</v>
+        <v>158.18</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>158.17</v>
+        <v>158.18</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>158.17</v>
+        <v>158.18</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="M20" s="28" t="n">
-        <v>165.97</v>
+        <v>165.98</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>165.97</v>
+        <v>165.98</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1.279</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>165.97</v>
+        <v>165.98</v>
       </c>
       <c r="R20" s="27" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" s="28" t="n">
-        <v>175.18</v>
+        <v>175.19</v>
       </c>
       <c r="T20" s="39" t="n">
         <v>0.0504</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0.9607</v>
@@ -5659,25 +5659,25 @@
         <v>1.156</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="N21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>1.156</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="T21" s="37" t="n">
         <v>0.0616</v>
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>183.689846</v>
+        <v>183.703402</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>134.72</v>
+        <v>134.73</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>134.72</v>
+        <v>134.73</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>0.7334000000000001</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>134.72</v>
+        <v>134.73</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="M22" s="28" t="n">
-        <v>146.11</v>
+        <v>146.12</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>146.11</v>
+        <v>146.12</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0.7954</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>146.11</v>
+        <v>146.12</v>
       </c>
       <c r="R22" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" s="28" t="n">
-        <v>220.43</v>
+        <v>220.44</v>
       </c>
       <c r="T22" s="39" t="n">
         <v>0.1539</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>6.374935</v>
+        <v>6.374928</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>0.0309</v>
@@ -5848,49 +5848,49 @@
         </is>
       </c>
       <c r="E24" s="38" t="n">
-        <v>4174.357607</v>
+        <v>4174.132824</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>4053.3</v>
+        <v>4053.08</v>
       </c>
       <c r="H24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>4053.3</v>
+        <v>4053.08</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>0.971</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>4053.3</v>
+        <v>4053.08</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="M24" s="28" t="n">
-        <v>6470.25</v>
+        <v>6469.91</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>6470.25</v>
+        <v>6469.91</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>6470.25</v>
+        <v>6469.91</v>
       </c>
       <c r="R24" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" s="28" t="n">
-        <v>5426.66</v>
+        <v>5426.37</v>
       </c>
       <c r="T24" s="39" t="n">
         <v>0.1285</v>
@@ -5919,49 +5919,49 @@
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>1744.734226</v>
+        <v>1744.076495</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>4325.55</v>
+        <v>4323.91</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>4325.55</v>
+        <v>4323.91</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>2.4792</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>4325.55</v>
+        <v>4323.91</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>3515.64</v>
+        <v>3514.31</v>
       </c>
       <c r="N25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>3515.64</v>
+        <v>3514.31</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>3515.64</v>
+        <v>3514.31</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>4187.36</v>
+        <v>4185.78</v>
       </c>
       <c r="T25" s="37" t="n">
         <v>0.0766</v>
@@ -5990,49 +5990,49 @@
         </is>
       </c>
       <c r="E26" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>694.12</v>
+        <v>694.05</v>
       </c>
       <c r="H26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>694.12</v>
+        <v>694.05</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>1.2189</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>694.12</v>
+        <v>694.05</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="M26" s="28" t="n">
-        <v>603.86</v>
+        <v>603.8</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>603.86</v>
+        <v>603.8</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>1.0604</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>603.86</v>
+        <v>603.8</v>
       </c>
       <c r="R26" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>740.3</v>
+        <v>740.23</v>
       </c>
       <c r="T26" s="39" t="n">
         <v>0.0592</v>
@@ -6061,49 +6061,49 @@
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>46.664963</v>
+        <v>46.642551</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>52.06</v>
+        <v>52.03</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>52.06</v>
+        <v>52.03</v>
       </c>
       <c r="J27" s="18" t="n">
         <v>1.1156</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>52.06</v>
+        <v>52.03</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>59.54</v>
+        <v>59.52</v>
       </c>
       <c r="N27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>59.54</v>
+        <v>59.52</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>1.276</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>59.54</v>
+        <v>59.52</v>
       </c>
       <c r="R27" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>65.33</v>
+        <v>65.3</v>
       </c>
       <c r="T27" s="37" t="n">
         <v>0.0698</v>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="E28" s="38" t="n">
-        <v>9.343978</v>
+        <v>9.344307000000001</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1.157</v>
@@ -6203,49 +6203,49 @@
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>63.61008</v>
+        <v>63.423144</v>
       </c>
       <c r="F29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>72.28</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>72.28</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>1.1363</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>72.28</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="L29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>78.56</v>
+        <v>78.33</v>
       </c>
       <c r="N29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>78.56</v>
+        <v>78.33</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>78.56</v>
+        <v>78.33</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>82.69</v>
+        <v>82.45</v>
       </c>
       <c r="T29" s="37" t="n">
         <v>0.0789</v>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="E30" s="38" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>1.064</v>
@@ -6316,7 +6316,7 @@
         <v>1.25</v>
       </c>
       <c r="S30" s="28" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="T30" s="39" t="n">
         <v>0.0504</v>
@@ -6345,49 +6345,49 @@
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>627.55</v>
+        <v>627.49</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>627.55</v>
+        <v>627.49</v>
       </c>
       <c r="J31" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>627.55</v>
+        <v>627.49</v>
       </c>
       <c r="L31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>570.6</v>
+        <v>570.55</v>
       </c>
       <c r="N31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>570.6</v>
+        <v>570.55</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>570.6</v>
+        <v>570.55</v>
       </c>
       <c r="R31" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>711.83</v>
+        <v>711.76</v>
       </c>
       <c r="T31" s="40" t="n">
         <v>0</v>
@@ -6416,49 +6416,49 @@
         </is>
       </c>
       <c r="E32" s="38" t="n">
-        <v>1382.529699</v>
+        <v>1381.9143</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>0.5062</v>
       </c>
       <c r="G32" s="28" t="n">
-        <v>699.84</v>
+        <v>699.53</v>
       </c>
       <c r="H32" s="27" t="n">
         <v>0.5366</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>741.87</v>
+        <v>741.54</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>0.5568</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>769.79</v>
+        <v>769.45</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>799.79</v>
+        <v>799.4400000000001</v>
       </c>
       <c r="N32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>799.79</v>
+        <v>799.4400000000001</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>0.5785</v>
       </c>
       <c r="Q32" s="28" t="n">
-        <v>799.79</v>
+        <v>799.4400000000001</v>
       </c>
       <c r="R32" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S32" s="28" t="n">
-        <v>760.39</v>
+        <v>760.05</v>
       </c>
       <c r="T32" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -6487,49 +6487,49 @@
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>1457.46283</v>
+        <v>1457.626546</v>
       </c>
       <c r="F33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1777.81</v>
+        <v>1778.01</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1777.81</v>
+        <v>1778.01</v>
       </c>
       <c r="J33" s="18" t="n">
         <v>1.2198</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1777.81</v>
+        <v>1778.01</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1909.28</v>
+        <v>1909.49</v>
       </c>
       <c r="N33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1909.28</v>
+        <v>1909.49</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>1909.28</v>
+        <v>1909.49</v>
       </c>
       <c r="R33" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>2113.32</v>
+        <v>2113.56</v>
       </c>
       <c r="T33" s="37" t="n">
         <v>0.1524</v>
@@ -6558,49 +6558,49 @@
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="G34" s="28" t="n">
-        <v>829.42</v>
+        <v>829.34</v>
       </c>
       <c r="H34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>829.42</v>
+        <v>829.34</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>1.4565</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>829.42</v>
+        <v>829.34</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="M34" s="28" t="n">
-        <v>739.16</v>
+        <v>739.09</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>739.16</v>
+        <v>739.09</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>1.298</v>
       </c>
       <c r="Q34" s="28" t="n">
-        <v>739.16</v>
+        <v>739.09</v>
       </c>
       <c r="R34" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="S34" s="28" t="n">
-        <v>654.88</v>
+        <v>654.8200000000001</v>
       </c>
       <c r="T34" s="39" t="n">
         <v>0.0503</v>
@@ -6629,49 +6629,49 @@
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>14.114736</v>
+        <v>14.130415</v>
       </c>
       <c r="F35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>18.37</v>
+        <v>18.39</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>18.37</v>
+        <v>18.39</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1.3016</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>18.37</v>
+        <v>18.39</v>
       </c>
       <c r="L35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>18.77</v>
+        <v>18.79</v>
       </c>
       <c r="N35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>18.77</v>
+        <v>18.79</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>18.77</v>
+        <v>18.79</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.6</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="T35" s="37" t="n">
         <v>0.0837</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>17.121639</v>
+        <v>17.11952</v>
       </c>
       <c r="F37" s="18" t="n">
         <v>1.19</v>
@@ -6842,49 +6842,49 @@
         </is>
       </c>
       <c r="E38" s="38" t="n">
-        <v>511.014831</v>
+        <v>509.538566</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>311.46</v>
+        <v>310.56</v>
       </c>
       <c r="H38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>311.46</v>
+        <v>310.56</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>0.6095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>311.46</v>
+        <v>310.56</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>290.36</v>
+        <v>289.52</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>290.36</v>
+        <v>289.52</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>0.5682</v>
       </c>
       <c r="Q38" s="28" t="n">
-        <v>290.36</v>
+        <v>289.52</v>
       </c>
       <c r="R38" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="S38" s="28" t="n">
-        <v>281.06</v>
+        <v>280.25</v>
       </c>
       <c r="T38" s="39" t="n">
         <v>0.06809999999999999</v>
@@ -6913,49 +6913,49 @@
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>2579.094525</v>
+        <v>2569.132481</v>
       </c>
       <c r="F39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>2424.35</v>
+        <v>2414.98</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>2424.35</v>
+        <v>2414.98</v>
       </c>
       <c r="J39" s="18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>2424.35</v>
+        <v>2414.98</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>2610.04</v>
+        <v>2599.96</v>
       </c>
       <c r="N39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>2610.04</v>
+        <v>2599.96</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>2610.04</v>
+        <v>2599.96</v>
       </c>
       <c r="R39" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>3223.87</v>
+        <v>3211.42</v>
       </c>
       <c r="T39" s="37" t="n">
         <v>0.0965</v>
@@ -6984,49 +6984,49 @@
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="G40" s="28" t="n">
-        <v>611.77</v>
+        <v>611.71</v>
       </c>
       <c r="H40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>611.77</v>
+        <v>611.71</v>
       </c>
       <c r="J40" s="27" t="n">
         <v>1.0743</v>
       </c>
       <c r="K40" s="28" t="n">
-        <v>611.77</v>
+        <v>611.71</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="M40" s="28" t="n">
-        <v>672.54</v>
+        <v>672.47</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>672.54</v>
+        <v>672.47</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>1.181</v>
       </c>
       <c r="Q40" s="28" t="n">
-        <v>672.54</v>
+        <v>672.47</v>
       </c>
       <c r="R40" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="S40" s="28" t="n">
-        <v>626.41</v>
+        <v>626.35</v>
       </c>
       <c r="T40" s="39" t="n">
         <v>0.0504</v>
@@ -7055,25 +7055,25 @@
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>2.927391</v>
+        <v>2.926309</v>
       </c>
       <c r="F41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>0.8661</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="L41" s="18" t="n">
         <v>0.7566000000000001</v>
@@ -7126,49 +7126,49 @@
         </is>
       </c>
       <c r="E42" s="38" t="n">
-        <v>3724.737851</v>
+        <v>3723.861301</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="G42" s="28" t="n">
-        <v>5143.86</v>
+        <v>5142.65</v>
       </c>
       <c r="H42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>5143.86</v>
+        <v>5142.65</v>
       </c>
       <c r="J42" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>5143.86</v>
+        <v>5142.65</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="M42" s="28" t="n">
-        <v>4283.45</v>
+        <v>4282.44</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>4283.45</v>
+        <v>4282.44</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>4283.45</v>
+        <v>4282.44</v>
       </c>
       <c r="R42" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" s="28" t="n">
-        <v>4842.16</v>
+        <v>4841.02</v>
       </c>
       <c r="T42" s="41" t="n">
         <v>0</v>
@@ -7197,49 +7197,49 @@
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>18.969397</v>
+        <v>18.956944</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24.1</v>
+        <v>24.09</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>24.1</v>
+        <v>24.09</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>1.2706</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>24.1</v>
+        <v>24.09</v>
       </c>
       <c r="L43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>19.37</v>
+        <v>19.36</v>
       </c>
       <c r="N43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>19.37</v>
+        <v>19.36</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>1.021</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>19.37</v>
+        <v>19.36</v>
       </c>
       <c r="R43" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>24.66</v>
+        <v>24.64</v>
       </c>
       <c r="T43" s="40" t="n">
         <v>0.0076</v>
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>132.722332</v>
+        <v>132.727443</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>42.5</v>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>922.0653620000001</v>
+        <v>916.813803</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>266.66</v>
+        <v>265.14</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>0.2892</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>623.5599999999999</v>
+        <v>623.5</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>1.095</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>14.031222</v>
+        <v>14.002901</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>1.0227</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>764.73</v>
+        <v>764.66</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>1.3429</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>2979.243996</v>
+        <v>2979.382137</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3508.36</v>
+        <v>3508.52</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>1.1776</v>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>941.21</v>
+        <v>941.11</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>1.6528</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>95.725523</v>
+        <v>95.716026</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>108.77</v>
+        <v>108.76</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>1.1363</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>752.9400000000001</v>
+        <v>752.87</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>1.3222</v>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>2291.748711</v>
+        <v>2283.099339</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2130.64</v>
+        <v>2122.6</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0.9297</v>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>52.745937</v>
+        <v>52.759664</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>20.7</v>
+        <v>20.71</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>0.3925</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="F14" s="28" t="n">
-        <v>18.04</v>
+        <v>18.05</v>
       </c>
       <c r="G14" s="27" t="n">
         <v>1.0537</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>155.27097</v>
+        <v>155.184648</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>105.86</v>
+        <v>105.8</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.6818</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>535.3</v>
+        <v>535.24</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.9399999999999999</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>11.020442</v>
+        <v>11.015379</v>
       </c>
       <c r="F17" s="19" t="n">
         <v>12.18</v>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>8767.130045</v>
+        <v>8766.83993</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>10414.47</v>
+        <v>10414.13</v>
       </c>
       <c r="G18" s="27" t="n">
         <v>1.1879</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>735.29</v>
+        <v>735.22</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>1.2912</v>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>129.765701</v>
+        <v>129.773208</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>158.17</v>
+        <v>158.18</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>1.2189</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="F21" s="19" t="n">
         <v>16.45</v>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>183.689846</v>
+        <v>183.703402</v>
       </c>
       <c r="F22" s="28" t="n">
-        <v>134.72</v>
+        <v>134.73</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>0.7334000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.374935</v>
+        <v>6.374928</v>
       </c>
       <c r="F23" s="19" t="n">
         <v>0.2</v>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4174.357607</v>
+        <v>4174.132824</v>
       </c>
       <c r="F24" s="28" t="n">
-        <v>4053.3</v>
+        <v>4053.08</v>
       </c>
       <c r="G24" s="27" t="n">
         <v>0.971</v>
@@ -8781,10 +8781,10 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1744.734226</v>
+        <v>1744.076495</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>4325.55</v>
+        <v>4323.91</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>2.4792</v>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F26" s="28" t="n">
-        <v>694.12</v>
+        <v>694.05</v>
       </c>
       <c r="G26" s="27" t="n">
         <v>1.2189</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>46.664963</v>
+        <v>46.642551</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>52.06</v>
+        <v>52.03</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1.1156</v>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>9.343978</v>
+        <v>9.344307000000001</v>
       </c>
       <c r="F28" s="28" t="n">
         <v>10.81</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>63.61008</v>
+        <v>63.423144</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>72.28</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>1.1363</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="F30" s="28" t="n">
         <v>18.22</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>627.55</v>
+        <v>627.49</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>1.102</v>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1382.529699</v>
+        <v>1381.9143</v>
       </c>
       <c r="F32" s="28" t="n">
-        <v>699.84</v>
+        <v>699.53</v>
       </c>
       <c r="G32" s="27" t="n">
         <v>0.5062</v>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>1457.46283</v>
+        <v>1457.626546</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>1777.81</v>
+        <v>1778.01</v>
       </c>
       <c r="G33" s="18" t="n">
         <v>1.2198</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>829.42</v>
+        <v>829.34</v>
       </c>
       <c r="G34" s="27" t="n">
         <v>1.4565</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>14.114736</v>
+        <v>14.130415</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>18.37</v>
+        <v>18.39</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>1.3016</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>17.121639</v>
+        <v>17.11952</v>
       </c>
       <c r="F37" s="19" t="n">
         <v>20.37</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>511.014831</v>
+        <v>509.538566</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>311.46</v>
+        <v>310.56</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>0.6095</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2579.094525</v>
+        <v>2569.132481</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>2424.35</v>
+        <v>2414.98</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>0.9399999999999999</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="F40" s="28" t="n">
-        <v>611.77</v>
+        <v>611.71</v>
       </c>
       <c r="G40" s="27" t="n">
         <v>1.0743</v>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>2.927391</v>
+        <v>2.926309</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>0.8661</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>3724.737851</v>
+        <v>3723.861301</v>
       </c>
       <c r="F42" s="28" t="n">
-        <v>5143.86</v>
+        <v>5142.65</v>
       </c>
       <c r="G42" s="27" t="n">
         <v>1.381</v>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>18.969397</v>
+        <v>18.956944</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>24.1</v>
+        <v>24.09</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>1.2706</v>
@@ -10244,13 +10244,13 @@
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>132.722332</v>
+        <v>132.727443</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>0.3363</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>44.63</v>
+        <v>44.64</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.217</v>
@@ -10262,7 +10262,7 @@
         <v>0.31</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>41.14</v>
+        <v>41.15</v>
       </c>
       <c r="K5" s="37" t="n">
         <v>0.0503</v>
@@ -10283,13 +10283,13 @@
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>52.745937</v>
+        <v>52.759664</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>0.434</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>22.89</v>
+        <v>22.9</v>
       </c>
       <c r="G6" s="27" t="n">
         <v>0.3689</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6.374935</v>
+        <v>6.374928</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0.0309</v>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>9.343978</v>
+        <v>9.344307000000001</v>
       </c>
       <c r="E8" s="27" t="n">
         <v>1.3853</v>
@@ -10400,25 +10400,25 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>511.014831</v>
+        <v>509.538566</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>0.651</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>332.67</v>
+        <v>331.71</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.6076</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>310.49</v>
+        <v>309.6</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>281.06</v>
+        <v>280.25</v>
       </c>
       <c r="K9" s="37" t="n">
         <v>0.06809999999999999</v>
@@ -10439,13 +10439,13 @@
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>2.927391</v>
+        <v>2.926309</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>0.8661</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>0.7566000000000001</v>
@@ -10549,25 +10549,25 @@
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>1.1501</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>654.9400000000001</v>
+        <v>654.87</v>
       </c>
       <c r="G16" s="18" t="n">
         <v>1.243</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>707.84</v>
+        <v>707.77</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>683.36</v>
+        <v>683.29</v>
       </c>
       <c r="K16" s="37" t="n">
         <v>0.0503</v>
@@ -10588,25 +10588,25 @@
         </is>
       </c>
       <c r="D17" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E17" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>803.23</v>
+        <v>803.15</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>1.177</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>670.26</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="I17" s="27" t="n">
         <v>1.38</v>
       </c>
       <c r="J17" s="28" t="n">
-        <v>785.86</v>
+        <v>785.78</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>0.0503</v>
@@ -10627,25 +10627,25 @@
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>95.725523</v>
+        <v>95.716026</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>1.2694</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>121.51</v>
+        <v>121.5</v>
       </c>
       <c r="G18" s="18" t="n">
         <v>1.121</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>107.31</v>
+        <v>107.3</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>1.22</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>116.79</v>
+        <v>116.77</v>
       </c>
       <c r="K18" s="37" t="n">
         <v>0.1171</v>
@@ -10666,7 +10666,7 @@
         </is>
       </c>
       <c r="D19" s="38" t="n">
-        <v>11.020442</v>
+        <v>11.015379</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>1.1609</v>
@@ -10705,25 +10705,25 @@
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8767.130045</v>
+        <v>8766.83993</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>11224.56</v>
+        <v>11224.19</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>1.341</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>11756.72</v>
+        <v>11756.33</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>1.28</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>11221.93</v>
+        <v>11221.56</v>
       </c>
       <c r="K20" s="37" t="n">
         <v>0.07780000000000001</v>
@@ -10744,25 +10744,25 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>1.3562</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>772.3099999999999</v>
+        <v>772.23</v>
       </c>
       <c r="G21" s="27" t="n">
         <v>1.166</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>663.99</v>
+        <v>663.9299999999999</v>
       </c>
       <c r="I21" s="27" t="n">
         <v>1.1</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>626.41</v>
+        <v>626.35</v>
       </c>
       <c r="K21" s="39" t="n">
         <v>0.0503</v>
@@ -10783,25 +10783,25 @@
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>183.689846</v>
+        <v>183.703402</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>0.8463000000000001</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>155.46</v>
+        <v>155.47</v>
       </c>
       <c r="G22" s="18" t="n">
         <v>0.9114</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>167.41</v>
+        <v>167.43</v>
       </c>
       <c r="I22" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>220.43</v>
+        <v>220.44</v>
       </c>
       <c r="K22" s="37" t="n">
         <v>0.1539</v>
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="D23" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>1.2911</v>
       </c>
       <c r="F23" s="28" t="n">
-        <v>735.23</v>
+        <v>735.16</v>
       </c>
       <c r="G23" s="27" t="n">
         <v>1.1233</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>639.6799999999999</v>
+        <v>639.61</v>
       </c>
       <c r="I23" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J23" s="28" t="n">
-        <v>740.3</v>
+        <v>740.23</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>0.0592</v>
@@ -10861,25 +10861,25 @@
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1.102</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>627.55</v>
+        <v>627.49</v>
       </c>
       <c r="G24" s="18" t="n">
         <v>1.002</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>570.6</v>
+        <v>570.55</v>
       </c>
       <c r="I24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>711.83</v>
+        <v>711.76</v>
       </c>
       <c r="K24" s="40" t="n">
         <v>0</v>
@@ -10900,25 +10900,25 @@
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>1382.529699</v>
+        <v>1381.9143</v>
       </c>
       <c r="E25" s="27" t="n">
         <v>0.786</v>
       </c>
       <c r="F25" s="28" t="n">
-        <v>1086.67</v>
+        <v>1086.18</v>
       </c>
       <c r="G25" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>1364.97</v>
+        <v>1364.36</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>760.39</v>
+        <v>760.05</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>0.5527000000000001</v>
@@ -10939,25 +10939,25 @@
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>1.5298</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>871.16</v>
+        <v>871.08</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1.298</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>739.16</v>
+        <v>739.09</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>1.15</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>654.88</v>
+        <v>654.8200000000001</v>
       </c>
       <c r="K26" s="37" t="n">
         <v>0.0503</v>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>1.1284</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>642.58</v>
+        <v>642.52</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1.181</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>672.54</v>
+        <v>672.47</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1.1</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>626.41</v>
+        <v>626.35</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>0.0504</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>2979.243996</v>
+        <v>2979.382137</v>
       </c>
       <c r="E34" s="18" t="n">
         <v>1.3345</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>3975.8</v>
+        <v>3975.99</v>
       </c>
       <c r="G34" s="18" t="n">
         <v>1.288</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>3837.27</v>
+        <v>3837.44</v>
       </c>
       <c r="I34" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>4319.9</v>
+        <v>4320.1</v>
       </c>
       <c r="K34" s="37" t="n">
         <v>0.1332</v>
@@ -11166,25 +11166,25 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>155.27097</v>
+        <v>155.184648</v>
       </c>
       <c r="E35" s="27" t="n">
         <v>0.792</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>122.97</v>
+        <v>122.91</v>
       </c>
       <c r="G35" s="27" t="n">
         <v>0.8355</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>129.73</v>
+        <v>129.66</v>
       </c>
       <c r="I35" s="27" t="n">
         <v>1.05</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>163.03</v>
+        <v>162.94</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>0.1616</v>
@@ -11205,25 +11205,25 @@
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>129.765701</v>
+        <v>129.773208</v>
       </c>
       <c r="E36" s="18" t="n">
         <v>1.2803</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>166.14</v>
+        <v>166.15</v>
       </c>
       <c r="G36" s="18" t="n">
         <v>1.279</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>165.97</v>
+        <v>165.98</v>
       </c>
       <c r="I36" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>175.18</v>
+        <v>175.19</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>0.0504</v>
@@ -11244,25 +11244,25 @@
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>4174.357607</v>
+        <v>4174.132824</v>
       </c>
       <c r="E37" s="27" t="n">
         <v>1.0958</v>
       </c>
       <c r="F37" s="28" t="n">
-        <v>4574.26</v>
+        <v>4574.01</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>1.55</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>6470.25</v>
+        <v>6469.91</v>
       </c>
       <c r="I37" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>5426.66</v>
+        <v>5426.37</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>0.1285</v>
@@ -11283,25 +11283,25 @@
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>1744.734226</v>
+        <v>1744.076495</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>2.6691</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>4656.87</v>
+        <v>4655.11</v>
       </c>
       <c r="G38" s="18" t="n">
         <v>2.015</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3515.64</v>
+        <v>3514.31</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>2.4</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>4187.36</v>
+        <v>4185.78</v>
       </c>
       <c r="K38" s="37" t="n">
         <v>0.0766</v>
@@ -11322,25 +11322,25 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>46.664963</v>
+        <v>46.642551</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>1.1935</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>55.69</v>
+        <v>55.67</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>1.276</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>59.54</v>
+        <v>59.52</v>
       </c>
       <c r="I39" s="27" t="n">
         <v>1.4</v>
       </c>
       <c r="J39" s="28" t="n">
-        <v>65.33</v>
+        <v>65.3</v>
       </c>
       <c r="K39" s="39" t="n">
         <v>0.0698</v>
@@ -11361,25 +11361,25 @@
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>1457.46283</v>
+        <v>1457.626546</v>
       </c>
       <c r="E40" s="18" t="n">
         <v>1.4057</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>2048.76</v>
+        <v>2048.99</v>
       </c>
       <c r="G40" s="18" t="n">
         <v>1.31</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>1909.28</v>
+        <v>1909.49</v>
       </c>
       <c r="I40" s="18" t="n">
         <v>1.45</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>2113.32</v>
+        <v>2113.56</v>
       </c>
       <c r="K40" s="37" t="n">
         <v>0.1524</v>
@@ -11400,25 +11400,25 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>14.114736</v>
+        <v>14.130415</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1.4105</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>19.91</v>
+        <v>19.93</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>1.33</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>18.77</v>
+        <v>18.79</v>
       </c>
       <c r="I41" s="27" t="n">
         <v>1.6</v>
       </c>
       <c r="J41" s="28" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="K41" s="39" t="n">
         <v>0.0837</v>
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>2579.094525</v>
+        <v>2569.132481</v>
       </c>
       <c r="E42" s="18" t="n">
         <v>1.0307</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>2658.27</v>
+        <v>2648</v>
       </c>
       <c r="G42" s="18" t="n">
         <v>1.012</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>2610.04</v>
+        <v>2599.96</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>3223.87</v>
+        <v>3211.42</v>
       </c>
       <c r="K42" s="37" t="n">
         <v>0.0965</v>
@@ -11478,25 +11478,25 @@
         </is>
       </c>
       <c r="D43" s="38" t="n">
-        <v>3724.737851</v>
+        <v>3723.861301</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>1.381</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5143.86</v>
+        <v>5142.65</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>1.15</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>4283.45</v>
+        <v>4282.44</v>
       </c>
       <c r="I43" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J43" s="28" t="n">
-        <v>4842.16</v>
+        <v>4841.02</v>
       </c>
       <c r="K43" s="41" t="n">
         <v>0</v>
@@ -11588,25 +11588,25 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E49" s="18" t="n">
         <v>1.736</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>988.59</v>
+        <v>988.49</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>2.154</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>1226.62</v>
+        <v>1226.5</v>
       </c>
       <c r="I49" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1025.03</v>
+        <v>1024.93</v>
       </c>
       <c r="K49" s="37" t="n">
         <v>0.0503</v>
@@ -11627,25 +11627,25 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E50" s="27" t="n">
         <v>1.3888</v>
       </c>
       <c r="F50" s="28" t="n">
-        <v>790.87</v>
+        <v>790.79</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>1.2083</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>688.08</v>
+        <v>688.01</v>
       </c>
       <c r="I50" s="27" t="n">
         <v>1.2</v>
       </c>
       <c r="J50" s="28" t="n">
-        <v>683.36</v>
+        <v>683.29</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>0.0504</v>
@@ -11666,25 +11666,25 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>2291.748711</v>
+        <v>2283.099339</v>
       </c>
       <c r="E51" s="18" t="n">
         <v>1.0524</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>2411.84</v>
+        <v>2402.73</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>0.862</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>1975.49</v>
+        <v>1968.03</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>2864.69</v>
+        <v>2853.87</v>
       </c>
       <c r="K51" s="37" t="n">
         <v>0.132</v>
@@ -11705,25 +11705,25 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E52" s="27" t="n">
         <v>0.9873</v>
       </c>
       <c r="F52" s="28" t="n">
-        <v>562.23</v>
+        <v>562.17</v>
       </c>
       <c r="G52" s="27" t="n">
         <v>0.9548</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>543.72</v>
+        <v>543.67</v>
       </c>
       <c r="I52" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="J52" s="28" t="n">
-        <v>512.52</v>
+        <v>512.47</v>
       </c>
       <c r="K52" s="39" t="n">
         <v>0.0503</v>
@@ -11815,25 +11815,25 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>922.0653620000001</v>
+        <v>916.813803</v>
       </c>
       <c r="E58" s="18" t="n">
         <v>0.3038</v>
       </c>
       <c r="F58" s="19" t="n">
-        <v>280.12</v>
+        <v>278.53</v>
       </c>
       <c r="G58" s="18" t="n">
         <v>0.4123</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>380.17</v>
+        <v>378</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>0.65</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>599.34</v>
+        <v>595.9299999999999</v>
       </c>
       <c r="K58" s="37" t="n">
         <v>0.0505</v>
@@ -11854,25 +11854,25 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>14.031222</v>
+        <v>14.002901</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>1.085</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>15.22</v>
+        <v>15.19</v>
       </c>
       <c r="G59" s="27" t="n">
         <v>1.041</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
       <c r="I59" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J59" s="28" t="n">
-        <v>17.54</v>
+        <v>17.5</v>
       </c>
       <c r="K59" s="39" t="n">
         <v>0.0609</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="D60" s="36" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>1.1067</v>
@@ -11911,7 +11911,7 @@
         <v>1.25</v>
       </c>
       <c r="J60" s="19" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>0.0503</v>
@@ -11932,25 +11932,25 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>1.0199</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>17.46</v>
+        <v>17.47</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>1.156</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="I61" s="27" t="n">
         <v>1.25</v>
       </c>
       <c r="J61" s="28" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="K61" s="39" t="n">
         <v>0.0616</v>
@@ -11971,25 +11971,25 @@
         </is>
       </c>
       <c r="D62" s="36" t="n">
-        <v>63.61008</v>
+        <v>63.423144</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>1.226</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>77.98999999999999</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>1.235</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>78.56</v>
+        <v>78.33</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>1.3</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>82.69</v>
+        <v>82.45</v>
       </c>
       <c r="K62" s="37" t="n">
         <v>0.0789</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="D63" s="38" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="E63" s="27" t="n">
         <v>1.1176</v>
@@ -12028,7 +12028,7 @@
         <v>1.25</v>
       </c>
       <c r="J63" s="28" t="n">
-        <v>21.4</v>
+        <v>21.41</v>
       </c>
       <c r="K63" s="39" t="n">
         <v>0.0504</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="D64" s="36" t="n">
-        <v>17.121639</v>
+        <v>17.11952</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>1.19</v>
@@ -12088,25 +12088,25 @@
         </is>
       </c>
       <c r="D65" s="38" t="n">
-        <v>18.969397</v>
+        <v>18.956944</v>
       </c>
       <c r="E65" s="27" t="n">
         <v>1.2803</v>
       </c>
       <c r="F65" s="28" t="n">
-        <v>24.29</v>
+        <v>24.27</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>1.021</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>19.37</v>
+        <v>19.36</v>
       </c>
       <c r="I65" s="27" t="n">
         <v>1.3</v>
       </c>
       <c r="J65" s="28" t="n">
-        <v>24.66</v>
+        <v>24.64</v>
       </c>
       <c r="K65" s="41" t="n">
         <v>0.0076</v>
@@ -12397,7 +12397,7 @@
         <v>2.6691</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>4656.87</v>
+        <v>4655.11</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0.3038</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>280.12</v>
+        <v>278.53</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.736</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>988.59</v>
+        <v>988.49</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>0.3363</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>44.63</v>
+        <v>44.64</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>1.5298</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>871.16</v>
+        <v>871.08</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>0.434</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>22.89</v>
+        <v>22.9</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.651</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>332.67</v>
+        <v>331.71</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>1.4105</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>803.23</v>
+        <v>803.15</v>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>0.786</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>1086.67</v>
+        <v>1086.18</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>1.4105</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>19.91</v>
+        <v>19.93</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>0.792</v>
       </c>
       <c r="N11" s="19" t="n">
-        <v>122.97</v>
+        <v>122.91</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>1.4057</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>2048.76</v>
+        <v>2048.99</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>155.46</v>
+        <v>155.47</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>1.3888</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>790.87</v>
+        <v>790.79</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>0.8661</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>0.9873</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>562.23</v>
+        <v>562.17</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>922.0653620000001</v>
+        <v>916.813803</v>
       </c>
       <c r="E3" s="63" t="n">
-        <v>0.00108452</v>
+        <v>0.00109073</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>2979.243996</v>
+        <v>2979.382137</v>
       </c>
       <c r="E4" s="65" t="n">
-        <v>0.00033566</v>
+        <v>0.00033564</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>14.031222</v>
+        <v>14.002901</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.07126963</v>
+        <v>0.07141377</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>2291.748711</v>
+        <v>2283.099339</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.00043635</v>
+        <v>0.000438</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>95.725523</v>
+        <v>95.716026</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.01044653</v>
+        <v>0.01044757</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>132.722332</v>
+        <v>132.727443</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.00753453</v>
+        <v>0.00753424</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>52.745937</v>
+        <v>52.759664</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.01895881</v>
+        <v>0.01895387</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>155.27097</v>
+        <v>155.184648</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.00644035</v>
+        <v>0.00644394</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>11.020442</v>
+        <v>11.015379</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.09074046</v>
+        <v>0.09078217</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -13710,10 +13710,10 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>74.18787</v>
+        <v>74.187814</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.01347929</v>
+        <v>0.0134793</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>8767.130045</v>
+        <v>8766.83993</v>
       </c>
       <c r="E15" s="63" t="n">
-        <v>0.00011406</v>
+        <v>0.00011407</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>129.765701</v>
+        <v>129.773208</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>0.0077062</v>
+        <v>0.00770575</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>427.097178</v>
+        <v>427.054805</v>
       </c>
       <c r="E17" s="63" t="n">
-        <v>0.00234139</v>
+        <v>0.00234162</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -13802,10 +13802,10 @@
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>183.689846</v>
+        <v>183.703402</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>0.00544396</v>
+        <v>0.00544356</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
@@ -13825,10 +13825,10 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="E19" s="63" t="n">
-        <v>0.05840584</v>
+        <v>0.05839014</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>6.374935</v>
+        <v>6.374928</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>0.15686434</v>
+        <v>0.15686452</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>9.343978</v>
+        <v>9.344307000000001</v>
       </c>
       <c r="E21" s="63" t="n">
-        <v>0.1070208</v>
+        <v>0.10701703</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="D22" s="26" t="n">
-        <v>4174.357607</v>
+        <v>4174.132824</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>0.00023956</v>
+        <v>0.00023957</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39.897298</v>
+        <v>39.897655</v>
       </c>
       <c r="E23" s="63" t="n">
-        <v>0.02506435</v>
+        <v>0.02506413</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>46.664963</v>
+        <v>46.642551</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>0.02142935</v>
+        <v>0.02143965</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>1744.734226</v>
+        <v>1744.076495</v>
       </c>
       <c r="E25" s="63" t="n">
-        <v>0.00057315</v>
+        <v>0.00057337</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -13986,10 +13986,10 @@
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>63.61008</v>
+        <v>63.423144</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>0.01572078</v>
+        <v>0.01576711</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="E27" s="63" t="n">
-        <v>0.05840584</v>
+        <v>0.05839014</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -14032,10 +14032,10 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1382.529699</v>
+        <v>1381.9143</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>0.00072331</v>
+        <v>0.00072363</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -14055,10 +14055,10 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>1457.46283</v>
+        <v>1457.626546</v>
       </c>
       <c r="E29" s="63" t="n">
-        <v>0.00068612</v>
+        <v>0.00068605</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>14.114736</v>
+        <v>14.130415</v>
       </c>
       <c r="E30" s="65" t="n">
-        <v>0.07084794</v>
+        <v>0.07076933000000001</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>511.014831</v>
+        <v>509.538566</v>
       </c>
       <c r="E31" s="63" t="n">
-        <v>0.00195689</v>
+        <v>0.00196256</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>571.311717</v>
+        <v>571.305515</v>
       </c>
       <c r="E33" s="63" t="n">
-        <v>0.00175036</v>
+        <v>0.00175038</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>4586.66529</v>
+        <v>4586.138619</v>
       </c>
       <c r="E34" s="65" t="n">
-        <v>0.00021802</v>
+        <v>0.00021805</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>21.269445</v>
+        <v>21.267335</v>
       </c>
       <c r="E35" s="63" t="n">
-        <v>0.0470158</v>
+        <v>0.04702047</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>17.121575</v>
+        <v>17.126179</v>
       </c>
       <c r="E36" s="65" t="n">
-        <v>0.05840584</v>
+        <v>0.05839014</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2.927391</v>
+        <v>2.926309</v>
       </c>
       <c r="E37" s="63" t="n">
-        <v>0.3416011</v>
+        <v>0.34172741</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>2579.094525</v>
+        <v>2569.132481</v>
       </c>
       <c r="E38" s="65" t="n">
-        <v>0.00038773</v>
+        <v>0.00038924</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
@@ -14285,10 +14285,10 @@
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>3724.737851</v>
+        <v>3723.861301</v>
       </c>
       <c r="E39" s="63" t="n">
-        <v>0.00026848</v>
+        <v>0.00026854</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E40" s="65" t="n">
-        <v>0.00175604</v>
+        <v>0.00175621</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>569.462904</v>
+        <v>569.4064069999999</v>
       </c>
       <c r="E41" s="63" t="n">
-        <v>0.00175604</v>
+        <v>0.00175621</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>17.121639</v>
+        <v>17.11952</v>
       </c>
       <c r="E42" s="65" t="n">
-        <v>0.05840562</v>
+        <v>0.05841285</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>18.969397</v>
+        <v>18.956944</v>
       </c>
       <c r="E43" s="63" t="n">
-        <v>0.05271649</v>
+        <v>0.05275112</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C4" s="70" t="inlineStr">
         <is>
-          <t>28 March 2026 — 06:53 UTC</t>
+          <t>29 March 2026 — 07:00 UTC</t>
         </is>
       </c>
     </row>
